--- a/docs/704_Collective___Internal_Tracker__Phase_1___Phase_2___UPDATED_2026-08-03.xlsx
+++ b/docs/704_Collective___Internal_Tracker__Phase_1___Phase_2___UPDATED_2026-08-03.xlsx
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
@@ -334,6 +334,33 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -591,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="1" min="1" max="1"/>
@@ -628,10 +655,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>IMMEDIATE SPRINT - PRE/POST-EVENT (added Aug 26) - 5 items</t>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>PRIORITY QUEUE — LOCKED BY ADAM SEP 21 (work in this order)   ·   4 items</t>
         </is>
       </c>
       <c r="B2" s="31" t="n"/>
@@ -639,564 +666,588 @@
       <c r="D2" s="31" t="n"/>
       <c r="E2" s="31" t="n"/>
     </row>
-    <row r="3" ht="46.25" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Realtime RSVP/cancel sync to Exchange engine + viewer</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
+          <t>1. Business application Typeform rebuild — awaiting team question verdict</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sep 21: the application form is being rebuilt as a Typeform-style flow. Believed broken since launch; the money+membership path gets maximum rigor.</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Blocked on the team's verdict on the application QUESTIONS (what we ask, in what order, what routes to membership vs Preferred Business vs sponsorship). Then: form -&gt; review/approval -&gt; payment -&gt; provisioning -&gt; comms, recon-first, keystroke-standard develop rehearsal both viewports, ship. Adam walkthrough Q&amp;A at build start (approval mechanics, reviewer, pricing incl. annual, notification emails).</t>
+        </is>
+      </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WAITING ON ADAM: team question verdict</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>RSVPs and cancellations must reflect immediately (no manual refresh) in /admin/exchange viewer (counts, pools, roster) and /admin/exchange/mixer (eligible roster). Candidates: Supabase Realtime subscriptions on attendance_credentials + exchange_intake scoped to the event, or tight polling. Must define cancel-mid-round behavior (current-round seat stands, excluded from next MIX; late check-ins already auto-join next round). Deadline: before Aug 27 event; freeze exception authorized by Adam; full develop rehearsal mandatory, both viewports, simulated RSVP+cancel during an active round.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="35.05" customHeight="1">
+          <t>PRIORITY 1. Absorbs the old "Business application process: fix, test, launch" sprint row and the empty "Verify the business application approval works" row. Pairs with "/business page rebuild with dynamic application".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>In-platform promo code: 50% off, valid 8/27-8/31, social + business</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
+          <t>2. Hub pages build (external hub pages) — walkthrough next; pre-gate CLEARED Sep 21</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Four audience-specific public landers (cltarrival / cltfounded / clteatsandevents / cltreset) that funnel Charlotte audiences into the club. These are the first outside-facing surfaces reading hub data, so the RLS audit was the mandatory pre-gate.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>4 public landers, shared skeleton, own design pass, fully pre-rendered + schema (see SEO item). They feed The Network. Pre-gate: cursor_report_rlsaudit.md — none of the 17 RLS-on/no-policy tables is a hub, task or member-surface table; leftover anon/authenticated grants stripped on prod (by hand) and develop (migration 20260921070000). Next step is Adam's walkthrough of the page set, then build.</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Build — walkthrough next</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Code entered and applied IN the platform before Stripe checkout. Social: at join checkout. Business: application-approval flow, code applies at post-approval payment. Needs Stripe coupon/promotion-code wiring in checkout creation, validity window hard-enforced 8/27-8/31, UI entry field. Open questions for build start: discount duration (first month vs recurring), exact code string(s), one code or per-tier. Deadline: live by Aug 27 morning. (Adam listed this twice; consolidated.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21.75" customHeight="1">
+          <t>PRIORITY 2. Pre-gate CLEARED Sep 21. Was "Charlotte hub landing sites (4 public landers)". Pairs with "The Network" (internal roll-up) and the SEO/pre-render row. Social members never appear on the public hubs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Business application process: fix, test, launch end-to-end</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
+          <t>3. Task management system — walkthrough</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>A super-light ClickUp-style task center for admins/super-admins: create, assign, track tasks. Sep 21: promoted from Phase 2 into the locked queue.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Adam walkthrough of the task model (create / assign / track, who sees what, notifications via the existing bell) then own detailed scope, then build. Reuse the existing tasks tables and task_assigned bell type where they fit.</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Build — walkthrough</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Believed broken since launch. Full flow: application form -&gt; review/approval -&gt; payment -&gt; member provisioning -&gt; comms. Recon-first (read-only trace of every step, identify all break points), then fix, keystroke-standard develop rehearsal, ship. Adam walkthrough Q&amp;A at build start (approval mechanics, reviewer, pricing incl. annual, notification emails). Deadline: live before Aug 27; timeline risk acknowledged, recon may resize; money+membership path = maximum rigor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="23.85" customHeight="1">
+          <t>PRIORITY 3. Was "Task center for admins (lite project tool)" under Phase 2 major builds. Note the existing "Speed up slow list pages (Events, Tasks, Hubs)" row touches the same tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Exchange mixer engine + viewer spacing fixes</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
+          <t>4. Mobile app — Apple transfer DONE; email sync + tickets waves ride before it</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>A full native mobile application. The largest Phase 2 build. Sep 21: Apple developer account transfer is DONE. Two identity waves ride before the app so it is built on a settled identity model.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Sequence: identity Wave 7 (email change keeps Stripe in sync) and Wave 9 (retire legacy tickets / capacity split-brain) first, then own detailed scope for the app, then build. Do not start the app on the dual-write ticket tables.</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Build — after Waves 7 + 9</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>UI spacing issues; Adam provides specifics at build time. Hard constraint: functionality must not break before the Aug 27 event; CSS-only strongly preferred; both viewports; develop rehearsal; ship pre-event only if trivially safe, else immediately post-event (Adam call at build).</t>
+          <t>PRIORITY 4. Was "Full mobile app" under Phase 2 major builds. Apple transfer done. The two prerequisite waves keep their own rows (MEMBERS &amp; MONEY / IDENTITY FOUNDATION).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Notification bell dropdown cannot scroll</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Member-facing: notification list under the bell is unscrollable, long lists unreachable. Likely overflow-y/max-height on the dropdown container. Both viewports. Low risk; can ride with R4's pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="35.05" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ONBOARDING &amp; SIGNUP   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>SEP 21 ADDITIONS — POST-IDENTITY-PACKAGE FOLLOW-UPS   ·   11 items</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Stripe Connect-mode webhook endpoint + second signing secret — before the first payout (~Nov)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Ambassador and member-referral payouts move money via Stripe Connect transfers. Connect-side events (account.updated for onboarding status, transfer/payout lifecycle) arrive on a Connect-mode webhook endpoint with its own signing secret; today only the account-mode endpoint and secret are wired into stripe-webhook. Without the second endpoint, Connect account status changes and transfer failures after the first real payout are invisible.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Create the Connect-mode endpoint in the Stripe dashboard pointing at stripe-webhook (or a sibling), store its secret as a second env (e.g. STRIPE_CONNECT_WEBHOOK_SECRET), verify signature against whichever secret matches, and route account.updated / transfer.* events. Rehearse on develop with canned events. Must land before the first real Monday payout, expected ~Nov 2026 (second-payment commission rule).</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Build — before ~Nov</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Dated dependency: the first member/ambassador payout is expected around Nov. Phase 2 payout tail (d996e1a) already syncs member_payout_accounts from account.updated on the account-mode endpoint; this row is the Connect-mode endpoint + secret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Collect phone for everyone at signup; gate texts on consent</t>
+          <t>Meta CAPI — server-side Purchase events (dedupe with the browser pixel by event_id)</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Phone is captured at signup now; the remaining work is gating SMS on the consent flag (not on whether a number exists) and re-collecting phone from pre-May-21 members whose number was never saved.</t>
+          <t>The Meta pixel (d31dba9) fires Purchase client-side with eventID = the checkout session id, deduped per session. Browser-only events are lost to ad blockers and in-app browsers (the Nyree case) — CAPI sends the same Purchase server-side from the webhook so Meta sees every paid conversion once.</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Confirm phone persists from signup metadata; gate SMS on the consent flag; add a re-collection prompt for pre-May-21 members.</t>
+          <t>From stripe-webhook checkout.session.completed (or the verify-checkout path): POST to the Conversions API with event_name Purchase, event_id = cs_ id (matches the pixel), value/currency, hashed email, fbclid/fbc from the session metadata already stamped by create-checkout. Env-gated like the pixel. Rehearse with Meta test_event_code on develop; no real Meta calls otherwise.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Phone capture + display already shipped; consent gate + backfill remain.</t>
+          <t>Depends on the Meta BM restructure + domain verification row (CAPI needs a verified domain and a system-user token). Pixel + UTM capture shipped Sep 15.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Prompt calendar-subscribe + wallet-pass add at signup</t>
+          <t>Meta Business Manager restructure + domain verification</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>As part of signup, walk the new member through subscribing to the event calendar and adding their wallet pass, so both are set up before they finish onboarding.</t>
+          <t>The ad account / pixel / page live in a Business Manager structure that needs restructuring, and 704collective.com is not domain-verified in Meta. Domain verification is required for aggregated event measurement and CAPI.</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Add a calendar-subscribe step and a wallet-add step to the signup / onboarding flow; confirm both stick.</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Adam (Meta side): restructure BM ownership, verify 704collective.com (meta-tag or DNS TXT), attach the pixel to the verified domain, create a system user + CAPI token. Repo side if needed: one meta-tag in the root layout for verification.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>ADAM — Meta side</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>New onboarding-flow ask — pairs with the lifecycle push to current members (see Email &amp; Drip).</t>
+          <t>Prerequisite for the CAPI row. Owner task; repo change is at most one meta tag.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>MEMBERS &amp; MONEY   ·   3 items</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Identity Wave 6E — drop the legacy contacts columns after soak (PARKED)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Waves 6A–6D-a are live: contacts link to people at write time (6C triggers), tags mirror to person_tags, opt-out truth is people.marketing_unsubscribed, email readers flipped. The legacy columns (contacts.unsubscribed, contact_tags as a read surface, profiles.marketing_unsubscribed for two profile-side readers) are still written for compatibility. 6E removes them.</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>After a soak and after 6D-b (admin surfaces) flips the last readers: drop/retire the legacy opt-out columns and contact_tags reads, repoint event-reminder and discussion-open off profiles.marketing_unsubscribed, remove the mirror lines from the 6C triggers. Migration + small code; rehearse on develop.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Deliberately parked: nothing is wrong today because 6C keeps every legacy column current. Sequenced after 6D-b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Verify the payment-to-membership chain end to end</t>
+          <t>Identity Wave 6D-b — admin CRM/contacts surfaces read person-side truth (rides the admin rebuild)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>The full money path (checkout -&gt; Stripe webhook -&gt; member activated) has no automated test.</t>
+          <t>The admin contacts/CRM pages, the attendee dialog and comp-invite still read contacts / contact_tags / legacy opt-out columns (cursor_report_wave6d.md §2). Correct today because 6C mirrors, but they are the last readers keeping the legacy shape alive.</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Run a Stripe-CLI end-to-end test of checkout -&gt; webhook -&gt; activation before scaling referrals on it.</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Flip the admin readers to people / person_tags / people.marketing_unsubscribed. Needs grant select on person_tags to authenticated + an admin-only select policy (person_tags is service-role only today). Ride with "Build the admin area into clean sections" so each page is touched once.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>QUEUED — rides admin rebuild</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>The money path — verify carefully; everything downstream assumes it works.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="35.05" customHeight="1">
+          <t>Deferred by design in the 6D recon. Unblocks 6E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Verify an email change keeps Stripe billing in sync</t>
+          <t>Identity Wave 8 — auth cutover (PARKED)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>When a member changes email, the Stripe customer should update too, so billing/receipts don't split into a second identity.</t>
+          <t>The final identity wave: auth-adjacent writes (signup, email change, password flows) key entirely on the person record with profiles as a settings/billing satellite. Wave A already mints a person at signup; 6C links every contact write; the cutover is the remaining piece.</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Change an email; confirm the Stripe customer email updates; no orphaned customer.</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Own scope before build. Regression-test logins + RLS from a non-admin session behind a verified backup/rollback, as the identity plan always required. Sequence after Wave 7 (email sync).</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>PARKED</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Now identity Wave 7 (email sync); resumes Aug 28. The person record has been keyed on a permanent auth_user_id since Wave 0, so an email change no longer splits identity internally - the Stripe-customer half is the remaining work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="35.05" customHeight="1">
+          <t>Parked until Waves 7 and 9 land and the mobile app scope is known — the app is the consumer that decides how much cutover is needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Migrate the 8 legacy $30 subscriptions</t>
+          <t>Expiring-card Stripe toggle — Adam, 5 seconds</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>The trusted member-count definitions are already established (member_counts view). The only residual is 8 subscriptions still on the retired $30 price.</t>
+          <t>Stripe can email customers automatically when a saved card is about to expire (Billing -&gt; Subscriptions and emails -&gt; "Send emails about expiring cards"). It is off. Turning it on removes a class of avoidable past_due.</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Move the 8 legacy $30 subs to current pricing in Stripe; $30 is retired everywhere else.</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Adam: Stripe dashboard -&gt; Settings -&gt; Billing -&gt; Subscriptions and emails -&gt; enable expiring-card emails. Confirm the sender/branding matches the receipts. No code.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ADAM — 5 seconds</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Count reconciliation itself is DONE — this is the leftover cleanup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>IDENTITY FOUNDATION   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="35.05" customHeight="1">
+          <t>Pairs with the past_due update-billing banner shipped Sep 3 (159fd52) and the renewal reminders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Social member profiles + the open-or-gated decision</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Social members need a profile surface (the four clean fields) and a decision on whether member profiles/cards are open to the public or gated behind login. The public card page exists (card/[public_id]) and already applies the single member-visibility predicate (7084b43); the product decision on what a non-member can see is not made.</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Adam decides open vs gated (and what fields are public if open). Then align the public card, the directory and the hub pages to that one rule. Builds on "Strip member profiles to four clean fields" and the privacy toggle row.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>WAITING ON ADAM: open or gated</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Decision gates part of the hub pages build (which member content the public hubs may show).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Merge every person into ONE record with a real login ID</t>
+          <t>Lint warnings someday-audit (475 warnings today, 0 errors)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>The same human exists across profiles/people/contacts, glued by matching email text — the root cause of recurring identity bugs (9 paying members recently couldn't RSVP). Locked: one canonical person keyed by a permanent auth_user_id.</t>
+          <t>npm run lint passes with 0 errors but ~475 warnings (unused vars/imports, no-unused-expressions, react-hooks deps). They are noise that hides new real warnings and 17 are auto-fixable.</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Add auth_user_id -&gt; repoint reads -&gt; repoint writes -&gt; auth-adjacent last, in waves. One resolver everywhere. Regression-test logins + RLS from a non-admin session before cutover, behind a verified backup/rollback. Member type stays a STATUS on the person.</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Someday: run eslint --fix for the auto-fixable set, then burn the rest down file-by-file in otherwise-idle sessions. Never as a big-bang commit; never mixed into a feature change.</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Someday</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Waves 0-6A + status pass complete and live (auth_user_id, resolver adopted by 15 fns, classification, vocabulary, count logic). Remaining: 6B-6E contacts fold, 7 email sync, 8 auth cutover, 9 tickets, 10 drift trio, 11 regression. Resumes Aug 28.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="23.85" customHeight="1">
+          <t>Count as of Sep 21 gates: 475 problems, 0 errors, 17 auto-fixable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Finish retiring the old ticket tables</t>
+          <t>cleanup-business-members: Social product id is a hard-coded constant</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>RSVP moved to one attendance table; a guest-pass follow-up tracker and one hook still dual-write the old 'tickets' table.</t>
+          <t>cleanup-business-members classifies a customer as business vs social by comparing the subscription's product to SOCIAL_PRODUCT_ID = "prod_TZI8im1xRNUMuy", a constant in the file rather than an env var. A future price/product change would silently reclassify every social member as business — and the function now cancels in Stripe before hiding, so the blast radius of a wrong classification grew with the Wave 10 weld.</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Repoint last guest-pass readers/writers to attendance_credentials, kill the dual-write, drop legacy tickets + guest_passes after a safe soak.</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Read the id from an env (STRIPE_SOCIAL_PRODUCT_ID, already the name other code uses) with the constant as fallback, and fail closed if neither resolves. Also clear the 3 pre-existing deno type errors in the file while there. Small.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Build — small</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Now identity Wave 9 (tickets), queued behind the contacts fold (6B-6E) and the auth cutover (8); resumes Aug 28. Still do not drop before the soak confirms nothing else reads them. Closes together with the capacity-trigger split-brain row. Wave 9 recon Aug 25: create-guest-pass writes legacy tickets PRIMARY; dashboard guest-pass list + get_community_stats (frozen 416 since Jul 19 vs live 969) read legacy; capacity trigger pair mapped; retirement order + mandatory backfill (8 of 26 mirrored).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="23.85" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>EVENTS &amp; CALENDAR   ·   19 items</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="31" t="n"/>
+          <t>Found during the Wave 10 rehearsal, where a wrong product id in the stub made the function (correctly, per its rules) cancel and hide every seeded social member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>stripe-webhook cascade dedupe — point handleSubscriptionDeleted at _shared/membershipCascade.ts</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Wave 10 lifted the membership-end cascade (hub seats, people status, credential void + wallet push) into supabase/functions/_shared/membershipCascade.ts for admin-delete-user, but left the webhook's own copies in place so its cancellation path stayed regression-locked. Two copies will drift on the next rule change.</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>After Wave 10 has soaked: replace the webhook's removeHubSeats / voidPersonCredentials bodies with imports from the shared module, assert byte-identical behaviour with the R4 canned subscription.deleted rehearsal, deploy stripe-webhook.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Build — small, after soak</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Same drift class as the comp-invite resolver replica row. Follow-up named in cursor_report_wave10_build.md §6.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.85" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Require an event category at creation</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Every event needs a category label at creation (a mis-filed event was shown to the wrong audience). Category is separate from access level.</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Two independent fields on the event form — Category (editable label) and Access level — both enforced at creation.</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Categories: The 704 / The Reserve / After Hours / The Reset / For the City / The Exchange / Coffee &amp; Connect.</t>
-        </is>
-      </c>
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>IMMEDIATE SPRINT - PRE/POST-EVENT (added Aug 26) - 3 items</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
     </row>
     <row r="20" ht="35.05" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Three event access levels: open / members / business</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Production already runs business-only events; the old two-bucket spec needs three: open to all, members only, business-members only.</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Implement a 3-value access field driving visibility + RSVP eligibility.</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
+          <t>Realtime RSVP/cancel sync to Exchange engine + viewer</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Drives both event visibility and who can RSVP.</t>
+          <t>RSVPs and cancellations must reflect immediately (no manual refresh) in /admin/exchange viewer (counts, pools, roster) and /admin/exchange/mixer (eligible roster). Candidates: Supabase Realtime subscriptions on attendance_credentials + exchange_intake scoped to the event, or tight polling. Must define cancel-mid-round behavior (current-round seat stands, excluded from next MIX; late check-ins already auto-join next round). Deadline: before Aug 27 event; freeze exception authorized by Adam; full develop rehearsal mandatory, both viewports, simulated RSVP+cancel during an active round.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="23.85" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>One simple event feed everyone sees</t>
+          <t>Exchange mixer/viewer remedy C — shed or wrap columns so the roster fits a 390px phone</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Locked: no separate social vs business feeds for now; one feed shows everyone all events.</t>
+          <t>R4 shipped remedy B (admin surfaces; header reachable, table cleanly bounded) but the mixer/viewer table is still ~1369px wide and needs sideways scrolling on a phone. Recon remedy C — shedding or wrapping columns — was explicitly left open.</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Ship the single simplest feed; access level still governs RSVP eligibility.</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
+          <t>Column-shedding or wrap layout for the mixer roster/viewer at 390px. CSS/markup only; engine untouched. Both viewports on develop before shipping. Adam names which columns can be shed at build time.</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Single feed for now; tiered feeds are explicitly deferred.</t>
+          <t>Was "mixer engine + viewer spacing fixes". Remedy B landed Sep (R4 build); remedy C is the remaining piece per cursor_report_r4build.md.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="35.05" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Confirm the 118 old calendar links work again</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>When the feed broke, ~118 members held subscribe-links returning an empty calendar; the June 10 rebuild likely revived them.</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Spot-check several of the 118 tokens against the live feed; if events return, close it — else send a re-subscribe email.</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Notification bell dropdown cannot scroll</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Likely already revived by the June 10 rebuild — confirm, then a soft 'your calendar works' note at most.</t>
+          <t>Member-facing: notification list under the bell is unscrollable, long lists unreachable. Likely overflow-y/max-height on the dropdown container. Both viewports. Low risk; can ride with R4's pass.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="35.05" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Alert if the calendar feed ever goes empty again</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>The feed broke silently last time.</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Cron/health-check comparing feed output to known future events; alert on mismatch.</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Catches a silent feed failure like the earlier one.</t>
-        </is>
-      </c>
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>ONBOARDING &amp; SIGNUP   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
     </row>
     <row r="24" ht="35.05" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Verify the event detail page handles every state</t>
+          <t>Collect phone for everyone at signup; gate texts on consent</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Member + public RSVP are verified; waitlist, paid purchase, capacity-full, and cancel/re-RSVP are not.</t>
+          <t>Phone is captured at signup now; the remaining work is gating SMS on the consent flag (not on whether a number exists) and re-collecting phone from pre-May-21 members whose number was never saved.</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Test the remaining EventDetail branches.</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Confirm phone persists from signup metadata; gate SMS on the consent flag; add a re-collection prompt for pre-May-21 members.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Core states already verified; this covers the edge branches.</t>
+          <t>Phone capture + display already shipped; consent gate + backfill remain.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Verify the RSVP status sidebar shows the right state</t>
+          <t>Prompt calendar-subscribe + wallet-pass add at signup</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Confirm the sidebar reflects all 7 RSVP states.</t>
+          <t>As part of signup, walk the new member through subscribing to the event calendar and adding their wallet pass, so both are set up before they finish onboarding.</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Walk all 7 states: not RSVP'd, RSVP'd, waitlisted, cancelled, attended, refunded, no-show.</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Add a calendar-subscribe step and a wallet-add step to the signup / onboarding flow; confirm both stick.</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Purely a verification walk-through; not a build.</t>
+          <t>New onboarding-flow ask — pairs with the lifecycle push to current members (see Email &amp; Drip).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="23.85" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Show non-members a teaser of members-only events</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>A non-member should see members-only events as a teaser: type + 'Members Only' tag, never the location. Creates FOMO, sells membership.</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Public view: type + tag, hide name details, always hide location.</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>Awaiting a fuller public-events-page spec before final build.</t>
-        </is>
-      </c>
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>MEMBERS &amp; MONEY   ·   3 items</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
     </row>
     <row r="27" ht="23.85" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Verify the remaining door check-in scan paths</t>
+          <t>Verify the payment-to-membership chain end to end</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Member check-in is verified; walk-in (no-RSVP) record, guest-pass scan, and junk-scan rejection are not.</t>
+          <t>The full money path (checkout -&gt; Stripe webhook -&gt; member activated) has no automated test.</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Test walk-in QR, guest-pass (GP-) scan, and gibberish-scan rejection.</t>
+          <t>Run a Stripe-CLI end-to-end test of checkout -&gt; webhook -&gt; activation before scaling referrals on it.</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1206,51 +1257,51 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Member check-in already verified; this covers walk-in, guest-pass, and bad scans.</t>
+          <t>The money path — verify carefully; everything downstream assumes it works.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="23.85" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Hide all event details until someone RSVPs</t>
+          <t>Verify an email change keeps Stripe billing in sync</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>By default, all event details are hidden from everyone (even in the portal) except photo, preview name, and date/time; full details reveal only after RSVP.</t>
+          <t>When a member changes email, the Stripe customer should update too, so billing/receipts don't split into a second identity.</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Default-hide name/location/details; reveal post-RSVP; controlled from the event manager.</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Change an email; confirm the Stripe customer email updates; no orphaned customer.</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Build after the core events work is stable.</t>
+          <t>Identity Wave 7 (email sync). Rides BEFORE the mobile app together with Wave 9 (tickets). Internally an email change no longer splits identity (auth_user_id key since Wave 0; contacts family linked at write time since 6C); the Stripe-customer half is the remaining work. Also closes the customer.updated webhook gap noted in the drift-trio recon.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="23.85" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Polite no-show email</t>
+          <t>Migrate the 8 legacy $30 subscriptions</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>When a member RSVPs but doesn't show (known from check-in), send a kind 'only RSVP if you can attend' email — resources are planned around counts.</t>
+          <t>The trusted member-count definitions are already established (member_counts view). The only residual is 8 subscriptions still on the retired $30 price.</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Trigger off check-in data (RSVP'd + not scanned = no-show).</t>
+          <t>Move the 8 legacy $30 subs to current pricing in Stripe; $30 is retired everywhere else.</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1260,51 +1311,35 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Depends on stricter RSVP + solid check-in data.</t>
+          <t>Count reconciliation itself is DONE — this is the leftover cleanup.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="23.85" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Persist public RSVP confirmation + on-page QR</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>When a non-member RSVPs, keep them confirmed on reload and show their QR on the confirmation page (+ email); no account required.</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Persist confirmed state on reload; render QR on the confirmation page + email.</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>No account creation for the public RSVP — just persistence + QR.</t>
-        </is>
-      </c>
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>IDENTITY FOUNDATION   ·   1 item</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
     </row>
     <row r="31" ht="23.85" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Optional event host (name + photo)</t>
+          <t>Finish retiring the old ticket tables</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Let an event optionally show a host with name and photo.</t>
+          <t>RSVP moved to one attendance table; a guest-pass follow-up tracker and one hook still dual-write the old 'tickets' table.</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Event host field + admin form + display.</t>
+          <t>Repoint last guest-pass readers/writers to attendance_credentials, kill the dual-write, drop legacy tickets + guest_passes after a safe soak.</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -1314,51 +1349,35 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Simple optional field; no dependencies.</t>
+          <t>Identity Wave 9 (tickets). Rides BEFORE the mobile app together with Wave 7 (email sync). Wave 9 recon Aug 25 stands: create-guest-pass writes legacy tickets PRIMARY; dashboard guest-pass list + get_community_stats read legacy; capacity trigger pair mapped; retirement order + mandatory backfill (8 of 26 mirrored). Do not drop before the soak confirms nothing else reads them. Closes together with the capacity-trigger split-brain row.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21.75" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Future-event visibility limits</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Define and enforce how far ahead events are visible (date range, tier, or capacity).</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Scope the limit dimension, then enforce.</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>Decide the limit dimension before enforcing.</t>
-        </is>
-      </c>
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>EVENTS &amp; CALENDAR   ·   19 items</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
     </row>
     <row r="33" ht="35.05" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Soft-delete for events</t>
+          <t>Require an event category at creation</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Let events be recoverable rather than hard-deleted.</t>
+          <t>Every event needs a category label at creation (a mis-filed event was shown to the wrong audience). Category is separate from access level.</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Soft-delete events.</t>
+          <t>Two independent fields on the event form — Category (editable label) and Access level — both enforced at creation.</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -1368,24 +1387,24 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Related to the event-DELETE RLS failure that the identity fix resolves.</t>
+          <t>Categories: The 704 / The Reserve / After Hours / The Reset / For the City / The Exchange / Coffee &amp; Connect.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="23.85" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Self-serve event management</t>
+          <t>Three event access levels: open / members / business</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Let hosts/business members propose or manage their own events (admins publish).</t>
+          <t>Production already runs business-only events; the old two-bucket spec needs three: open to all, members only, business-members only.</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Define permissions — likely 'propose -&gt; admin publish'.</t>
+          <t>Implement a 3-value access field driving visibility + RSVP eligibility.</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -1395,24 +1414,24 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Needs scoping before build.</t>
+          <t>Drives both event visibility and who can RSVP.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="23.85" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Event reorganization</t>
+          <t>One simple event feed everyone sees</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Restructure how events are displayed per the events direction.</t>
+          <t>Locked: no separate social vs business feeds for now; one feed shows everyone all events.</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Needs the detailed events-page spec.</t>
+          <t>Ship the single simplest feed; access level still governs RSVP eligibility.</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -1422,51 +1441,51 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Blocked on the detailed events-page spec.</t>
+          <t>Single feed for now; tiered feeds are explicitly deferred.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="23.85" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Calendar scope picker in settings</t>
+          <t>Confirm the 118 old calendar links work again</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Optional: let business members narrow their calendar to business-only.</t>
+          <t>When the feed broke, ~118 members held subscribe-links returning an empty calendar; the June 10 rebuild likely revived them.</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Implement only if tiered feeds return.</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Spot-check several of the 118 tokens against the live feed; if events return, close it — else send a re-subscribe email.</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Optional given the single-feed decision; only relevant if tiered feeds return.</t>
+          <t>Likely already revived by the June 10 rebuild — confirm, then a soft 'your calendar works' note at most.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="23.85" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Instant Google Calendar updates</t>
+          <t>Alert if the calendar feed ever goes empty again</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Subscribed calendars refresh every 8-24h; true instant needs a Google Calendar API push integration.</t>
+          <t>The feed broke silently last time.</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Service account writing to each member's calendar.</t>
+          <t>Cron/health-check comparing feed output to known future events; alert on mismatch.</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1476,35 +1495,51 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Larger effort — a Google Calendar API push integration.</t>
+          <t>Catches a silent feed failure like the earlier one.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21.75" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>WALLET PASS   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="n"/>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Verify the event detail page handles every state</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Member + public RSVP are verified; waitlist, paid purchase, capacity-full, and cancel/re-RSVP are not.</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Test the remaining EventDetail branches.</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Core states already verified; this covers the edge branches.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="46.25" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Verify Apple Wallet passes work on real phones</t>
+          <t>Verify the RSVP status sidebar shows the right state</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Confirm generate, deliver (dashboard + email), and update-on-status-change end to end; code is further along than expected.</t>
+          <t>Confirm the sidebar reflects all 7 RSVP states.</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Test on a real iPhone; fix gaps.</t>
+          <t>Walk all 7 states: not RSVP'd, RSVP'd, waitlisted, cancelled, attended, refunded, no-show.</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -1514,78 +1549,78 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Generation + push-update already exist — verify on a real device, then close gaps.</t>
+          <t>Purely a verification walk-through; not a build.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="23.85" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Kill a membership pass when someone cancels</t>
+          <t>Show non-members a teaser of members-only events</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>When membership lapses/cancels, the pass must stop scanning at the door; a void function exists.</t>
+          <t>A non-member should see members-only events as a teaser: type + 'Members Only' tag, never the location. Creates FOMO, sells membership.</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Verify cancellation voids the pass and it dies on-device.</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Public view: type + tag, hide name details, always hide location.</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Nothing should scan at the door after membership ends.</t>
+          <t>Awaiting a fuller public-events-page spec before final build.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="23.85" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Give members a QR backup if their pass fails</t>
+          <t>Verify the remaining door check-in scan paths</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Door failure modes: dead battery, no signal, deleted pass.</t>
+          <t>Member check-in is verified; walk-in (no-RSVP) record, guest-pass scan, and junk-scan rejection are not.</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Dashboard QR fallback + 'resend my pass' button.</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Test walk-in QR, guest-pass (GP-) scan, and gibberish-scan rejection.</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Assume bad connectivity at the door.</t>
+          <t>Member check-in already verified; this covers walk-in, guest-pass, and bad scans.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Complete Google Wallet passes</t>
+          <t>Hide all event details until someone RSVPs</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Bring Google Wallet to parity with Apple (generate/deliver/update); the scaffold is partial.</t>
+          <t>By default, all event details are hidden from everyone (even in the portal) except photo, preview name, and date/time; full details reveal only after RSVP.</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Finish Google Wallet generation + delivery + update.</t>
+          <t>Default-hide name/location/details; reveal post-RSVP; controlled from the event manager.</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -1595,24 +1630,24 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Scaffold is partial; bring to parity with Apple.</t>
+          <t>Build after the core events work is stable.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="23.85" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Apple Wallet push notifications + email attachment</t>
+          <t>Polite no-show email</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Push on changes + pass-as-email-attachment.</t>
+          <t>When a member RSVPs but doesn't show (known from check-in), send a kind 'only RSVP if you can attend' email — resources are planned around counts.</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>APNs push + email attachment.</t>
+          <t>Trigger off check-in data (RSVP'd + not scanned = no-show).</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -1622,89 +1657,105 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>After pass voiding is working.</t>
+          <t>Depends on stricter RSVP + solid check-in data.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>AMBASSADORS   ·   8 items</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="n"/>
-      <c r="C44" s="31" t="n"/>
-      <c r="D44" s="31" t="n"/>
-      <c r="E44" s="31" t="n"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Persist public RSVP confirmation + on-page QR</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>When a non-member RSVPs, keep them confirmed on reload and show their QR on the confirmation page (+ email); no account required.</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Persist confirmed state on reload; render QR on the confirmation page + email.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>No account creation for the public RSVP — just persistence + QR.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.85" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Finish and test the full ambassador referral + payout system</t>
+          <t>Optional event host (name + photo)</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Locked Phase 1. Core attribution bug half-fixed: referral-writes failed silently on wrong column names (17 ambassadors / 0 logged); the column fix is live but not yet confirmed writing a real row.</t>
+          <t>Let an event optionally show a host with name and photo.</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Verify the column fix writes one real referral; fix business-tier stamping in create-checkout; build payout rails + manual queue; wire the second-payment commission; then strip the diagnostic logs.</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Needs Testing</t>
+          <t>Event host field + admin form + display.</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Commission counts on the member's SECOND payment (locked). Diagnostic logs left as the witness — remove only after confirmed writing.</t>
+          <t>Simple optional field; no dependencies.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="23.85" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Verify the referral price applies at checkout</t>
+          <t>Future-event visibility limits</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Confirm the $35 ambassador-referred social price applies via a referral link (vs $49).</t>
+          <t>Define and enforce how far ahead events are visible (date range, tier, or capacity).</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Confirm referral checkout shows $35.</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Scope the limit dimension, then enforce.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Checks the $35 referral price vs the standard $49.</t>
+          <t>Decide the limit dimension before enforcing.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21.75" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Build the ambassador payout infrastructure</t>
+          <t>Soft-delete for events</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>The money-movement side of payouts (Stripe Connect Express or a manual queue).</t>
+          <t>Let events be recoverable rather than hard-deleted.</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Build payout rails; decide Connect vs manual queue.</t>
+          <t>Soft-delete events.</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -1714,24 +1765,24 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Pairs with the referral-fix row.</t>
+          <t>Related to the event-DELETE RLS failure that the identity fix resolves.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="23.85" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Build the manual payout queue UI</t>
+          <t>Self-serve event management</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>An admin UI to review and release ambassador payouts.</t>
+          <t>Let hosts/business members propose or manage their own events (admins publish).</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Payout queue UI for admins.</t>
+          <t>Define permissions — likely 'propose -&gt; admin publish'.</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -1741,24 +1792,24 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Where an admin reviews and releases payouts.</t>
+          <t>Needs scoping before build.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="102.2" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Weekly automated ambassador payouts</t>
+          <t>Event reorganization</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Scheduled automatic payouts once the rails exist.</t>
+          <t>Restructure how events are displayed per the events direction.</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>pg_cron weekly payout run.</t>
+          <t>Needs the detailed events-page spec.</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -1768,24 +1819,24 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>After the payout infrastructure exists.</t>
+          <t>Blocked on the detailed events-page spec.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21.75" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Ambassador leaderboard</t>
+          <t>Calendar scope picker in settings</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>A leaderboard ranking ambassadors by referrals.</t>
+          <t>Optional: let business members narrow their calendar to business-only.</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Ambassador leaderboard.</t>
+          <t>Implement only if tiered feeds return.</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -1795,24 +1846,24 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Ranks ambassadors by referrals.</t>
+          <t>Optional given the single-feed decision; only relevant if tiered feeds return.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="35.05" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Read-only ambassador tab</t>
+          <t>Instant Google Calendar updates</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>A view-only tab for ambassadors to see their own referral activity.</t>
+          <t>Subscribed calendars refresh every 8-24h; true instant needs a Google Calendar API push integration.</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>View-only ambassador tab.</t>
+          <t>Service account writing to each member's calendar.</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -1822,89 +1873,89 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Ambassadors see only their own activity.</t>
+          <t>Larger effort — a Google Calendar API push integration.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="35.05" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Unified admin users view (members + ambassadors)</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>One admin view combining members and ambassadors.</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>/admin/users unified view.</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>Combines members + ambassadors in one admin view.</t>
-        </is>
-      </c>
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>WALLET PASS   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="n"/>
+      <c r="C52" s="31" t="n"/>
+      <c r="D52" s="31" t="n"/>
+      <c r="E52" s="31" t="n"/>
     </row>
     <row r="53" ht="23.85" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>MEMBER TEXTING   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="n"/>
-      <c r="C53" s="31" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="31" t="n"/>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Verify Apple Wallet passes work on real phones</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Confirm generate, deliver (dashboard + email), and update-on-status-change end to end; code is further along than expected.</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Test on a real iPhone; fix gaps.</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Generation + push-update already exist — verify on a real device, then close gaps.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="21.75" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Confirm we're cleared to send texts (Twilio A2P 10DLC)</t>
+          <t>Kill a membership pass when someone cancels</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Records conflict on whether A2P 10DLC is approved; one call to Twilio settles it. Gates all texting.</t>
+          <t>When membership lapses/cancels, the pass must stop scanning at the door; a void function exists.</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Confirm A2P 10DLC status directly with Twilio; assign an owner + date.</t>
-        </is>
-      </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>Blocker</t>
+          <t>Verify cancellation voids the pass and it dies on-device.</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Nothing SMS ships until this is confirmed.</t>
+          <t>Nothing should scan at the door after membership ends.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="35.05" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Build the portal-baked texting inbox (Charlotte number, shared, consent + STOP)</t>
+          <t>Give members a QR backup if their pass fails</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>All member texting runs through ONE Charlotte-based Twilio number wired into the admin portal — no managed third-party tool, and no text ever reaches a personal phone. Inbound messages hit a webhook, write to our database, and appear in a shared team inbox where every co-founder can read and reply; replies send from the club number. Consent and STOP are enforced and stored on the canonical person record.</t>
+          <t>Door failure modes: dead battery, no signal, deleted pass.</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Twilio number -&gt; inbound webhook (Edge Function) -&gt; DB -&gt; portal Messages inbox (threads per member) -&gt; reply sends from the club number. Enforce consent + instant STOP; log idempotently before send; dedup in one shared send function. Inbound triggers an alert (email + the in-portal notification bell). Standard outbound: welcome, Monday digest, day-before reminders, week-1/2 nudges. Layer 1 only — no AI agent. Burn in 5-7 days.</t>
+          <t>Dashboard QR fallback + 'resend my pass' button.</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -1914,262 +1965,262 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>HARD REQUIREMENT: nothing lands on a personal cell; fully transparent + team-managed. Gated on the A2P confirmation, the phone-storage model, and the identity foundation.</t>
+          <t>Assume bad connectivity at the door.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="35.05" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>SECURITY   ·   3 items</t>
-        </is>
-      </c>
-      <c r="B56" s="31" t="n"/>
-      <c r="C56" s="31" t="n"/>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="31" t="n"/>
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Complete Google Wallet passes</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Bring Google Wallet to parity with Apple (generate/deliver/update); the scaffold is partial.</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Finish Google Wallet generation + delivery + update.</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Scaffold is partial; bring to parity with Apple.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="35.05" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Rotate the shared admin password before the developer starts</t>
+          <t>Apple Wallet push notifications + email attachment</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>The super-admin password was shared in working sessions; rotate it before any third-party developer gets repo/dashboard access.</t>
+          <t>Push on changes + pass-as-email-attachment.</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Rotate super-admin + test-account credentials before granting access (~10 min).</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>Blocker</t>
+          <t>APNs push + email attachment.</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Owner task — a prerequisite before onboarding the developer.</t>
+          <t>After pass voiding is working.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Rotate and remove secrets committed to the code</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Live GroupMe join tokens were committed to git history; the file was deleted but the tokens stay readable until rotated.</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>Rotate the exposed tokens (rotate-only, no history rewrite).</t>
-        </is>
-      </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>Blocker</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>Rotate so the committed copies become useless; no history rewrite.</t>
-        </is>
-      </c>
+      <c r="A58" s="35" t="inlineStr">
+        <is>
+          <t>AMBASSADORS   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="n"/>
+      <c r="C58" s="31" t="n"/>
+      <c r="D58" s="31" t="n"/>
+      <c r="E58" s="31" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Run a database security + linter pass</t>
+          <t>Verify the referral price applies at checkout</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A sweep for DB security issues and schema problems before scaling.</t>
+          <t>Confirm the $35 ambassador-referred social price applies via a referral link (vs $49).</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Run the DB linter + security audit; fix findings.</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Confirm referral checkout shows $35.</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Also re-confirm the already-shipped public-checkout auth fix here — don't redo it.</t>
+          <t>Checks the $35 referral price vs the standard $49.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="23.85" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>SECURITY &amp; MONITORING   ·   6 items</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="n"/>
-      <c r="C60" s="31" t="n"/>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="31" t="n"/>
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Build the manual payout queue UI</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>An admin UI to review and release ambassador payouts.</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Payout queue UI for admins.</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Where an admin reviews and releases payouts.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>send-email service-role auth: replace SB_SECRET_KEY duplicate with verified getClaims check</t>
+          <t>Ambassador leaderboard</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>On 2026-08-12 the sb_secret_ prefix grant and the unverified-JWT-payload grant were removed from send-email and ambassador-payout (both were forgeable). That broke every restricted-template send on prod for about 10 minutes, because the app's legacy eyJ service-role JWT does NOT equal the SUPABASE_SERVICE_ROLE_KEY the function runtime sees - it had been passing via the unverified decode all along. Mitigated by setting SB_SECRET_KEY on prod to the same legacy JWT the app sends, restoring an exact match. That works but stores one credential under two names.</t>
+          <t>A leaderboard ranking ambassadors by referrals.</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Replace the SB_SECRET_KEY exact-match branch with supabase.auth.getClaims(token) plus a claims.role === 'service_role' check. getClaims verifies the signature, so it is not forgeable, unlike the removed base64 decode. Confirm a user-scoped token can never surface role service_role in verified claims before relying on it. Then delete the SB_SECRET_KEY secret from prod. CRITICAL: test with the REAL prod service-role key against PROD before deploying - develop cannot catch this class of bug because develop's key is the new sb_secret_ format which the gateway rejects outright. Restricted templates affected if this breaks again: password-setup, welcome-new, welcome-back, welcome-setup, guest-pass, admin-invite, public-rsvp-confirmation and 22 others.</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>Raised 2026-08-12 after causing and resolving a live 10-minute prod outage on restricted-template email. Prod currently healthy via SB_SECRET_KEY. Verified: Vercel prod and .env.local hold the same 219-char legacy JWT.</t>
+          <t>Ambassador leaderboard.</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Ranks ambassadors by referrals.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21.75" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Dead trigger: last_attended_at never updates from public check-ins</t>
+          <t>Read-only ambassador tab</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>The trigger trg_update_last_attended_from_public_rsvp fires on event_public_rsvps check-in and is meant to stamp profiles.last_attended_at. It looks up contacts.converted_to_member_id first, and NO code anywhere writes that column (0 of 207 rows on prod have it set), so the trigger always exits early. Members who check in through the public RSVP path never get their last-attended date updated.</t>
+          <t>A view-only tab for ambassadors to see their own referral activity.</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Two options. Either populate contacts.converted_to_member_id when a contact becomes a member (a real CRM flow that does not currently exist), or rewrite the trigger to resolve the profile by email or through the people bridge instead of the dead column. The second is far smaller. Note the conversion-rate report widget that depended on the same column was removed on 2026-08-12 because it always rendered 0 percent.</t>
-        </is>
-      </c>
-      <c r="D62" s="14" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>Raised 2026-08-12 during a contacts table audit. Fails safe - does nothing rather than something wrong.</t>
+          <t>View-only ambassador tab.</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Ambassadors see only their own activity.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="23.85" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Turn on error monitoring (Sentry)</t>
+          <t>Unified admin users view (members + ambassadors)</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Sentry is installed but never switched on, with no server-side capture; until it's on, no fix is provably working in production.</t>
+          <t>One admin view combining members and ambassadors.</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Initialize across client + server + API routes + a root ErrorBoundary. Company-owned.</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>DONE Jul 9: @sentry/nextjs wired (client+server+API+global-error), CSP allowance added, DSN in Vercel, source-map upload configured, admin /admin/sentry page activated. Prod capture VERIFIED (smoke-test error landed). Commits 417fb37/d779885/5d12aac/b437166/a00cc50-adjacent. Until it's on, no fix is provable in production — it's the verification backbone.</t>
+          <t>/admin/users unified view.</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Combines members + ambassadors in one admin view.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="23.85" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Add a deploy pipeline so changes go live safely</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>DB/function changes are pushed by hand today — the root cause of code/live drift. Locked: hand-patching stops once this lands (with a written emergency lane).</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>GitHub Actions: merge to main -&gt; db push + functions deploy. Needs 3 repo secrets.</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Once in, hand-patching stops; needed before two people touch production in parallel.</t>
-        </is>
-      </c>
+      <c r="A64" s="35" t="inlineStr">
+        <is>
+          <t>MEMBER TEXTING   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n"/>
+      <c r="C64" s="31" t="n"/>
+      <c r="D64" s="31" t="n"/>
+      <c r="E64" s="31" t="n"/>
     </row>
     <row r="65" ht="23.85" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Make the code able to rebuild the live database</t>
+          <t>Confirm we're cleared to send texts (Twilio A2P 10DLC)</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Several live DB objects were made by hand and aren't in migration history, so the repo can't recreate prod.</t>
+          <t>Records conflict on whether A2P 10DLC is approved; one call to Twilio settles it. Gates all texting.</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Snapshot prod schema, diff vs migrations, commit a baseline migration.</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Confirm A2P 10DLC status directly with Twilio; assign an owner + date.</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Absorbs recent hand-made objects (RSVP backfill, a few functions, the unsubscribe function).</t>
+          <t>Nothing SMS ships until this is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="23.85" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Add three safety tests on the things that can't break</t>
+          <t>Build the portal-baked texting inbox (Charlotte number, shared, consent + STOP)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Effectively no automated testing exists.</t>
+          <t>All member texting runs through ONE Charlotte-based Twilio number wired into the admin portal — no managed third-party tool, and no text ever reaches a personal phone. Inbound messages hit a webhook, write to our database, and appear in a shared team inbox where every co-founder can read and reply; replies send from the club number. Consent and STOP are enforced and stored on the canonical person record.</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Three critical-path tests — (1) checkout -&gt; webhook -&gt; activated, (2) RSVP -&gt; attendance, (3) unsubscribe honored — and remove passWithNoTests so CI gates.</t>
+          <t>Twilio number -&gt; inbound webhook (Edge Function) -&gt; DB -&gt; portal Messages inbox (threads per member) -&gt; reply sends from the club number. Enforce consent + instant STOP; log idempotently before send; dedup in one shared send function. Inbound triggers an alert (email + the in-portal notification bell). Standard outbound: welcome, Monday digest, day-before reminders, week-1/2 nudges. Layer 1 only — no AI agent. Burn in 5-7 days.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -2179,14 +2230,14 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>The three failures that hurt most; flips CI from passing with zero tests.</t>
+          <t>HARD REQUIREMENT: nothing lands on a personal cell; fully transparent + team-managed. Gated on the A2P confirmation, the phone-storage model, and the identity foundation.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="23.85" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>EMAIL &amp; COMPLIANCE   ·   3 items</t>
+      <c r="A67" s="35" t="inlineStr">
+        <is>
+          <t>SECURITY   ·   2 items</t>
         </is>
       </c>
       <c r="B67" s="31" t="n"/>
@@ -2197,143 +2248,163 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Make every email sender respect unsubscribes</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>The unsubscribe page/link policy is fixed, but two senders (drip processor, renewal reminders) still don't check the opt-out flag, and one reminder may skip members on a null value.</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Add opt-out filtering to process-drips + renewal-reminders; fix event-reminder null handling. One opt-out flag is the source of truth.</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>send-email unsubscribe-block work is in flight; process-drips + renewal-reminders filtering to confirm/finish.</t>
+          <t>Rotate the shared admin password before the developer starts</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>The super-admin password was shared in working sessions; rotate it before any third-party developer gets repo/dashboard access.</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Rotate super-admin + test-account credentials before granting access (~10 min).</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Owner task — a prerequisite before onboarding the developer.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="23.85" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Make unsubscribe links forgery-proof</t>
+          <t>Rotate and remove secrets committed to the code</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>The unsubscribe token is currently guessable/forgeable (low stakes).</t>
+          <t>Live GroupMe join tokens were committed to git history; the file was deleted but the tokens stay readable until rotated.</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>HMAC-sign the token; align format across send-campaign, send-email, and unsubscribe.</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Rotate the exposed tokens (rotate-only, no history rewrite).</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Align the token format across the three places that generate/read it.</t>
+          <t>Rotate so the committed copies become useless; no history rewrite.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="23.85" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>Remove unsubscribe links from ALL emails; members cannot unsubscribe (manual-only)</t>
-        </is>
-      </c>
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t>SECURITY &amp; MONITORING   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n"/>
+      <c r="C70" s="31" t="n"/>
+      <c r="D70" s="31" t="n"/>
+      <c r="E70" s="31" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>ADMIN &amp; OPERATIONS   ·   10 items</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n"/>
-      <c r="C71" s="31" t="n"/>
-      <c r="D71" s="31" t="n"/>
-      <c r="E71" s="31" t="n"/>
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>send-email service-role auth: replace SB_SECRET_KEY duplicate with verified getClaims check</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>On 2026-08-12 the sb_secret_ prefix grant and the unverified-JWT-payload grant were removed from send-email and ambassador-payout (both were forgeable). That broke every restricted-template send on prod for about 10 minutes, because the app's legacy eyJ service-role JWT does NOT equal the SUPABASE_SERVICE_ROLE_KEY the function runtime sees - it had been passing via the unverified decode all along. Mitigated by setting SB_SECRET_KEY on prod to the same legacy JWT the app sends, restoring an exact match. That works but stores one credential under two names.</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Replace the SB_SECRET_KEY exact-match branch with supabase.auth.getClaims(token) plus a claims.role === 'service_role' check. getClaims verifies the signature, so it is not forgeable, unlike the removed base64 decode. Confirm a user-scoped token can never surface role service_role in verified claims before relying on it. Then delete the SB_SECRET_KEY secret from prod. CRITICAL: test with the REAL prod service-role key against PROD before deploying - develop cannot catch this class of bug because develop's key is the new sb_secret_ format which the gateway rejects outright. Restricted templates affected if this breaks again: password-setup, welcome-new, welcome-back, welcome-setup, guest-pass, admin-invite, public-rsvp-confirmation and 22 others.</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>Raised 2026-08-12 after causing and resolving a live 10-minute prod outage on restricted-template email. Prod currently healthy via SB_SECRET_KEY. Verified: Vercel prod and .env.local hold the same 219-char legacy JWT.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="46.25" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>send-campaign audience fixes - SHIPPED 2026-08-12</t>
+          <t>Dead trigger: last_attended_at never updates from public check-ins</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Three defects in the campaign audience resolver, all shipped to production on 2026-08-12. (1) all_contacts and segment both selected contacts.first_name and contacts.last_name, columns that have never existed on that table. PostgREST returned 400, the code discarded the error, and both audiences silently resolved to ZERO recipients while reporting success. all_contacts reached 0 of 214 people; segment reached 0 of 212. (2) all_contacts had no membership filter, so once the column bug was fixed it would have reached 47 active or comped members with prospect-facing copy. (3) The member exclusion lookup had no explicit limit and would have silently truncated past PostgREST's 1000-row default.</t>
+          <t>The trigger trg_update_last_attended_from_public_rsvp fires on event_public_rsvps check-in and is meant to stamp profiles.last_attended_at. It looks up contacts.converted_to_member_id first, and NO code anywhere writes that column (0 of 207 rows on prod have it set), so the trigger always exits early. Members who check in through the public RSVP path never get their last-attended date updated.</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>DONE. Commits b43d59c (full_name plus error propagation on both branches), a2fe05a (exclude active and comped members from all_contacts), f453dd4 (explicit limit on the exclusion lookup). Verified on develop against independently computed ground truth, then deployed to prod and confirmed by reading the deployed source. The segment branch deliberately does NOT exclude members - tag-driven audiences are explicitly targeted and filtering them would break legitimate use.</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>Prod all_contacts now resolves to 167 prospects (214 minus 47 members) with real names from full_name. The campaigns page preview will jump from 0 to 167 - that is the fix, not a bug. NOTE the earlier '89 members' figure in this row was wrong: it counted any profile match including cancelled and non-member accounts. The correct active/comped figure is 47. Neither audience had worked for an unknown period, so any past all_contacts campaign that appeared to send reached nobody.</t>
+          <t>Two options. Either populate contacts.converted_to_member_id when a contact becomes a member (a real CRM flow that does not currently exist), or rewrite the trigger to resolve the profile by email or through the people bridge instead of the dead column. The second is far smaller. Note the conversion-rate report widget that depended on the same column was removed on 2026-08-12 because it always rendered 0 percent.</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>Raised 2026-08-12 during a contacts table audit. Fails safe - does nothing rather than something wrong.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21.75" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Add a private notes section on each member</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Internal request: a notes area per member for context (e.g. 'comped through August').</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>Read: admin + super-admin. Write/edit: super-admin only. Not member-visible.</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Internal-only; super-admin writes, admins read, members never see it.</t>
+          <t>Add a deploy pipeline so changes go live safely</t>
+        </is>
+      </c>
+      <c r="B73" s="36" t="inlineStr">
+        <is>
+          <t>DB/function changes are pushed by hand today — the root cause of code/live drift. Locked: hand-patching stops once this lands (with a written emergency lane).</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="inlineStr">
+        <is>
+          <t>GitHub Actions: merge to main -&gt; db push + functions deploy. Needs 3 repo secrets.</t>
+        </is>
+      </c>
+      <c r="D73" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E73" s="36" t="inlineStr">
+        <is>
+          <t>Once in, hand-patching stops; needed before two people touch production in parallel.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="23.85" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Build the admin health dashboard</t>
+          <t>Make the code able to rebuild the live database</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>One screen showing system health at a glance; catches silent failures before members do.</t>
+          <t>Several live DB objects were made by hand and aren't in migration history, so the repo can't recreate prod.</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>5 widgets — cron, webhooks, drip health, email tracking, payment sync. Sits on /api/health.</t>
+          <t>Snapshot prod schema, diff vs migrations, commit a baseline migration.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -2343,24 +2414,24 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Reads /api/health + checks; surfaces silent failures.</t>
+          <t>Absorbs recent hand-made objects (RSVP backfill, a few functions, the unsubscribe function).</t>
         </is>
       </c>
     </row>
     <row r="75" ht="68.65000000000001" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Let admins change a member's tier and have billing follow</t>
+          <t>Add three safety tests on the things that can't break</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>App-side tier change/comp exists; the Stripe billing side doesn't follow.</t>
+          <t>Effectively no automated testing exists.</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Wire admin tier-change to Stripe subscription cancel/modify/start.</t>
+          <t>Three critical-path tests — (1) checkout -&gt; webhook -&gt; activated, (2) RSVP -&gt; attendance, (3) unsubscribe honored — and remove passWithNoTests so CI gates.</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -2370,78 +2441,62 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>App-side override already exists; this is the Stripe billing reconciliation.</t>
+          <t>The three failures that hurt most; flips CI from passing with zero tests.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="57.45" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>Harden the admin cancel-subscription flow</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Make admin cancel safe (running twice shouldn't double-act).</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>Add idempotency + structured logging + alert to admin-cancel-subscription.</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Idempotent + logged + alerted so a double-run can't double-act.</t>
-        </is>
-      </c>
+      <c r="A76" s="35" t="inlineStr">
+        <is>
+          <t>EMAIL &amp; COMPLIANCE   ·   3 items</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n"/>
+      <c r="C76" s="31" t="n"/>
+      <c r="D76" s="31" t="n"/>
+      <c r="E76" s="31" t="n"/>
     </row>
     <row r="77" ht="23.85" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Build the admin area into clean sections</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Reorganize admin into Today / People / Events / Network / Money / Messages / Settings with one source of truth per question.</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>7-section IA; folds in nav cleanup, per-event check-in start, financial accuracy, tier tools, and guest upload.</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>The Messages section is where the texting inbox lives.</t>
+          <t>Make every email sender respect unsubscribes</t>
+        </is>
+      </c>
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>The unsubscribe page/link policy is fixed, but two senders (drip processor, renewal reminders) still don't check the opt-out flag, and one reminder may skip members on a null value.</t>
+        </is>
+      </c>
+      <c r="C77" s="36" t="inlineStr">
+        <is>
+          <t>Add opt-out filtering to process-drips + renewal-reminders; fix event-reminder null handling. One opt-out flag is the source of truth.</t>
+        </is>
+      </c>
+      <c r="D77" s="36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E77" s="36" t="inlineStr">
+        <is>
+          <t>send-email unsubscribe-block work is in flight; process-drips + renewal-reminders filtering to confirm/finish.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="23.85" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Shared admin navigation config</t>
+          <t>Make unsubscribe links forgery-proof</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>One shared config for admin nav so it's consistent and not duplicated.</t>
+          <t>The unsubscribe token is currently guessable/forgeable (low stakes).</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Single adminNav config; remove duplicated nav definitions.</t>
+          <t>HMAC-sign the token; align format across send-campaign, send-email, and unsubscribe.</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
@@ -2451,78 +2506,42 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>One config; removes duplicated nav definitions.</t>
+          <t>Align the token format across the three places that generate/read it.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Guest list upload tool</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Let admins upload a guest list for an event.</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>Guest list upload UI.</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>Also unblocks future guest-conversion automation.</t>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>Remove unsubscribe links from ALL emails; members cannot unsubscribe (manual-only)</t>
         </is>
       </c>
     </row>
     <row r="80" ht="23.85" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>Fix the organization settings table</t>
-        </is>
-      </c>
-      <c r="B80" s="29" t="inlineStr">
-        <is>
-          <t>organization_settings has the wrong schema.</t>
-        </is>
-      </c>
-      <c r="C80" s="29" t="inlineStr">
-        <is>
-          <t>Correct the organization_settings schema.</t>
-        </is>
-      </c>
-      <c r="D80" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E80" s="30" t="inlineStr">
-        <is>
-          <t>Schema is currently wrong; correct it.</t>
-        </is>
-      </c>
+      <c r="A80" s="35" t="inlineStr">
+        <is>
+          <t>ADMIN &amp; OPERATIONS   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="n"/>
+      <c r="C80" s="31" t="n"/>
+      <c r="D80" s="31" t="n"/>
+      <c r="E80" s="31" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Route Stripe receipts to the team inbox</t>
+          <t>Add a private notes section on each member</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Receipt/invoice emails should also go to hello@704collective.com.</t>
+          <t>Internal request: a notes area per member for context (e.g. 'comped through August').</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Stripe email settings -&gt; CC hello@ (or a forwarding rule).</t>
+          <t>Read: admin + super-admin. Write/edit: super-admin only. Not member-visible.</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -2532,35 +2551,51 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>CC hello@ on Stripe receipts, or add a forwarding rule.</t>
+          <t>Internal-only; super-admin writes, admins read, members never see it.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="23.85" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>MEMBER EXPERIENCE   ·   9 items</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n"/>
-      <c r="C82" s="31" t="n"/>
-      <c r="D82" s="31" t="n"/>
-      <c r="E82" s="31" t="n"/>
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Build the admin health dashboard</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>One screen showing system health at a glance; catches silent failures before members do.</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>5 widgets — cron, webhooks, drip health, email tracking, payment sync. Sits on /api/health.</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Reads /api/health + checks; surfaces silent failures.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="21.75" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Strip member profiles to four clean fields</t>
+          <t>Let admins change a member's tier and have billing follow</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Simplify the profile to name, photo, what you do, and a one-line bio — as real columns, not JSON. Locked: archive the other 15+ fields (kept in DB, hidden) for future matchmaking.</t>
+          <t>App-side tier change/comp exists; the Stripe billing side doesn't follow.</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>4 visible fields as real columns; align onboarding + settings + directory. The 4-field data move rides with the identity foundation (same plumbing).</t>
+          <t>Wire admin tier-change to Stripe subscription cancel/modify/start.</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -2570,24 +2605,24 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Archive (don't delete) the rest — raw material for future matchmaking.</t>
+          <t>App-side override already exists; this is the Stripe billing reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="23.85" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Build the one merged member portal with tiered views</t>
+          <t>Harden the admin cancel-subscription flow</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Locked: replace the two portals (member dashboard + business portal) with ONE codebase; business gets an elevated view, social the standard view; clear type distinction preserved.</t>
+          <t>Make admin cancel safe (running twice shouldn't double-act).</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>One portal codebase; gate business-only modules behind member type. Replaces /dashboard vs /business-portal.</t>
+          <t>Add idempotency + structured logging + alert to admin-cancel-subscription.</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -2597,51 +2632,51 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Replaces /dashboard vs /business-portal with one tier-gated codebase.</t>
+          <t>Idempotent + logged + alerted so a double-run can't double-act.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="23.85" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Rebuild onboarding questionnaire + member brief</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Store responses in their own table and generate a 'member brief' for future matchmaking/AI.</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>Onboarding rebuild + onboarding_responses table + member_brief column.</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>Responses in their own table; feeds a future member brief.</t>
+          <t>Build the admin area into clean sections</t>
+        </is>
+      </c>
+      <c r="B85" s="36" t="inlineStr">
+        <is>
+          <t>Reorganize admin into Today / People / Events / Network / Money / Messages / Settings with one source of truth per question.</t>
+        </is>
+      </c>
+      <c r="C85" s="36" t="inlineStr">
+        <is>
+          <t>7-section IA; folds in nav cleanup, per-event check-in start, financial accuracy, tier tools, and guest upload.</t>
+        </is>
+      </c>
+      <c r="D85" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E85" s="36" t="inlineStr">
+        <is>
+          <t>The Messages section is where the texting inbox lives.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="23.85" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Member portal / dashboard redesign</t>
+          <t>Shared admin navigation config</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>The redesign: 5-tab bottom nav, pass-first / next-event hero, onboarding checklist removed after completion, plus resources/bookings tabs. The shared activity feed is KEPT and built on (members post / share / like; event discussions surface there) — only the minor personal activity-log widget from the old dashboard is retired.</t>
+          <t>One shared config for admin nav so it's consistent and not duplicated.</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Multi-week. SEQUENCING: the visual redesign lands AFTER the identity foundation is built and verified — not concurrent with it (one big change at a time on a no-staging system). Resources/bookings depend on vendor partnerships.</t>
+          <t>Single adminNav config; remove duplicated nav definitions.</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -2651,78 +2686,78 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Activity feed stays; only the personal activity-log widget is retired. Visual redesign sequenced after identity.</t>
+          <t>One config; removes duplicated nav definitions.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Member directory — people-finder for all member + partner types</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>A members-only people-finder where social members, business members, and partners can all find and see each other — profiles only, WITHOUT the business-listings view. Visible to everyone logged in, regardless of type. A privacy toggle lets a member hide from it.</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Logged-in directory of people (social + business + partner). Profiles only — no business view (that lives in The Network). Visible to all logged-in types; honor the privacy toggle.</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Distinct from The Network (hubs + business/partner listings). Pairs with the privacy toggle below.</t>
+          <t>Guest list upload tool</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Let admins upload a guest list for an event.</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Guest list upload UI.</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Also unblocks future guest-conversion automation.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="23.85" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Profile privacy toggle</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>A toggle for members to control whether they appear in the directory and the internal Network member view.</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>Build the opt-out toggle; default is listed, members can hide themselves.</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>Confirmed feature — the directory is opt-out via this toggle.</t>
+          <t>Fix the organization settings table</t>
+        </is>
+      </c>
+      <c r="B88" s="37" t="inlineStr">
+        <is>
+          <t>organization_settings has the wrong schema.</t>
+        </is>
+      </c>
+      <c r="C88" s="37" t="inlineStr">
+        <is>
+          <t>Correct the organization_settings schema.</t>
+        </is>
+      </c>
+      <c r="D88" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E88" s="38" t="inlineStr">
+        <is>
+          <t>Schema is currently wrong; correct it.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21.75" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Member cancellation retention flow</t>
+          <t>Route Stripe receipts to the team inbox</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Improve the cancellation flow with retention UX.</t>
+          <t>Receipt/invoice emails should also go to hello@704collective.com.</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Retention UX on cancellation (offers, pauses, feedback).</t>
+          <t>Stripe email settings -&gt; CC hello@ (or a forwarding rule).</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -2732,100 +2767,116 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Offers / pauses / feedback on cancellation.</t>
+          <t>CC hello@ on Stripe receipts, or add a forwarding rule.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="23.85" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>Member spotlight on calendar/home</t>
-        </is>
-      </c>
-      <c r="B90" s="29" t="inlineStr">
-        <is>
-          <t>Feature a member spotlight on the calendar/home pages.</t>
-        </is>
-      </c>
-      <c r="C90" s="29" t="inlineStr">
-        <is>
-          <t>Member spotlight feature.</t>
-        </is>
-      </c>
-      <c r="D90" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E90" s="30" t="inlineStr">
-        <is>
-          <t>Feature a member on calendar/home.</t>
-        </is>
-      </c>
+      <c r="A90" s="35" t="inlineStr">
+        <is>
+          <t>MEMBER EXPERIENCE   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B90" s="31" t="n"/>
+      <c r="C90" s="31" t="n"/>
+      <c r="D90" s="31" t="n"/>
+      <c r="E90" s="31" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Unlimited guest passes for dream-team members</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="6" t="n"/>
+          <t>Strip member profiles to four clean fields</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Simplify the profile to name, photo, what you do, and a one-line bio — as real columns, not JSON. Locked: archive the other 15+ fields (kept in DB, hidden) for future matchmaking.</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>4 visible fields as real columns; align onboarding + settings + directory. The 4-field data move rides with the identity foundation (same plumbing).</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Archive (don't delete) the rest — raw material for future matchmaking.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>PERFORMANCE   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B92" s="31" t="n"/>
-      <c r="C92" s="31" t="n"/>
-      <c r="D92" s="31" t="n"/>
-      <c r="E92" s="31" t="n"/>
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Build the one merged member portal with tiered views</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Locked: replace the two portals (member dashboard + business portal) with ONE codebase; business gets an elevated view, social the standard view; clear type distinction preserved.</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>One portal codebase; gate business-only modules behind member type. Replaces /dashboard vs /business-portal.</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Replaces /dashboard vs /business-portal with one tier-gated codebase.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Speed up slow list pages (Events, Tasks, Hubs)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>These pages make many small repeated DB calls (N+1) that get slow as data grows.</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Resolve the N+1 query patterns; batch them.</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Batch the repeated calls on Events, Tasks, Hubs.</t>
+          <t>Rebuild onboarding questionnaire + member brief</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Store responses in their own table and generate a 'member brief' for future matchmaking/AI.</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Onboarding rebuild + onboarding_responses table + member_brief column.</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Responses in their own table; feeds a future member brief.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Make bulk member adds all-or-nothing</t>
+          <t>Member portal / dashboard redesign</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Bulk add isn't transactional — a partial failure leaves half-written data.</t>
+          <t>The redesign: 5-tab bottom nav, pass-first / next-event hero, onboarding checklist removed after completion, plus resources/bookings tabs. The shared activity feed is KEPT and built on (members post / share / like; event discussions surface there) — only the minor personal activity-log widget from the old dashboard is retired.</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Make add-members and hub-delete atomic.</t>
+          <t>Multi-week. SEQUENCING: the visual redesign lands AFTER the identity foundation is built and verified — not concurrent with it (one big change at a time on a no-staging system). Resources/bookings depend on vendor partnerships.</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -2835,247 +2886,263 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>All-or-nothing; same for hub deletes.</t>
+          <t>Activity feed stays; only the personal activity-log widget is retired. Visual redesign sequenced after identity.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Move heavy admin queries to the server</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Keep the browser from doing heavy lifting on admin overview + email dashboard.</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>Add server-side RPCs: admin_overview, email_dashboard.</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>Move admin overview + email dashboard to server RPCs.</t>
+          <t>Member directory — people-finder for all member + partner types</t>
+        </is>
+      </c>
+      <c r="B95" s="36" t="inlineStr">
+        <is>
+          <t>A members-only people-finder where social members, business members, and partners can all find and see each other — profiles only, WITHOUT the business-listings view. Visible to everyone logged in, regardless of type. A privacy toggle lets a member hide from it.</t>
+        </is>
+      </c>
+      <c r="C95" s="36" t="inlineStr">
+        <is>
+          <t>Logged-in directory of people (social + business + partner). Profiles only — no business view (that lives in The Network). Visible to all logged-in types; honor the privacy toggle.</t>
+        </is>
+      </c>
+      <c r="D95" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E95" s="36" t="inlineStr">
+        <is>
+          <t>Distinct from The Network (hubs + business/partner listings). Pairs with the privacy toggle below.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21.75" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Standardize how data is loaded (React Query)</t>
-        </is>
-      </c>
-      <c r="B96" s="29" t="inlineStr">
-        <is>
-          <t>Make loading behavior uniform and reliable.</t>
-        </is>
-      </c>
-      <c r="C96" s="29" t="inlineStr">
-        <is>
-          <t>React Query rollout across data fetching.</t>
-        </is>
-      </c>
-      <c r="D96" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E96" s="30" t="inlineStr">
-        <is>
-          <t>Uniform data-loading / caching across the app.</t>
+          <t>Profile privacy toggle</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>A toggle for members to control whether they appear in the directory and the internal Network member view.</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Build the opt-out toggle; default is listed, members can hide themselves.</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed feature — the directory is opt-out via this toggle.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="23.85" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Audit shortcut data fields for correctness</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="6" t="n"/>
+          <t>Member cancellation retention flow</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Improve the cancellation flow with retention UX.</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Retention UX on cancellation (offers, pauses, feedback).</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Offers / pauses / feedback on cancellation.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="21.75" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>AUTH   ·   7 items</t>
-        </is>
-      </c>
-      <c r="B98" s="31" t="n"/>
-      <c r="C98" s="31" t="n"/>
-      <c r="D98" s="31" t="n"/>
-      <c r="E98" s="31" t="n"/>
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Member spotlight on calendar/home</t>
+        </is>
+      </c>
+      <c r="B98" s="37" t="inlineStr">
+        <is>
+          <t>Feature a member spotlight on the calendar/home pages.</t>
+        </is>
+      </c>
+      <c r="C98" s="37" t="inlineStr">
+        <is>
+          <t>Member spotlight feature.</t>
+        </is>
+      </c>
+      <c r="D98" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E98" s="38" t="inlineStr">
+        <is>
+          <t>Feature a member on calendar/home.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Verify magic-link login across two devices</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Phone-to-desktop: request a link on a phone, type the 8-digit code on the desktop.</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>Cross-device OTP test; confirm same-device + resend cooldown too.</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>Requires a second device (owner-run).</t>
-        </is>
-      </c>
+          <t>Unlimited guest passes for dream-team members</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="6" t="n"/>
     </row>
     <row r="100" ht="23.85" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>Verify magic-link login works in production</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>End-to-end check the email magic-link round-trip works live.</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>Test request -&gt; click -&gt; signed in, in prod.</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>End-to-end live round-trip check.</t>
-        </is>
-      </c>
+      <c r="A100" s="35" t="inlineStr">
+        <is>
+          <t>PERFORMANCE   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B100" s="31" t="n"/>
+      <c r="C100" s="31" t="n"/>
+      <c r="D100" s="31" t="n"/>
+      <c r="E100" s="31" t="n"/>
     </row>
     <row r="101" ht="23.85" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Verify sessions refresh correctly on expiry</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Confirm cookie-based refresh works when a token expires so members aren't kicked out.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Verify @supabase/ssr middleware refreshes session on token expiry.</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Confirm members aren't kicked out when a token expires.</t>
+          <t>Speed up slow list pages (Events, Tasks, Hubs)</t>
+        </is>
+      </c>
+      <c r="B101" s="36" t="inlineStr">
+        <is>
+          <t>These pages make many small repeated DB calls (N+1) that get slow as data grows.</t>
+        </is>
+      </c>
+      <c r="C101" s="36" t="inlineStr">
+        <is>
+          <t>Resolve the N+1 query patterns; batch them.</t>
+        </is>
+      </c>
+      <c r="D101" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E101" s="36" t="inlineStr">
+        <is>
+          <t>Batch the repeated calls on Events, Tasks, Hubs.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Verify Google sign-in works</t>
+          <t>Make bulk member adds all-or-nothing</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Confirm Google login/signup paths work in production.</t>
+          <t>Bulk add isn't transactional — a partial failure leaves half-written data.</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Test Google OAuth signup + sign-in.</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Make add-members and hub-delete atomic.</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Confirm Google login/signup in production.</t>
+          <t>All-or-nothing; same for hub deletes.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Apple Sign-In</t>
+          <t>Move heavy admin queries to the server</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Keep the browser from doing heavy lifting on admin overview + email dashboard.</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Add server-side RPCs: admin_overview, email_dashboard.</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Move admin overview + email dashboard to server RPCs.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="23.85" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Branded auth links (stop showing supabase.co URLs)</t>
-        </is>
-      </c>
-      <c r="B104" s="29" t="n"/>
-      <c r="C104" s="29" t="n"/>
-      <c r="D104" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E104" s="30" t="n"/>
+          <t>Standardize how data is loaded (React Query)</t>
+        </is>
+      </c>
+      <c r="B104" s="37" t="inlineStr">
+        <is>
+          <t>Make loading behavior uniform and reliable.</t>
+        </is>
+      </c>
+      <c r="C104" s="37" t="inlineStr">
+        <is>
+          <t>React Query rollout across data fetching.</t>
+        </is>
+      </c>
+      <c r="D104" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E104" s="38" t="inlineStr">
+        <is>
+          <t>Uniform data-loading / caching across the app.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="21.75" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Password rules hardening (min length 6 to 8, leaked-password check)</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>Supabase minimum password length is 6 and the leaked-password check is off. Both are weaker than they should be for a paid membership platform.</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>Do the UI copy FIRST, then the dashboard toggles. Update /setup-password and every password field to state the real rule before raising the server minimum to 8, otherwise members get rejected by a rule the screen never showed them. Then enable Prevent use of leaked passwords and confirm the rejection message renders cleanly. Leave Require current password when updating OFF, it breaks the no-password comp-invite setup flow. Rehearse on develop both viewports.</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>Raised 2026-08-06 during the Email OTP expiration change (3600 to 86400).</t>
-        </is>
-      </c>
+          <t>Audit shortcut data fields for correctness</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="6" t="n"/>
     </row>
     <row r="106" ht="23.85" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>BUSINESS   ·   1 item</t>
+      <c r="A106" s="35" t="inlineStr">
+        <is>
+          <t>AUTH   ·   7 items</t>
         </is>
       </c>
       <c r="B106" s="31" t="n"/>
@@ -3086,277 +3153,261 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Verify the business application approval works</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="5" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="6" t="n"/>
+          <t>Verify magic-link login across two devices</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Phone-to-desktop: request a link on a phone, type the 8-digit code on the desktop.</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Cross-device OTP test; confirm same-device + resend cooldown too.</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>Requires a second device (owner-run).</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="23.85" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIALS   ·   6 items</t>
-        </is>
-      </c>
-      <c r="B108" s="31" t="n"/>
-      <c r="C108" s="31" t="n"/>
-      <c r="D108" s="31" t="n"/>
-      <c r="E108" s="31" t="n"/>
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Verify magic-link login works in production</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>End-to-end check the email magic-link round-trip works live.</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>Test request -&gt; click -&gt; signed in, in prod.</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>End-to-end live round-trip check.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="23.85" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Verify the financial dashboard</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Confirm it reports MRR, churn, and revenue by tier correctly (churn once showed 2055%).</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>Verify financial dashboard accuracy.</t>
-        </is>
-      </c>
-      <c r="D109" s="11" t="inlineStr">
+          <t>Verify sessions refresh correctly on expiry</t>
+        </is>
+      </c>
+      <c r="B109" s="36" t="inlineStr">
+        <is>
+          <t>Confirm cookie-based refresh works when a token expires so members aren't kicked out.</t>
+        </is>
+      </c>
+      <c r="C109" s="36" t="inlineStr">
+        <is>
+          <t>Verify @supabase/ssr middleware refreshes session on token expiry.</t>
+        </is>
+      </c>
+      <c r="D109" s="36" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>Built in Lovable originally — accuracy unconfirmed.</t>
+      <c r="E109" s="36" t="inlineStr">
+        <is>
+          <t>Confirm members aren't kicked out when a token expires.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="23.85" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>Verify the admin financial data function</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Confirm the edge function feeding admin financials returns correct numbers.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Verify admin-financial-data.</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>Verify Google sign-in works</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Confirm Google login/signup paths work in production.</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Test Google OAuth signup + sign-in.</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Confirm the numbers it returns are correct.</t>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>Confirm Google login/signup in production.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="23.85" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Three-bucket revenue view</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Show revenue split three ways.</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>Collected / projected / churned split.</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>Collected / projected / churned.</t>
+          <t>Apple Sign-In</t>
         </is>
       </c>
     </row>
     <row r="112" ht="23.85" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Member-facing financial widget</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>A small financial widget members can see.</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>Member-facing billing-status widget.</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>Small billing-status widget for members.</t>
-        </is>
-      </c>
+          <t>Branded auth links (stop showing supabase.co URLs)</t>
+        </is>
+      </c>
+      <c r="B112" s="29" t="n"/>
+      <c r="C112" s="29" t="n"/>
+      <c r="D112" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E112" s="30" t="n"/>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Reduce redundant Stripe scans</t>
-        </is>
-      </c>
-      <c r="B113" s="29" t="inlineStr">
-        <is>
-          <t>Cut how often the system scans Stripe, for performance/cost.</t>
-        </is>
-      </c>
-      <c r="C113" s="29" t="inlineStr">
-        <is>
-          <t>Reduce Stripe API scan frequency.</t>
-        </is>
-      </c>
-      <c r="D113" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E113" s="30" t="inlineStr">
-        <is>
-          <t>Cut scan frequency for cost / performance.</t>
+          <t>Password rules hardening (min length 6 to 8, leaked-password check)</t>
+        </is>
+      </c>
+      <c r="B113" s="39" t="inlineStr">
+        <is>
+          <t>Supabase minimum password length is 6 and the leaked-password check is off. Both are weaker than they should be for a paid membership platform.</t>
+        </is>
+      </c>
+      <c r="C113" s="39" t="inlineStr">
+        <is>
+          <t>Do the UI copy FIRST, then the dashboard toggles. Update /setup-password and every password field to state the real rule before raising the server minimum to 8, otherwise members get rejected by a rule the screen never showed them. Then enable Prevent use of leaked passwords and confirm the rejection message renders cleanly. Leave Require current password when updating OFF, it breaks the no-password comp-invite setup flow. Rehearse on develop both viewports.</t>
+        </is>
+      </c>
+      <c r="D113" s="39" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
+        <is>
+          <t>Raised 2026-08-06 during the Email OTP expiration change (3600 to 86400).</t>
         </is>
       </c>
     </row>
     <row r="114" ht="23.85" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>Past-due dismissal flow</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="6" t="n"/>
+      <c r="A114" s="35" t="inlineStr">
+        <is>
+          <t>BUSINESS   ·   1 item</t>
+        </is>
+      </c>
+      <c r="B114" s="31" t="n"/>
+      <c r="C114" s="31" t="n"/>
+      <c r="D114" s="31" t="n"/>
+      <c r="E114" s="31" t="n"/>
     </row>
     <row r="115" ht="46.25" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>EMAIL &amp; DRIP   ·   13 items</t>
-        </is>
-      </c>
-      <c r="B115" s="31" t="n"/>
-      <c r="C115" s="31" t="n"/>
-      <c r="D115" s="31" t="n"/>
-      <c r="E115" s="31" t="n"/>
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>Verify the business application approval works</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="6" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>Drip email health banner</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>A banner flagging when drips are silently failing or stalled.</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>Drip health-check banner.</t>
-        </is>
-      </c>
-      <c r="D116" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>Flags silently failing / stalled drips.</t>
-        </is>
-      </c>
+      <c r="A116" s="35" t="inlineStr">
+        <is>
+          <t>FINANCIALS   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B116" s="31" t="n"/>
+      <c r="C116" s="31" t="n"/>
+      <c r="D116" s="31" t="n"/>
+      <c r="E116" s="31" t="n"/>
     </row>
     <row r="117" ht="23.85" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Guest follow-up drip (7 + 20 day)</t>
+          <t>Verify the financial dashboard</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Automatic emails to guests at day 7 and 20 to convert them.</t>
+          <t>Confirm it reports MRR, churn, and revenue by tier correctly (churn once showed 2055%).</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Guest 7-day + 20-day drip.</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Verify financial dashboard accuracy.</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Converts guests at day 7 and 20.</t>
+          <t>Built in Lovable originally — accuracy unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="23.85" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>14-day RSVP prompt for new members</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Nudge new members who haven't RSVP'd within 14 days.</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>14-day RSVP prompt drip.</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>Nudges new members who haven't RSVP'd.</t>
+          <t>Verify the admin financial data function</t>
+        </is>
+      </c>
+      <c r="B118" s="36" t="inlineStr">
+        <is>
+          <t>Confirm the edge function feeding admin financials returns correct numbers.</t>
+        </is>
+      </c>
+      <c r="C118" s="36" t="inlineStr">
+        <is>
+          <t>Verify admin-financial-data.</t>
+        </is>
+      </c>
+      <c r="D118" s="36" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E118" s="36" t="inlineStr">
+        <is>
+          <t>Confirm the numbers it returns are correct.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="21.75" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Confirm the email log matches actual sends</t>
+          <t>Three-bucket revenue view</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Today failures are swallowed; make 'did this send' provable.</t>
+          <t>Show revenue split three ways.</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>email_log row matching; stop swallowing failures.</t>
+          <t>Collected / projected / churned split.</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -3366,24 +3417,24 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Stop swallowing failures so 'did this send' is provable.</t>
+          <t>Collected / projected / churned.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="23.85" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Per-email open/click analytics</t>
+          <t>Member-facing financial widget</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Track opens/clicks per template so we know what works.</t>
+          <t>A small financial widget members can see.</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Per-template email analytics.</t>
+          <t>Member-facing billing-status widget.</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -3393,78 +3444,62 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Per-template open / click tracking.</t>
+          <t>Small billing-status widget for members.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="23.85" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Per-member engagement scoring</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>Score each member's engagement from email/event activity.</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>Engagement scoring per member.</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>Score members from email / event activity.</t>
+          <t>Reduce redundant Stripe scans</t>
+        </is>
+      </c>
+      <c r="B121" s="37" t="inlineStr">
+        <is>
+          <t>Cut how often the system scans Stripe, for performance/cost.</t>
+        </is>
+      </c>
+      <c r="C121" s="37" t="inlineStr">
+        <is>
+          <t>Reduce Stripe API scan frequency.</t>
+        </is>
+      </c>
+      <c r="D121" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E121" s="38" t="inlineStr">
+        <is>
+          <t>Cut scan frequency for cost / performance.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="23.85" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>Category-level unsubscribe preferences</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>Let members opt out of specific categories, not all-or-nothing; builds on the one-flag fix.</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>Per-category opt-out prefs + a member settings page.</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>Builds on the one-flag opt-out fix.</t>
-        </is>
-      </c>
+      <c r="A122" s="35" t="inlineStr">
+        <is>
+          <t>EMAIL &amp; DRIP   ·   13 items</t>
+        </is>
+      </c>
+      <c r="B122" s="31" t="n"/>
+      <c r="C122" s="31" t="n"/>
+      <c r="D122" s="31" t="n"/>
+      <c r="E122" s="31" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Branching drips based on opens/clicks</t>
+          <t>Drip email health banner</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>Drip sequences that branch on open/click.</t>
+          <t>A banner flagging when drips are silently failing or stalled.</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Open/click-branching drips.</t>
+          <t>Drip health-check banner.</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -3474,51 +3509,51 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Branch sequences on open / click.</t>
+          <t>Flags silently failing / stalled drips.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="68.65000000000001" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Send email from a contact record</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Let an admin email directly from a member/contact record.</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Send-email action on the contact record.</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Admin emails directly from a member record.</t>
+          <t>Guest follow-up drip (7 + 20 day)</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Automatic emails to guests at day 7 and 20 to convert them.</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>Guest 7-day + 20-day drip.</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>Converts guests at day 7 and 20.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="23.85" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Attachments and images on event email campaigns</t>
+          <t>14-day RSVP prompt for new members</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>Let campaign emails include attachments and images.</t>
+          <t>Nudge new members who haven't RSVP'd within 14 days.</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Extend the campaign editor for attachments + images.</t>
+          <t>14-day RSVP prompt drip.</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -3528,154 +3563,186 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Extend the campaign editor.</t>
+          <t>Nudges new members who haven't RSVP'd.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="21.75" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Live test the guest-pass drip</t>
+          <t>Confirm the email log matches actual sends</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Confirm the drip fires correctly on a guest pass.</t>
+          <t>Today failures are swallowed; make 'did this send' provable.</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Live test the drip on guest_pass.</t>
-        </is>
-      </c>
-      <c r="D126" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>email_log row matching; stop swallowing failures.</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Confirm it fires on a guest pass.</t>
+          <t>Stop swallowing failures so 'did this send' is provable.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Merge guest follow-up into the drip processor</t>
-        </is>
-      </c>
-      <c r="B127" s="29" t="inlineStr">
-        <is>
-          <t>Retire the separate guest-followup function and fold it into the main processor.</t>
-        </is>
-      </c>
-      <c r="C127" s="29" t="inlineStr">
-        <is>
-          <t>Consolidate guest-followup into process-drips.</t>
-        </is>
-      </c>
-      <c r="D127" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E127" s="30" t="inlineStr">
-        <is>
-          <t>Fold guest-followup into process-drips.</t>
+          <t>Per-email open/click analytics</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>Track opens/clicks per template so we know what works.</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Per-template email analytics.</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>Per-template open / click tracking.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="23.85" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Push current members to subscribe to the calendar + add their pass</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="5" t="n"/>
-      <c r="D128" s="5" t="n"/>
-      <c r="E128" s="6" t="n"/>
+          <t>Per-member engagement scoring</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Score each member's engagement from email/event activity.</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Engagement scoring per member.</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>Score members from email / event activity.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="23.85" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>DATA &amp; CLEANUP   ·   6 items</t>
-        </is>
-      </c>
-      <c r="B129" s="31" t="n"/>
-      <c r="C129" s="31" t="n"/>
-      <c r="D129" s="31" t="n"/>
-      <c r="E129" s="31" t="n"/>
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Category-level unsubscribe preferences</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>Let members opt out of specific categories, not all-or-nothing; builds on the one-flag fix.</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Per-category opt-out prefs + a member settings page.</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>Builds on the one-flag opt-out fix.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="35.05" customHeight="1">
-      <c r="A130" s="17" t="inlineStr">
-        <is>
-          <t>Add CHECK constraints incrementally (enums REJECTED — too risky)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Was 'convert status text -&gt; enums'. DIAGNOSED Jul 9 as too risky: ~35 tables / 60+ write paths, and profiles.subscription_status is fed by the Stripe webhook with Stripe's full status vocabulary (trialing/paused/incomplete/etc). An enum built from observed values would make the webhook UPDATE throw on the first unseen status — silent breakage in the PAYMENT path. Enums rejected.</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>If typo-prevention is wanted later: add per-table CHECK constraints (NOT enums), table-by-table, starting with attendance_credentials (values: active/used/voided). Trivially reversible. Its own scoped task — never wholesale.</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Reclassified Jul 9. Do NOT rush — payment-path risk. CHECK constraints are the safe 80/20 if revisited.</t>
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Branching drips based on opens/clicks</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Drip sequences that branch on open/click.</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Open/click-branching drips.</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>Branch sequences on open / click.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="35.05" customHeight="1">
-      <c r="A131" s="17" t="inlineStr">
-        <is>
-          <t>RSVP attribution by event ID</t>
-        </is>
-      </c>
-      <c r="B131" s="15" t="inlineStr">
-        <is>
-          <t>DIAGNOSED Jul 9: bigger than 'add a column'. Per-event RSVP tagging is DEAD — the code that slug-tagged events was removed; since Apr 21 a public RSVP only gets a generic 'free-event-rsvp' tag, so you can't segment 'RSVP'd to event X' for any recent event. 6 frozen slug-tags remain (105 rows) and rot on rename. contact_tags has NO event_id column.</t>
-        </is>
-      </c>
-      <c r="C131" s="15" t="inlineStr">
-        <is>
-          <t>HALF-DAY scoped task (not a quick close): (1) migration add nullable event_id uuid REFERENCES events(id) to contact_tags; (2) re-add per-event tagging in capture-public-rsvp (event_id already in scope) + optionally create-guest-pass; (3) backfill — 5 of 6 slug-tags map to real event_ids by title-slug match (1 unmatched: coffee-and-connect-tabbris-co-working). Deploys + tests.</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E131" s="15" t="inlineStr">
-        <is>
-          <t>Jul 9: revives dead per-event attribution. Own task, budget a half-day. Backfill mostly possible.</t>
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Send email from a contact record</t>
+        </is>
+      </c>
+      <c r="B131" s="36" t="inlineStr">
+        <is>
+          <t>Let an admin email directly from a member/contact record.</t>
+        </is>
+      </c>
+      <c r="C131" s="36" t="inlineStr">
+        <is>
+          <t>Send-email action on the contact record.</t>
+        </is>
+      </c>
+      <c r="D131" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E131" s="36" t="inlineStr">
+        <is>
+          <t>Admin emails directly from a member record.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="68.65000000000001" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Drop ~35 empty leftover tables</t>
+          <t>Attachments and images on event email campaigns</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>~35 empty scaffolding tables (old CRM, social manager, feed, DMs).</t>
+          <t>Let campaign emails include attachments and images.</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Export copies as a receipt, then drop.</t>
+          <t>Extend the campaign editor for attachments + images.</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -3685,134 +3752,154 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Don't drop without exporting copies first.</t>
+          <t>Extend the campaign editor.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="23.85" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Drop old backup tables after soak</t>
-        </is>
-      </c>
-      <c r="B133" s="29" t="inlineStr">
-        <is>
-          <t>Backup tables from recent migrations await a 2-4 week no-regression soak.</t>
-        </is>
-      </c>
-      <c r="C133" s="29" t="inlineStr">
-        <is>
-          <t>Drop dated backup_* tables after soak; confirm stability first.</t>
-        </is>
-      </c>
-      <c r="D133" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E133" s="30" t="inlineStr">
-        <is>
-          <t>Only after a 2-4 week no-regression soak.</t>
+          <t>Live test the guest-pass drip</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>Confirm the drip fires correctly on a guest pass.</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Live test the drip on guest_pass.</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>Confirm it fires on a guest pass.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Delete dead admin member components</t>
+          <t>Merge guest follow-up into the drip processor</t>
+        </is>
+      </c>
+      <c r="B134" s="37" t="inlineStr">
+        <is>
+          <t>Retire the separate guest-followup function and fold it into the main processor.</t>
+        </is>
+      </c>
+      <c r="C134" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate guest-followup into process-drips.</t>
+        </is>
+      </c>
+      <c r="D134" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E134" s="38" t="inlineStr">
+        <is>
+          <t>Fold guest-followup into process-drips.</t>
         </is>
       </c>
     </row>
     <row r="135" ht="35.05" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>MARKETING &amp; FRONT-END   ·   10 items</t>
-        </is>
-      </c>
-      <c r="B135" s="31" t="n"/>
-      <c r="C135" s="31" t="n"/>
-      <c r="D135" s="31" t="n"/>
-      <c r="E135" s="31" t="n"/>
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Push current members to subscribe to the calendar + add their pass</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="6" t="n"/>
     </row>
     <row r="136" ht="23.85" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>SEO + schema markup + pre-rendering (all front pages + 4 hub landers)</t>
-        </is>
-      </c>
-      <c r="B136" s="29" t="n"/>
-      <c r="C136" s="29" t="n"/>
-      <c r="D136" s="29" t="n"/>
-      <c r="E136" s="30" t="n"/>
+      <c r="A136" s="35" t="inlineStr">
+        <is>
+          <t>DATA &amp; CLEANUP   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B136" s="31" t="n"/>
+      <c r="C136" s="31" t="n"/>
+      <c r="D136" s="31" t="n"/>
+      <c r="E136" s="31" t="n"/>
     </row>
     <row r="137" ht="21.75" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>Homepage hero rebuild + image optimization</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>Rebuild the hero and compress oversized hero images (currently 24-30MB, should be 200-800KB).</t>
-        </is>
-      </c>
-      <c r="C137" s="8" t="inlineStr">
-        <is>
-          <t>Hero rebuild + compress images.</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t>Includes compressing 24-30MB hero images to 200-800KB.</t>
+      <c r="A137" s="17" t="inlineStr">
+        <is>
+          <t>Add CHECK constraints incrementally (enums REJECTED — too risky)</t>
+        </is>
+      </c>
+      <c r="B137" s="36" t="inlineStr">
+        <is>
+          <t>Was 'convert status text -&gt; enums'. DIAGNOSED Jul 9 as too risky: ~35 tables / 60+ write paths, and profiles.subscription_status is fed by the Stripe webhook with Stripe's full status vocabulary (trialing/paused/incomplete/etc). An enum built from observed values would make the webhook UPDATE throw on the first unseen status — silent breakage in the PAYMENT path. Enums rejected.</t>
+        </is>
+      </c>
+      <c r="C137" s="36" t="inlineStr">
+        <is>
+          <t>If typo-prevention is wanted later: add per-table CHECK constraints (NOT enums), table-by-table, starting with attendance_credentials (values: active/used/voided). Trivially reversible. Its own scoped task — never wholesale.</t>
+        </is>
+      </c>
+      <c r="D137" s="36" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="E137" s="36" t="inlineStr">
+        <is>
+          <t>Reclassified Jul 9. Do NOT rush — payment-path risk. CHECK constraints are the safe 80/20 if revisited.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="113.4" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Homepage copy rewrite + slogan</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Rewrite homepage body/section copy and update the slogan.</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
-        <is>
-          <t>Body + section copy + slogan.</t>
-        </is>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>Needs the copy spec.</t>
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>RSVP attribution by event ID</t>
+        </is>
+      </c>
+      <c r="B138" s="15" t="inlineStr">
+        <is>
+          <t>DIAGNOSED Jul 9: bigger than 'add a column'. Per-event RSVP tagging is DEAD — the code that slug-tagged events was removed; since Apr 21 a public RSVP only gets a generic 'free-event-rsvp' tag, so you can't segment 'RSVP'd to event X' for any recent event. 6 frozen slug-tags remain (105 rows) and rot on rename. contact_tags has NO event_id column.</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="inlineStr">
+        <is>
+          <t>HALF-DAY scoped task (not a quick close): (1) migration add nullable event_id uuid REFERENCES events(id) to contact_tags; (2) re-add per-event tagging in capture-public-rsvp (event_id already in scope) + optionally create-guest-pass; (3) backfill — 5 of 6 slug-tags map to real event_ids by title-slug match (1 unmatched: coffee-and-connect-tabbris-co-working). Deploys + tests.</t>
+        </is>
+      </c>
+      <c r="D138" s="19" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E138" s="15" t="inlineStr">
+        <is>
+          <t>Jul 9: revives dead per-event attribution. Own task, budget a half-day. Backfill mostly possible.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="57.45" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Fix the mobile hero sliding bug</t>
+          <t>Drop ~35 empty leftover tables</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>A visual bug where the hero image slides on mobile.</t>
+          <t>~35 empty scaffolding tables (old CRM, social manager, feed, DMs).</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Mobile hero sliding fix.</t>
+          <t>Export copies as a receipt, then drop.</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -3822,767 +3909,715 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Fix the hero sliding on mobile.</t>
+          <t>Don't drop without exporting copies first.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="46.25" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>The Exchange page</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Build The Exchange page (speaker-driven business event product page).</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t>The Exchange page.</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t>Speaker-driven business-event product page.</t>
+          <t>Backup tables: keep or drop — Adam's call (13 hand-made snapshots; auth-hash pair flagged)</t>
+        </is>
+      </c>
+      <c r="B140" s="37" t="inlineStr">
+        <is>
+          <t>cursor_report_rlsaudit.md (Sep 21): 13 hand-made backup tables from Apr–Jun 2026 remain in public (presweep x7, 20260610 x4, _auth_*backup_20260428 x2). Nothing references them; RLS deny-all holds and the leftover anon/authenticated grants were stripped on prod (by hand) and develop (migration 20260921070000). _auth_backup_20260428 holds old_encrypted_password for 24 users — the one pair that should not linger. backup_ambassador_referrals_presweep is empty.</t>
+        </is>
+      </c>
+      <c r="C140" s="37" t="inlineStr">
+        <is>
+          <t>Adam decides per snapshot whether its purpose is closed. Suggested order: the two _auth_* tables (export with pg_dump -t if a cold copy is wanted, then drop), the empty ambassador backup, then the presweep/20260610 sets once the identity sweep and sauna merge are considered settled. No drops proposed in SQL without provenance.</t>
+        </is>
+      </c>
+      <c r="D140" s="37" t="inlineStr">
+        <is>
+          <t>WAITING ON ADAM: keep or drop</t>
+        </is>
+      </c>
+      <c r="E140" s="38" t="inlineStr">
+        <is>
+          <t>Security posture is already correct (grants stripped, 17/17 receipt). This row is hygiene + the password-hash pair. Provenance for all 13 is the July baseline dump only.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="46.25" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Sponsor page (likely folds into /business)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Sponsor functionality — likely folds into the /business application routing.</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Probably absorbed by the /business rebuild.</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Likely folds into the /business rebuild — confirm first.</t>
+          <t>Delete dead admin member components</t>
         </is>
       </c>
     </row>
     <row r="142" ht="46.25" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>/business page rebuild with dynamic application</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Rebuild /business as one page with a dynamic application routing prospects to membership, Preferred Business, or sponsorship by their answers.</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="inlineStr">
-        <is>
-          <t>Dynamic diagnose-before-offer application.</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t>Routes prospects to membership, Preferred Business, or sponsorship.</t>
-        </is>
-      </c>
+      <c r="A142" s="35" t="inlineStr">
+        <is>
+          <t>MARKETING &amp; FRONT-END   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B142" s="31" t="n"/>
+      <c r="C142" s="31" t="n"/>
+      <c r="D142" s="31" t="n"/>
+      <c r="E142" s="31" t="n"/>
     </row>
     <row r="143" ht="57.45" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Charlotte hub landing sites (4 public landers)</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
-        <is>
-          <t>Four audience-specific public landers (cltarrival / cltfounded / clteatsandevents / cltreset) that funnel Charlotte audiences into the club.</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t>4 public landers, shared skeleton, own design pass, fully pre-rendered + schema (see SEO item). They feed The Network.</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>Public landers can ship earlier; they pair with The Network below.</t>
-        </is>
-      </c>
+          <t>SEO + schema markup + pre-rendering (all front pages + 4 hub landers)</t>
+        </is>
+      </c>
+      <c r="B143" s="29" t="n"/>
+      <c r="C143" s="29" t="n"/>
+      <c r="D143" s="29" t="n"/>
+      <c r="E143" s="30" t="n"/>
     </row>
     <row r="144" ht="57.45" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>The Network — four hubs + members rolled up</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>The four hubs rolled up into one view, plus all members. Two faces reading the same data: a PUBLIC face (the hub landers + business/partner listings — the sales asset) and an INTERNAL in-portal view that rolls up everyone. Social members appear ONLY on the internal in-portal view — never on the public hubs.</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Roll the four hubs into one Network view + members. Public face = hubs / business + partner listings (social members excluded). Internal face = full rolled-up view including social members. Reads the same hub data as the landers.</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Depends on the portal + identity foundation. Social members are internal-only on The Network. Separate from the member directory (people-only).</t>
+          <t>Homepage hero rebuild + image optimization</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Rebuild the hero and compress oversized hero images (currently 24-30MB, should be 200-800KB).</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>Hero rebuild + compress images.</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>Includes compressing 24-30MB hero images to 200-800KB.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="57.45" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Instagram comment auto-DM (ManyChat)</t>
+          <t>Homepage copy rewrite + slogan</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Rewrite homepage body/section copy and update the slogan.</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>Body + section copy + slogan.</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>Needs the copy spec.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>AI / AGENTS (LATER EFFORT)   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B146" s="31" t="n"/>
-      <c r="C146" s="31" t="n"/>
-      <c r="D146" s="31" t="n"/>
-      <c r="E146" s="31" t="n"/>
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>Fix the mobile hero sliding bug</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>A visual bug where the hero image slides on mobile.</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>Mobile hero sliding fix.</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>Fix the hero sliding on mobile.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="57.45" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>AI concierge + agent platform</t>
-        </is>
-      </c>
-      <c r="B147" s="29" t="n"/>
-      <c r="C147" s="29" t="n"/>
-      <c r="D147" s="29" t="n"/>
-      <c r="E147" s="30" t="n"/>
+          <t>The Exchange page</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>Build The Exchange page (speaker-driven business event product page).</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>The Exchange page.</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>Speaker-driven business-event product page.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="46.25" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>AI foundations (memory, embeddings, coordination)</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>Supporting infra for the agents: shared memory, member embeddings, multi-agent coordination, model routing.</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t>pgvector + embeddings, agent_memory, multi-agent coordination, model routing.</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t>A later effort; supports the agents (embeddings, memory, routing).</t>
+          <t>Sponsor page (likely folds into /business)</t>
+        </is>
+      </c>
+      <c r="B148" s="36" t="inlineStr">
+        <is>
+          <t>Sponsor functionality — likely folds into the /business application routing.</t>
+        </is>
+      </c>
+      <c r="C148" s="36" t="inlineStr">
+        <is>
+          <t>Probably absorbed by the /business rebuild.</t>
+        </is>
+      </c>
+      <c r="D148" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E148" s="36" t="inlineStr">
+        <is>
+          <t>Likely folds into the /business rebuild — confirm first.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="57.45" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>EVENT DISCUSSION &amp; NOTIFICATIONS + JUL-5/6 FINDINGS — IN-HOUSE (NOT ON THE DEVELOPER SHEET)   ·   10 items</t>
-        </is>
-      </c>
-      <c r="B149" s="31" t="n"/>
-      <c r="C149" s="31" t="n"/>
-      <c r="D149" s="31" t="n"/>
-      <c r="E149" s="31" t="n"/>
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>/business page rebuild with dynamic application</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>Rebuild /business as one page with a dynamic application routing prospects to membership, Preferred Business, or sponsorship by their answers.</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic diagnose-before-offer application.</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>Routes prospects to membership, Preferred Business, or sponsorship.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="23.85" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>Rotate the R2 media token (exposed key)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>The R2 Access Key ID + Secret for bucket 704-discussion-media were exposed in a working chat (screenshot/paste). Scope = that one media bucket only — low blast radius, but rotate.</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>After 6c ships: Cloudflare -&gt; R2 -&gt; API tokens -&gt; re-create 704-discussion-upload (Object Read &amp; Write, bucket-scoped) -&gt; supabase secrets set the two new values -&gt; confirm an upload still works.</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Declined</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Adam declined rotation Jul 5 - standing watch item. Key scope = one media bucket only (no member data / money / DB). Say 'rotate' anytime: ~2 min.</t>
+          <t>The Network — four hubs + members rolled up</t>
+        </is>
+      </c>
+      <c r="B150" s="36" t="inlineStr">
+        <is>
+          <t>The four hubs rolled up into one view, plus all members. Two faces reading the same data: a PUBLIC face (the hub landers + business/partner listings — the sales asset) and an INTERNAL in-portal view that rolls up everyone. Social members appear ONLY on the internal in-portal view — never on the public hubs.</t>
+        </is>
+      </c>
+      <c r="C150" s="36" t="inlineStr">
+        <is>
+          <t>Roll the four hubs into one Network view + members. Public face = hubs / business + partner listings (social members excluded). Internal face = full rolled-up view including social members. Reads the same hub data as the landers.</t>
+        </is>
+      </c>
+      <c r="D150" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E150" s="36" t="inlineStr">
+        <is>
+          <t>Depends on the portal + identity foundation. Social members are internal-only on The Network. Separate from the member directory (people-only).</t>
         </is>
       </c>
     </row>
     <row r="151" ht="23.85" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>Verify/finish the Alerts page (full history, discussion types)</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="inlineStr">
-        <is>
-          <t>Locked: bell badge clears on open, items dismiss via X, but the ALERTS PAGE keeps every notification forever - markable read (single + all). PARTIAL Jul 5: /dashboard/notifications now honors action_url (deep-links verified end to end). Remaining: full-history + mark-read behavior verification.</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t>Read the Alerts page code; verify full-history + mark-read behavior and that all discussion notification types display with correct deep-links; fix gaps. Desktop + mobile test.</t>
-        </is>
-      </c>
-      <c r="D151" s="20" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t>Deep-links fixed+verified Jul 5 (commit e9f6250). Remaining: verify full-history retention + mark-read (single + all).</t>
+          <t>Instagram comment auto-DM (ManyChat)</t>
         </is>
       </c>
     </row>
     <row r="152" ht="23.85" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>Messaging: bells for messages in existing conversations</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="inlineStr">
-        <is>
-          <t>Messaging was resurrected Jul 5 (DMs/groups had NEVER worked since launch: RETURNING/RLS deadlock, participants-insert policy tautology, content-vs-body + title-vs-name schema mismatches, 4 missing messages columns - all fixed and verified end to end). Remaining gap: notifyNewConversation only fires on conversation CREATION, so messages into an existing thread produce no bell.</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="inlineStr">
-        <is>
-          <t>Add a new_message bell per message into an existing conversation, throttled (e.g. skip if an unread new_message bell for that conversation already exists).</t>
-        </is>
-      </c>
-      <c r="D152" s="20" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t>Follow-on to the Jul 5 messaging resurrection. Recipients currently only get notified on the first-ever message.</t>
-        </is>
-      </c>
+      <c r="A152" s="35" t="inlineStr">
+        <is>
+          <t>AI / AGENTS (LATER EFFORT)   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B152" s="31" t="n"/>
+      <c r="C152" s="31" t="n"/>
+      <c r="D152" s="31" t="n"/>
+      <c r="E152" s="31" t="n"/>
     </row>
     <row r="153" ht="23.85" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>Messaging: attachment uploads (images/files)</t>
-        </is>
-      </c>
-      <c r="B153" s="29" t="inlineStr">
-        <is>
-          <t>MessagingView has image/file upload code paths and messages now has image_urls/file_urls/file_names columns (added Jul 5), but the storage wiring (bucket, upload flow) has never been tested and may not exist.</t>
-        </is>
-      </c>
-      <c r="C153" s="29" t="inlineStr">
-        <is>
-          <t>Audit the attachment path end to end: storage bucket, upload call, render. Fix or wire what's missing. Desktop + mobile test.</t>
-        </is>
-      </c>
-      <c r="D153" s="29" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E153" s="30" t="inlineStr">
-        <is>
-          <t>Text messaging + edits verified Jul 5; attachments explicitly skipped in that test.</t>
-        </is>
-      </c>
+          <t>AI concierge + agent platform</t>
+        </is>
+      </c>
+      <c r="B153" s="29" t="n"/>
+      <c r="C153" s="29" t="n"/>
+      <c r="D153" s="29" t="n"/>
+      <c r="E153" s="30" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
+          <t>AI foundations (memory, embeddings, coordination)</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Supporting infra for the agents: shared memory, member embeddings, multi-agent coordination, model routing.</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>pgvector + embeddings, agent_memory, multi-agent coordination, model routing.</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>A later effort; supports the agents (embeddings, memory, routing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="35" t="inlineStr">
+        <is>
+          <t>EVENT DISCUSSION &amp; NOTIFICATIONS + JUL-5/6 FINDINGS — IN-HOUSE (NOT ON THE DEVELOPER SHEET)   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B155" s="31" t="n"/>
+      <c r="C155" s="31" t="n"/>
+      <c r="D155" s="31" t="n"/>
+      <c r="E155" s="31" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>Rotate the R2 media token (exposed key)</t>
+        </is>
+      </c>
+      <c r="B156" s="36" t="inlineStr">
+        <is>
+          <t>The R2 Access Key ID + Secret for bucket 704-discussion-media were exposed in a working chat (screenshot/paste). Scope = that one media bucket only — low blast radius, but rotate.</t>
+        </is>
+      </c>
+      <c r="C156" s="36" t="inlineStr">
+        <is>
+          <t>After 6c ships: Cloudflare -&gt; R2 -&gt; API tokens -&gt; re-create 704-discussion-upload (Object Read &amp; Write, bucket-scoped) -&gt; supabase secrets set the two new values -&gt; confirm an upload still works.</t>
+        </is>
+      </c>
+      <c r="D156" s="36" t="inlineStr">
+        <is>
+          <t>Declined</t>
+        </is>
+      </c>
+      <c r="E156" s="36" t="inlineStr">
+        <is>
+          <t>Adam declined rotation Jul 5 - standing watch item. Key scope = one media bucket only (no member data / money / DB). Say 'rotate' anytime: ~2 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>Verify/finish the Alerts page (full history, discussion types)</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>Locked: bell badge clears on open, items dismiss via X, but the ALERTS PAGE keeps every notification forever - markable read (single + all). PARTIAL Jul 5: /dashboard/notifications now honors action_url (deep-links verified end to end). Remaining: full-history + mark-read behavior verification.</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Read the Alerts page code; verify full-history + mark-read behavior and that all discussion notification types display with correct deep-links; fix gaps. Desktop + mobile test.</t>
+        </is>
+      </c>
+      <c r="D157" s="20" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>Deep-links fixed+verified Jul 5 (commit e9f6250). Remaining: verify full-history retention + mark-read (single + all).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>Messaging: bells for messages in existing conversations</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Messaging was resurrected Jul 5 (DMs/groups had NEVER worked since launch: RETURNING/RLS deadlock, participants-insert policy tautology, content-vs-body + title-vs-name schema mismatches, 4 missing messages columns - all fixed and verified end to end). Remaining gap: notifyNewConversation only fires on conversation CREATION, so messages into an existing thread produce no bell.</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>Add a new_message bell per message into an existing conversation, throttled (e.g. skip if an unread new_message bell for that conversation already exists).</t>
+        </is>
+      </c>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>Follow-on to the Jul 5 messaging resurrection. Recipients currently only get notified on the first-ever message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>Messaging: attachment uploads (images/files)</t>
+        </is>
+      </c>
+      <c r="B159" s="37" t="inlineStr">
+        <is>
+          <t>MessagingView has image/file upload code paths and messages now has image_urls/file_urls/file_names columns (added Jul 5), but the storage wiring (bucket, upload flow) has never been tested and may not exist.</t>
+        </is>
+      </c>
+      <c r="C159" s="37" t="inlineStr">
+        <is>
+          <t>Audit the attachment path end to end: storage bucket, upload call, render. Fix or wire what's missing. Desktop + mobile test.</t>
+        </is>
+      </c>
+      <c r="D159" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E159" s="38" t="inlineStr">
+        <is>
+          <t>Text messaging + edits verified Jul 5; attachments explicitly skipped in that test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="21.75" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
           <t>Verify the first real-money admin refund (Remove &amp; Refund)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>Admin Remove &amp; Refund shipped Jul 5 (edge fn admin-refund-ticket: admin gate, Stripe refund, void credential, seat freed; + attendee-dialog button, mobile-safe). Every branch proven EXCEPT the successful real-money refund line: void-only path, 403 gate, already-voided idempotency, and the Stripe-failure 502 fail-safe (no seat freed without money returned) all tested live.</t>
         </is>
       </c>
-      <c r="C154" s="8" t="inlineStr">
+      <c r="C160" s="8" t="inlineStr">
         <is>
           <t>WAIT mode: on the next genuine member refund request, use Remove &amp; Refund in the event attendee dialog and verify: Stripe refunded, credential voided, seat freed, toast correct.</t>
         </is>
       </c>
-      <c r="D154" s="20" t="inlineStr">
+      <c r="D160" s="20" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E154" s="8" t="inlineStr">
+      <c r="E160" s="8" t="inlineStr">
         <is>
           <t>Zero-cost proof on the next real request. Sacred Walker (Jul 5) handled manually pre-feature; her case is the template.</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="21" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="41" t="inlineStr">
         <is>
           <t>SESSION LOG — JUL 7–9 2026 (COMPLETED; kept as record, esp. the security fix)</t>
         </is>
       </c>
-      <c r="B155" s="32" t="n"/>
-      <c r="C155" s="32" t="n"/>
-      <c r="D155" s="32" t="n"/>
-      <c r="E155" s="32" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Security: dropped anon-readable active_members view + locked event_participants_view</t>
-        </is>
-      </c>
-      <c r="B156" s="23" t="inlineStr">
-        <is>
-          <t>CRITICAL FIX Jul 9: active_members and event_participants_view were SECURITY DEFINER views with ALL privileges granted to anon — an unauthenticated internet caller could read every member's email/phone/Stripe customer ID + all attendee contact info, AND active_members (auto-updatable single-table view) exposed an anon WRITE path into profiles. active_members had ZERO callers -&gt; DROPPED. event_participants_view -&gt; security_invoker=true + REVOKE anon/authenticated (sole caller send-campaign uses service-role, unaffected). member_counts left as-is (intentional).</t>
-        </is>
-      </c>
-      <c r="C156" s="23" t="inlineStr">
-        <is>
-          <t>DONE via SQL. Verified from OUTSIDE with anon key: active_members=404, event_participants_view=401 permission denied. No rows leaked. send-campaign confirmed still works.</t>
-        </is>
-      </c>
-      <c r="D156" s="24" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E156" s="23" t="inlineStr">
-        <is>
-          <t>Biggest find of the session. Was disguised as a 'review Security Definer flags' tracker row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Nine-job cron auth resurrection + 2 guards, all 10 jobs healthy</t>
-        </is>
-      </c>
-      <c r="B157" s="23" t="inlineStr">
-        <is>
-          <t>Full audit found NINE broken crons (sheet knew of 2). Fixed: Vault key was legacy JWT but runtime injects sb_secret_ (updated Vault); SQL typo value-&gt;decrypted_secret on jobs 3/4/13; event-reminder had no service-key path + a no-auth-header mass-email hole (both fixed, commit 09d637d). Then built 2 guards: business-profile-reminder 14-day cooldown via contact_activity + internal-account exclusion (503548c); guest-event-match at-capacity exclusion (d722800). Both jobs 2 &amp; 10 re-enabled. All 10 cron jobs now active + healthy.</t>
-        </is>
-      </c>
-      <c r="C157" s="23" t="inlineStr">
-        <is>
-          <t>All confirmed 200 on live ticks. Guards dry-run/logic verified. WATCH: first live ticks of job 2 (14:00 UTC every 2 days) + job 10 (13:00 UTC daily) — read-only confirm right people emailed.</t>
-        </is>
-      </c>
-      <c r="D157" s="24" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E157" s="23" t="inlineStr">
-        <is>
-          <t>Commits 09d637d, 503548c, d722800 + Vault + SQL. event-reminder security hole closed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Sentry error monitoring — live + verified in prod</t>
-        </is>
-      </c>
-      <c r="B158" s="23" t="inlineStr">
-        <is>
-          <t>@sentry/nextjs wired (client+server+API+global-error), CSP allowance, instrumentation moved into src/ (Next ignores root-level with a src/ dir), DSN + source-map auth token in Vercel, /admin/sentry page activated. Prod capture VERIFIED (smoke-test error landed in feed).</t>
-        </is>
-      </c>
-      <c r="C158" s="23" t="inlineStr">
-        <is>
-          <t>Verified. WATCH: confirm Sentry project SLUG is exactly '704-collective' in a Vercel build log (source-map upload) — if wrong, traces stay minified (one-word fix).</t>
-        </is>
-      </c>
-      <c r="D158" s="24" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E158" s="23" t="inlineStr">
-        <is>
-          <t>Commits 417fb37/d779885/5d12aac/b437166. The safety net — Stage 1 complete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Josh Ahart full removal (exit workstream)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>De-privileged (super_admin-&gt;lead), permanent ban, all 8 sessions + 64 tokens killed, profile deactivated, ambassador row disabled, removed from public /about page (0cc8c66), 2 dormant test dupe accounts hard-deleted. Stripe sub cancelled + Connect account rejected (Adam, dashboard). Platform passwords rotated (Adam).</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Verified: role=lead, 0 sessions/tokens, banned. Public site scrubbed. Dashboard-member removal confirmed by Adam.</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>NOT on the build sheet — exit workstream. Recorded here for completeness. Aug 25: Josh hub purge DONE - his 4 remaining hub_members rows (one per hub, all joined 2026-05-21 03:11:32, all added by Adam) were deleted; verified afterwards at 0 hub memberships, 0 posts, 0 comments, 0 likes, 0 resources. CORRECTION to an earlier wording of this note: Josh created NO hubs. All four hubs are created_by Adam, so nothing was owned by him and the purge was membership rows only - the cascade risk on hubs.created_by is a separate finding about Adam's profile (see that row). Also noted while verifying: the hub display queries in dashboard/hubs/[id] and admin/hubs join profiles without a deleted_at filter, which is why his soft-deleted profile kept rendering and inflated each hub's member count by one. Closes the hub residue of the exit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="21.75" customHeight="1">
-      <c r="A160" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Member status batch (Jul 9)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Nicholas Stathopoulos + Robert Villante -&gt; non_member/inactive/override off/lead (Nick admin revoked + sessions killed). Whitney Cleland + Brenna Dunne + Kaelah Torres -&gt; ERASED (auth+profile+people+credentials deleted; all comped, no Stripe to cancel). More status changes flagged as coming.</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>All verified via SQL (zeros on erase). Read-first footprint audit confirmed safe (no owned content cascaded).</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Adam noted more member changes coming next session. Aug 25: Audrey Handleton converted to non-member - DONE, and recorded here as the next entry in this running member-status record. Verified end state: profiles reads non_member / inactive / membership_override false; the people row reads roles ['prospect'] with member_tier and member_status both null (never-was, not canceled). She was a comp who had drifted - profile said social while her people row still said business - and she never paid a cent, so there was no Stripe side to cancel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Business-event RSVP tier leak — closed + Annslee voided</t>
-        </is>
-      </c>
-      <c r="B161" s="23" t="inlineStr">
-        <is>
-          <t>Social members could RSVP business-only events: create-member-rsvp never checked required_tier, and the mobile sticky RSVP bar bypassed the desktop gate. Fixed: server-side tier gate in the edge function (ff20ba9, admins exempt) + mobile CTA respects canRsvp (952fbb2). Annslee Bottoms' live breach credential on Jul-14 Business Member Meeting VOIDED. Past legacy breaches intentionally left (real attendance history).</t>
-        </is>
-      </c>
-      <c r="C161" s="23" t="inlineStr">
-        <is>
-          <t>Verified: socialtest gets 403 'business members only' + red toast; direct-invoke blocked; Annslee active count on event = 0.</t>
-        </is>
-      </c>
-      <c r="D161" s="24" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E161" s="23" t="inlineStr">
-        <is>
-          <t>Commits ff20ba9, 952fbb2. Guest-side email opt-out gap noted -&gt; folds into unsubscribe policy work.</t>
-        </is>
-      </c>
+      <c r="B161" s="32" t="n"/>
+      <c r="C161" s="32" t="n"/>
+      <c r="D161" s="32" t="n"/>
+      <c r="E161" s="32" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Discussion edit/delete (comments+posts+photos) + admin always-on access</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Owners + admins can now edit/delete their own discussion comments (ecec3f8), posts (1e3adc1), and remove their own gallery photos (bcf746f); admins moderate anyone's. '(edited)' marker, soft-delete, silent removal. Also: admins now see the discussion link on any open event regardless of RSVP (583b343 — backend was already admin-exempt; was a missing-link discovery bug). Feed/comment/DM URL linkify (561403e).</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>All browser-tested desktop+mobile. Backend RLS already permitted; these were frontend gaps.</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+          <t>[DONE] Security: dropped anon-readable active_members view + locked event_participants_view</t>
+        </is>
+      </c>
+      <c r="B162" s="23" t="inlineStr">
+        <is>
+          <t>CRITICAL FIX Jul 9: active_members and event_participants_view were SECURITY DEFINER views with ALL privileges granted to anon — an unauthenticated internet caller could read every member's email/phone/Stripe customer ID + all attendee contact info, AND active_members (auto-updatable single-table view) exposed an anon WRITE path into profiles. active_members had ZERO callers -&gt; DROPPED. event_participants_view -&gt; security_invoker=true + REVOKE anon/authenticated (sole caller send-campaign uses service-role, unaffected). member_counts left as-is (intentional).</t>
+        </is>
+      </c>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>DONE via SQL. Verified from OUTSIDE with anon key: active_members=404, event_participants_view=401 permission denied. No rows leaked. send-campaign confirmed still works.</t>
+        </is>
+      </c>
+      <c r="D162" s="24" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>5 commits. Discussion feature now fully moderatable.</t>
+      <c r="E162" s="23" t="inlineStr">
+        <is>
+          <t>Biggest find of the session. Was disguised as a 'review Security Definer flags' tracker row.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="16" t="inlineStr">
         <is>
+          <t>[DONE] Nine-job cron auth resurrection + 2 guards, all 10 jobs healthy</t>
+        </is>
+      </c>
+      <c r="B163" s="23" t="inlineStr">
+        <is>
+          <t>Full audit found NINE broken crons (sheet knew of 2). Fixed: Vault key was legacy JWT but runtime injects sb_secret_ (updated Vault); SQL typo value-&gt;decrypted_secret on jobs 3/4/13; event-reminder had no service-key path + a no-auth-header mass-email hole (both fixed, commit 09d637d). Then built 2 guards: business-profile-reminder 14-day cooldown via contact_activity + internal-account exclusion (503548c); guest-event-match at-capacity exclusion (d722800). Both jobs 2 &amp; 10 re-enabled. All 10 cron jobs now active + healthy.</t>
+        </is>
+      </c>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>All confirmed 200 on live ticks. Guards dry-run/logic verified. WATCH: first live ticks of job 2 (14:00 UTC every 2 days) + job 10 (13:00 UTC daily) — read-only confirm right people emailed.</t>
+        </is>
+      </c>
+      <c r="D163" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E163" s="23" t="inlineStr">
+        <is>
+          <t>Commits 09d637d, 503548c, d722800 + Vault + SQL. event-reminder security hole closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>[DONE] Sentry error monitoring — live + verified in prod</t>
+        </is>
+      </c>
+      <c r="B164" s="23" t="inlineStr">
+        <is>
+          <t>@sentry/nextjs wired (client+server+API+global-error), CSP allowance, instrumentation moved into src/ (Next ignores root-level with a src/ dir), DSN + source-map auth token in Vercel, /admin/sentry page activated. Prod capture VERIFIED (smoke-test error landed in feed).</t>
+        </is>
+      </c>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>Verified. WATCH: confirm Sentry project SLUG is exactly '704-collective' in a Vercel build log (source-map upload) — if wrong, traces stay minified (one-word fix).</t>
+        </is>
+      </c>
+      <c r="D164" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E164" s="23" t="inlineStr">
+        <is>
+          <t>Commits 417fb37/d779885/5d12aac/b437166. The safety net — Stage 1 complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t>[DONE] Josh Ahart full removal (exit workstream)</t>
+        </is>
+      </c>
+      <c r="B165" s="36" t="inlineStr">
+        <is>
+          <t>De-privileged (super_admin-&gt;lead), permanent ban, all 8 sessions + 64 tokens killed, profile deactivated, ambassador row disabled, removed from public /about page (0cc8c66), 2 dormant test dupe accounts hard-deleted. Stripe sub cancelled + Connect account rejected (Adam, dashboard). Platform passwords rotated (Adam).</t>
+        </is>
+      </c>
+      <c r="C165" s="36" t="inlineStr">
+        <is>
+          <t>Verified: role=lead, 0 sessions/tokens, banned. Public site scrubbed. Dashboard-member removal confirmed by Adam.</t>
+        </is>
+      </c>
+      <c r="D165" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E165" s="36" t="inlineStr">
+        <is>
+          <t>NOT on the build sheet — exit workstream. Recorded here for completeness. Aug 25: Josh hub purge DONE - his 4 remaining hub_members rows (one per hub, all joined 2026-05-21 03:11:32, all added by Adam) were deleted; verified afterwards at 0 hub memberships, 0 posts, 0 comments, 0 likes, 0 resources. CORRECTION to an earlier wording of this note: Josh created NO hubs. All four hubs are created_by Adam, so nothing was owned by him and the purge was membership rows only - the cascade risk on hubs.created_by is a separate finding about Adam's profile (see that row). Also noted while verifying: the hub display queries in dashboard/hubs/[id] and admin/hubs join profiles without a deleted_at filter, which is why his soft-deleted profile kept rendering and inflated each hub's member count by one. Closes the hub residue of the exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>[DONE] Member status batch (Jul 9)</t>
+        </is>
+      </c>
+      <c r="B166" s="36" t="inlineStr">
+        <is>
+          <t>Nicholas Stathopoulos + Robert Villante -&gt; non_member/inactive/override off/lead (Nick admin revoked + sessions killed). Whitney Cleland + Brenna Dunne + Kaelah Torres -&gt; ERASED (auth+profile+people+credentials deleted; all comped, no Stripe to cancel). More status changes flagged as coming.</t>
+        </is>
+      </c>
+      <c r="C166" s="36" t="inlineStr">
+        <is>
+          <t>All verified via SQL (zeros on erase). Read-first footprint audit confirmed safe (no owned content cascaded).</t>
+        </is>
+      </c>
+      <c r="D166" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E166" s="36" t="inlineStr">
+        <is>
+          <t>Adam noted more member changes coming next session. Aug 25: Audrey Handleton converted to non-member - DONE, and recorded here as the next entry in this running member-status record. Verified end state: profiles reads non_member / inactive / membership_override false; the people row reads roles ['prospect'] with member_tier and member_status both null (never-was, not canceled). She was a comp who had drifted - profile said social while her people row still said business - and she never paid a cent, so there was no Stripe side to cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>[DONE] Business-event RSVP tier leak — closed + Annslee voided</t>
+        </is>
+      </c>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>Social members could RSVP business-only events: create-member-rsvp never checked required_tier, and the mobile sticky RSVP bar bypassed the desktop gate. Fixed: server-side tier gate in the edge function (ff20ba9, admins exempt) + mobile CTA respects canRsvp (952fbb2). Annslee Bottoms' live breach credential on Jul-14 Business Member Meeting VOIDED. Past legacy breaches intentionally left (real attendance history).</t>
+        </is>
+      </c>
+      <c r="C167" s="23" t="inlineStr">
+        <is>
+          <t>Verified: socialtest gets 403 'business members only' + red toast; direct-invoke blocked; Annslee active count on event = 0.</t>
+        </is>
+      </c>
+      <c r="D167" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E167" s="23" t="inlineStr">
+        <is>
+          <t>Commits ff20ba9, 952fbb2. Guest-side email opt-out gap noted -&gt; folds into unsubscribe policy work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
+        <is>
+          <t>[DONE] Discussion edit/delete (comments+posts+photos) + admin always-on access</t>
+        </is>
+      </c>
+      <c r="B168" s="36" t="inlineStr">
+        <is>
+          <t>Owners + admins can now edit/delete their own discussion comments (ecec3f8), posts (1e3adc1), and remove their own gallery photos (bcf746f); admins moderate anyone's. '(edited)' marker, soft-delete, silent removal. Also: admins now see the discussion link on any open event regardless of RSVP (583b343 — backend was already admin-exempt; was a missing-link discovery bug). Feed/comment/DM URL linkify (561403e).</t>
+        </is>
+      </c>
+      <c r="C168" s="36" t="inlineStr">
+        <is>
+          <t>All browser-tested desktop+mobile. Backend RLS already permitted; these were frontend gaps.</t>
+        </is>
+      </c>
+      <c r="D168" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E168" s="36" t="inlineStr">
+        <is>
+          <t>5 commits. Discussion feature now fully moderatable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
+        <is>
           <t>[DONE] Small fixes: hubs 404, week_label, dead components, partners 400, org_settings, last_attended</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B169" s="36" t="inlineStr">
         <is>
           <t>hubs preview widget queried non-existent 'business_hubs' -&gt; fixed to 'hubs' (a00cc50, restored a silently-broken business-tier feature). ambassador-payout phantom week_label column removed (1f46e88). 3 dead admin components deleted, 1376 lines (306efa4). partners 400 fixed via column aliasing (d95a337, latent partner-disappearing bug). organization_settings tracker row was STALE (schema fine, closed). last_attended already built+firing -&gt; backfilled 17 pre-trigger rows, closed.</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C169" s="36" t="inlineStr">
         <is>
           <t>All tsc+browser verified. org_settings &amp; last_attended were already-done rows.</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D169" s="36" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E169" s="36" t="inlineStr">
         <is>
           <t>Commits a00cc50, 1f46e88, 306efa4, d95a337 + 2 SQL closes.</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="25" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="42" t="inlineStr">
         <is>
           <t>PHASE 2  ·  MAJOR BUILDS (each gets its own detailed scope before build)</t>
         </is>
       </c>
-      <c r="B164" s="33" t="n"/>
-      <c r="C164" s="33" t="n"/>
-      <c r="D164" s="33" t="n"/>
-      <c r="E164" s="33" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR BUILDS — EACH GETS ITS OWN DETAILED SCOPE BEFORE BUILD   ·   7 items</t>
-        </is>
-      </c>
-      <c r="B165" s="31" t="n"/>
-      <c r="C165" s="31" t="n"/>
-      <c r="D165" s="31" t="n"/>
-      <c r="E165" s="31" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t>CRM system</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>Full customer-relationship system built ON the merged person record: 360-degree member view, segments/audiences, lifecycle tracking. The internal data model IS the CRM (not a re-introduced external tool).</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D166" s="26" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t>Built on the canonical person record from Phase 1. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag (carve-out keeps /admin/crm/campaigns live for the newsletter).</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t>Preferred Business Network</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>New paid product: vetted local-business listings, $300/mo to be listed. Lives in the portal first, public domains later. Includes the internal 'Seats' system. Social members browse this to find services.</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D167" s="26" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t>Plugs into The Network surface built in Phase 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t>Partner Portal (audit, then repurpose or remove)</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>An existing, mostly-built partner portal of unclear purpose. Audit it, then either repurpose it as the Preferred Business Network management surface or remove it. Frozen until then.</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Audit first; likely becomes the Preferred Business Network management surface. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>Task center for admins (lite project tool)</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>A super-light ClickUp-style task center for admins/super-admins: create, assign, track tasks.</t>
-        </is>
-      </c>
-      <c r="C169" s="8" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D169" s="26" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t>Lite task assignment + tracking for admin / super-admin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>Shared email inbox view for super-admins</t>
-        </is>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>A shared inbox view so super-admins can see the team email (hello@) in one place.</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D170" s="26" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E170" s="8" t="inlineStr">
-        <is>
-          <t>Super-admin visibility into hello@.</t>
-        </is>
-      </c>
+      <c r="B170" s="33" t="n"/>
+      <c r="C170" s="33" t="n"/>
+      <c r="D170" s="33" t="n"/>
+      <c r="E170" s="33" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>Corporate / bulk-sales floating-seats portal</t>
-        </is>
-      </c>
-      <c r="B171" s="29" t="inlineStr">
-        <is>
-          <t>A portal for selling memberships in bulk to companies, with reassignable 'floating' seats.</t>
-        </is>
-      </c>
-      <c r="C171" s="29" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D171" s="29" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E171" s="30" t="inlineStr">
-        <is>
-          <t>Reassignable floating seats for companies.</t>
-        </is>
-      </c>
+      <c r="A171" s="35" t="inlineStr">
+        <is>
+          <t>MAJOR BUILDS — EACH GETS ITS OWN DETAILED SCOPE BEFORE BUILD   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B171" s="31" t="n"/>
+      <c r="C171" s="31" t="n"/>
+      <c r="D171" s="31" t="n"/>
+      <c r="E171" s="31" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>Full mobile app</t>
+          <t>CRM system</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>A full native mobile application. The largest Phase 2 build.</t>
+          <t>Full customer-relationship system built ON the merged person record: 360-degree member view, segments/audiences, lifecycle tracking. The internal data model IS the CRM (not a re-introduced external tool).</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
@@ -4597,143 +4632,143 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>The final, largest Phase 2 effort.</t>
+          <t>Built on the canonical person record from Phase 1. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag (carve-out keeps /admin/crm/campaigns live for the newsletter).</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>OPEN WATCH ITEMS — ADDED 2026-07-19   ·   7 items</t>
-        </is>
-      </c>
-      <c r="B173" s="31" t="n"/>
-      <c r="C173" s="31" t="n"/>
-      <c r="D173" s="31" t="n"/>
-      <c r="E173" s="31" t="n"/>
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>Preferred Business Network</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>New paid product: vetted local-business listings, $300/mo to be listed. Lives in the portal first, public domains later. Includes the internal 'Seats' system. Social members browse this to find services.</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>Own detailed scope before build.</t>
+        </is>
+      </c>
+      <c r="D173" s="26" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>Plugs into The Network surface built in Phase 1.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>Refill the Vercel NEXT_PUBLIC_TURNSTILE_SITE_KEY value (hardcode fallback active)</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>The prod env var was set to an empty string, which made the Turnstile widget render nothing and locked members out during an incident. A hardcoded public site-key fallback in TurnstileWidget.tsx currently masks the missing value. Fallback fails CLOSED (blocks rather than bypasses); the code docstring claims the opposite and is wrong.</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
-        <is>
-          <t>Set the real public site key for NEXT_PUBLIC_TURNSTILE_SITE_KEY in Vercel (production), redeploy, confirm the widget renders from the env var, then optionally remove the hardcoded fallback.</t>
-        </is>
-      </c>
-      <c r="D174" s="9" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>Public site key (safe): 0x4AAAAAAD3gqCivsYyImeUH. Fallback keeps login working today; refill so config isn't hidden in code.</t>
+          <t>Partner Portal (audit, then repurpose or remove)</t>
+        </is>
+      </c>
+      <c r="B174" s="36" t="inlineStr">
+        <is>
+          <t>An existing, mostly-built partner portal of unclear purpose. Audit it, then either repurpose it as the Preferred Business Network management surface or remove it. Frozen until then.</t>
+        </is>
+      </c>
+      <c r="C174" s="36" t="inlineStr">
+        <is>
+          <t>Own detailed scope before build.</t>
+        </is>
+      </c>
+      <c r="D174" s="36" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="E174" s="36" t="inlineStr">
+        <is>
+          <t>Audit first; likely becomes the Preferred Business Network management surface. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>Resolve the capacity-trigger split-brain (tickets vs attendance_credentials counting)</t>
+          <t>Shared email inbox view for super-admins</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>Event capacity is enforced by triggers on two tables (attendance_credentials and legacy tickets) that count independently, so the seated count can disagree depending on the write path.</t>
+          <t>A shared inbox view so super-admins can see the team email (hello@) in one place.</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Pick one source of truth (attendance_credentials); make both trigger families count consistently, or retire the legacy tickets capacity path once tickets is fully retired. Coordinates with 'Finish retiring the old ticket tables'.</t>
-        </is>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Own detailed scope before build.</t>
+        </is>
+      </c>
+      <c r="D175" s="26" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>The admin_override bypass now spans both trigger families; the underlying counting split remains until tickets is retired. Closes with identity Wave 9 (tickets); resumes Aug 28. Wave 9 recon Aug 25: create-guest-pass writes legacy tickets PRIMARY; dashboard guest-pass list + get_community_stats (frozen 416 since Jul 19 vs live 969) read legacy; capacity trigger pair mapped; retirement order + mandatory backfill (8 of 26 mirrored).</t>
+          <t>Super-admin visibility into hello@.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>Q6 canceled-but-paying tripwire (canceled-drift detection)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Members whose app status shows canceled while Stripe still bills them (or the inverse) - a billing/status drift that should trip an alert instead of going silent.</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Add a scheduled check comparing profiles.subscription_status vs the live Stripe subscription state; alert on canceled-in-app-but-active-in-Stripe and the inverse.</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>The develop seed carries a canceled-drift (Q6) dummy for rehearsal. Folds into the DB/Stripe drift watch + admin health dashboard.</t>
+          <t>Corporate / bulk-sales floating-seats portal</t>
+        </is>
+      </c>
+      <c r="B176" s="37" t="inlineStr">
+        <is>
+          <t>A portal for selling memberships in bulk to companies, with reassignable 'floating' seats.</t>
+        </is>
+      </c>
+      <c r="C176" s="37" t="inlineStr">
+        <is>
+          <t>Own detailed scope before build.</t>
+        </is>
+      </c>
+      <c r="D176" s="37" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="E176" s="38" t="inlineStr">
+        <is>
+          <t>Reassignable floating seats for companies.</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="7" t="inlineStr">
-        <is>
-          <t>Delete the stray Stripe Connect account</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="inlineStr">
-        <is>
-          <t>A leftover Stripe Connect (Express) account from the ambassador / exit workstream needs removing so it doesn't linger.</t>
-        </is>
-      </c>
-      <c r="C177" s="8" t="inlineStr">
-        <is>
-          <t>Confirm the account has no pending balance or payouts, then delete/reject it in the Stripe dashboard. Owner task.</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E177" s="8" t="inlineStr">
-        <is>
-          <t>Cleanup item from the ambassador / Connect work; low blast radius.</t>
-        </is>
-      </c>
+      <c r="A177" s="35" t="inlineStr">
+        <is>
+          <t>OPEN WATCH ITEMS — ADDED 2026-07-19   ·   6 items</t>
+        </is>
+      </c>
+      <c r="B177" s="31" t="n"/>
+      <c r="C177" s="31" t="n"/>
+      <c r="D177" s="31" t="n"/>
+      <c r="E177" s="31" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>ManyChat - disconnect the Instagram-side integration</t>
+          <t>Refill the Vercel NEXT_PUBLIC_TURNSTILE_SITE_KEY value (hardcode fallback active)</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>The IG-side ManyChat connection needs to be disconnected / cleaned up. This is teardown of the current Instagram link, separate from the auto-DM build.</t>
+          <t>The prod env var was set to an empty string, which made the Turnstile widget render nothing and locked members out during an incident. A hardcoded public site-key fallback in TurnstileWidget.tsx currently masks the missing value. Fallback fails CLOSED (blocks rather than bypasses); the code docstring claims the opposite and is wrong.</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Disconnect the Instagram account from ManyChat (owner task in ManyChat / Meta); confirm no active automations still reference it.</t>
+          <t>Set the real public site key for NEXT_PUBLIC_TURNSTILE_SITE_KEY in Vercel (production), redeploy, confirm the widget renders from the env var, then optionally remove the hardcoded fallback.</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
@@ -4743,413 +4778,413 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Distinct from the 'Instagram comment auto-DM (ManyChat)' build row above - that row stays as-is.</t>
+          <t>Public site key (safe): 0x4AAAAAAD3gqCivsYyImeUH. Fallback keeps login working today; refill so config isn't hidden in code.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>DB / Stripe drift watch items</t>
-        </is>
-      </c>
-      <c r="B179" s="29" t="inlineStr">
-        <is>
-          <t>Ongoing watch on the places where the database and Stripe can drift out of sync: subscription statuses, customer email on email-change, retired legacy prices, orphaned Stripe customers.</t>
-        </is>
-      </c>
-      <c r="C179" s="29" t="inlineStr">
-        <is>
-          <t>Track and periodically reconcile; surface on the admin health dashboard. Pairs with the Q6 tripwire and the 'email change keeps Stripe billing in sync' verify.</t>
-        </is>
-      </c>
-      <c r="D179" s="29" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="E179" s="30" t="inlineStr">
-        <is>
-          <t>Umbrella watch item; individual drifts get their own rows as they surface.</t>
+          <t>Resolve the capacity-trigger split-brain (tickets vs attendance_credentials counting)</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>Event capacity is enforced by triggers on two tables (attendance_credentials and legacy tickets) that count independently, so the seated count can disagree depending on the write path.</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>Pick one source of truth (attendance_credentials); make both trigger families count consistently, or retire the legacy tickets capacity path once tickets is fully retired. Coordinates with 'Finish retiring the old ticket tables'.</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>Closes with identity Wave 9 (tickets), which now rides before the mobile app. The admin_override bypass spans both trigger families; the counting split remains until tickets is retired.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
+          <t>Delete the stray Stripe Connect account</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>A leftover Stripe Connect (Express) account from the ambassador / exit workstream needs removing so it doesn't linger.</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>Confirm the account has no pending balance or payouts, then delete/reject it in the Stripe dashboard. Owner task.</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>Cleanup item from the ambassador / Connect work; low blast radius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>ManyChat - disconnect the Instagram-side integration</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>The IG-side ManyChat connection needs to be disconnected / cleaned up. This is teardown of the current Instagram link, separate from the auto-DM build.</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>Disconnect the Instagram account from ManyChat (owner task in ManyChat / Meta); confirm no active automations still reference it.</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>Distinct from the 'Instagram comment auto-DM (ManyChat)' build row above - that row stays as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>DB / Stripe drift watch items</t>
+        </is>
+      </c>
+      <c r="B182" s="37" t="inlineStr">
+        <is>
+          <t>Ongoing watch on the places where the database and Stripe can drift out of sync: subscription statuses, customer email on email-change, retired legacy prices, orphaned Stripe customers.</t>
+        </is>
+      </c>
+      <c r="C182" s="37" t="inlineStr">
+        <is>
+          <t>Track and periodically reconcile; surface on the admin health dashboard. Pairs with the Q6 tripwire and the 'email change keeps Stripe billing in sync' verify.</t>
+        </is>
+      </c>
+      <c r="D182" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E182" s="38" t="inlineStr">
+        <is>
+          <t>Status drift is now DETECTED nightly by stripe-drift-check (Wave 10, live Sep 18: drift_checks receipts, super-admin bell + email on ghost-member / still-billed shapes; first manual run on prod was clean, 0 alerts). Remaining watch items here: customer email on email-change (Wave 7), retired legacy prices, orphaned Stripe customers. Payment-ledger drift is the Financial Truth phase 3 row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
           <t>Waitlist claim links - monitor first real-world use</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>Cancel frees a seat -&gt; the first waitlister is emailed a 24h claim link -&gt; they claim it. Rehearsed as a full matrix on develop and shipped to prod; needs a read-only confirm on its first genuine use.</t>
         </is>
       </c>
-      <c r="C180" s="8" t="inlineStr">
+      <c r="C183" s="8" t="inlineStr">
         <is>
           <t>On the next real cancellation that frees a seat on a full, waitlisted event, confirm: notified_at/expires_at stamped, the email sent, the claimant claimed (member_rsvp with metadata source=waitlist_claim), and the waitlist row deleted.</t>
         </is>
       </c>
-      <c r="D180" s="9" t="inlineStr">
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
+      <c r="E183" s="8" t="inlineStr">
         <is>
           <t>Shipped 2026-07-19. Zero-cost proof on first real use, like the Remove &amp; Refund WAIT-mode row.</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="27" t="inlineStr">
-        <is>
-          <t>BILLING-VIEWS ERA — ADDED 2026-08-03   ·   15 items</t>
-        </is>
-      </c>
-      <c r="B181" s="34" t="n"/>
-      <c r="C181" s="34" t="n"/>
-      <c r="D181" s="34" t="n"/>
-      <c r="E181" s="34" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="28" t="inlineStr">
-        <is>
-          <t>Billing views: admin billing panel + member price/renewal display</t>
-        </is>
-      </c>
-      <c r="B182" s="28" t="inlineStr">
-        <is>
-          <t>Admin contact billing panel + member-facing price/renewal display. Three new profile columns (comp_reason, external_paid_through, external_payment_note) are live on both DBs; the UI/code build is in flight.</t>
-        </is>
-      </c>
-      <c r="C182" s="28" t="inlineStr">
-        <is>
-          <t>Extend admin contact detail with live Stripe billing; surface price/renewal/discount on member settings; wire the three new profile columns into admin editors.</t>
-        </is>
-      </c>
-      <c r="D182" s="28" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="E182" s="28" t="inlineStr">
-        <is>
-          <t>Columns live both DBs; code build in flight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="28" t="inlineStr">
-        <is>
-          <t>Report builder: admin/super_admin any-filter member/payment reports</t>
-        </is>
-      </c>
-      <c r="B183" s="28" t="inlineStr">
-        <is>
-          <t>Admin/super_admin reporting with arbitrary filters over members and payments. Data-cleanup prerequisite is DONE; build after billing views.</t>
-        </is>
-      </c>
-      <c r="C183" s="28" t="inlineStr">
-        <is>
-          <t>Build after billing views lands. Admin/super_admin only; any-filter member + payment reports.</t>
-        </is>
-      </c>
-      <c r="D183" s="28" t="inlineStr">
-        <is>
-          <t>QUEUED-BACKLOGGED</t>
-        </is>
-      </c>
-      <c r="E183" s="28" t="inlineStr">
-        <is>
-          <t>v1 proposal complete and approved-in-principle (DB-only cut, 3 entities, column picker, CSV export, 4 presets, server-paginated, ~7 files); resume at build sign-off. Cheap adds discussed: ambassador-referred, price tier, cancel reasons.</t>
-        </is>
-      </c>
-    </row>
     <row r="184">
-      <c r="A184" s="28" t="inlineStr">
-        <is>
-          <t>Business comp invite flow: welcome template + admin invite tool</t>
-        </is>
-      </c>
-      <c r="B184" s="28" t="inlineStr">
-        <is>
-          <t>Welcome email template plus an admin tool to invite a business member (comp path).</t>
-        </is>
-      </c>
-      <c r="C184" s="28" t="inlineStr">
-        <is>
-          <t>Blocked on Adam: invitee list + design answers. Then template + admin invite UI.</t>
-        </is>
-      </c>
-      <c r="D184" s="28" t="inlineStr">
-        <is>
-          <t>WAITING ON ADAM: list + design answers</t>
-        </is>
-      </c>
-      <c r="E184" s="28" t="inlineStr">
-        <is>
-          <t>Needs invitee list + design answers from Adam.</t>
-        </is>
-      </c>
+      <c r="A184" s="43" t="inlineStr">
+        <is>
+          <t>BILLING-VIEWS ERA — ADDED 2026-08-03   ·   12 items</t>
+        </is>
+      </c>
+      <c r="B184" s="34" t="n"/>
+      <c r="C184" s="34" t="n"/>
+      <c r="D184" s="34" t="n"/>
+      <c r="E184" s="34" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="28" t="inlineStr">
         <is>
-          <t>Admin 'Invite comp member' button - form (name, company, email, phone, comp note), creates comp'd account + sends welcome email, note auto-attached to billing view (member + admin); v1 invite flow built without UI, button is the addon</t>
+          <t>Billing views: admin billing panel + member price/renewal display</t>
         </is>
       </c>
       <c r="B185" s="28" t="inlineStr">
         <is>
-          <t>Admin UI button/form to invite a complimentary business member: name, company, email, phone, and comp note. Creates the comp'd account, sends the welcome email, and attaches the note to the billing view for both member and admin.</t>
+          <t>Admin contact billing panel + member-facing price/renewal display. Three new profile columns (comp_reason, external_paid_through, external_payment_note) are live on both DBs; the UI/code build is in flight.</t>
         </is>
       </c>
       <c r="C185" s="28" t="inlineStr">
         <is>
-          <t>Addon after v1 invite flow (API/ops path without UI). Build the Invite comp member button + form once the headless invite path exists.</t>
+          <t>Extend admin contact detail with live Stripe billing; surface price/renewal/discount on member settings; wire the three new profile columns into admin editors.</t>
         </is>
       </c>
       <c r="D185" s="28" t="inlineStr">
         <is>
-          <t>QUEUED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="E185" s="28" t="inlineStr">
         <is>
-          <t>v1 invite flow built without UI; this button is the future addon.</t>
+          <t>Columns live both DBs; code build in flight.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="28" t="inlineStr">
         <is>
-          <t>Mike Perez: account cleanup + re-join link at $150 founding</t>
+          <t>Report builder: admin/super_admin any-filter member/payment reports</t>
         </is>
       </c>
       <c r="B186" s="28" t="inlineStr">
         <is>
-          <t>After Adam's conversation: clean up Mike's canceled/failed-billing account and send a founding-rate $150 re-join link.</t>
+          <t>Admin/super_admin reporting with arbitrary filters over members and payments. Data-cleanup prerequisite is DONE; build after billing views.</t>
         </is>
       </c>
       <c r="C186" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM conversation first. Then cleanup + founding $150 checkout/re-join link.</t>
+          <t>Build after billing views lands. Admin/super_admin only; any-filter member + payment reports.</t>
         </is>
       </c>
       <c r="D186" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: conversation first</t>
+          <t>QUEUED-BACKLOGGED</t>
         </is>
       </c>
       <c r="E186" s="28" t="inlineStr">
         <is>
-          <t>Founding $150; conversation first.</t>
+          <t>v1 proposal complete and approved-in-principle (DB-only cut, 3 entities, column picker, CSV export, 4 presets, server-paginated, ~7 files); resume at build sign-off. Cheap adds discussed: ambassador-referred, price tier, cancel reasons.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="28" t="inlineStr">
         <is>
-          <t>Zane Mackey comp_reason entry</t>
+          <t>Business comp invite flow: welcome template + admin invite tool</t>
         </is>
       </c>
       <c r="B187" s="28" t="inlineStr">
         <is>
-          <t>Record a one-phrase comp_reason on Zane Mackey's profile now that the column exists.</t>
+          <t>Welcome email template plus an admin tool to invite a business member (comp path).</t>
         </is>
       </c>
       <c r="C187" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: one phrase for comp_reason.</t>
+          <t>Blocked on Adam: invitee list + design answers. Then template + admin invite UI.</t>
         </is>
       </c>
       <c r="D187" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: one phrase</t>
+          <t>WAITING ON ADAM: list + design answers</t>
         </is>
       </c>
       <c r="E187" s="28" t="inlineStr">
         <is>
-          <t>One phrase for comp_reason.</t>
+          <t>Needs invitee list + design answers from Adam.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="28" t="inlineStr">
         <is>
-          <t>Zach Trusky renewal ~Nov/Dec 2026 — honored $1,034 annual</t>
+          <t>Admin 'Invite comp member' button - form (name, company, email, phone, comp note), creates comp'd account + sends welcome email, note auto-attached to billing view (member + admin); v1 invite flow built without UI, button is the addon</t>
         </is>
       </c>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Zach's annual amount lives outside Stripe ($1,034 honored). Need reminder + collection path decision around Nov/Dec 2026.</t>
+          <t>Admin UI button/form to invite a complimentary business member: name, company, email, phone, and comp note. Creates the comp'd account, sends the welcome email, and attaches the note to the billing view for both member and admin.</t>
         </is>
       </c>
       <c r="C188" s="28" t="inlineStr">
         <is>
-          <t>Schedule reminder; decide collection path (manual invoice vs Stripe annual vs override).</t>
+          <t>Addon after v1 invite flow (API/ops path without UI). Build the Invite comp member button + form once the headless invite path exists.</t>
         </is>
       </c>
       <c r="D188" s="28" t="inlineStr">
         <is>
-          <t>SCHEDULED NOV 2026</t>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="E188" s="28" t="inlineStr">
         <is>
-          <t>Honored $1,034 annual; no Stripe customer today.</t>
+          <t>v1 invite flow built without UI; this button is the future addon.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="28" t="inlineStr">
         <is>
-          <t>Security: unknown third-party script (batatatech.com) on Glue Up admin pages</t>
+          <t>Zane Mackey comp_reason entry</t>
         </is>
       </c>
       <c r="B189" s="28" t="inlineStr">
         <is>
-          <t>Unknown batatatech.com script firing on Glue Up admin pages — treat as extension/malware until proven otherwise; audit browsers + rotate passwords.</t>
+          <t>Record a one-phrase comp_reason on Zane Mackey's profile now that the column exists.</t>
         </is>
       </c>
       <c r="C189" s="28" t="inlineStr">
         <is>
-          <t>Browser extension audit on machines that use Glue Up admin; password rotation for affected accounts.</t>
+          <t>WAITING ON ADAM: one phrase for comp_reason.</t>
         </is>
       </c>
       <c r="D189" s="28" t="inlineStr">
         <is>
-          <t>OPEN - Adam chrome://extensions only</t>
+          <t>WAITING ON ADAM: one phrase</t>
         </is>
       </c>
       <c r="E189" s="28" t="inlineStr">
         <is>
-          <t>repo confirmed clean 8/4 - scope is Adam's chrome://extensions only</t>
+          <t>One phrase for comp_reason.</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>[DONE] Promo system endstate 8/5</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Promo endstate 8/5: server-side attach only, native box removed everywhere (create-checkout v64, create-ticket-checkout v65), Josh coupon shadow eliminated (2 free subs + 5 customers deleted, 3 abuse codes deactivated), 3 live promos + ambassador system verified.</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Supersedes Stripe support ticket + ticket-checkout promo fast-follow (removed).</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Promo endstate 8/5: server-side attach only, native box removed everywhere (create-checkout v64, create-ticket-checkout v65), Josh coupon shadow eliminated (2 free subs + 5 customers deleted, 3 abuse codes deactivated), 3 live promos + ambassador system verified.</t>
+      <c r="A190" s="28" t="inlineStr">
+        <is>
+          <t>Zach Trusky renewal ~Nov/Dec 2026 — honored $1,034 annual</t>
+        </is>
+      </c>
+      <c r="B190" s="28" t="inlineStr">
+        <is>
+          <t>Zach's annual amount lives outside Stripe ($1,034 honored). Need reminder + collection path decision around Nov/Dec 2026.</t>
+        </is>
+      </c>
+      <c r="C190" s="28" t="inlineStr">
+        <is>
+          <t>Schedule reminder; decide collection path (manual invoice vs Stripe annual vs override).</t>
+        </is>
+      </c>
+      <c r="D190" s="28" t="inlineStr">
+        <is>
+          <t>SCHEDULED NOV 2026</t>
+        </is>
+      </c>
+      <c r="E190" s="28" t="inlineStr">
+        <is>
+          <t>Honored $1,034 annual; no Stripe customer today.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="28" t="inlineStr">
         <is>
-          <t>Calendar update-leg verification via throwaway event</t>
+          <t>Security: unknown third-party script (batatatech.com) on Glue Up admin pages</t>
         </is>
       </c>
       <c r="B191" s="28" t="inlineStr">
         <is>
-          <t>Verify that event-edit REQUEST invites actually move real calendars (ICS sequence / update leg) using a throwaway event.</t>
+          <t>Unknown batatatech.com script firing on Glue Up admin pages — treat as extension/malware until proven otherwise; audit browsers + rotate passwords.</t>
         </is>
       </c>
       <c r="C191" s="28" t="inlineStr">
         <is>
-          <t>Create throwaway event, subscribe, edit, confirm calendars update; then delete throwaway.</t>
+          <t>Browser extension audit on machines that use Glue Up admin; password rotation for affected accounts.</t>
         </is>
       </c>
       <c r="D191" s="28" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN - Adam chrome://extensions only</t>
         </is>
       </c>
       <c r="E191" s="28" t="inlineStr">
         <is>
-          <t>Throwaway event verification of REQUEST/update path.</t>
+          <t>repo confirmed clean 8/4 - scope is Adam's chrome://extensions only</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="28" t="inlineStr">
         <is>
-          <t>Resend click-tracking subdomain (DNS)</t>
+          <t>Calendar update-leg verification via throwaway event</t>
         </is>
       </c>
       <c r="B192" s="28" t="inlineStr">
         <is>
-          <t>Configure Resend click-tracking subdomain — Adam hands / DNS.</t>
+          <t>Verify that event-edit REQUEST invites actually move real calendars (ICS sequence / update leg) using a throwaway event.</t>
         </is>
       </c>
       <c r="C192" s="28" t="inlineStr">
         <is>
-          <t>ADAM DNS: add Resend click-tracking subdomain CNAME + add Resend to SPF include (current SPF is Google-only). Confirmed missing 8/4.</t>
+          <t>Create throwaway event, subscribe, edit, confirm calendars update; then delete throwaway.</t>
         </is>
       </c>
       <c r="D192" s="28" t="inlineStr">
         <is>
-          <t>ADAM - DNS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E192" s="28" t="inlineStr">
         <is>
-          <t>confirmed NOT configured 8/4; also add Resend to SPF include during same DNS visit</t>
+          <t>Throwaway event verification of REQUEST/update path.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="28" t="inlineStr">
         <is>
-          <t>/welcome checkout-flow coverage on develop</t>
+          <t>Resend click-tracking subdomain (DNS)</t>
         </is>
       </c>
       <c r="B193" s="28" t="inlineStr">
         <is>
-          <t>/welcome checkout flow is still untested on develop (no Stripe checkout env there).</t>
+          <t>Configure Resend click-tracking subdomain — Adam hands / DNS.</t>
         </is>
       </c>
       <c r="C193" s="28" t="inlineStr">
         <is>
-          <t>WATCH until develop has a Stripe checkout path; then cover /welcome end to end.</t>
+          <t>ADAM DNS: add Resend click-tracking subdomain CNAME + add Resend to SPF include (current SPF is Google-only). Confirmed missing 8/4.</t>
         </is>
       </c>
       <c r="D193" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>ADAM - DNS</t>
         </is>
       </c>
       <c r="E193" s="28" t="inlineStr">
         <is>
-          <t>Untested on develop; no Stripe checkout env.</t>
+          <t>confirmed NOT configured 8/4; also add Resend to SPF include during same DNS visit</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="28" t="inlineStr">
         <is>
-          <t>Stripe/DB drift trio: admin-delete-user + cleanup-business-members + member pause flow</t>
+          <t>/welcome checkout-flow coverage on develop</t>
         </is>
       </c>
       <c r="B194" s="28" t="inlineStr">
         <is>
-          <t>admin-delete-user leaves unlinked Stripe subs; cleanup-business-members does not cancel in Stripe. Third defect discovered 2026-08-20: the member-facing pause flow writes member/subscription status 'paused', a status word every login gate rejects (middleware, AuthContext, postAuthRedirect), so a member who pauses their own membership locks themselves out of the portal while still being a paying-but-paused customer.</t>
+          <t>/welcome checkout flow is still untested on develop (no Stripe checkout env there).</t>
         </is>
       </c>
       <c r="C194" s="28" t="inlineStr">
         <is>
-          <t>WATCH — revisit in identity-bridge work. Ensure deletes/cancels hit Stripe or leave an explicit orphan alert. The pause flow must write a status the three gates accept (active plus a pause marker), never 'paused'.</t>
+          <t>WATCH until develop has a Stripe checkout path; then cover /welcome end to end.</t>
         </is>
       </c>
       <c r="D194" s="28" t="inlineStr">
@@ -5159,7 +5194,7 @@
       </c>
       <c r="E194" s="28" t="inlineStr">
         <is>
-          <t>Now identity Wave 10 (drift trio); resumes Aug 28. The pause defect is the live one: Annslee's Aug-20 pause was deliberately set on the Stripe side (pause_collection void, resumes Nov 16 2026) precisely to avoid the app-side paused word.</t>
+          <t>Untested on develop; no Stripe checkout env.</t>
         </is>
       </c>
     </row>
@@ -5218,9 +5253,9 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="27" t="inlineStr">
-        <is>
-          <t>IDENTITY WAVES 0-6A + EXCHANGE ERA — ADDED 2026-08-24   ·   11 items</t>
+      <c r="A197" s="43" t="inlineStr">
+        <is>
+          <t>IDENTITY WAVES 0-6A + EXCHANGE ERA — ADDED 2026-08-24   ·   9 items</t>
         </is>
       </c>
       <c r="B197" s="34" t="n"/>
@@ -5366,190 +5401,190 @@
     <row r="203">
       <c r="A203" s="28" t="inlineStr">
         <is>
-          <t>Wave 3D: mention-search + attendee-list DB functions still resolve pre-resolver and lack the is_internal filter</t>
+          <t>comp-invite carries a local resolver replica (three copies of resolution logic)</t>
         </is>
       </c>
       <c r="B203" s="28" t="inlineStr">
         <is>
-          <t>Three SECURITY DEFINER functions - search_event_discussion_mentionables, get_event_discussion_mentionable_ids and get_event_attendees - do their own person lookups instead of going through the unified resolver, and none of them filter is_internal. Internal and test identities can therefore appear in @-mention autocomplete and in the who's-going list on a real event.</t>
+          <t>comp-invite implements its own person-resolution logic instead of importing _shared/resolvePerson, so identity resolution now lives in three places: the shared resolver (15 adopters), the three Wave 3D database functions, and this local replica. Each copy drifts independently the next time the resolution rules change.</t>
         </is>
       </c>
       <c r="C203" s="28" t="inlineStr">
         <is>
-          <t>Repoint the three functions onto the canonical person record and add the is_internal exclusion, mirroring the five member-facing filters shipped in Wave 5. This is SQL-side, so it needs a migration rather than a function deploy. Rehearse on develop with a known internal identity and confirm it disappears from both surfaces.</t>
+          <t>Repoint comp-invite onto _shared/resolvePerson and delete the replica. Do not modify the shared resolver to accommodate it; if the adoption is impossible without a resolver change, stop and report which prior adopters would need redeploy.</t>
         </is>
       </c>
       <c r="D203" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E203" s="28" t="inlineStr">
         <is>
-          <t>The last resolver holdouts: the 15 edge functions are adopted, these three DB functions are not. Scheduled as Wave 3D.</t>
+          <t>Drift watch. Not wrong today, but it is the one edge function guaranteed to disagree with the other 15 after the next rule change.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="28" t="inlineStr">
         <is>
-          <t>comp-invite carries a local resolver replica (three copies of resolution logic)</t>
+          <t>Duplicate people rows labeled, merge adjudication deferred (Josh x3, Lance x3)</t>
         </is>
       </c>
       <c r="B204" s="28" t="inlineStr">
         <is>
-          <t>comp-invite implements its own person-resolution logic instead of importing _shared/resolvePerson, so identity resolution now lives in three places: the shared resolver (15 adopters), the three Wave 3D database functions, and this local replica. Each copy drifts independently the next time the resolution rules change.</t>
+          <t>Two humans hold three people rows each. Josh: two canceled member rows plus a crystal.66 row. Lance: one active row plus two relics that hold zero attendance credentials and zero exchange_intake references. All six were labeled during the status pass; none were merged, because choosing the canonical row is a judgment call and Adam adjudicates fuzzies.</t>
         </is>
       </c>
       <c r="C204" s="28" t="inlineStr">
         <is>
-          <t>Repoint comp-invite onto _shared/resolvePerson and delete the replica. Do not modify the shared resolver to accommodate it; if the adoption is impossible without a resolver change, stop and report which prior adopters would need redeploy.</t>
+          <t>Adam picks the surviving row per human. Then merge additively: repoint references to the survivor and keep the losers as tombstones with metadata rather than deleting them. Re-confirm the two Lance relics still hold zero references immediately before any merge.</t>
         </is>
       </c>
       <c r="D204" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WAITING ON ADAM</t>
         </is>
       </c>
       <c r="E204" s="28" t="inlineStr">
         <is>
-          <t>Drift watch. Not wrong today, but it is the one edge function guaranteed to disagree with the other 15 after the next rule change.</t>
+          <t>Labeled during the Aug 19 status pass and deliberately left unmerged. Six rows, two humans. Folds naturally into the contacts fold (6B-6E). 2026-08-25: Josh's 4 hub_members rows were purged on the primary identity (a5f1b294) only; both duplicate rows held zero hub memberships, so that cleanup did not depend on this adjudication and does not constrain it.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="28" t="inlineStr">
         <is>
-          <t>Duplicate people rows labeled, merge adjudication deferred (Josh x3, Lance x3)</t>
+          <t>Andrea Baquero past_due watch (invited Exchange registrant)</t>
         </is>
       </c>
       <c r="B205" s="28" t="inlineStr">
         <is>
-          <t>Two humans hold three people rows each. Josh: two canceled member rows plus a crystal.66 row. Lance: one active row plus two relics that hold zero attendance credentials and zero exchange_intake references. All six were labeled during the status pass; none were merged, because choosing the canonical row is a judgment call and Adam adjudicates fuzzies.</t>
+          <t>Andrea Baquero is past_due on billing and is also an invited registrant for the Aug 27 Exchange. If the past_due state persists, member gating could turn her away at a door she was personally invited to.</t>
         </is>
       </c>
       <c r="C205" s="28" t="inlineStr">
         <is>
-          <t>Adam picks the surviving row per human. Then merge additively: repoint references to the survivor and keep the losers as tombstones with metadata rather than deleting them. Re-confirm the two Lance relics still hold zero references immediately before any merge.</t>
+          <t>Watch through Aug 27. Either resolve the billing state before the event or confirm her Exchange credential is not tier-gated. Read-only until Adam decides how to handle the billing side.</t>
         </is>
       </c>
       <c r="D205" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E205" s="28" t="inlineStr">
         <is>
-          <t>Labeled during the Aug 19 status pass and deliberately left unmerged. Six rows, two humans. Folds naturally into the contacts fold (6B-6E). 2026-08-25: Josh's 4 hub_members rows were purged on the primary identity (a5f1b294) only; both duplicate rows held zero hub memberships, so that cleanup did not depend on this adjudication and does not constrain it.</t>
+          <t>Time-boxed: this row closes after the Aug 27 Exchange, either resolved or converted into an ordinary billing follow-up. Aug 25: the 3+1 member_tier repairs done tonight included the tier-null row the payment-failure webhook re-created on this account Aug 24 — see the member_tier invariant row. The past_due watch itself still stands through Aug 27. Aug 26: RESOLVED to watch-only — billing email sent Aug 26; card in Stripe auto-retry; attends Aug 27 event; Adam reports ~2 attended events never captured at check-in.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="28" t="inlineStr">
         <is>
-          <t>Andrea Baquero past_due watch (invited Exchange registrant)</t>
+          <t>Exchange v2 blueprint (mixer + intake, post-Aug-27)</t>
         </is>
       </c>
       <c r="B206" s="28" t="inlineStr">
         <is>
-          <t>Andrea Baquero is past_due on billing and is also an invited registrant for the Aug 27 Exchange. If the past_due state persists, member gating could turn her away at a door she was personally invited to.</t>
+          <t>Everything the dress rehearsal surfaced that did not justify building before the event: a reset control with a confirm guard; a standalone discard for a pending round (today only reshuffle exists, which replaces rather than discards); drag-a-person-between-tables; revisiting the 30-second minimum clamp on round duration (saveConfig floors it, so short demo rounds are impossible from the UI); a create-flow for setting up a mixer night from scratch; a partner-pool toggle; and answer-aware matching that seats people by their four intake answers rather than purely by repeat-pair avoidance.</t>
         </is>
       </c>
       <c r="C206" s="28" t="inlineStr">
         <is>
-          <t>Watch through Aug 27. Either resolve the billing state before the event or confirm her Exchange credential is not tier-gated. Read-only until Adam decides how to handle the billing side.</t>
+          <t>Own detailed scope after Aug 27, informed by what actually happens on the night. Nothing here blocks v1. Sequence by what the night proves is missing, not by the order of this list.</t>
         </is>
       </c>
       <c r="D206" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E206" s="28" t="inlineStr">
         <is>
-          <t>Time-boxed: this row closes after the Aug 27 Exchange, either resolved or converted into an ordinary billing follow-up. Aug 25: the 3+1 member_tier repairs done tonight included the tier-null row the payment-failure webhook re-created on this account Aug 24 — see the member_tier invariant row. The past_due watch itself still stands through Aug 27. Aug 26: RESOLVED to watch-only — billing email sent Aug 26; card in Stripe auto-retry; attends Aug 27 event; Adam reports ~2 attended events never captured at check-in.</t>
+          <t>Compiled from the Aug 24 full-dress rehearsal. v1 shipped Aug 24 (viewer, mixer engine, board, UTM capture); the two findings worth fixing immediately - unseated visibility and the board email fallback - already shipped.</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="28" t="inlineStr">
-        <is>
-          <t>Exchange v2 blueprint (mixer + intake, post-Aug-27)</t>
-        </is>
-      </c>
-      <c r="B207" s="28" t="inlineStr">
-        <is>
-          <t>Everything the dress rehearsal surfaced that did not justify building before the event: a reset control with a confirm guard; a standalone discard for a pending round (today only reshuffle exists, which replaces rather than discards); drag-a-person-between-tables; revisiting the 30-second minimum clamp on round duration (saveConfig floors it, so short demo rounds are impossible from the UI); a create-flow for setting up a mixer night from scratch; a partner-pool toggle; and answer-aware matching that seats people by their four intake answers rather than purely by repeat-pair avoidance.</t>
-        </is>
-      </c>
-      <c r="C207" s="28" t="inlineStr">
-        <is>
-          <t>Own detailed scope after Aug 27, informed by what actually happens on the night. Nothing here blocks v1. Sequence by what the night proves is missing, not by the order of this list.</t>
-        </is>
-      </c>
-      <c r="D207" s="28" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E207" s="28" t="inlineStr">
-        <is>
-          <t>Compiled from the Aug 24 full-dress rehearsal. v1 shipped Aug 24 (viewer, mixer engine, board, UTM capture); the two findings worth fixing immediately - unseated visibility and the board email fallback - already shipped.</t>
-        </is>
-      </c>
+      <c r="A207" s="43" t="inlineStr">
+        <is>
+          <t>[P0] FINANCIAL TRUTH PROJECT + AUG 25 FINDINGS — ADDED 2026-08-25   ·   8 items</t>
+        </is>
+      </c>
+      <c r="B207" s="34" t="n"/>
+      <c r="C207" s="34" t="n"/>
+      <c r="D207" s="34" t="n"/>
+      <c r="E207" s="34" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="28" t="inlineStr">
         <is>
-          <t>UTM capture is a floor, not a ceiling (session-scoped attribution)</t>
+          <t>[P0] Financial truth phase 1 — backfill the payment ledger from Stripe (all-time)</t>
         </is>
       </c>
       <c r="B208" s="28" t="inlineStr">
         <is>
-          <t>The UTM capture shipped with Exchange v1 records utm_source / utm_medium / utm_campaign at intake, scoped to the session that submitted the form. It answers "which ad did this registration come from" and nothing more: it does not survive a cross-device journey, does not attribute a later membership purchase back to the ad, and does not join to the per-event RSVP tagging that has been dead since Apr 21.</t>
+          <t>The database has never held a complete record of money received. 62 payment rows are confirmed missing, and the gap is not a single window: it spans the pre-app era (money collected before this application existed and therefore never written anywhere), the 5 subscribers who were never migrated into the app, and ordinary in-app payments the webhook dropped. Trinity French is the worked case study — $225 paid to Stripe, $0 of it in the ledger — and she is one of 62, not an exception. Every downstream number (MRR, churn, revenue by tier, the financial dashboard, any report built on payments) is computed from this incomplete table, so all of them are wrong by an unknown amount until the ledger is whole.</t>
         </is>
       </c>
       <c r="C208" s="28" t="inlineStr">
         <is>
-          <t>Treat the current capture as the floor. If real attribution is wanted, the next step is a durable first-touch / last-touch record on the person rather than on the submission, joined with the contact_tags event_id work. Decide whether attribution is worth that before building it.</t>
+          <t>Backfill from Stripe as the source of truth, all-time, before touching anything downstream. Pull every charge / invoice / payment_intent from account creation forward, match to the person record through the unified resolver, and write the missing rows idempotently keyed on the Stripe object id so a re-run cannot double-post. Cover the three populations explicitly: pre-app-era payments, the 5 unmigrated subscribers, and the 62 confirmed misses. Reconcile the $809 of open invoices in the same pass — $645 is stranded on canceled subscriptions and should be voided, $170 is pre-app era, and only $114 is genuinely collectible. Rehearse the whole backfill on develop and diff the resulting totals against Stripe before running it against prod.</t>
         </is>
       </c>
       <c r="D208" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E208" s="28" t="inlineStr">
         <is>
-          <t>Written down so nobody later reads a UTM column and believes it is full-funnel attribution. Related: the RSVP-attribution-by-event-ID row.</t>
+          <t>Phase 1 of 4. Blocks phases 2-4 and every financial number in the product. Evidence: 62 confirmed missing payment rows; Trinity French $225 paid / $0 recorded; $809 open invoices ($645 to void on canceled subs, $170 pre-app era, $114 real). Backfill must be idempotent — it will be run more than once.</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="27" t="inlineStr">
-        <is>
-          <t>[P0] FINANCIAL TRUTH PROJECT + AUG 25 FINDINGS — ADDED 2026-08-25   ·   8 items</t>
-        </is>
-      </c>
-      <c r="B209" s="34" t="n"/>
-      <c r="C209" s="34" t="n"/>
-      <c r="D209" s="34" t="n"/>
-      <c r="E209" s="34" t="n"/>
+      <c r="A209" s="28" t="inlineStr">
+        <is>
+          <t>[P0] Financial truth phase 2 — fix the webhook silent-skip defect + add stripe_payment_intent_id</t>
+        </is>
+      </c>
+      <c r="B209" s="28" t="inlineStr">
+        <is>
+          <t>The Stripe webhook silently skips payments rather than failing loudly, which is why the ledger drifted without anyone noticing: a dropped payment produces no error, no alert and no row, so the only evidence is an absence nobody is looking for. The payments table also has no stripe_payment_intent_id column, so there is no durable key tying a stored row back to the Stripe object it came from — which makes both deduplication and reconciliation guesswork.</t>
+        </is>
+      </c>
+      <c r="C209" s="28" t="inlineStr">
+        <is>
+          <t>Two changes, both prerequisites for the reconciliation in phase 3. (1) Replace every silent skip in the webhook handler with a loud failure: log the Stripe event id, the reason, and alert — never return 200 on an unwritten payment. (2) Add stripe_payment_intent_id to the payments table with a unique index, populate it in the phase 1 backfill, and write it on every new payment. Prove the fix with a Stripe-CLI replay of the exact event shapes that were being skipped, on develop first.</t>
+        </is>
+      </c>
+      <c r="D209" s="28" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E209" s="28" t="inlineStr">
+        <is>
+          <t>Phase 2 of 4. This is the defect that created the hole — fixing it stops the ledger re-diverging the moment phase 1 finishes. The new column is what phase 3 joins on. Aug 26: Requirement: journal invoice.voided (Stripe currently sole truth on voids, Rich case Aug 26).</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 1 — backfill the payment ledger from Stripe (all-time)</t>
+          <t>[P0] Financial truth phase 3 — nightly two-way reconciliation with loud mismatch alerts</t>
         </is>
       </c>
       <c r="B210" s="28" t="inlineStr">
         <is>
-          <t>The database has never held a complete record of money received. 62 payment rows are confirmed missing, and the gap is not a single window: it spans the pre-app era (money collected before this application existed and therefore never written anywhere), the 5 subscribers who were never migrated into the app, and ordinary in-app payments the webhook dropped. Trinity French is the worked case study — $225 paid to Stripe, $0 of it in the ledger — and she is one of 62, not an exception. Every downstream number (MRR, churn, revenue by tier, the financial dashboard, any report built on payments) is computed from this incomplete table, so all of them are wrong by an unknown amount until the ledger is whole.</t>
+          <t>Once the ledger is whole (phase 1) and the webhook stops dropping rows (phase 2), the remaining risk is silent drift: any future gap between Stripe and the database is invisible until someone audits by hand, which is exactly how 62 rows accumulated. Nothing today compares the two systems on a schedule.</t>
         </is>
       </c>
       <c r="C210" s="28" t="inlineStr">
         <is>
-          <t>Backfill from Stripe as the source of truth, all-time, before touching anything downstream. Pull every charge / invoice / payment_intent from account creation forward, match to the person record through the unified resolver, and write the missing rows idempotently keyed on the Stripe object id so a re-run cannot double-post. Cover the three populations explicitly: pre-app-era payments, the 5 unmigrated subscribers, and the 62 confirmed misses. Reconcile the $809 of open invoices in the same pass — $645 is stranded on canceled subscriptions and should be voided, $170 is pre-app era, and only $114 is genuinely collectible. Rehearse the whole backfill on develop and diff the resulting totals against Stripe before running it against prod.</t>
+          <t>Scheduled nightly job that reconciles in BOTH directions — every Stripe payment must exist in the ledger, and every ledger row must exist in Stripe — joined on stripe_payment_intent_id. Any mismatch alerts loudly (not a log line nobody reads) with the offending ids attached, and surfaces on the admin health dashboard alongside the cron / webhook widgets. Pairs with the Q6 canceled-drift tripwire and the DB/Stripe drift watch rows; consider folding them into one money-drift check rather than three.</t>
         </is>
       </c>
       <c r="D210" s="28" t="inlineStr">
@@ -5559,24 +5594,24 @@
       </c>
       <c r="E210" s="28" t="inlineStr">
         <is>
-          <t>Phase 1 of 4. Blocks phases 2-4 and every financial number in the product. Evidence: 62 confirmed missing payment rows; Trinity French $225 paid / $0 recorded; $809 open invoices ($645 to void on canceled subs, $170 pre-app era, $114 real). Backfill must be idempotent — it will be run more than once.</t>
+          <t>Phase 3 of 4. Turns 'the numbers are right tonight' into 'the numbers stay right'. Depends on the stripe_payment_intent_id column from phase 2.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 2 — fix the webhook silent-skip defect + add stripe_payment_intent_id</t>
+          <t>[P0] Financial truth phase 4 — rebuild the financial dashboard on the clean ledger</t>
         </is>
       </c>
       <c r="B211" s="28" t="inlineStr">
         <is>
-          <t>The Stripe webhook silently skips payments rather than failing loudly, which is why the ledger drifted without anyone noticing: a dropped payment produces no error, no alert and no row, so the only evidence is an absence nobody is looking for. The payments table also has no stripe_payment_intent_id column, so there is no durable key tying a stored row back to the Stripe object it came from — which makes both deduplication and reconciliation guesswork.</t>
+          <t>The financial dashboard was built in Lovable on the incomplete payments table and has never been trusted (churn once displayed 2055%). Rebuilding it before the ledger is whole would only re-derive wrong numbers from a wrong source, so it is deliberately sequenced last.</t>
         </is>
       </c>
       <c r="C211" s="28" t="inlineStr">
         <is>
-          <t>Two changes, both prerequisites for the reconciliation in phase 3. (1) Replace every silent skip in the webhook handler with a loud failure: log the Stripe event id, the reason, and alert — never return 200 on an unwritten payment. (2) Add stripe_payment_intent_id to the payments table with a unique index, populate it in the phase 1 backfill, and write it on every new payment. Prove the fix with a Stripe-CLI replay of the exact event shapes that were being skipped, on develop first.</t>
+          <t>After phases 1-3 land, rebuild MRR, churn and revenue-by-tier directly on the reconciled ledger, then verify each figure against Stripe by hand once before trusting it. Absorbs the existing 'verify the financial dashboard' and 'verify the admin financial data function' rows, and is where the three-bucket collected / projected / churned view should land.</t>
         </is>
       </c>
       <c r="D211" s="28" t="inlineStr">
@@ -5586,24 +5621,24 @@
       </c>
       <c r="E211" s="28" t="inlineStr">
         <is>
-          <t>Phase 2 of 4. This is the defect that created the hole — fixing it stops the ledger re-diverging the moment phase 1 finishes. The new column is what phase 3 joins on. Aug 26: Requirement: journal invoice.voided (Stripe currently sole truth on voids, Rich case Aug 26).</t>
+          <t>Phase 4 of 4. Do NOT start before phase 1 completes — a dashboard on a partial ledger is the current problem, rebuilt. Supersedes the older FINANCIALS verify rows.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 3 — nightly two-way reconciliation with loud mismatch alerts</t>
+          <t>member_tier invariant hole: an active member can hold a null tier, and the webhook re-creates them</t>
         </is>
       </c>
       <c r="B212" s="28" t="inlineStr">
         <is>
-          <t>Once the ledger is whole (phase 1) and the webhook stops dropping rows (phase 2), the remaining risk is silent drift: any future gap between Stripe and the database is invisible until someone audits by hand, which is exactly how 62 rows accumulated. Nothing today compares the two systems on a schedule.</t>
+          <t>Nothing in the schema forbids the broken state. There is no CHECK constraint and no default preventing an active member from having a null member_tier, the partner member type has no tier mapping at all (so partners are structurally tier-null), and the payment-failure webhook re-creates tier-null rows even after they have been repaired by hand — Andrea's Aug 24 case is the proof that manual repair alone does not hold. Anything that gates on tier (event access, portal views, pricing) behaves unpredictably against a null.</t>
         </is>
       </c>
       <c r="C212" s="28" t="inlineStr">
         <is>
-          <t>Scheduled nightly job that reconciles in BOTH directions — every Stripe payment must exist in the ledger, and every ledger row must exist in Stripe — joined on stripe_payment_intent_id. Any mismatch alerts loudly (not a log line nobody reads) with the offending ids attached, and surfaces on the admin health dashboard alongside the cron / webhook widgets. Pairs with the Q6 canceled-drift tripwire and the DB/Stripe drift watch rows; consider folding them into one money-drift check rather than three.</t>
+          <t>Close the hole at the database level rather than by repeated repair. Decide the correct tier for the partner type first (it needs a real mapping, not a null), then add a CHECK constraint or default that makes 'active with null tier' unrepresentable, and fix the payment-failure webhook path so it preserves the existing tier instead of writing a row without one. Repair the outstanding rows in the same pass and re-check after the next real payment failure. Follow the incremental CHECK-constraint approach already agreed on the enums row — one table, carefully, not a schema-wide sweep.</t>
         </is>
       </c>
       <c r="D212" s="28" t="inlineStr">
@@ -5613,24 +5648,24 @@
       </c>
       <c r="E212" s="28" t="inlineStr">
         <is>
-          <t>Phase 3 of 4. Turns 'the numbers are right tonight' into 'the numbers stay right'. Depends on the stripe_payment_intent_id column from phase 2.</t>
+          <t>Aug 25: the 3+1 tier repairs were done tonight, but they are repairs, not a fix — the webhook will re-create tier-null rows until the write path and the constraint both change. Partner-type mapping is the open decision inside this row. Verified end state 2026-08-25: Jacob Cohen, JD Davis and Vaishali Willis all read member_tier 'social'; Andrea Baquero's row reads social too (updated 20:19:51 UTC) but she is still past_due, so the Stripe retry did not clear the money. 13 people rows holding a member role still carry a null tier, and exactly ONE of those is active - partnertest@704collective.com - which is the partner-type mapping hole above rather than a missed repair. ~20 people rows carry member role with null status; partnertest maps to no tier; normalize during invariant fix.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 4 — rebuild the financial dashboard on the clean ledger</t>
+          <t>hubs.created_by is NOT NULL ON DELETE CASCADE — deleting a creator profile destroys their hubs</t>
         </is>
       </c>
       <c r="B213" s="28" t="inlineStr">
         <is>
-          <t>The financial dashboard was built in Lovable on the incomplete payments table and has never been trusted (churn once displayed 2055%). Rebuilding it before the ledger is whole would only re-derive wrong numbers from a wrong source, so it is deliberately sequenced last.</t>
+          <t>The hubs.created_by foreign key is NOT NULL with ON DELETE CASCADE, so hard-deleting a profile deletes every hub that person created and everything those hubs contain. This is a live footgun on any exit or cleanup workstream: an ordinary-looking profile delete silently takes member-facing content with it, and there is nothing in the admin UI that warns about it.</t>
         </is>
       </c>
       <c r="C213" s="28" t="inlineStr">
         <is>
-          <t>After phases 1-3 land, rebuild MRR, churn and revenue-by-tier directly on the reconciled ledger, then verify each figure against Stripe by hand once before trusting it. Absorbs the existing 'verify the financial dashboard' and 'verify the admin financial data function' rows, and is where the three-bucket collected / projected / churned view should land.</t>
+          <t>Change the cascade to something survivable: make created_by nullable with ON DELETE SET NULL, or repoint deleted creators to an organisation-owned system account, so hubs outlive the person who made them. Until that lands, treat any profile hard-delete as a two-step operation — audit owned content first (the read-first footprint audit already used on member removals), reassign or purge deliberately, then delete.</t>
         </is>
       </c>
       <c r="D213" s="28" t="inlineStr">
@@ -5640,143 +5675,143 @@
       </c>
       <c r="E213" s="28" t="inlineStr">
         <is>
-          <t>Phase 4 of 4. Do NOT start before phase 1 completes — a dashboard on a partial ledger is the current problem, rebuilt. Supersedes the older FINANCIALS verify rows.</t>
+          <t>Aug 25: surfaced during the Josh hub-membership cleanup forensics, not because Josh owned anything - he created zero hubs. All four hubs (The Arrival, Business Founders, Eats &amp; Experiences, The Wellness) are created_by Adam, so the whole Network content structure hangs off one profile row and that is where the exposure sits. Soft deletes are safe; the hard-delete path (admin-delete-user, manual profile delete) is the footgun. Same class as the bulk-delete atomicity row.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="28" t="inlineStr">
         <is>
-          <t>member_tier invariant hole: an active member can hold a null tier, and the webhook re-creates them</t>
+          <t>Retention watch: 7 members exiting by Sep 13 — $287/mo MRR at risk</t>
         </is>
       </c>
       <c r="B214" s="28" t="inlineStr">
         <is>
-          <t>Nothing in the schema forbids the broken state. There is no CHECK constraint and no default preventing an active member from having a null member_tier, the partner member type has no tier mapping at all (so partners are structurally tier-null), and the payment-failure webhook re-creates tier-null rows even after they have been repaired by hand — Andrea's Aug 24 case is the proof that manual repair alone does not hold. Anything that gates on tier (event access, portal views, pricing) behaves unpredictably against a null.</t>
+          <t>Seven members are on track to exit by Sep 13, representing $287 per month of recurring revenue. Recorded as a dated watch so the number is tracked deliberately rather than discovered in a month-end total.</t>
         </is>
       </c>
       <c r="C214" s="28" t="inlineStr">
         <is>
-          <t>Close the hole at the database level rather than by repeated repair. Decide the correct tier for the partner type first (it needs a real mapping, not a null), then add a CHECK constraint or default that makes 'active with null tier' unrepresentable, and fix the payment-failure webhook path so it preserves the existing tier instead of writing a row without one. Repair the outstanding rows in the same pass and re-check after the next real payment failure. Follow the incremental CHECK-constraint approach already agreed on the enums row — one table, carefully, not a schema-wide sweep.</t>
+          <t>Track through Sep 13. Decide per member whether anything is worth doing (conversation, offer, pause instead of cancel) before the exits land, and confirm the actual outcome against this figure afterwards. Feeds the member-cancellation retention flow row — that build should be scoped by what these seven actually say.</t>
         </is>
       </c>
       <c r="D214" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E214" s="28" t="inlineStr">
         <is>
-          <t>Aug 25: the 3+1 tier repairs were done tonight, but they are repairs, not a fix — the webhook will re-create tier-null rows until the write path and the constraint both change. Partner-type mapping is the open decision inside this row. Verified end state 2026-08-25: Jacob Cohen, JD Davis and Vaishali Willis all read member_tier 'social'; Andrea Baquero's row reads social too (updated 20:19:51 UTC) but she is still past_due, so the Stripe retry did not clear the money. 13 people rows holding a member role still carry a null tier, and exactly ONE of those is active - partnertest@704collective.com - which is the partner-type mapping hole above rather than a missed repair. ~20 people rows carry member role with null status; partnertest maps to no tier; normalize during invariant fix.</t>
+          <t>Time-boxed: this row closes after Sep 13, either as a recorded loss or as retained members. $287/mo across 7 members. Note the financial figures here come from Stripe, not from the ledger the financial-truth project is fixing.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="28" t="inlineStr">
         <is>
-          <t>hubs.created_by is NOT NULL ON DELETE CASCADE — deleting a creator profile destroys their hubs</t>
+          <t>Members-by-type admin view — spec discussion in progress, build pending Adam's five answers</t>
         </is>
       </c>
       <c r="B215" s="28" t="inlineStr">
         <is>
-          <t>The hubs.created_by foreign key is NOT NULL with ON DELETE CASCADE, so hard-deleting a profile deletes every hub that person created and everything those hubs contain. This is a live footgun on any exit or cleanup workstream: an ordinary-looking profile delete silently takes member-facing content with it, and there is nothing in the admin UI that warns about it.</t>
+          <t>An admin view of members broken out by type. The spec conversation with Adam is underway but not finished: five questions remain open, and the build is deliberately not started until they are answered, so that the view is built once against a settled definition rather than reworked.</t>
         </is>
       </c>
       <c r="C215" s="28" t="inlineStr">
         <is>
-          <t>Change the cascade to something survivable: make created_by nullable with ON DELETE SET NULL, or repoint deleted creators to an organisation-owned system account, so hubs outlive the person who made them. Until that lands, treat any profile hard-delete as a two-step operation — audit owned content first (the read-first footprint audit already used on member removals), reassign or purge deliberately, then delete.</t>
+          <t>Finish the spec discussion with Adam and capture the five answers here, then build. Reuse the canonical person record and the existing member-type vocabulary rather than inventing a parallel definition — the same classification that the member_counts view and the directory work already use.</t>
         </is>
       </c>
       <c r="D215" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WAITING ON ADAM: five answers</t>
         </is>
       </c>
       <c r="E215" s="28" t="inlineStr">
         <is>
-          <t>Aug 25: surfaced during the Josh hub-membership cleanup forensics, not because Josh owned anything - he created zero hubs. All four hubs (The Arrival, Business Founders, Eats &amp; Experiences, The Wellness) are created_by Adam, so the whole Network content structure hangs off one profile row and that is where the exposure sits. Soft deletes are safe; the hard-delete path (admin-delete-user, manual profile delete) is the footgun. Same class as the bulk-delete atomicity row.</t>
+          <t>Spec in progress as of Aug 25. Build is intentionally blocked, not forgotten. Related to the unified admin users view and the member directory rows.</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="28" t="inlineStr">
-        <is>
-          <t>Retention watch: 7 members exiting by Sep 13 — $287/mo MRR at risk</t>
-        </is>
-      </c>
-      <c r="B216" s="28" t="inlineStr">
-        <is>
-          <t>Seven members are on track to exit by Sep 13, representing $287 per month of recurring revenue. Recorded as a dated watch so the number is tracked deliberately rather than discovered in a month-end total.</t>
-        </is>
-      </c>
-      <c r="C216" s="28" t="inlineStr">
-        <is>
-          <t>Track through Sep 13. Decide per member whether anything is worth doing (conversation, offer, pause instead of cancel) before the exits land, and confirm the actual outcome against this figure afterwards. Feeds the member-cancellation retention flow row — that build should be scoped by what these seven actually say.</t>
-        </is>
-      </c>
-      <c r="D216" s="28" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="E216" s="28" t="inlineStr">
-        <is>
-          <t>Time-boxed: this row closes after Sep 13, either as a recorded loss or as retained members. $287/mo across 7 members. Note the financial figures here come from Stripe, not from the ledger the financial-truth project is fixing.</t>
-        </is>
-      </c>
+      <c r="A216" s="43" t="inlineStr">
+        <is>
+          <t>AUG 26 FINDINGS — ADDED 2026-08-26   ·   4 items</t>
+        </is>
+      </c>
+      <c r="B216" s="34" t="n"/>
+      <c r="C216" s="34" t="n"/>
+      <c r="D216" s="34" t="n"/>
+      <c r="E216" s="34" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="28" t="inlineStr">
         <is>
-          <t>Members-by-type admin view — spec discussion in progress, build pending Adam's five answers</t>
+          <t>Attendance undercount is systemic — door discipline, not a data bug</t>
         </is>
       </c>
       <c r="B217" s="28" t="inlineStr">
         <is>
-          <t>An admin view of members broken out by type. The spec conversation with Adam is underway but not finished: five questions remain open, and the build is deliberately not started until they are answered, so that the view is built once against a settled definition rather than reworked.</t>
+          <t>Attendance is only ever as true as the door. Adam reports roughly two events Andrea Baquero attended that were never captured at check-in, and the same gap exists for anyone scanned inconsistently. This is not a reporting defect: the records are never written at all, so every downstream number that rests on attendance is quietly low and nothing signals it. It is event-critical for the Exchange specifically, because the mixer roster is built from check-ins — an uncaptured arrival is a person the engine will never seat.</t>
         </is>
       </c>
       <c r="C217" s="28" t="inlineStr">
         <is>
-          <t>Finish the spec discussion with Adam and capture the five answers here, then build. Reuse the canonical person record and the existing member-type vocabulary rather than inventing a parallel definition — the same classification that the member_counts view and the directory work already use.</t>
+          <t>Treat as an operations fix first, not a code fix. Add an explicit check-in line to the run-of-show for the Aug 27 Exchange so every arrival is scanned or recorded by hand, then measure that night's capture against the known headcount. Only if capture is still short does this become an instrumentation problem in the door path. Backfilling historical attendance is a separate decision, and not worth making until live capture is trustworthy.</t>
         </is>
       </c>
       <c r="D217" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: five answers</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E217" s="28" t="inlineStr">
         <is>
-          <t>Spec in progress as of Aug 25. Build is intentionally blocked, not forgotten. Related to the unified admin users view and the member directory rows.</t>
+          <t>Raised Aug 26 from the Andrea Baquero case (~2 attended events never captured). Immediate lever is the Aug 27 run-of-show line.</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="27" t="inlineStr">
-        <is>
-          <t>AUG 26 FINDINGS — ADDED 2026-08-26   ·   4 items</t>
-        </is>
-      </c>
-      <c r="B218" s="34" t="n"/>
-      <c r="C218" s="34" t="n"/>
-      <c r="D218" s="34" t="n"/>
-      <c r="E218" s="34" t="n"/>
+      <c r="A218" s="28" t="inlineStr">
+        <is>
+          <t>Hub add-member search still surfaces banned business members</t>
+        </is>
+      </c>
+      <c r="B218" s="28" t="inlineStr">
+        <is>
+          <t>The add-member search on /admin/hubs was narrowed Aug 26 to active business members with is_internal false, but banned was deliberately left out of the filter set. A banned business member with an active subscription therefore still appears in the search and can still be added to a hub. The member-facing hub tab hides them correctly, so the effect is an invisible member occupying a row rather than a data leak.</t>
+        </is>
+      </c>
+      <c r="C218" s="28" t="inlineStr">
+        <is>
+          <t>One line in the add-member search query: .eq('banned', false), alongside the existing deleted_at, member_type and is_internal filters. Same rehearsal shape as the Aug 26 hub work — seed a banned business member, confirm it is absent from the search, and confirm the member-facing tab is unchanged.</t>
+        </is>
+      </c>
+      <c r="D218" s="28" t="inlineStr">
+        <is>
+          <t>WAITING ON ADAM</t>
+        </is>
+      </c>
+      <c r="E218" s="28" t="inlineStr">
+        <is>
+          <t>Left open on purpose Aug 26: the shipped scope named member_type and is_internal only, so the gap was reported rather than silently widened. One-line change whenever Adam approves.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="28" t="inlineStr">
         <is>
-          <t>Attendance undercount is systemic — door discipline, not a data bug</t>
+          <t>Email logo still partially inverts in Gmail dark mode</t>
         </is>
       </c>
       <c r="B219" s="28" t="inlineStr">
         <is>
-          <t>Attendance is only ever as true as the door. Adam reports roughly two events Andrea Baquero attended that were never captured at check-in, and the same gap exists for anyone scanned inconsistently. This is not a reporting defect: the records are never written at all, so every downstream number that rests on attendance is quietly low and nothing signals it. It is event-critical for the Exchange specifically, because the mixer roster is built from check-ins — an uncaptured arrival is a person the engine will never seat.</t>
+          <t>The member blast logo was changed Aug 26 from the white-on-dark mark to the circular badge on an opaque white circle. That fixed the logo disappearing entirely and was render-verified for contrast in both light and dark-emulated views. In real Gmail, dark-mode inversion still partially affects the surrounding shell, so the badge is legible but the treatment is an improvement rather than a complete answer.</t>
         </is>
       </c>
       <c r="C219" s="28" t="inlineStr">
         <is>
-          <t>Treat as an operations fix first, not a code fix. Add an explicit check-in line to the run-of-show for the Aug 27 Exchange so every arrival is scanned or recorded by hand, then measure that night's capture against the known headcount. Only if capture is still short does this become an instrumentation problem in the door path. Backfilling historical attendance is a separate decision, and not worth making until live capture is trustworthy.</t>
+          <t>Next lever is a dark-mode-aware CSS asset: prefers-color-scheme rules plus explicit background locks on the shell, and where Gmail ignores those, a pre-composited image asset that cannot be inverted. Verify against a real Gmail dark-mode client, not only an emulated render — the emulated view is what passed while the real client still differed.</t>
         </is>
       </c>
       <c r="D219" s="28" t="inlineStr">
@@ -5786,86 +5821,32 @@
       </c>
       <c r="E219" s="28" t="inlineStr">
         <is>
-          <t>Raised Aug 26 from the Andrea Baquero case (~2 attended events never captured). Immediate lever is the Aug 27 run-of-show line.</t>
+          <t>Badge shipped Aug 26 and is legible; this row covers the remaining shell inversion. Cosmetic and low urgency, but it touches every member-facing send.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="28" t="inlineStr">
         <is>
-          <t>Hub add-member search still surfaces banned business members</t>
+          <t>Sentry: "load" error thrown on /dashboard (~Aug 24), undiagnosed</t>
         </is>
       </c>
       <c r="B220" s="28" t="inlineStr">
         <is>
-          <t>The add-member search on /admin/hubs was narrowed Aug 26 to active business members with is_internal false, but banned was deliberately left out of the filter set. A banned business member with an active subscription therefore still appears in the search and can still be added to a hub. The member-facing hub tab hides them correctly, so the effect is an invisible member occupying a row rather than a data leak.</t>
+          <t>Sentry reports an error on the member dashboard in which a Supabase error object appears to be thrown rather than handled, surfacing with the message "load". It first appears around Aug 24. Nothing else is known — frequency, affected users, and whether the page actually degrades are all unread, because the issue detail has not been opened.</t>
         </is>
       </c>
       <c r="C220" s="28" t="inlineStr">
         <is>
-          <t>One line in the add-member search query: .eq('banned', false), alongside the existing deleted_at, member_type and is_internal filters. Same rehearsal shape as the Aug 26 hub work — seed a banned business member, confirm it is absent from the search, and confirm the member-facing tab is unchanged.</t>
+          <t>Blocked on evidence, not on effort. Adam sends the Sentry issue-detail screenshot (stack, breadcrumbs, event count, affected users) and diagnosis follows from there. Likely shape is an unchecked Supabase call whose error object is thrown as-is, which is why the message reads as the object rather than a cause — but that is a guess until the throw site is visible.</t>
         </is>
       </c>
       <c r="D220" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM</t>
+          <t>WAITING ON ADAM: issue-detail screenshot</t>
         </is>
       </c>
       <c r="E220" s="28" t="inlineStr">
-        <is>
-          <t>Left open on purpose Aug 26: the shipped scope named member_type and is_internal only, so the gap was reported rather than silently widened. One-line change whenever Adam approves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="28" t="inlineStr">
-        <is>
-          <t>Email logo still partially inverts in Gmail dark mode</t>
-        </is>
-      </c>
-      <c r="B221" s="28" t="inlineStr">
-        <is>
-          <t>The member blast logo was changed Aug 26 from the white-on-dark mark to the circular badge on an opaque white circle. That fixed the logo disappearing entirely and was render-verified for contrast in both light and dark-emulated views. In real Gmail, dark-mode inversion still partially affects the surrounding shell, so the badge is legible but the treatment is an improvement rather than a complete answer.</t>
-        </is>
-      </c>
-      <c r="C221" s="28" t="inlineStr">
-        <is>
-          <t>Next lever is a dark-mode-aware CSS asset: prefers-color-scheme rules plus explicit background locks on the shell, and where Gmail ignores those, a pre-composited image asset that cannot be inverted. Verify against a real Gmail dark-mode client, not only an emulated render — the emulated view is what passed while the real client still differed.</t>
-        </is>
-      </c>
-      <c r="D221" s="28" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E221" s="28" t="inlineStr">
-        <is>
-          <t>Badge shipped Aug 26 and is legible; this row covers the remaining shell inversion. Cosmetic and low urgency, but it touches every member-facing send.</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="28" t="inlineStr">
-        <is>
-          <t>Sentry: "load" error thrown on /dashboard (~Aug 24), undiagnosed</t>
-        </is>
-      </c>
-      <c r="B222" s="28" t="inlineStr">
-        <is>
-          <t>Sentry reports an error on the member dashboard in which a Supabase error object appears to be thrown rather than handled, surfacing with the message "load". It first appears around Aug 24. Nothing else is known — frequency, affected users, and whether the page actually degrades are all unread, because the issue detail has not been opened.</t>
-        </is>
-      </c>
-      <c r="C222" s="28" t="inlineStr">
-        <is>
-          <t>Blocked on evidence, not on effort. Adam sends the Sentry issue-detail screenshot (stack, breadcrumbs, event count, affected users) and diagnosis follows from there. Likely shape is an unchecked Supabase call whose error object is thrown as-is, which is why the message reads as the object rather than a cause — but that is a guess until the throw site is visible.</t>
-        </is>
-      </c>
-      <c r="D222" s="28" t="inlineStr">
-        <is>
-          <t>WAITING ON ADAM: issue-detail screenshot</t>
-        </is>
-      </c>
-      <c r="E222" s="28" t="inlineStr">
         <is>
           <t>Raised Aug 26. Cannot be triaged from the title alone; the throw site is what identifies it. First seen ~Aug 24.</t>
         </is>

--- a/docs/704_Collective___Internal_Tracker__Phase_1___Phase_2___UPDATED_2026-08-03.xlsx
+++ b/docs/704_Collective___Internal_Tracker__Phase_1___Phase_2___UPDATED_2026-08-03.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>SEP 21 ADDITIONS — POST-IDENTITY-PACKAGE FOLLOW-UPS   ·   11 items</t>
+          <t>SEP 21 ADDITIONS — POST-IDENTITY-PACKAGE FOLLOW-UPS   ·   10 items</t>
         </is>
       </c>
       <c r="B7" s="31" t="n"/>
@@ -788,319 +788,319 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Stripe Connect-mode webhook endpoint + second signing secret — before the first payout (~Nov)</t>
+          <t>Meta CAPI — server-side Purchase events (dedupe with the browser pixel by event_id)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Ambassador and member-referral payouts move money via Stripe Connect transfers. Connect-side events (account.updated for onboarding status, transfer/payout lifecycle) arrive on a Connect-mode webhook endpoint with its own signing secret; today only the account-mode endpoint and secret are wired into stripe-webhook. Without the second endpoint, Connect account status changes and transfer failures after the first real payout are invisible.</t>
+          <t>The Meta pixel (d31dba9) fires Purchase client-side with eventID = the checkout session id, deduped per session. Browser-only events are lost to ad blockers and in-app browsers (the Nyree case) — CAPI sends the same Purchase server-side from the webhook so Meta sees every paid conversion once.</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Create the Connect-mode endpoint in the Stripe dashboard pointing at stripe-webhook (or a sibling), store its secret as a second env (e.g. STRIPE_CONNECT_WEBHOOK_SECRET), verify signature against whichever secret matches, and route account.updated / transfer.* events. Rehearse on develop with canned events. Must land before the first real Monday payout, expected ~Nov 2026 (second-payment commission rule).</t>
+          <t>From stripe-webhook checkout.session.completed (or the verify-checkout path): POST to the Conversions API with event_name Purchase, event_id = cs_ id (matches the pixel), value/currency, hashed email, fbclid/fbc from the session metadata already stamped by create-checkout. Env-gated like the pixel. Rehearse with Meta test_event_code on develop; no real Meta calls otherwise.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Build — before ~Nov</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Dated dependency: the first member/ambassador payout is expected around Nov. Phase 2 payout tail (d996e1a) already syncs member_payout_accounts from account.updated on the account-mode endpoint; this row is the Connect-mode endpoint + secret.</t>
+          <t>Depends on the Meta BM restructure + domain verification row (CAPI needs a verified domain and a system-user token). Pixel + UTM capture shipped Sep 15.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Meta CAPI — server-side Purchase events (dedupe with the browser pixel by event_id)</t>
+          <t>Meta Business Manager restructure + domain verification</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>The Meta pixel (d31dba9) fires Purchase client-side with eventID = the checkout session id, deduped per session. Browser-only events are lost to ad blockers and in-app browsers (the Nyree case) — CAPI sends the same Purchase server-side from the webhook so Meta sees every paid conversion once.</t>
+          <t>The ad account / pixel / page live in a Business Manager structure that needs restructuring, and 704collective.com is not domain-verified in Meta. Domain verification is required for aggregated event measurement and CAPI.</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>From stripe-webhook checkout.session.completed (or the verify-checkout path): POST to the Conversions API with event_name Purchase, event_id = cs_ id (matches the pixel), value/currency, hashed email, fbclid/fbc from the session metadata already stamped by create-checkout. Env-gated like the pixel. Rehearse with Meta test_event_code on develop; no real Meta calls otherwise.</t>
+          <t>Adam (Meta side): restructure BM ownership, verify 704collective.com (meta-tag or DNS TXT), attach the pixel to the verified domain, create a system user + CAPI token. Repo side if needed: one meta-tag in the root layout for verification.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>ADAM — Meta side</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Depends on the Meta BM restructure + domain verification row (CAPI needs a verified domain and a system-user token). Pixel + UTM capture shipped Sep 15.</t>
+          <t>Prerequisite for the CAPI row. Owner task; repo change is at most one meta tag.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Meta Business Manager restructure + domain verification</t>
+          <t>Identity Wave 6E — drop the legacy contacts columns after soak (PARKED)</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>The ad account / pixel / page live in a Business Manager structure that needs restructuring, and 704collective.com is not domain-verified in Meta. Domain verification is required for aggregated event measurement and CAPI.</t>
+          <t>Waves 6A–6D-a are live: contacts link to people at write time (6C triggers), tags mirror to person_tags, opt-out truth is people.marketing_unsubscribed, email readers flipped. The legacy columns (contacts.unsubscribed, contact_tags as a read surface, profiles.marketing_unsubscribed for two profile-side readers) are still written for compatibility. 6E removes them.</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Adam (Meta side): restructure BM ownership, verify 704collective.com (meta-tag or DNS TXT), attach the pixel to the verified domain, create a system user + CAPI token. Repo side if needed: one meta-tag in the root layout for verification.</t>
+          <t>After a soak and after 6D-b (admin surfaces) flips the last readers: drop/retire the legacy opt-out columns and contact_tags reads, repoint event-reminder and discussion-open off profiles.marketing_unsubscribed, remove the mirror lines from the 6C triggers. Migration + small code; rehearse on develop.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>ADAM — Meta side</t>
+          <t>PARKED</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Prerequisite for the CAPI row. Owner task; repo change is at most one meta tag.</t>
+          <t>Deliberately parked: nothing is wrong today because 6C keeps every legacy column current. Sequenced after 6D-b.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Identity Wave 6E — drop the legacy contacts columns after soak (PARKED)</t>
+          <t>Identity Wave 6D-b — admin CRM/contacts surfaces read person-side truth (rides the admin rebuild)</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Waves 6A–6D-a are live: contacts link to people at write time (6C triggers), tags mirror to person_tags, opt-out truth is people.marketing_unsubscribed, email readers flipped. The legacy columns (contacts.unsubscribed, contact_tags as a read surface, profiles.marketing_unsubscribed for two profile-side readers) are still written for compatibility. 6E removes them.</t>
+          <t>The admin contacts/CRM pages, the attendee dialog and comp-invite still read contacts / contact_tags / legacy opt-out columns (cursor_report_wave6d.md §2). Correct today because 6C mirrors, but they are the last readers keeping the legacy shape alive.</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>After a soak and after 6D-b (admin surfaces) flips the last readers: drop/retire the legacy opt-out columns and contact_tags reads, repoint event-reminder and discussion-open off profiles.marketing_unsubscribed, remove the mirror lines from the 6C triggers. Migration + small code; rehearse on develop.</t>
+          <t>Flip the admin readers to people / person_tags / people.marketing_unsubscribed. Needs grant select on person_tags to authenticated + an admin-only select policy (person_tags is service-role only today). Ride with "Build the admin area into clean sections" so each page is touched once.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>PARKED</t>
+          <t>QUEUED — rides admin rebuild</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Deliberately parked: nothing is wrong today because 6C keeps every legacy column current. Sequenced after 6D-b.</t>
+          <t>Deferred by design in the 6D recon. Unblocks 6E.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Identity Wave 6D-b — admin CRM/contacts surfaces read person-side truth (rides the admin rebuild)</t>
+          <t>Identity Wave 8 — auth cutover (PARKED)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>The admin contacts/CRM pages, the attendee dialog and comp-invite still read contacts / contact_tags / legacy opt-out columns (cursor_report_wave6d.md §2). Correct today because 6C mirrors, but they are the last readers keeping the legacy shape alive.</t>
+          <t>The final identity wave: auth-adjacent writes (signup, email change, password flows) key entirely on the person record with profiles as a settings/billing satellite. Wave A already mints a person at signup; 6C links every contact write; the cutover is the remaining piece.</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Flip the admin readers to people / person_tags / people.marketing_unsubscribed. Needs grant select on person_tags to authenticated + an admin-only select policy (person_tags is service-role only today). Ride with "Build the admin area into clean sections" so each page is touched once.</t>
+          <t>Own scope before build. Regression-test logins + RLS from a non-admin session behind a verified backup/rollback, as the identity plan always required. Sequence after Wave 7 (email sync).</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>QUEUED — rides admin rebuild</t>
+          <t>PARKED</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Deferred by design in the 6D recon. Unblocks 6E.</t>
+          <t>Parked until Waves 7 and 9 land and the mobile app scope is known — the app is the consumer that decides how much cutover is needed.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Identity Wave 8 — auth cutover (PARKED)</t>
+          <t>Expiring-card Stripe toggle — Adam, 5 seconds</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>The final identity wave: auth-adjacent writes (signup, email change, password flows) key entirely on the person record with profiles as a settings/billing satellite. Wave A already mints a person at signup; 6C links every contact write; the cutover is the remaining piece.</t>
+          <t>Stripe can email customers automatically when a saved card is about to expire (Billing -&gt; Subscriptions and emails -&gt; "Send emails about expiring cards"). It is off. Turning it on removes a class of avoidable past_due.</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Own scope before build. Regression-test logins + RLS from a non-admin session behind a verified backup/rollback, as the identity plan always required. Sequence after Wave 7 (email sync).</t>
+          <t>Adam: Stripe dashboard -&gt; Settings -&gt; Billing -&gt; Subscriptions and emails -&gt; enable expiring-card emails. Confirm the sender/branding matches the receipts. No code.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>PARKED</t>
+          <t>ADAM — 5 seconds</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Parked until Waves 7 and 9 land and the mobile app scope is known — the app is the consumer that decides how much cutover is needed.</t>
+          <t>Pairs with the past_due update-billing banner shipped Sep 3 (159fd52) and the renewal reminders.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Expiring-card Stripe toggle — Adam, 5 seconds</t>
+          <t>Social member profiles + the open-or-gated decision</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Stripe can email customers automatically when a saved card is about to expire (Billing -&gt; Subscriptions and emails -&gt; "Send emails about expiring cards"). It is off. Turning it on removes a class of avoidable past_due.</t>
+          <t>Social members need a profile surface (the four clean fields) and a decision on whether member profiles/cards are open to the public or gated behind login. The public card page exists (card/[public_id]) and already applies the single member-visibility predicate (7084b43); the product decision on what a non-member can see is not made.</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Adam: Stripe dashboard -&gt; Settings -&gt; Billing -&gt; Subscriptions and emails -&gt; enable expiring-card emails. Confirm the sender/branding matches the receipts. No code.</t>
+          <t>Adam decides open vs gated (and what fields are public if open). Then align the public card, the directory and the hub pages to that one rule. Builds on "Strip member profiles to four clean fields" and the privacy toggle row.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>ADAM — 5 seconds</t>
+          <t>WAITING ON ADAM: open or gated</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Pairs with the past_due update-billing banner shipped Sep 3 (159fd52) and the renewal reminders.</t>
+          <t>Decision gates part of the hub pages build (which member content the public hubs may show).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Social member profiles + the open-or-gated decision</t>
+          <t>Lint warnings someday-audit (475 warnings today, 0 errors)</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Social members need a profile surface (the four clean fields) and a decision on whether member profiles/cards are open to the public or gated behind login. The public card page exists (card/[public_id]) and already applies the single member-visibility predicate (7084b43); the product decision on what a non-member can see is not made.</t>
+          <t>npm run lint passes with 0 errors but ~475 warnings (unused vars/imports, no-unused-expressions, react-hooks deps). They are noise that hides new real warnings and 17 are auto-fixable.</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Adam decides open vs gated (and what fields are public if open). Then align the public card, the directory and the hub pages to that one rule. Builds on "Strip member profiles to four clean fields" and the privacy toggle row.</t>
+          <t>Someday: run eslint --fix for the auto-fixable set, then burn the rest down file-by-file in otherwise-idle sessions. Never as a big-bang commit; never mixed into a feature change.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: open or gated</t>
+          <t>Someday</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Decision gates part of the hub pages build (which member content the public hubs may show).</t>
+          <t>Count as of Sep 21 gates: 475 problems, 0 errors, 17 auto-fixable.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Lint warnings someday-audit (475 warnings today, 0 errors)</t>
+          <t>cleanup-business-members: Social product id is a hard-coded constant</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>npm run lint passes with 0 errors but ~475 warnings (unused vars/imports, no-unused-expressions, react-hooks deps). They are noise that hides new real warnings and 17 are auto-fixable.</t>
+          <t>cleanup-business-members classifies a customer as business vs social by comparing the subscription's product to SOCIAL_PRODUCT_ID = "prod_TZI8im1xRNUMuy", a constant in the file rather than an env var. A future price/product change would silently reclassify every social member as business — and the function now cancels in Stripe before hiding, so the blast radius of a wrong classification grew with the Wave 10 weld.</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Someday: run eslint --fix for the auto-fixable set, then burn the rest down file-by-file in otherwise-idle sessions. Never as a big-bang commit; never mixed into a feature change.</t>
+          <t>Read the id from an env (STRIPE_SOCIAL_PRODUCT_ID, already the name other code uses) with the constant as fallback, and fail closed if neither resolves. Also clear the 3 pre-existing deno type errors in the file while there. Small.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Someday</t>
+          <t>Build — small</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Count as of Sep 21 gates: 475 problems, 0 errors, 17 auto-fixable.</t>
+          <t>Found during the Wave 10 rehearsal, where a wrong product id in the stub made the function (correctly, per its rules) cancel and hide every seeded social member.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>cleanup-business-members: Social product id is a hard-coded constant</t>
+          <t>stripe-webhook cascade dedupe — point handleSubscriptionDeleted at _shared/membershipCascade.ts</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>cleanup-business-members classifies a customer as business vs social by comparing the subscription's product to SOCIAL_PRODUCT_ID = "prod_TZI8im1xRNUMuy", a constant in the file rather than an env var. A future price/product change would silently reclassify every social member as business — and the function now cancels in Stripe before hiding, so the blast radius of a wrong classification grew with the Wave 10 weld.</t>
+          <t>Wave 10 lifted the membership-end cascade (hub seats, people status, credential void + wallet push) into supabase/functions/_shared/membershipCascade.ts for admin-delete-user, but left the webhook's own copies in place so its cancellation path stayed regression-locked. Two copies will drift on the next rule change.</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Read the id from an env (STRIPE_SOCIAL_PRODUCT_ID, already the name other code uses) with the constant as fallback, and fail closed if neither resolves. Also clear the 3 pre-existing deno type errors in the file while there. Small.</t>
+          <t>After Wave 10 has soaked: replace the webhook's removeHubSeats / voidPersonCredentials bodies with imports from the shared module, assert byte-identical behaviour with the R4 canned subscription.deleted rehearsal, deploy stripe-webhook.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Build — small</t>
+          <t>Build — small, after soak</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Found during the Wave 10 rehearsal, where a wrong product id in the stub made the function (correctly, per its rules) cancel and hide every seeded social member.</t>
+          <t>Same drift class as the comp-invite resolver replica row. Follow-up named in cursor_report_wave10_build.md §6.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>stripe-webhook cascade dedupe — point handleSubscriptionDeleted at _shared/membershipCascade.ts</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Wave 10 lifted the membership-end cascade (hub seats, people status, credential void + wallet push) into supabase/functions/_shared/membershipCascade.ts for admin-delete-user, but left the webhook's own copies in place so its cancellation path stayed regression-locked. Two copies will drift on the next rule change.</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>After Wave 10 has soaked: replace the webhook's removeHubSeats / voidPersonCredentials bodies with imports from the shared module, assert byte-identical behaviour with the R4 canned subscription.deleted rehearsal, deploy stripe-webhook.</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Build — small, after soak</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>Same drift class as the comp-invite resolver replica row. Follow-up named in cursor_report_wave10_build.md §6.</t>
-        </is>
-      </c>
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>IMMEDIATE SPRINT - PRE/POST-EVENT (added Aug 26) - 3 items</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
     </row>
     <row r="19" ht="23.85" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>IMMEDIATE SPRINT - PRE/POST-EVENT (added Aug 26) - 3 items</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="31" t="n"/>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Realtime RSVP/cancel sync to Exchange engine + viewer</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>RSVPs and cancellations must reflect immediately (no manual refresh) in /admin/exchange viewer (counts, pools, roster) and /admin/exchange/mixer (eligible roster). Candidates: Supabase Realtime subscriptions on attendance_credentials + exchange_intake scoped to the event, or tight polling. Must define cancel-mid-round behavior (current-round seat stands, excluded from next MIX; late check-ins already auto-join next round). Deadline: before Aug 27 event; freeze exception authorized by Adam; full develop rehearsal mandatory, both viewports, simulated RSVP+cancel during an active round.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="35.05" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Realtime RSVP/cancel sync to Exchange engine + viewer</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
+          <t>Exchange mixer/viewer remedy C — shed or wrap columns so the roster fits a 390px phone</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>R4 shipped remedy B (admin surfaces; header reachable, table cleanly bounded) but the mixer/viewer table is still ~1369px wide and needs sideways scrolling on a phone. Recon remedy C — shedding or wrapping columns — was explicitly left open.</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Column-shedding or wrap layout for the mixer roster/viewer at 390px. CSS/markup only; engine untouched. Both viewports on develop before shipping. Adam names which columns can be shed at build time.</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Build</t>
@@ -1108,26 +1108,18 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>RSVPs and cancellations must reflect immediately (no manual refresh) in /admin/exchange viewer (counts, pools, roster) and /admin/exchange/mixer (eligible roster). Candidates: Supabase Realtime subscriptions on attendance_credentials + exchange_intake scoped to the event, or tight polling. Must define cancel-mid-round behavior (current-round seat stands, excluded from next MIX; late check-ins already auto-join next round). Deadline: before Aug 27 event; freeze exception authorized by Adam; full develop rehearsal mandatory, both viewports, simulated RSVP+cancel during an active round.</t>
+          <t>Was "mixer engine + viewer spacing fixes". Remedy B landed Sep (R4 build); remedy C is the remaining piece per cursor_report_r4build.md.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="23.85" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Exchange mixer/viewer remedy C — shed or wrap columns so the roster fits a 390px phone</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>R4 shipped remedy B (admin surfaces; header reachable, table cleanly bounded) but the mixer/viewer table is still ~1369px wide and needs sideways scrolling on a phone. Recon remedy C — shedding or wrapping columns — was explicitly left open.</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Column-shedding or wrap layout for the mixer roster/viewer at 390px. CSS/markup only; engine untouched. Both viewports on develop before shipping. Adam names which columns can be shed at build time.</t>
-        </is>
-      </c>
+          <t>Notification bell dropdown cannot scroll</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
       <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Build</t>
@@ -1135,119 +1127,127 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Was "mixer engine + viewer spacing fixes". Remedy B landed Sep (R4 build); remedy C is the remaining piece per cursor_report_r4build.md.</t>
+          <t>Member-facing: notification list under the bell is unscrollable, long lists unreachable. Likely overflow-y/max-height on the dropdown container. Both viewports. Low risk; can ride with R4's pass.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="35.05" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Notification bell dropdown cannot scroll</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Member-facing: notification list under the bell is unscrollable, long lists unreachable. Likely overflow-y/max-height on the dropdown container. Both viewports. Low risk; can ride with R4's pass.</t>
-        </is>
-      </c>
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>ONBOARDING &amp; SIGNUP   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
     </row>
     <row r="23" ht="35.05" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>ONBOARDING &amp; SIGNUP   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Collect phone for everyone at signup; gate texts on consent</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Phone is captured at signup now; the remaining work is gating SMS on the consent flag (not on whether a number exists) and re-collecting phone from pre-May-21 members whose number was never saved.</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Confirm phone persists from signup metadata; gate SMS on the consent flag; add a re-collection prompt for pre-May-21 members.</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Phone capture + display already shipped; consent gate + backfill remain.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="35.05" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Collect phone for everyone at signup; gate texts on consent</t>
+          <t>Prompt calendar-subscribe + wallet-pass add at signup</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Phone is captured at signup now; the remaining work is gating SMS on the consent flag (not on whether a number exists) and re-collecting phone from pre-May-21 members whose number was never saved.</t>
+          <t>As part of signup, walk the new member through subscribing to the event calendar and adding their wallet pass, so both are set up before they finish onboarding.</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Confirm phone persists from signup metadata; gate SMS on the consent flag; add a re-collection prompt for pre-May-21 members.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Add a calendar-subscribe step and a wallet-add step to the signup / onboarding flow; confirm both stick.</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Phone capture + display already shipped; consent gate + backfill remain.</t>
+          <t>New onboarding-flow ask — pairs with the lifecycle push to current members (see Email &amp; Drip).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Prompt calendar-subscribe + wallet-pass add at signup</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>As part of signup, walk the new member through subscribing to the event calendar and adding their wallet pass, so both are set up before they finish onboarding.</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Add a calendar-subscribe step and a wallet-add step to the signup / onboarding flow; confirm both stick.</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>New onboarding-flow ask — pairs with the lifecycle push to current members (see Email &amp; Drip).</t>
-        </is>
-      </c>
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>MEMBERS &amp; MONEY   ·   3 items</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
     </row>
     <row r="26" ht="23.85" customHeight="1">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>MEMBERS &amp; MONEY   ·   3 items</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Verify the payment-to-membership chain end to end</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>The full money path (checkout -&gt; Stripe webhook -&gt; member activated) has no automated test.</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Run a Stripe-CLI end-to-end test of checkout -&gt; webhook -&gt; activation before scaling referrals on it.</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>The money path — verify carefully; everything downstream assumes it works.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.85" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Verify the payment-to-membership chain end to end</t>
+          <t>Verify an email change keeps Stripe billing in sync</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>The full money path (checkout -&gt; Stripe webhook -&gt; member activated) has no automated test.</t>
+          <t>When a member changes email, the Stripe customer should update too, so billing/receipts don't split into a second identity.</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Run a Stripe-CLI end-to-end test of checkout -&gt; webhook -&gt; activation before scaling referrals on it.</t>
+          <t>Change an email; confirm the Stripe customer email updates; no orphaned customer.</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1257,127 +1257,127 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>The money path — verify carefully; everything downstream assumes it works.</t>
+          <t>Identity Wave 7 (email sync). Rides BEFORE the mobile app together with Wave 9 (tickets). Internally an email change no longer splits identity (auth_user_id key since Wave 0; contacts family linked at write time since 6C); the Stripe-customer half is the remaining work. Also closes the customer.updated webhook gap noted in the drift-trio recon.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="23.85" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Verify an email change keeps Stripe billing in sync</t>
+          <t>Migrate the 8 legacy $30 subscriptions</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>When a member changes email, the Stripe customer should update too, so billing/receipts don't split into a second identity.</t>
+          <t>The trusted member-count definitions are already established (member_counts view). The only residual is 8 subscriptions still on the retired $30 price.</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Change an email; confirm the Stripe customer email updates; no orphaned customer.</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Move the 8 legacy $30 subs to current pricing in Stripe; $30 is retired everywhere else.</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Identity Wave 7 (email sync). Rides BEFORE the mobile app together with Wave 9 (tickets). Internally an email change no longer splits identity (auth_user_id key since Wave 0; contacts family linked at write time since 6C); the Stripe-customer half is the remaining work. Also closes the customer.updated webhook gap noted in the drift-trio recon.</t>
+          <t>Count reconciliation itself is DONE — this is the leftover cleanup.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="23.85" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Migrate the 8 legacy $30 subscriptions</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>The trusted member-count definitions are already established (member_counts view). The only residual is 8 subscriptions still on the retired $30 price.</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Move the 8 legacy $30 subs to current pricing in Stripe; $30 is retired everywhere else.</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Count reconciliation itself is DONE — this is the leftover cleanup.</t>
-        </is>
-      </c>
+      <c r="A29" s="35" t="inlineStr">
+        <is>
+          <t>IDENTITY FOUNDATION   ·   1 item</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
     </row>
     <row r="30" ht="23.85" customHeight="1">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t>IDENTITY FOUNDATION   ·   1 item</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Finish retiring the old ticket tables</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>RSVP moved to one attendance table; a guest-pass follow-up tracker and one hook still dual-write the old 'tickets' table.</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Repoint last guest-pass readers/writers to attendance_credentials, kill the dual-write, drop legacy tickets + guest_passes after a safe soak.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Identity Wave 9 (tickets). Rides BEFORE the mobile app together with Wave 7 (email sync). Wave 9 recon Aug 25 stands: create-guest-pass writes legacy tickets PRIMARY; dashboard guest-pass list + get_community_stats read legacy; capacity trigger pair mapped; retirement order + mandatory backfill (8 of 26 mirrored). Do not drop before the soak confirms nothing else reads them. Closes together with the capacity-trigger split-brain row.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.85" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Finish retiring the old ticket tables</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>RSVP moved to one attendance table; a guest-pass follow-up tracker and one hook still dual-write the old 'tickets' table.</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Repoint last guest-pass readers/writers to attendance_credentials, kill the dual-write, drop legacy tickets + guest_passes after a safe soak.</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Identity Wave 9 (tickets). Rides BEFORE the mobile app together with Wave 7 (email sync). Wave 9 recon Aug 25 stands: create-guest-pass writes legacy tickets PRIMARY; dashboard guest-pass list + get_community_stats read legacy; capacity trigger pair mapped; retirement order + mandatory backfill (8 of 26 mirrored). Do not drop before the soak confirms nothing else reads them. Closes together with the capacity-trigger split-brain row.</t>
-        </is>
-      </c>
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>EVENTS &amp; CALENDAR   ·   19 items</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>EVENTS &amp; CALENDAR   ·   19 items</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Require an event category at creation</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Every event needs a category label at creation (a mis-filed event was shown to the wrong audience). Category is separate from access level.</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Two independent fields on the event form — Category (editable label) and Access level — both enforced at creation.</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Categories: The 704 / The Reserve / After Hours / The Reset / For the City / The Exchange / Coffee &amp; Connect.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="35.05" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Require an event category at creation</t>
+          <t>Three event access levels: open / members / business</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Every event needs a category label at creation (a mis-filed event was shown to the wrong audience). Category is separate from access level.</t>
+          <t>Production already runs business-only events; the old two-bucket spec needs three: open to all, members only, business-members only.</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Two independent fields on the event form — Category (editable label) and Access level — both enforced at creation.</t>
+          <t>Implement a 3-value access field driving visibility + RSVP eligibility.</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -1387,24 +1387,24 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Categories: The 704 / The Reserve / After Hours / The Reset / For the City / The Exchange / Coffee &amp; Connect.</t>
+          <t>Drives both event visibility and who can RSVP.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="23.85" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Three event access levels: open / members / business</t>
+          <t>One simple event feed everyone sees</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Production already runs business-only events; the old two-bucket spec needs three: open to all, members only, business-members only.</t>
+          <t>Locked: no separate social vs business feeds for now; one feed shows everyone all events.</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Implement a 3-value access field driving visibility + RSVP eligibility.</t>
+          <t>Ship the single simplest feed; access level still governs RSVP eligibility.</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -1414,105 +1414,105 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Drives both event visibility and who can RSVP.</t>
+          <t>Single feed for now; tiered feeds are explicitly deferred.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="23.85" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>One simple event feed everyone sees</t>
+          <t>Confirm the 118 old calendar links work again</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Locked: no separate social vs business feeds for now; one feed shows everyone all events.</t>
+          <t>When the feed broke, ~118 members held subscribe-links returning an empty calendar; the June 10 rebuild likely revived them.</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Ship the single simplest feed; access level still governs RSVP eligibility.</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Spot-check several of the 118 tokens against the live feed; if events return, close it — else send a re-subscribe email.</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Single feed for now; tiered feeds are explicitly deferred.</t>
+          <t>Likely already revived by the June 10 rebuild — confirm, then a soft 'your calendar works' note at most.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="23.85" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Confirm the 118 old calendar links work again</t>
+          <t>Alert if the calendar feed ever goes empty again</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>When the feed broke, ~118 members held subscribe-links returning an empty calendar; the June 10 rebuild likely revived them.</t>
+          <t>The feed broke silently last time.</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Spot-check several of the 118 tokens against the live feed; if events return, close it — else send a re-subscribe email.</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Cron/health-check comparing feed output to known future events; alert on mismatch.</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Likely already revived by the June 10 rebuild — confirm, then a soft 'your calendar works' note at most.</t>
+          <t>Catches a silent feed failure like the earlier one.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="23.85" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Alert if the calendar feed ever goes empty again</t>
+          <t>Verify the event detail page handles every state</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>The feed broke silently last time.</t>
+          <t>Member + public RSVP are verified; waitlist, paid purchase, capacity-full, and cancel/re-RSVP are not.</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Cron/health-check comparing feed output to known future events; alert on mismatch.</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Test the remaining EventDetail branches.</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Catches a silent feed failure like the earlier one.</t>
+          <t>Core states already verified; this covers the edge branches.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21.75" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Verify the event detail page handles every state</t>
+          <t>Verify the RSVP status sidebar shows the right state</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Member + public RSVP are verified; waitlist, paid purchase, capacity-full, and cancel/re-RSVP are not.</t>
+          <t>Confirm the sidebar reflects all 7 RSVP states.</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Test the remaining EventDetail branches.</t>
+          <t>Walk all 7 states: not RSVP'd, RSVP'd, waitlisted, cancelled, attended, refunded, no-show.</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -1522,105 +1522,105 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Core states already verified; this covers the edge branches.</t>
+          <t>Purely a verification walk-through; not a build.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="46.25" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Verify the RSVP status sidebar shows the right state</t>
+          <t>Show non-members a teaser of members-only events</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Confirm the sidebar reflects all 7 RSVP states.</t>
+          <t>A non-member should see members-only events as a teaser: type + 'Members Only' tag, never the location. Creates FOMO, sells membership.</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Walk all 7 states: not RSVP'd, RSVP'd, waitlisted, cancelled, attended, refunded, no-show.</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Public view: type + tag, hide name details, always hide location.</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Purely a verification walk-through; not a build.</t>
+          <t>Awaiting a fuller public-events-page spec before final build.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="23.85" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Show non-members a teaser of members-only events</t>
+          <t>Verify the remaining door check-in scan paths</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>A non-member should see members-only events as a teaser: type + 'Members Only' tag, never the location. Creates FOMO, sells membership.</t>
+          <t>Member check-in is verified; walk-in (no-RSVP) record, guest-pass scan, and junk-scan rejection are not.</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Public view: type + tag, hide name details, always hide location.</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Test walk-in QR, guest-pass (GP-) scan, and gibberish-scan rejection.</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Awaiting a fuller public-events-page spec before final build.</t>
+          <t>Member check-in already verified; this covers walk-in, guest-pass, and bad scans.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="23.85" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Verify the remaining door check-in scan paths</t>
+          <t>Hide all event details until someone RSVPs</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Member check-in is verified; walk-in (no-RSVP) record, guest-pass scan, and junk-scan rejection are not.</t>
+          <t>By default, all event details are hidden from everyone (even in the portal) except photo, preview name, and date/time; full details reveal only after RSVP.</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Test walk-in QR, guest-pass (GP-) scan, and gibberish-scan rejection.</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Default-hide name/location/details; reveal post-RSVP; controlled from the event manager.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Member check-in already verified; this covers walk-in, guest-pass, and bad scans.</t>
+          <t>Build after the core events work is stable.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Hide all event details until someone RSVPs</t>
+          <t>Polite no-show email</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>By default, all event details are hidden from everyone (even in the portal) except photo, preview name, and date/time; full details reveal only after RSVP.</t>
+          <t>When a member RSVPs but doesn't show (known from check-in), send a kind 'only RSVP if you can attend' email — resources are planned around counts.</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Default-hide name/location/details; reveal post-RSVP; controlled from the event manager.</t>
+          <t>Trigger off check-in data (RSVP'd + not scanned = no-show).</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -1630,24 +1630,24 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Build after the core events work is stable.</t>
+          <t>Depends on stricter RSVP + solid check-in data.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="23.85" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Polite no-show email</t>
+          <t>Persist public RSVP confirmation + on-page QR</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>When a member RSVPs but doesn't show (known from check-in), send a kind 'only RSVP if you can attend' email — resources are planned around counts.</t>
+          <t>When a non-member RSVPs, keep them confirmed on reload and show their QR on the confirmation page (+ email); no account required.</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Trigger off check-in data (RSVP'd + not scanned = no-show).</t>
+          <t>Persist confirmed state on reload; render QR on the confirmation page + email.</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -1657,24 +1657,24 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Depends on stricter RSVP + solid check-in data.</t>
+          <t>No account creation for the public RSVP — just persistence + QR.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Persist public RSVP confirmation + on-page QR</t>
+          <t>Optional event host (name + photo)</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>When a non-member RSVPs, keep them confirmed on reload and show their QR on the confirmation page (+ email); no account required.</t>
+          <t>Let an event optionally show a host with name and photo.</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Persist confirmed state on reload; render QR on the confirmation page + email.</t>
+          <t>Event host field + admin form + display.</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -1684,24 +1684,24 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>No account creation for the public RSVP — just persistence + QR.</t>
+          <t>Simple optional field; no dependencies.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="23.85" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Optional event host (name + photo)</t>
+          <t>Future-event visibility limits</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Let an event optionally show a host with name and photo.</t>
+          <t>Define and enforce how far ahead events are visible (date range, tier, or capacity).</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Event host field + admin form + display.</t>
+          <t>Scope the limit dimension, then enforce.</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Simple optional field; no dependencies.</t>
+          <t>Decide the limit dimension before enforcing.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="23.85" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Future-event visibility limits</t>
+          <t>Soft-delete for events</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Define and enforce how far ahead events are visible (date range, tier, or capacity).</t>
+          <t>Let events be recoverable rather than hard-deleted.</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Scope the limit dimension, then enforce.</t>
+          <t>Soft-delete events.</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -1738,24 +1738,24 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Decide the limit dimension before enforcing.</t>
+          <t>Related to the event-DELETE RLS failure that the identity fix resolves.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21.75" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Soft-delete for events</t>
+          <t>Self-serve event management</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Let events be recoverable rather than hard-deleted.</t>
+          <t>Let hosts/business members propose or manage their own events (admins publish).</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Soft-delete events.</t>
+          <t>Define permissions — likely 'propose -&gt; admin publish'.</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -1765,24 +1765,24 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Related to the event-DELETE RLS failure that the identity fix resolves.</t>
+          <t>Needs scoping before build.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="23.85" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Self-serve event management</t>
+          <t>Event reorganization</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Let hosts/business members propose or manage their own events (admins publish).</t>
+          <t>Restructure how events are displayed per the events direction.</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Define permissions — likely 'propose -&gt; admin publish'.</t>
+          <t>Needs the detailed events-page spec.</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -1792,24 +1792,24 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Needs scoping before build.</t>
+          <t>Blocked on the detailed events-page spec.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="102.2" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Event reorganization</t>
+          <t>Calendar scope picker in settings</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Restructure how events are displayed per the events direction.</t>
+          <t>Optional: let business members narrow their calendar to business-only.</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Needs the detailed events-page spec.</t>
+          <t>Implement only if tiered feeds return.</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -1819,24 +1819,24 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Blocked on the detailed events-page spec.</t>
+          <t>Optional given the single-feed decision; only relevant if tiered feeds return.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21.75" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Calendar scope picker in settings</t>
+          <t>Instant Google Calendar updates</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Optional: let business members narrow their calendar to business-only.</t>
+          <t>Subscribed calendars refresh every 8-24h; true instant needs a Google Calendar API push integration.</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Implement only if tiered feeds return.</t>
+          <t>Service account writing to each member's calendar.</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -1846,62 +1846,62 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Optional given the single-feed decision; only relevant if tiered feeds return.</t>
+          <t>Larger effort — a Google Calendar API push integration.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="35.05" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Instant Google Calendar updates</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Subscribed calendars refresh every 8-24h; true instant needs a Google Calendar API push integration.</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>Service account writing to each member's calendar.</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>Larger effort — a Google Calendar API push integration.</t>
-        </is>
-      </c>
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>WALLET PASS   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n"/>
+      <c r="C51" s="31" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="31" t="n"/>
     </row>
     <row r="52" ht="35.05" customHeight="1">
-      <c r="A52" s="35" t="inlineStr">
-        <is>
-          <t>WALLET PASS   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="n"/>
-      <c r="C52" s="31" t="n"/>
-      <c r="D52" s="31" t="n"/>
-      <c r="E52" s="31" t="n"/>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Verify Apple Wallet passes work on real phones</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Confirm generate, deliver (dashboard + email), and update-on-status-change end to end; code is further along than expected.</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Test on a real iPhone; fix gaps.</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Generation + push-update already exist — verify on a real device, then close gaps.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="23.85" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Verify Apple Wallet passes work on real phones</t>
+          <t>Kill a membership pass when someone cancels</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Confirm generate, deliver (dashboard + email), and update-on-status-change end to end; code is further along than expected.</t>
+          <t>When membership lapses/cancels, the pass must stop scanning at the door; a void function exists.</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Test on a real iPhone; fix gaps.</t>
+          <t>Verify cancellation voids the pass and it dies on-device.</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -1911,51 +1911,51 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Generation + push-update already exist — verify on a real device, then close gaps.</t>
+          <t>Nothing should scan at the door after membership ends.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21.75" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Kill a membership pass when someone cancels</t>
+          <t>Give members a QR backup if their pass fails</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>When membership lapses/cancels, the pass must stop scanning at the door; a void function exists.</t>
+          <t>Door failure modes: dead battery, no signal, deleted pass.</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Verify cancellation voids the pass and it dies on-device.</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Dashboard QR fallback + 'resend my pass' button.</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Nothing should scan at the door after membership ends.</t>
+          <t>Assume bad connectivity at the door.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="35.05" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Give members a QR backup if their pass fails</t>
+          <t>Complete Google Wallet passes</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Door failure modes: dead battery, no signal, deleted pass.</t>
+          <t>Bring Google Wallet to parity with Apple (generate/deliver/update); the scaffold is partial.</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Dashboard QR fallback + 'resend my pass' button.</t>
+          <t>Finish Google Wallet generation + delivery + update.</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -1965,24 +1965,24 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Assume bad connectivity at the door.</t>
+          <t>Scaffold is partial; bring to parity with Apple.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="35.05" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Complete Google Wallet passes</t>
+          <t>Apple Wallet push notifications + email attachment</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Bring Google Wallet to parity with Apple (generate/deliver/update); the scaffold is partial.</t>
+          <t>Push on changes + pass-as-email-attachment.</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Finish Google Wallet generation + delivery + update.</t>
+          <t>APNs push + email attachment.</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -1992,89 +1992,89 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Scaffold is partial; bring to parity with Apple.</t>
+          <t>After pass voiding is working.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="35.05" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Apple Wallet push notifications + email attachment</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Push on changes + pass-as-email-attachment.</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>APNs push + email attachment.</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>After pass voiding is working.</t>
-        </is>
-      </c>
+      <c r="A57" s="35" t="inlineStr">
+        <is>
+          <t>AMBASSADORS   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="31" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="35" t="inlineStr">
-        <is>
-          <t>AMBASSADORS   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="n"/>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Verify the referral price applies at checkout</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Confirm the $35 ambassador-referred social price applies via a referral link (vs $49).</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Confirm referral checkout shows $35.</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Checks the $35 referral price vs the standard $49.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="21.75" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Verify the referral price applies at checkout</t>
+          <t>Build the manual payout queue UI</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Confirm the $35 ambassador-referred social price applies via a referral link (vs $49).</t>
+          <t>An admin UI to review and release ambassador payouts.</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Confirm referral checkout shows $35.</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
+          <t>Payout queue UI for admins.</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Checks the $35 referral price vs the standard $49.</t>
+          <t>Where an admin reviews and releases payouts.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="23.85" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Build the manual payout queue UI</t>
+          <t>Ambassador leaderboard</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>An admin UI to review and release ambassador payouts.</t>
+          <t>A leaderboard ranking ambassadors by referrals.</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Payout queue UI for admins.</t>
+          <t>Ambassador leaderboard.</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -2084,24 +2084,24 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Where an admin reviews and releases payouts.</t>
+          <t>Ranks ambassadors by referrals.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Ambassador leaderboard</t>
+          <t>Read-only ambassador tab</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A leaderboard ranking ambassadors by referrals.</t>
+          <t>A view-only tab for ambassadors to see their own referral activity.</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Ambassador leaderboard.</t>
+          <t>View-only ambassador tab.</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -2111,24 +2111,24 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Ranks ambassadors by referrals.</t>
+          <t>Ambassadors see only their own activity.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21.75" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Read-only ambassador tab</t>
+          <t>Unified admin users view (members + ambassadors)</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A view-only tab for ambassadors to see their own referral activity.</t>
+          <t>One admin view combining members and ambassadors.</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>View-only ambassador tab.</t>
+          <t>/admin/users unified view.</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -2138,127 +2138,127 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Ambassadors see only their own activity.</t>
+          <t>Combines members + ambassadors in one admin view.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="23.85" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Unified admin users view (members + ambassadors)</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>One admin view combining members and ambassadors.</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>/admin/users unified view.</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Combines members + ambassadors in one admin view.</t>
-        </is>
-      </c>
+      <c r="A63" s="35" t="inlineStr">
+        <is>
+          <t>MEMBER TEXTING   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="n"/>
+      <c r="C63" s="31" t="n"/>
+      <c r="D63" s="31" t="n"/>
+      <c r="E63" s="31" t="n"/>
     </row>
     <row r="64" ht="23.85" customHeight="1">
-      <c r="A64" s="35" t="inlineStr">
-        <is>
-          <t>MEMBER TEXTING   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n"/>
-      <c r="C64" s="31" t="n"/>
-      <c r="D64" s="31" t="n"/>
-      <c r="E64" s="31" t="n"/>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Confirm we're cleared to send texts (Twilio A2P 10DLC)</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Records conflict on whether A2P 10DLC is approved; one call to Twilio settles it. Gates all texting.</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Confirm A2P 10DLC status directly with Twilio; assign an owner + date.</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Nothing SMS ships until this is confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="23.85" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Confirm we're cleared to send texts (Twilio A2P 10DLC)</t>
+          <t>Build the portal-baked texting inbox (Charlotte number, shared, consent + STOP)</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Records conflict on whether A2P 10DLC is approved; one call to Twilio settles it. Gates all texting.</t>
+          <t>All member texting runs through ONE Charlotte-based Twilio number wired into the admin portal — no managed third-party tool, and no text ever reaches a personal phone. Inbound messages hit a webhook, write to our database, and appear in a shared team inbox where every co-founder can read and reply; replies send from the club number. Consent and STOP are enforced and stored on the canonical person record.</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Confirm A2P 10DLC status directly with Twilio; assign an owner + date.</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="inlineStr">
+          <t>Twilio number -&gt; inbound webhook (Edge Function) -&gt; DB -&gt; portal Messages inbox (threads per member) -&gt; reply sends from the club number. Enforce consent + instant STOP; log idempotently before send; dedup in one shared send function. Inbound triggers an alert (email + the in-portal notification bell). Standard outbound: welcome, Monday digest, day-before reminders, week-1/2 nudges. Layer 1 only — no AI agent. Burn in 5-7 days.</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>HARD REQUIREMENT: nothing lands on a personal cell; fully transparent + team-managed. Gated on the A2P confirmation, the phone-storage model, and the identity foundation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="23.85" customHeight="1">
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t>SECURITY   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="n"/>
+      <c r="C66" s="31" t="n"/>
+      <c r="D66" s="31" t="n"/>
+      <c r="E66" s="31" t="n"/>
+    </row>
+    <row r="67" ht="23.85" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Rotate the shared admin password before the developer starts</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>The super-admin password was shared in working sessions; rotate it before any third-party developer gets repo/dashboard access.</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Rotate super-admin + test-account credentials before granting access (~10 min).</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>Nothing SMS ships until this is confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="23.85" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Build the portal-baked texting inbox (Charlotte number, shared, consent + STOP)</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>All member texting runs through ONE Charlotte-based Twilio number wired into the admin portal — no managed third-party tool, and no text ever reaches a personal phone. Inbound messages hit a webhook, write to our database, and appear in a shared team inbox where every co-founder can read and reply; replies send from the club number. Consent and STOP are enforced and stored on the canonical person record.</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>Twilio number -&gt; inbound webhook (Edge Function) -&gt; DB -&gt; portal Messages inbox (threads per member) -&gt; reply sends from the club number. Enforce consent + instant STOP; log idempotently before send; dedup in one shared send function. Inbound triggers an alert (email + the in-portal notification bell). Standard outbound: welcome, Monday digest, day-before reminders, week-1/2 nudges. Layer 1 only — no AI agent. Burn in 5-7 days.</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>HARD REQUIREMENT: nothing lands on a personal cell; fully transparent + team-managed. Gated on the A2P confirmation, the phone-storage model, and the identity foundation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="23.85" customHeight="1">
-      <c r="A67" s="35" t="inlineStr">
-        <is>
-          <t>SECURITY   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="n"/>
-      <c r="C67" s="31" t="n"/>
-      <c r="D67" s="31" t="n"/>
-      <c r="E67" s="31" t="n"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Owner task — a prerequisite before onboarding the developer.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Rotate the shared admin password before the developer starts</t>
+          <t>Rotate and remove secrets committed to the code</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>The super-admin password was shared in working sessions; rotate it before any third-party developer gets repo/dashboard access.</t>
+          <t>Live GroupMe join tokens were committed to git history; the file was deleted but the tokens stay readable until rotated.</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Rotate super-admin + test-account credentials before granting access (~10 min).</t>
+          <t>Rotate the exposed tokens (rotate-only, no history rewrite).</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
@@ -2268,62 +2268,62 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Owner task — a prerequisite before onboarding the developer.</t>
+          <t>Rotate so the committed copies become useless; no history rewrite.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="23.85" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>Rotate and remove secrets committed to the code</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Live GroupMe join tokens were committed to git history; the file was deleted but the tokens stay readable until rotated.</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>Rotate the exposed tokens (rotate-only, no history rewrite).</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>Blocker</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>Rotate so the committed copies become useless; no history rewrite.</t>
-        </is>
-      </c>
+      <c r="A69" s="35" t="inlineStr">
+        <is>
+          <t>SECURITY &amp; MONITORING   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n"/>
+      <c r="C69" s="31" t="n"/>
+      <c r="D69" s="31" t="n"/>
+      <c r="E69" s="31" t="n"/>
     </row>
     <row r="70" ht="23.85" customHeight="1">
-      <c r="A70" s="35" t="inlineStr">
-        <is>
-          <t>SECURITY &amp; MONITORING   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n"/>
-      <c r="C70" s="31" t="n"/>
-      <c r="D70" s="31" t="n"/>
-      <c r="E70" s="31" t="n"/>
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>send-email service-role auth: replace SB_SECRET_KEY duplicate with verified getClaims check</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>On 2026-08-12 the sb_secret_ prefix grant and the unverified-JWT-payload grant were removed from send-email and ambassador-payout (both were forgeable). That broke every restricted-template send on prod for about 10 minutes, because the app's legacy eyJ service-role JWT does NOT equal the SUPABASE_SERVICE_ROLE_KEY the function runtime sees - it had been passing via the unverified decode all along. Mitigated by setting SB_SECRET_KEY on prod to the same legacy JWT the app sends, restoring an exact match. That works but stores one credential under two names.</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Replace the SB_SECRET_KEY exact-match branch with supabase.auth.getClaims(token) plus a claims.role === 'service_role' check. getClaims verifies the signature, so it is not forgeable, unlike the removed base64 decode. Confirm a user-scoped token can never surface role service_role in verified claims before relying on it. Then delete the SB_SECRET_KEY secret from prod. CRITICAL: test with the REAL prod service-role key against PROD before deploying - develop cannot catch this class of bug because develop's key is the new sb_secret_ format which the gateway rejects outright. Restricted templates affected if this breaks again: password-setup, welcome-new, welcome-back, welcome-setup, guest-pass, admin-invite, public-rsvp-confirmation and 22 others.</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>Raised 2026-08-12 after causing and resolving a live 10-minute prod outage on restricted-template email. Prod currently healthy via SB_SECRET_KEY. Verified: Vercel prod and .env.local hold the same 219-char legacy JWT.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>send-email service-role auth: replace SB_SECRET_KEY duplicate with verified getClaims check</t>
+          <t>Dead trigger: last_attended_at never updates from public check-ins</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>On 2026-08-12 the sb_secret_ prefix grant and the unverified-JWT-payload grant were removed from send-email and ambassador-payout (both were forgeable). That broke every restricted-template send on prod for about 10 minutes, because the app's legacy eyJ service-role JWT does NOT equal the SUPABASE_SERVICE_ROLE_KEY the function runtime sees - it had been passing via the unverified decode all along. Mitigated by setting SB_SECRET_KEY on prod to the same legacy JWT the app sends, restoring an exact match. That works but stores one credential under two names.</t>
+          <t>The trigger trg_update_last_attended_from_public_rsvp fires on event_public_rsvps check-in and is meant to stamp profiles.last_attended_at. It looks up contacts.converted_to_member_id first, and NO code anywhere writes that column (0 of 207 rows on prod have it set), so the trigger always exits early. Members who check in through the public RSVP path never get their last-attended date updated.</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Replace the SB_SECRET_KEY exact-match branch with supabase.auth.getClaims(token) plus a claims.role === 'service_role' check. getClaims verifies the signature, so it is not forgeable, unlike the removed base64 decode. Confirm a user-scoped token can never surface role service_role in verified claims before relying on it. Then delete the SB_SECRET_KEY secret from prod. CRITICAL: test with the REAL prod service-role key against PROD before deploying - develop cannot catch this class of bug because develop's key is the new sb_secret_ format which the gateway rejects outright. Restricted templates affected if this breaks again: password-setup, welcome-new, welcome-back, welcome-setup, guest-pass, admin-invite, public-rsvp-confirmation and 22 others.</t>
+          <t>Two options. Either populate contacts.converted_to_member_id when a contact becomes a member (a real CRM flow that does not currently exist), or rewrite the trigger to resolve the profile by email or through the people bridge instead of the dead column. The second is far smaller. Note the conversion-rate report widget that depended on the same column was removed on 2026-08-12 because it always rendered 0 percent.</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -2333,78 +2333,78 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Raised 2026-08-12 after causing and resolving a live 10-minute prod outage on restricted-template email. Prod currently healthy via SB_SECRET_KEY. Verified: Vercel prod and .env.local hold the same 219-char legacy JWT.</t>
+          <t>Raised 2026-08-12 during a contacts table audit. Fails safe - does nothing rather than something wrong.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="46.25" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Dead trigger: last_attended_at never updates from public check-ins</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>The trigger trg_update_last_attended_from_public_rsvp fires on event_public_rsvps check-in and is meant to stamp profiles.last_attended_at. It looks up contacts.converted_to_member_id first, and NO code anywhere writes that column (0 of 207 rows on prod have it set), so the trigger always exits early. Members who check in through the public RSVP path never get their last-attended date updated.</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>Two options. Either populate contacts.converted_to_member_id when a contact becomes a member (a real CRM flow that does not currently exist), or rewrite the trigger to resolve the profile by email or through the people bridge instead of the dead column. The second is far smaller. Note the conversion-rate report widget that depended on the same column was removed on 2026-08-12 because it always rendered 0 percent.</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>Raised 2026-08-12 during a contacts table audit. Fails safe - does nothing rather than something wrong.</t>
+          <t>Add a deploy pipeline so changes go live safely</t>
+        </is>
+      </c>
+      <c r="B72" s="36" t="inlineStr">
+        <is>
+          <t>DB/function changes are pushed by hand today — the root cause of code/live drift. Locked: hand-patching stops once this lands (with a written emergency lane).</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="inlineStr">
+        <is>
+          <t>GitHub Actions: merge to main -&gt; db push + functions deploy. Needs 3 repo secrets.</t>
+        </is>
+      </c>
+      <c r="D72" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E72" s="36" t="inlineStr">
+        <is>
+          <t>Once in, hand-patching stops; needed before two people touch production in parallel.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21.75" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Add a deploy pipeline so changes go live safely</t>
-        </is>
-      </c>
-      <c r="B73" s="36" t="inlineStr">
-        <is>
-          <t>DB/function changes are pushed by hand today — the root cause of code/live drift. Locked: hand-patching stops once this lands (with a written emergency lane).</t>
-        </is>
-      </c>
-      <c r="C73" s="36" t="inlineStr">
-        <is>
-          <t>GitHub Actions: merge to main -&gt; db push + functions deploy. Needs 3 repo secrets.</t>
-        </is>
-      </c>
-      <c r="D73" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E73" s="36" t="inlineStr">
-        <is>
-          <t>Once in, hand-patching stops; needed before two people touch production in parallel.</t>
+          <t>Make the code able to rebuild the live database</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Several live DB objects were made by hand and aren't in migration history, so the repo can't recreate prod.</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Snapshot prod schema, diff vs migrations, commit a baseline migration.</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Absorbs recent hand-made objects (RSVP backfill, a few functions, the unsubscribe function).</t>
         </is>
       </c>
     </row>
     <row r="74" ht="23.85" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Make the code able to rebuild the live database</t>
+          <t>Add three safety tests on the things that can't break</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Several live DB objects were made by hand and aren't in migration history, so the repo can't recreate prod.</t>
+          <t>Effectively no automated testing exists.</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Snapshot prod schema, diff vs migrations, commit a baseline migration.</t>
+          <t>Three critical-path tests — (1) checkout -&gt; webhook -&gt; activated, (2) RSVP -&gt; attendance, (3) unsubscribe honored — and remove passWithNoTests so CI gates.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -2414,134 +2414,134 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Absorbs recent hand-made objects (RSVP backfill, a few functions, the unsubscribe function).</t>
+          <t>The three failures that hurt most; flips CI from passing with zero tests.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="68.65000000000001" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Add three safety tests on the things that can't break</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Effectively no automated testing exists.</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>Three critical-path tests — (1) checkout -&gt; webhook -&gt; activated, (2) RSVP -&gt; attendance, (3) unsubscribe honored — and remove passWithNoTests so CI gates.</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>The three failures that hurt most; flips CI from passing with zero tests.</t>
-        </is>
-      </c>
+      <c r="A75" s="35" t="inlineStr">
+        <is>
+          <t>EMAIL &amp; COMPLIANCE   ·   3 items</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n"/>
+      <c r="C75" s="31" t="n"/>
+      <c r="D75" s="31" t="n"/>
+      <c r="E75" s="31" t="n"/>
     </row>
     <row r="76" ht="57.45" customHeight="1">
-      <c r="A76" s="35" t="inlineStr">
-        <is>
-          <t>EMAIL &amp; COMPLIANCE   ·   3 items</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n"/>
-      <c r="C76" s="31" t="n"/>
-      <c r="D76" s="31" t="n"/>
-      <c r="E76" s="31" t="n"/>
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Make every email sender respect unsubscribes</t>
+        </is>
+      </c>
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>The unsubscribe page/link policy is fixed, but two senders (drip processor, renewal reminders) still don't check the opt-out flag, and one reminder may skip members on a null value.</t>
+        </is>
+      </c>
+      <c r="C76" s="36" t="inlineStr">
+        <is>
+          <t>Add opt-out filtering to process-drips + renewal-reminders; fix event-reminder null handling. One opt-out flag is the source of truth.</t>
+        </is>
+      </c>
+      <c r="D76" s="36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E76" s="36" t="inlineStr">
+        <is>
+          <t>send-email unsubscribe-block work is in flight; process-drips + renewal-reminders filtering to confirm/finish.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="23.85" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Make every email sender respect unsubscribes</t>
-        </is>
-      </c>
-      <c r="B77" s="36" t="inlineStr">
-        <is>
-          <t>The unsubscribe page/link policy is fixed, but two senders (drip processor, renewal reminders) still don't check the opt-out flag, and one reminder may skip members on a null value.</t>
-        </is>
-      </c>
-      <c r="C77" s="36" t="inlineStr">
-        <is>
-          <t>Add opt-out filtering to process-drips + renewal-reminders; fix event-reminder null handling. One opt-out flag is the source of truth.</t>
-        </is>
-      </c>
-      <c r="D77" s="36" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E77" s="36" t="inlineStr">
-        <is>
-          <t>send-email unsubscribe-block work is in flight; process-drips + renewal-reminders filtering to confirm/finish.</t>
+          <t>Make unsubscribe links forgery-proof</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>The unsubscribe token is currently guessable/forgeable (low stakes).</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>HMAC-sign the token; align format across send-campaign, send-email, and unsubscribe.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Align the token format across the three places that generate/read it.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="23.85" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Make unsubscribe links forgery-proof</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>The unsubscribe token is currently guessable/forgeable (low stakes).</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>HMAC-sign the token; align format across send-campaign, send-email, and unsubscribe.</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>Align the token format across the three places that generate/read it.</t>
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Remove unsubscribe links from ALL emails; members cannot unsubscribe (manual-only)</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>Remove unsubscribe links from ALL emails; members cannot unsubscribe (manual-only)</t>
-        </is>
-      </c>
+      <c r="A79" s="35" t="inlineStr">
+        <is>
+          <t>ADMIN &amp; OPERATIONS   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n"/>
+      <c r="C79" s="31" t="n"/>
+      <c r="D79" s="31" t="n"/>
+      <c r="E79" s="31" t="n"/>
     </row>
     <row r="80" ht="23.85" customHeight="1">
-      <c r="A80" s="35" t="inlineStr">
-        <is>
-          <t>ADMIN &amp; OPERATIONS   ·   9 items</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="n"/>
-      <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
-      <c r="E80" s="31" t="n"/>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Add a private notes section on each member</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Internal request: a notes area per member for context (e.g. 'comped through August').</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Read: admin + super-admin. Write/edit: super-admin only. Not member-visible.</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Internal-only; super-admin writes, admins read, members never see it.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Add a private notes section on each member</t>
+          <t>Build the admin health dashboard</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Internal request: a notes area per member for context (e.g. 'comped through August').</t>
+          <t>One screen showing system health at a glance; catches silent failures before members do.</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Read: admin + super-admin. Write/edit: super-admin only. Not member-visible.</t>
+          <t>5 widgets — cron, webhooks, drip health, email tracking, payment sync. Sits on /api/health.</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -2551,24 +2551,24 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Internal-only; super-admin writes, admins read, members never see it.</t>
+          <t>Reads /api/health + checks; surfaces silent failures.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="23.85" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Build the admin health dashboard</t>
+          <t>Let admins change a member's tier and have billing follow</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>One screen showing system health at a glance; catches silent failures before members do.</t>
+          <t>App-side tier change/comp exists; the Stripe billing side doesn't follow.</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>5 widgets — cron, webhooks, drip health, email tracking, payment sync. Sits on /api/health.</t>
+          <t>Wire admin tier-change to Stripe subscription cancel/modify/start.</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -2578,24 +2578,24 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Reads /api/health + checks; surfaces silent failures.</t>
+          <t>App-side override already exists; this is the Stripe billing reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="21.75" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Let admins change a member's tier and have billing follow</t>
+          <t>Harden the admin cancel-subscription flow</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>App-side tier change/comp exists; the Stripe billing side doesn't follow.</t>
+          <t>Make admin cancel safe (running twice shouldn't double-act).</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Wire admin tier-change to Stripe subscription cancel/modify/start.</t>
+          <t>Add idempotency + structured logging + alert to admin-cancel-subscription.</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -2605,78 +2605,78 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>App-side override already exists; this is the Stripe billing reconciliation.</t>
+          <t>Idempotent + logged + alerted so a double-run can't double-act.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="23.85" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Harden the admin cancel-subscription flow</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Make admin cancel safe (running twice shouldn't double-act).</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>Add idempotency + structured logging + alert to admin-cancel-subscription.</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>Idempotent + logged + alerted so a double-run can't double-act.</t>
+          <t>Build the admin area into clean sections</t>
+        </is>
+      </c>
+      <c r="B84" s="36" t="inlineStr">
+        <is>
+          <t>Reorganize admin into Today / People / Events / Network / Money / Messages / Settings with one source of truth per question.</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="inlineStr">
+        <is>
+          <t>7-section IA; folds in nav cleanup, per-event check-in start, financial accuracy, tier tools, and guest upload.</t>
+        </is>
+      </c>
+      <c r="D84" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E84" s="36" t="inlineStr">
+        <is>
+          <t>The Messages section is where the texting inbox lives.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="23.85" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Build the admin area into clean sections</t>
-        </is>
-      </c>
-      <c r="B85" s="36" t="inlineStr">
-        <is>
-          <t>Reorganize admin into Today / People / Events / Network / Money / Messages / Settings with one source of truth per question.</t>
-        </is>
-      </c>
-      <c r="C85" s="36" t="inlineStr">
-        <is>
-          <t>7-section IA; folds in nav cleanup, per-event check-in start, financial accuracy, tier tools, and guest upload.</t>
-        </is>
-      </c>
-      <c r="D85" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E85" s="36" t="inlineStr">
-        <is>
-          <t>The Messages section is where the texting inbox lives.</t>
+          <t>Shared admin navigation config</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>One shared config for admin nav so it's consistent and not duplicated.</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Single adminNav config; remove duplicated nav definitions.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>One config; removes duplicated nav definitions.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="23.85" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Shared admin navigation config</t>
+          <t>Guest list upload tool</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>One shared config for admin nav so it's consistent and not duplicated.</t>
+          <t>Let admins upload a guest list for an event.</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Single adminNav config; remove duplicated nav definitions.</t>
+          <t>Guest list upload UI.</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -2686,116 +2686,116 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>One config; removes duplicated nav definitions.</t>
+          <t>Also unblocks future guest-conversion automation.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Guest list upload tool</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Let admins upload a guest list for an event.</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>Guest list upload UI.</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>Also unblocks future guest-conversion automation.</t>
+          <t>Fix the organization settings table</t>
+        </is>
+      </c>
+      <c r="B87" s="37" t="inlineStr">
+        <is>
+          <t>organization_settings has the wrong schema.</t>
+        </is>
+      </c>
+      <c r="C87" s="37" t="inlineStr">
+        <is>
+          <t>Correct the organization_settings schema.</t>
+        </is>
+      </c>
+      <c r="D87" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E87" s="38" t="inlineStr">
+        <is>
+          <t>Schema is currently wrong; correct it.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="23.85" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Fix the organization settings table</t>
-        </is>
-      </c>
-      <c r="B88" s="37" t="inlineStr">
-        <is>
-          <t>organization_settings has the wrong schema.</t>
-        </is>
-      </c>
-      <c r="C88" s="37" t="inlineStr">
-        <is>
-          <t>Correct the organization_settings schema.</t>
-        </is>
-      </c>
-      <c r="D88" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E88" s="38" t="inlineStr">
-        <is>
-          <t>Schema is currently wrong; correct it.</t>
+          <t>Route Stripe receipts to the team inbox</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Receipt/invoice emails should also go to hello@704collective.com.</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Stripe email settings -&gt; CC hello@ (or a forwarding rule).</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>CC hello@ on Stripe receipts, or add a forwarding rule.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21.75" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Route Stripe receipts to the team inbox</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Receipt/invoice emails should also go to hello@704collective.com.</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>Stripe email settings -&gt; CC hello@ (or a forwarding rule).</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>CC hello@ on Stripe receipts, or add a forwarding rule.</t>
-        </is>
-      </c>
+      <c r="A89" s="35" t="inlineStr">
+        <is>
+          <t>MEMBER EXPERIENCE   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="n"/>
+      <c r="C89" s="31" t="n"/>
+      <c r="D89" s="31" t="n"/>
+      <c r="E89" s="31" t="n"/>
     </row>
     <row r="90" ht="23.85" customHeight="1">
-      <c r="A90" s="35" t="inlineStr">
-        <is>
-          <t>MEMBER EXPERIENCE   ·   9 items</t>
-        </is>
-      </c>
-      <c r="B90" s="31" t="n"/>
-      <c r="C90" s="31" t="n"/>
-      <c r="D90" s="31" t="n"/>
-      <c r="E90" s="31" t="n"/>
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Strip member profiles to four clean fields</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Simplify the profile to name, photo, what you do, and a one-line bio — as real columns, not JSON. Locked: archive the other 15+ fields (kept in DB, hidden) for future matchmaking.</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>4 visible fields as real columns; align onboarding + settings + directory. The 4-field data move rides with the identity foundation (same plumbing).</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Archive (don't delete) the rest — raw material for future matchmaking.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Strip member profiles to four clean fields</t>
+          <t>Build the one merged member portal with tiered views</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Simplify the profile to name, photo, what you do, and a one-line bio — as real columns, not JSON. Locked: archive the other 15+ fields (kept in DB, hidden) for future matchmaking.</t>
+          <t>Locked: replace the two portals (member dashboard + business portal) with ONE codebase; business gets an elevated view, social the standard view; clear type distinction preserved.</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>4 visible fields as real columns; align onboarding + settings + directory. The 4-field data move rides with the identity foundation (same plumbing).</t>
+          <t>One portal codebase; gate business-only modules behind member type. Replaces /dashboard vs /business-portal.</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Archive (don't delete) the rest — raw material for future matchmaking.</t>
+          <t>Replaces /dashboard vs /business-portal with one tier-gated codebase.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Build the one merged member portal with tiered views</t>
+          <t>Rebuild onboarding questionnaire + member brief</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Locked: replace the two portals (member dashboard + business portal) with ONE codebase; business gets an elevated view, social the standard view; clear type distinction preserved.</t>
+          <t>Store responses in their own table and generate a 'member brief' for future matchmaking/AI.</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>One portal codebase; gate business-only modules behind member type. Replaces /dashboard vs /business-portal.</t>
+          <t>Onboarding rebuild + onboarding_responses table + member_brief column.</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Replaces /dashboard vs /business-portal with one tier-gated codebase.</t>
+          <t>Responses in their own table; feeds a future member brief.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Rebuild onboarding questionnaire + member brief</t>
+          <t>Member portal / dashboard redesign</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Store responses in their own table and generate a 'member brief' for future matchmaking/AI.</t>
+          <t>The redesign: 5-tab bottom nav, pass-first / next-event hero, onboarding checklist removed after completion, plus resources/bookings tabs. The shared activity feed is KEPT and built on (members post / share / like; event discussions surface there) — only the minor personal activity-log widget from the old dashboard is retired.</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Onboarding rebuild + onboarding_responses table + member_brief column.</t>
+          <t>Multi-week. SEQUENCING: the visual redesign lands AFTER the identity foundation is built and verified — not concurrent with it (one big change at a time on a no-staging system). Resources/bookings depend on vendor partnerships.</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -2859,78 +2859,78 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Responses in their own table; feeds a future member brief.</t>
+          <t>Activity feed stays; only the personal activity-log widget is retired. Visual redesign sequenced after identity.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Member portal / dashboard redesign</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>The redesign: 5-tab bottom nav, pass-first / next-event hero, onboarding checklist removed after completion, plus resources/bookings tabs. The shared activity feed is KEPT and built on (members post / share / like; event discussions surface there) — only the minor personal activity-log widget from the old dashboard is retired.</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>Multi-week. SEQUENCING: the visual redesign lands AFTER the identity foundation is built and verified — not concurrent with it (one big change at a time on a no-staging system). Resources/bookings depend on vendor partnerships.</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>Activity feed stays; only the personal activity-log widget is retired. Visual redesign sequenced after identity.</t>
+          <t>Member directory — people-finder for all member + partner types</t>
+        </is>
+      </c>
+      <c r="B94" s="36" t="inlineStr">
+        <is>
+          <t>A members-only people-finder where social members, business members, and partners can all find and see each other — profiles only, WITHOUT the business-listings view. Visible to everyone logged in, regardless of type. A privacy toggle lets a member hide from it.</t>
+        </is>
+      </c>
+      <c r="C94" s="36" t="inlineStr">
+        <is>
+          <t>Logged-in directory of people (social + business + partner). Profiles only — no business view (that lives in The Network). Visible to all logged-in types; honor the privacy toggle.</t>
+        </is>
+      </c>
+      <c r="D94" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E94" s="36" t="inlineStr">
+        <is>
+          <t>Distinct from The Network (hubs + business/partner listings). Pairs with the privacy toggle below.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Member directory — people-finder for all member + partner types</t>
-        </is>
-      </c>
-      <c r="B95" s="36" t="inlineStr">
-        <is>
-          <t>A members-only people-finder where social members, business members, and partners can all find and see each other — profiles only, WITHOUT the business-listings view. Visible to everyone logged in, regardless of type. A privacy toggle lets a member hide from it.</t>
-        </is>
-      </c>
-      <c r="C95" s="36" t="inlineStr">
-        <is>
-          <t>Logged-in directory of people (social + business + partner). Profiles only — no business view (that lives in The Network). Visible to all logged-in types; honor the privacy toggle.</t>
-        </is>
-      </c>
-      <c r="D95" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E95" s="36" t="inlineStr">
-        <is>
-          <t>Distinct from The Network (hubs + business/partner listings). Pairs with the privacy toggle below.</t>
+          <t>Profile privacy toggle</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>A toggle for members to control whether they appear in the directory and the internal Network member view.</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Build the opt-out toggle; default is listed, members can hide themselves.</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed feature — the directory is opt-out via this toggle.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21.75" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Profile privacy toggle</t>
+          <t>Member cancellation retention flow</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>A toggle for members to control whether they appear in the directory and the internal Network member view.</t>
+          <t>Improve the cancellation flow with retention UX.</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Build the opt-out toggle; default is listed, members can hide themselves.</t>
+          <t>Retention UX on cancellation (offers, pauses, feedback).</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -2940,127 +2940,127 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Confirmed feature — the directory is opt-out via this toggle.</t>
+          <t>Offers / pauses / feedback on cancellation.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="23.85" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Member cancellation retention flow</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Improve the cancellation flow with retention UX.</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>Retention UX on cancellation (offers, pauses, feedback).</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>Offers / pauses / feedback on cancellation.</t>
+          <t>Member spotlight on calendar/home</t>
+        </is>
+      </c>
+      <c r="B97" s="37" t="inlineStr">
+        <is>
+          <t>Feature a member spotlight on the calendar/home pages.</t>
+        </is>
+      </c>
+      <c r="C97" s="37" t="inlineStr">
+        <is>
+          <t>Member spotlight feature.</t>
+        </is>
+      </c>
+      <c r="D97" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E97" s="38" t="inlineStr">
+        <is>
+          <t>Feature a member on calendar/home.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21.75" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Member spotlight on calendar/home</t>
-        </is>
-      </c>
-      <c r="B98" s="37" t="inlineStr">
-        <is>
-          <t>Feature a member spotlight on the calendar/home pages.</t>
-        </is>
-      </c>
-      <c r="C98" s="37" t="inlineStr">
-        <is>
-          <t>Member spotlight feature.</t>
-        </is>
-      </c>
-      <c r="D98" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E98" s="38" t="inlineStr">
-        <is>
-          <t>Feature a member on calendar/home.</t>
-        </is>
-      </c>
+          <t>Unlimited guest passes for dream-team members</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="6" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>Unlimited guest passes for dream-team members</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="n"/>
-      <c r="E99" s="6" t="n"/>
+      <c r="A99" s="35" t="inlineStr">
+        <is>
+          <t>PERFORMANCE   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B99" s="31" t="n"/>
+      <c r="C99" s="31" t="n"/>
+      <c r="D99" s="31" t="n"/>
+      <c r="E99" s="31" t="n"/>
     </row>
     <row r="100" ht="23.85" customHeight="1">
-      <c r="A100" s="35" t="inlineStr">
-        <is>
-          <t>PERFORMANCE   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B100" s="31" t="n"/>
-      <c r="C100" s="31" t="n"/>
-      <c r="D100" s="31" t="n"/>
-      <c r="E100" s="31" t="n"/>
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>Speed up slow list pages (Events, Tasks, Hubs)</t>
+        </is>
+      </c>
+      <c r="B100" s="36" t="inlineStr">
+        <is>
+          <t>These pages make many small repeated DB calls (N+1) that get slow as data grows.</t>
+        </is>
+      </c>
+      <c r="C100" s="36" t="inlineStr">
+        <is>
+          <t>Resolve the N+1 query patterns; batch them.</t>
+        </is>
+      </c>
+      <c r="D100" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E100" s="36" t="inlineStr">
+        <is>
+          <t>Batch the repeated calls on Events, Tasks, Hubs.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="23.85" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Speed up slow list pages (Events, Tasks, Hubs)</t>
-        </is>
-      </c>
-      <c r="B101" s="36" t="inlineStr">
-        <is>
-          <t>These pages make many small repeated DB calls (N+1) that get slow as data grows.</t>
-        </is>
-      </c>
-      <c r="C101" s="36" t="inlineStr">
-        <is>
-          <t>Resolve the N+1 query patterns; batch them.</t>
-        </is>
-      </c>
-      <c r="D101" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E101" s="36" t="inlineStr">
-        <is>
-          <t>Batch the repeated calls on Events, Tasks, Hubs.</t>
+          <t>Make bulk member adds all-or-nothing</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Bulk add isn't transactional — a partial failure leaves half-written data.</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Make add-members and hub-delete atomic.</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>All-or-nothing; same for hub deletes.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Make bulk member adds all-or-nothing</t>
+          <t>Move heavy admin queries to the server</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Bulk add isn't transactional — a partial failure leaves half-written data.</t>
+          <t>Keep the browser from doing heavy lifting on admin overview + email dashboard.</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Make add-members and hub-delete atomic.</t>
+          <t>Add server-side RPCs: admin_overview, email_dashboard.</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -3070,100 +3070,100 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>All-or-nothing; same for hub deletes.</t>
+          <t>Move admin overview + email dashboard to server RPCs.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Move heavy admin queries to the server</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Keep the browser from doing heavy lifting on admin overview + email dashboard.</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>Add server-side RPCs: admin_overview, email_dashboard.</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>Move admin overview + email dashboard to server RPCs.</t>
+          <t>Standardize how data is loaded (React Query)</t>
+        </is>
+      </c>
+      <c r="B103" s="37" t="inlineStr">
+        <is>
+          <t>Make loading behavior uniform and reliable.</t>
+        </is>
+      </c>
+      <c r="C103" s="37" t="inlineStr">
+        <is>
+          <t>React Query rollout across data fetching.</t>
+        </is>
+      </c>
+      <c r="D103" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E103" s="38" t="inlineStr">
+        <is>
+          <t>Uniform data-loading / caching across the app.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="23.85" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Standardize how data is loaded (React Query)</t>
-        </is>
-      </c>
-      <c r="B104" s="37" t="inlineStr">
-        <is>
-          <t>Make loading behavior uniform and reliable.</t>
-        </is>
-      </c>
-      <c r="C104" s="37" t="inlineStr">
-        <is>
-          <t>React Query rollout across data fetching.</t>
-        </is>
-      </c>
-      <c r="D104" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E104" s="38" t="inlineStr">
-        <is>
-          <t>Uniform data-loading / caching across the app.</t>
-        </is>
-      </c>
+          <t>Audit shortcut data fields for correctness</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="6" t="n"/>
     </row>
     <row r="105" ht="21.75" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>Audit shortcut data fields for correctness</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="6" t="n"/>
+      <c r="A105" s="35" t="inlineStr">
+        <is>
+          <t>AUTH   ·   7 items</t>
+        </is>
+      </c>
+      <c r="B105" s="31" t="n"/>
+      <c r="C105" s="31" t="n"/>
+      <c r="D105" s="31" t="n"/>
+      <c r="E105" s="31" t="n"/>
     </row>
     <row r="106" ht="23.85" customHeight="1">
-      <c r="A106" s="35" t="inlineStr">
-        <is>
-          <t>AUTH   ·   7 items</t>
-        </is>
-      </c>
-      <c r="B106" s="31" t="n"/>
-      <c r="C106" s="31" t="n"/>
-      <c r="D106" s="31" t="n"/>
-      <c r="E106" s="31" t="n"/>
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Verify magic-link login across two devices</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Phone-to-desktop: request a link on a phone, type the 8-digit code on the desktop.</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Cross-device OTP test; confirm same-device + resend cooldown too.</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Requires a second device (owner-run).</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Verify magic-link login across two devices</t>
+          <t>Verify magic-link login works in production</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Phone-to-desktop: request a link on a phone, type the 8-digit code on the desktop.</t>
+          <t>End-to-end check the email magic-link round-trip works live.</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Cross-device OTP test; confirm same-device + resend cooldown too.</t>
+          <t>Test request -&gt; click -&gt; signed in, in prod.</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
@@ -3173,241 +3173,241 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Requires a second device (owner-run).</t>
+          <t>End-to-end live round-trip check.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="23.85" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Verify magic-link login works in production</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>End-to-end check the email magic-link round-trip works live.</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>Test request -&gt; click -&gt; signed in, in prod.</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="inlineStr">
+          <t>Verify sessions refresh correctly on expiry</t>
+        </is>
+      </c>
+      <c r="B108" s="36" t="inlineStr">
+        <is>
+          <t>Confirm cookie-based refresh works when a token expires so members aren't kicked out.</t>
+        </is>
+      </c>
+      <c r="C108" s="36" t="inlineStr">
+        <is>
+          <t>Verify @supabase/ssr middleware refreshes session on token expiry.</t>
+        </is>
+      </c>
+      <c r="D108" s="36" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>End-to-end live round-trip check.</t>
+      <c r="E108" s="36" t="inlineStr">
+        <is>
+          <t>Confirm members aren't kicked out when a token expires.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="23.85" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Verify sessions refresh correctly on expiry</t>
-        </is>
-      </c>
-      <c r="B109" s="36" t="inlineStr">
-        <is>
-          <t>Confirm cookie-based refresh works when a token expires so members aren't kicked out.</t>
-        </is>
-      </c>
-      <c r="C109" s="36" t="inlineStr">
-        <is>
-          <t>Verify @supabase/ssr middleware refreshes session on token expiry.</t>
-        </is>
-      </c>
-      <c r="D109" s="36" t="inlineStr">
+          <t>Verify Google sign-in works</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Confirm Google login/signup paths work in production.</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Test Google OAuth signup + sign-in.</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E109" s="36" t="inlineStr">
-        <is>
-          <t>Confirm members aren't kicked out when a token expires.</t>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>Confirm Google login/signup in production.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="23.85" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>Verify Google sign-in works</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Confirm Google login/signup paths work in production.</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>Test Google OAuth signup + sign-in.</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>Confirm Google login/signup in production.</t>
+          <t>Apple Sign-In</t>
         </is>
       </c>
     </row>
     <row r="111" ht="23.85" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Apple Sign-In</t>
-        </is>
-      </c>
+          <t>Branded auth links (stop showing supabase.co URLs)</t>
+        </is>
+      </c>
+      <c r="B111" s="29" t="n"/>
+      <c r="C111" s="29" t="n"/>
+      <c r="D111" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E111" s="30" t="n"/>
     </row>
     <row r="112" ht="23.85" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Branded auth links (stop showing supabase.co URLs)</t>
-        </is>
-      </c>
-      <c r="B112" s="29" t="n"/>
-      <c r="C112" s="29" t="n"/>
-      <c r="D112" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E112" s="30" t="n"/>
+          <t>Password rules hardening (min length 6 to 8, leaked-password check)</t>
+        </is>
+      </c>
+      <c r="B112" s="39" t="inlineStr">
+        <is>
+          <t>Supabase minimum password length is 6 and the leaked-password check is off. Both are weaker than they should be for a paid membership platform.</t>
+        </is>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>Do the UI copy FIRST, then the dashboard toggles. Update /setup-password and every password field to state the real rule before raising the server minimum to 8, otherwise members get rejected by a rule the screen never showed them. Then enable Prevent use of leaked passwords and confirm the rejection message renders cleanly. Leave Require current password when updating OFF, it breaks the no-password comp-invite setup flow. Rehearse on develop both viewports.</t>
+        </is>
+      </c>
+      <c r="D112" s="39" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E112" s="40" t="inlineStr">
+        <is>
+          <t>Raised 2026-08-06 during the Email OTP expiration change (3600 to 86400).</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>Password rules hardening (min length 6 to 8, leaked-password check)</t>
-        </is>
-      </c>
-      <c r="B113" s="39" t="inlineStr">
-        <is>
-          <t>Supabase minimum password length is 6 and the leaked-password check is off. Both are weaker than they should be for a paid membership platform.</t>
-        </is>
-      </c>
-      <c r="C113" s="39" t="inlineStr">
-        <is>
-          <t>Do the UI copy FIRST, then the dashboard toggles. Update /setup-password and every password field to state the real rule before raising the server minimum to 8, otherwise members get rejected by a rule the screen never showed them. Then enable Prevent use of leaked passwords and confirm the rejection message renders cleanly. Leave Require current password when updating OFF, it breaks the no-password comp-invite setup flow. Rehearse on develop both viewports.</t>
-        </is>
-      </c>
-      <c r="D113" s="39" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E113" s="40" t="inlineStr">
-        <is>
-          <t>Raised 2026-08-06 during the Email OTP expiration change (3600 to 86400).</t>
-        </is>
-      </c>
+      <c r="A113" s="35" t="inlineStr">
+        <is>
+          <t>BUSINESS   ·   1 item</t>
+        </is>
+      </c>
+      <c r="B113" s="31" t="n"/>
+      <c r="C113" s="31" t="n"/>
+      <c r="D113" s="31" t="n"/>
+      <c r="E113" s="31" t="n"/>
     </row>
     <row r="114" ht="23.85" customHeight="1">
-      <c r="A114" s="35" t="inlineStr">
-        <is>
-          <t>BUSINESS   ·   1 item</t>
-        </is>
-      </c>
-      <c r="B114" s="31" t="n"/>
-      <c r="C114" s="31" t="n"/>
-      <c r="D114" s="31" t="n"/>
-      <c r="E114" s="31" t="n"/>
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>Verify the business application approval works</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="6" t="n"/>
     </row>
     <row r="115" ht="46.25" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>Verify the business application approval works</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="6" t="n"/>
+      <c r="A115" s="35" t="inlineStr">
+        <is>
+          <t>FINANCIALS   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B115" s="31" t="n"/>
+      <c r="C115" s="31" t="n"/>
+      <c r="D115" s="31" t="n"/>
+      <c r="E115" s="31" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="35" t="inlineStr">
-        <is>
-          <t>FINANCIALS   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B116" s="31" t="n"/>
-      <c r="C116" s="31" t="n"/>
-      <c r="D116" s="31" t="n"/>
-      <c r="E116" s="31" t="n"/>
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Verify the financial dashboard</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Confirm it reports MRR, churn, and revenue by tier correctly (churn once showed 2055%).</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Verify financial dashboard accuracy.</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>Built in Lovable originally — accuracy unconfirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="23.85" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Verify the financial dashboard</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>Confirm it reports MRR, churn, and revenue by tier correctly (churn once showed 2055%).</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>Verify financial dashboard accuracy.</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
+          <t>Verify the admin financial data function</t>
+        </is>
+      </c>
+      <c r="B117" s="36" t="inlineStr">
+        <is>
+          <t>Confirm the edge function feeding admin financials returns correct numbers.</t>
+        </is>
+      </c>
+      <c r="C117" s="36" t="inlineStr">
+        <is>
+          <t>Verify admin-financial-data.</t>
+        </is>
+      </c>
+      <c r="D117" s="36" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>Built in Lovable originally — accuracy unconfirmed.</t>
+      <c r="E117" s="36" t="inlineStr">
+        <is>
+          <t>Confirm the numbers it returns are correct.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="23.85" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Verify the admin financial data function</t>
-        </is>
-      </c>
-      <c r="B118" s="36" t="inlineStr">
-        <is>
-          <t>Confirm the edge function feeding admin financials returns correct numbers.</t>
-        </is>
-      </c>
-      <c r="C118" s="36" t="inlineStr">
-        <is>
-          <t>Verify admin-financial-data.</t>
-        </is>
-      </c>
-      <c r="D118" s="36" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E118" s="36" t="inlineStr">
-        <is>
-          <t>Confirm the numbers it returns are correct.</t>
+          <t>Three-bucket revenue view</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Show revenue split three ways.</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Collected / projected / churned split.</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>Collected / projected / churned.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="21.75" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Three-bucket revenue view</t>
+          <t>Member-facing financial widget</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Show revenue split three ways.</t>
+          <t>A small financial widget members can see.</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Collected / projected / churned split.</t>
+          <t>Member-facing billing-status widget.</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -3417,89 +3417,89 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Collected / projected / churned.</t>
+          <t>Small billing-status widget for members.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="23.85" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Member-facing financial widget</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>A small financial widget members can see.</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>Member-facing billing-status widget.</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>Small billing-status widget for members.</t>
+          <t>Reduce redundant Stripe scans</t>
+        </is>
+      </c>
+      <c r="B120" s="37" t="inlineStr">
+        <is>
+          <t>Cut how often the system scans Stripe, for performance/cost.</t>
+        </is>
+      </c>
+      <c r="C120" s="37" t="inlineStr">
+        <is>
+          <t>Reduce Stripe API scan frequency.</t>
+        </is>
+      </c>
+      <c r="D120" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E120" s="38" t="inlineStr">
+        <is>
+          <t>Cut scan frequency for cost / performance.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="23.85" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>Reduce redundant Stripe scans</t>
-        </is>
-      </c>
-      <c r="B121" s="37" t="inlineStr">
-        <is>
-          <t>Cut how often the system scans Stripe, for performance/cost.</t>
-        </is>
-      </c>
-      <c r="C121" s="37" t="inlineStr">
-        <is>
-          <t>Reduce Stripe API scan frequency.</t>
-        </is>
-      </c>
-      <c r="D121" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E121" s="38" t="inlineStr">
-        <is>
-          <t>Cut scan frequency for cost / performance.</t>
-        </is>
-      </c>
+      <c r="A121" s="35" t="inlineStr">
+        <is>
+          <t>EMAIL &amp; DRIP   ·   13 items</t>
+        </is>
+      </c>
+      <c r="B121" s="31" t="n"/>
+      <c r="C121" s="31" t="n"/>
+      <c r="D121" s="31" t="n"/>
+      <c r="E121" s="31" t="n"/>
     </row>
     <row r="122" ht="23.85" customHeight="1">
-      <c r="A122" s="35" t="inlineStr">
-        <is>
-          <t>EMAIL &amp; DRIP   ·   13 items</t>
-        </is>
-      </c>
-      <c r="B122" s="31" t="n"/>
-      <c r="C122" s="31" t="n"/>
-      <c r="D122" s="31" t="n"/>
-      <c r="E122" s="31" t="n"/>
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Drip email health banner</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>A banner flagging when drips are silently failing or stalled.</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Drip health-check banner.</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>Flags silently failing / stalled drips.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Drip email health banner</t>
+          <t>Guest follow-up drip (7 + 20 day)</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>A banner flagging when drips are silently failing or stalled.</t>
+          <t>Automatic emails to guests at day 7 and 20 to convert them.</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Drip health-check banner.</t>
+          <t>Guest 7-day + 20-day drip.</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -3509,24 +3509,24 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Flags silently failing / stalled drips.</t>
+          <t>Converts guests at day 7 and 20.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="68.65000000000001" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Guest follow-up drip (7 + 20 day)</t>
+          <t>14-day RSVP prompt for new members</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Automatic emails to guests at day 7 and 20 to convert them.</t>
+          <t>Nudge new members who haven't RSVP'd within 14 days.</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Guest 7-day + 20-day drip.</t>
+          <t>14-day RSVP prompt drip.</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -3536,24 +3536,24 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Converts guests at day 7 and 20.</t>
+          <t>Nudges new members who haven't RSVP'd.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="23.85" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>14-day RSVP prompt for new members</t>
+          <t>Confirm the email log matches actual sends</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>Nudge new members who haven't RSVP'd within 14 days.</t>
+          <t>Today failures are swallowed; make 'did this send' provable.</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>14-day RSVP prompt drip.</t>
+          <t>email_log row matching; stop swallowing failures.</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -3563,24 +3563,24 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nudges new members who haven't RSVP'd.</t>
+          <t>Stop swallowing failures so 'did this send' is provable.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="21.75" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Confirm the email log matches actual sends</t>
+          <t>Per-email open/click analytics</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Today failures are swallowed; make 'did this send' provable.</t>
+          <t>Track opens/clicks per template so we know what works.</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>email_log row matching; stop swallowing failures.</t>
+          <t>Per-template email analytics.</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -3590,24 +3590,24 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Stop swallowing failures so 'did this send' is provable.</t>
+          <t>Per-template open / click tracking.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Per-email open/click analytics</t>
+          <t>Per-member engagement scoring</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>Track opens/clicks per template so we know what works.</t>
+          <t>Score each member's engagement from email/event activity.</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Per-template email analytics.</t>
+          <t>Engagement scoring per member.</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -3617,24 +3617,24 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Per-template open / click tracking.</t>
+          <t>Score members from email / event activity.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="23.85" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Per-member engagement scoring</t>
+          <t>Category-level unsubscribe preferences</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Score each member's engagement from email/event activity.</t>
+          <t>Let members opt out of specific categories, not all-or-nothing; builds on the one-flag fix.</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Engagement scoring per member.</t>
+          <t>Per-category opt-out prefs + a member settings page.</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -3644,24 +3644,24 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Score members from email / event activity.</t>
+          <t>Builds on the one-flag opt-out fix.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="23.85" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Category-level unsubscribe preferences</t>
+          <t>Branching drips based on opens/clicks</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>Let members opt out of specific categories, not all-or-nothing; builds on the one-flag fix.</t>
+          <t>Drip sequences that branch on open/click.</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Per-category opt-out prefs + a member settings page.</t>
+          <t>Open/click-branching drips.</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -3671,318 +3671,318 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Builds on the one-flag opt-out fix.</t>
+          <t>Branch sequences on open / click.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="35.05" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Branching drips based on opens/clicks</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>Drip sequences that branch on open/click.</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
-        <is>
-          <t>Open/click-branching drips.</t>
-        </is>
-      </c>
-      <c r="D130" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>Branch sequences on open / click.</t>
+          <t>Send email from a contact record</t>
+        </is>
+      </c>
+      <c r="B130" s="36" t="inlineStr">
+        <is>
+          <t>Let an admin email directly from a member/contact record.</t>
+        </is>
+      </c>
+      <c r="C130" s="36" t="inlineStr">
+        <is>
+          <t>Send-email action on the contact record.</t>
+        </is>
+      </c>
+      <c r="D130" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E130" s="36" t="inlineStr">
+        <is>
+          <t>Admin emails directly from a member record.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="35.05" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Send email from a contact record</t>
-        </is>
-      </c>
-      <c r="B131" s="36" t="inlineStr">
-        <is>
-          <t>Let an admin email directly from a member/contact record.</t>
-        </is>
-      </c>
-      <c r="C131" s="36" t="inlineStr">
-        <is>
-          <t>Send-email action on the contact record.</t>
-        </is>
-      </c>
-      <c r="D131" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E131" s="36" t="inlineStr">
-        <is>
-          <t>Admin emails directly from a member record.</t>
+          <t>Attachments and images on event email campaigns</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>Let campaign emails include attachments and images.</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Extend the campaign editor for attachments + images.</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>Extend the campaign editor.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="68.65000000000001" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Attachments and images on event email campaigns</t>
+          <t>Live test the guest-pass drip</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Let campaign emails include attachments and images.</t>
+          <t>Confirm the drip fires correctly on a guest pass.</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Extend the campaign editor for attachments + images.</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
+          <t>Live test the drip on guest_pass.</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Extend the campaign editor.</t>
+          <t>Confirm it fires on a guest pass.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="23.85" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Live test the guest-pass drip</t>
-        </is>
-      </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>Confirm the drip fires correctly on a guest pass.</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t>Live test the drip on guest_pass.</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E133" s="8" t="inlineStr">
-        <is>
-          <t>Confirm it fires on a guest pass.</t>
+          <t>Merge guest follow-up into the drip processor</t>
+        </is>
+      </c>
+      <c r="B133" s="37" t="inlineStr">
+        <is>
+          <t>Retire the separate guest-followup function and fold it into the main processor.</t>
+        </is>
+      </c>
+      <c r="C133" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate guest-followup into process-drips.</t>
+        </is>
+      </c>
+      <c r="D133" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E133" s="38" t="inlineStr">
+        <is>
+          <t>Fold guest-followup into process-drips.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Merge guest follow-up into the drip processor</t>
-        </is>
-      </c>
-      <c r="B134" s="37" t="inlineStr">
-        <is>
-          <t>Retire the separate guest-followup function and fold it into the main processor.</t>
-        </is>
-      </c>
-      <c r="C134" s="37" t="inlineStr">
-        <is>
-          <t>Consolidate guest-followup into process-drips.</t>
-        </is>
-      </c>
-      <c r="D134" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E134" s="38" t="inlineStr">
-        <is>
-          <t>Fold guest-followup into process-drips.</t>
-        </is>
-      </c>
+          <t>Push current members to subscribe to the calendar + add their pass</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="5" t="n"/>
+      <c r="D134" s="5" t="n"/>
+      <c r="E134" s="6" t="n"/>
     </row>
     <row r="135" ht="35.05" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>Push current members to subscribe to the calendar + add their pass</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="n"/>
-      <c r="C135" s="5" t="n"/>
-      <c r="D135" s="5" t="n"/>
-      <c r="E135" s="6" t="n"/>
+      <c r="A135" s="35" t="inlineStr">
+        <is>
+          <t>DATA &amp; CLEANUP   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B135" s="31" t="n"/>
+      <c r="C135" s="31" t="n"/>
+      <c r="D135" s="31" t="n"/>
+      <c r="E135" s="31" t="n"/>
     </row>
     <row r="136" ht="23.85" customHeight="1">
-      <c r="A136" s="35" t="inlineStr">
-        <is>
-          <t>DATA &amp; CLEANUP   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B136" s="31" t="n"/>
-      <c r="C136" s="31" t="n"/>
-      <c r="D136" s="31" t="n"/>
-      <c r="E136" s="31" t="n"/>
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>Add CHECK constraints incrementally (enums REJECTED — too risky)</t>
+        </is>
+      </c>
+      <c r="B136" s="36" t="inlineStr">
+        <is>
+          <t>Was 'convert status text -&gt; enums'. DIAGNOSED Jul 9 as too risky: ~35 tables / 60+ write paths, and profiles.subscription_status is fed by the Stripe webhook with Stripe's full status vocabulary (trialing/paused/incomplete/etc). An enum built from observed values would make the webhook UPDATE throw on the first unseen status — silent breakage in the PAYMENT path. Enums rejected.</t>
+        </is>
+      </c>
+      <c r="C136" s="36" t="inlineStr">
+        <is>
+          <t>If typo-prevention is wanted later: add per-table CHECK constraints (NOT enums), table-by-table, starting with attendance_credentials (values: active/used/voided). Trivially reversible. Its own scoped task — never wholesale.</t>
+        </is>
+      </c>
+      <c r="D136" s="36" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="E136" s="36" t="inlineStr">
+        <is>
+          <t>Reclassified Jul 9. Do NOT rush — payment-path risk. CHECK constraints are the safe 80/20 if revisited.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="21.75" customHeight="1">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t>Add CHECK constraints incrementally (enums REJECTED — too risky)</t>
-        </is>
-      </c>
-      <c r="B137" s="36" t="inlineStr">
-        <is>
-          <t>Was 'convert status text -&gt; enums'. DIAGNOSED Jul 9 as too risky: ~35 tables / 60+ write paths, and profiles.subscription_status is fed by the Stripe webhook with Stripe's full status vocabulary (trialing/paused/incomplete/etc). An enum built from observed values would make the webhook UPDATE throw on the first unseen status — silent breakage in the PAYMENT path. Enums rejected.</t>
-        </is>
-      </c>
-      <c r="C137" s="36" t="inlineStr">
-        <is>
-          <t>If typo-prevention is wanted later: add per-table CHECK constraints (NOT enums), table-by-table, starting with attendance_credentials (values: active/used/voided). Trivially reversible. Its own scoped task — never wholesale.</t>
-        </is>
-      </c>
-      <c r="D137" s="36" t="inlineStr">
-        <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="E137" s="36" t="inlineStr">
-        <is>
-          <t>Reclassified Jul 9. Do NOT rush — payment-path risk. CHECK constraints are the safe 80/20 if revisited.</t>
+          <t>RSVP attribution by event ID</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="inlineStr">
+        <is>
+          <t>DIAGNOSED Jul 9: bigger than 'add a column'. Per-event RSVP tagging is DEAD — the code that slug-tagged events was removed; since Apr 21 a public RSVP only gets a generic 'free-event-rsvp' tag, so you can't segment 'RSVP'd to event X' for any recent event. 6 frozen slug-tags remain (105 rows) and rot on rename. contact_tags has NO event_id column.</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="inlineStr">
+        <is>
+          <t>HALF-DAY scoped task (not a quick close): (1) migration add nullable event_id uuid REFERENCES events(id) to contact_tags; (2) re-add per-event tagging in capture-public-rsvp (event_id already in scope) + optionally create-guest-pass; (3) backfill — 5 of 6 slug-tags map to real event_ids by title-slug match (1 unmatched: coffee-and-connect-tabbris-co-working). Deploys + tests.</t>
+        </is>
+      </c>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E137" s="15" t="inlineStr">
+        <is>
+          <t>Jul 9: revives dead per-event attribution. Own task, budget a half-day. Backfill mostly possible.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="113.4" customHeight="1">
-      <c r="A138" s="17" t="inlineStr">
-        <is>
-          <t>RSVP attribution by event ID</t>
-        </is>
-      </c>
-      <c r="B138" s="15" t="inlineStr">
-        <is>
-          <t>DIAGNOSED Jul 9: bigger than 'add a column'. Per-event RSVP tagging is DEAD — the code that slug-tagged events was removed; since Apr 21 a public RSVP only gets a generic 'free-event-rsvp' tag, so you can't segment 'RSVP'd to event X' for any recent event. 6 frozen slug-tags remain (105 rows) and rot on rename. contact_tags has NO event_id column.</t>
-        </is>
-      </c>
-      <c r="C138" s="15" t="inlineStr">
-        <is>
-          <t>HALF-DAY scoped task (not a quick close): (1) migration add nullable event_id uuid REFERENCES events(id) to contact_tags; (2) re-add per-event tagging in capture-public-rsvp (event_id already in scope) + optionally create-guest-pass; (3) backfill — 5 of 6 slug-tags map to real event_ids by title-slug match (1 unmatched: coffee-and-connect-tabbris-co-working). Deploys + tests.</t>
-        </is>
-      </c>
-      <c r="D138" s="19" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E138" s="15" t="inlineStr">
-        <is>
-          <t>Jul 9: revives dead per-event attribution. Own task, budget a half-day. Backfill mostly possible.</t>
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>Drop ~35 empty leftover tables</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>~35 empty scaffolding tables (old CRM, social manager, feed, DMs).</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>Export copies as a receipt, then drop.</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>Don't drop without exporting copies first.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="57.45" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Drop ~35 empty leftover tables</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
-        <is>
-          <t>~35 empty scaffolding tables (old CRM, social manager, feed, DMs).</t>
-        </is>
-      </c>
-      <c r="C139" s="8" t="inlineStr">
-        <is>
-          <t>Export copies as a receipt, then drop.</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>Don't drop without exporting copies first.</t>
+          <t>Backup tables: keep or drop — Adam's call (13 hand-made snapshots; auth-hash pair flagged)</t>
+        </is>
+      </c>
+      <c r="B139" s="37" t="inlineStr">
+        <is>
+          <t>cursor_report_rlsaudit.md (Sep 21): 13 hand-made backup tables from Apr–Jun 2026 remain in public (presweep x7, 20260610 x4, _auth_*backup_20260428 x2). Nothing references them; RLS deny-all holds and the leftover anon/authenticated grants were stripped on prod (by hand) and develop (migration 20260921070000). _auth_backup_20260428 holds old_encrypted_password for 24 users — the one pair that should not linger. backup_ambassador_referrals_presweep is empty.</t>
+        </is>
+      </c>
+      <c r="C139" s="37" t="inlineStr">
+        <is>
+          <t>Adam decides per snapshot whether its purpose is closed. Suggested order: the two _auth_* tables (export with pg_dump -t if a cold copy is wanted, then drop), the empty ambassador backup, then the presweep/20260610 sets once the identity sweep and sauna merge are considered settled. No drops proposed in SQL without provenance.</t>
+        </is>
+      </c>
+      <c r="D139" s="37" t="inlineStr">
+        <is>
+          <t>WAITING ON ADAM: keep or drop</t>
+        </is>
+      </c>
+      <c r="E139" s="38" t="inlineStr">
+        <is>
+          <t>Security posture is already correct (grants stripped, 17/17 receipt). This row is hygiene + the password-hash pair. Provenance for all 13 is the July baseline dump only.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="46.25" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Backup tables: keep or drop — Adam's call (13 hand-made snapshots; auth-hash pair flagged)</t>
-        </is>
-      </c>
-      <c r="B140" s="37" t="inlineStr">
-        <is>
-          <t>cursor_report_rlsaudit.md (Sep 21): 13 hand-made backup tables from Apr–Jun 2026 remain in public (presweep x7, 20260610 x4, _auth_*backup_20260428 x2). Nothing references them; RLS deny-all holds and the leftover anon/authenticated grants were stripped on prod (by hand) and develop (migration 20260921070000). _auth_backup_20260428 holds old_encrypted_password for 24 users — the one pair that should not linger. backup_ambassador_referrals_presweep is empty.</t>
-        </is>
-      </c>
-      <c r="C140" s="37" t="inlineStr">
-        <is>
-          <t>Adam decides per snapshot whether its purpose is closed. Suggested order: the two _auth_* tables (export with pg_dump -t if a cold copy is wanted, then drop), the empty ambassador backup, then the presweep/20260610 sets once the identity sweep and sauna merge are considered settled. No drops proposed in SQL without provenance.</t>
-        </is>
-      </c>
-      <c r="D140" s="37" t="inlineStr">
-        <is>
-          <t>WAITING ON ADAM: keep or drop</t>
-        </is>
-      </c>
-      <c r="E140" s="38" t="inlineStr">
-        <is>
-          <t>Security posture is already correct (grants stripped, 17/17 receipt). This row is hygiene + the password-hash pair. Provenance for all 13 is the July baseline dump only.</t>
+          <t>Delete dead admin member components</t>
         </is>
       </c>
     </row>
     <row r="141" ht="46.25" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>Delete dead admin member components</t>
-        </is>
-      </c>
+      <c r="A141" s="35" t="inlineStr">
+        <is>
+          <t>MARKETING &amp; FRONT-END   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B141" s="31" t="n"/>
+      <c r="C141" s="31" t="n"/>
+      <c r="D141" s="31" t="n"/>
+      <c r="E141" s="31" t="n"/>
     </row>
     <row r="142" ht="46.25" customHeight="1">
-      <c r="A142" s="35" t="inlineStr">
-        <is>
-          <t>MARKETING &amp; FRONT-END   ·   9 items</t>
-        </is>
-      </c>
-      <c r="B142" s="31" t="n"/>
-      <c r="C142" s="31" t="n"/>
-      <c r="D142" s="31" t="n"/>
-      <c r="E142" s="31" t="n"/>
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>SEO + schema markup + pre-rendering (all front pages + 4 hub landers)</t>
+        </is>
+      </c>
+      <c r="B142" s="29" t="n"/>
+      <c r="C142" s="29" t="n"/>
+      <c r="D142" s="29" t="n"/>
+      <c r="E142" s="30" t="n"/>
     </row>
     <row r="143" ht="57.45" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>SEO + schema markup + pre-rendering (all front pages + 4 hub landers)</t>
-        </is>
-      </c>
-      <c r="B143" s="29" t="n"/>
-      <c r="C143" s="29" t="n"/>
-      <c r="D143" s="29" t="n"/>
-      <c r="E143" s="30" t="n"/>
+          <t>Homepage hero rebuild + image optimization</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Rebuild the hero and compress oversized hero images (currently 24-30MB, should be 200-800KB).</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>Hero rebuild + compress images.</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>Includes compressing 24-30MB hero images to 200-800KB.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="57.45" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Homepage hero rebuild + image optimization</t>
+          <t>Homepage copy rewrite + slogan</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Rebuild the hero and compress oversized hero images (currently 24-30MB, should be 200-800KB).</t>
+          <t>Rewrite homepage body/section copy and update the slogan.</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Hero rebuild + compress images.</t>
+          <t>Body + section copy + slogan.</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -3992,24 +3992,24 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Includes compressing 24-30MB hero images to 200-800KB.</t>
+          <t>Needs the copy spec.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="57.45" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Homepage copy rewrite + slogan</t>
+          <t>Fix the mobile hero sliding bug</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Rewrite homepage body/section copy and update the slogan.</t>
+          <t>A visual bug where the hero image slides on mobile.</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Body + section copy + slogan.</t>
+          <t>Mobile hero sliding fix.</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Needs the copy spec.</t>
+          <t>Fix the hero sliding on mobile.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>Fix the mobile hero sliding bug</t>
+          <t>The Exchange page</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>A visual bug where the hero image slides on mobile.</t>
+          <t>Build The Exchange page (speaker-driven business event product page).</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Mobile hero sliding fix.</t>
+          <t>The Exchange page.</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -4046,345 +4046,345 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Fix the hero sliding on mobile.</t>
+          <t>Speaker-driven business-event product page.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="57.45" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>The Exchange page</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>Build The Exchange page (speaker-driven business event product page).</t>
-        </is>
-      </c>
-      <c r="C147" s="8" t="inlineStr">
-        <is>
-          <t>The Exchange page.</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t>Speaker-driven business-event product page.</t>
+          <t>Sponsor page (likely folds into /business)</t>
+        </is>
+      </c>
+      <c r="B147" s="36" t="inlineStr">
+        <is>
+          <t>Sponsor functionality — likely folds into the /business application routing.</t>
+        </is>
+      </c>
+      <c r="C147" s="36" t="inlineStr">
+        <is>
+          <t>Probably absorbed by the /business rebuild.</t>
+        </is>
+      </c>
+      <c r="D147" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E147" s="36" t="inlineStr">
+        <is>
+          <t>Likely folds into the /business rebuild — confirm first.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="46.25" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>Sponsor page (likely folds into /business)</t>
-        </is>
-      </c>
-      <c r="B148" s="36" t="inlineStr">
-        <is>
-          <t>Sponsor functionality — likely folds into the /business application routing.</t>
-        </is>
-      </c>
-      <c r="C148" s="36" t="inlineStr">
-        <is>
-          <t>Probably absorbed by the /business rebuild.</t>
-        </is>
-      </c>
-      <c r="D148" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E148" s="36" t="inlineStr">
-        <is>
-          <t>Likely folds into the /business rebuild — confirm first.</t>
+          <t>/business page rebuild with dynamic application</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>Rebuild /business as one page with a dynamic application routing prospects to membership, Preferred Business, or sponsorship by their answers.</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic diagnose-before-offer application.</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>Routes prospects to membership, Preferred Business, or sponsorship.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="57.45" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>/business page rebuild with dynamic application</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="inlineStr">
-        <is>
-          <t>Rebuild /business as one page with a dynamic application routing prospects to membership, Preferred Business, or sponsorship by their answers.</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t>Dynamic diagnose-before-offer application.</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t>Routes prospects to membership, Preferred Business, or sponsorship.</t>
+          <t>The Network — four hubs + members rolled up</t>
+        </is>
+      </c>
+      <c r="B149" s="36" t="inlineStr">
+        <is>
+          <t>The four hubs rolled up into one view, plus all members. Two faces reading the same data: a PUBLIC face (the hub landers + business/partner listings — the sales asset) and an INTERNAL in-portal view that rolls up everyone. Social members appear ONLY on the internal in-portal view — never on the public hubs.</t>
+        </is>
+      </c>
+      <c r="C149" s="36" t="inlineStr">
+        <is>
+          <t>Roll the four hubs into one Network view + members. Public face = hubs / business + partner listings (social members excluded). Internal face = full rolled-up view including social members. Reads the same hub data as the landers.</t>
+        </is>
+      </c>
+      <c r="D149" s="36" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E149" s="36" t="inlineStr">
+        <is>
+          <t>Depends on the portal + identity foundation. Social members are internal-only on The Network. Separate from the member directory (people-only).</t>
         </is>
       </c>
     </row>
     <row r="150" ht="23.85" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>The Network — four hubs + members rolled up</t>
-        </is>
-      </c>
-      <c r="B150" s="36" t="inlineStr">
-        <is>
-          <t>The four hubs rolled up into one view, plus all members. Two faces reading the same data: a PUBLIC face (the hub landers + business/partner listings — the sales asset) and an INTERNAL in-portal view that rolls up everyone. Social members appear ONLY on the internal in-portal view — never on the public hubs.</t>
-        </is>
-      </c>
-      <c r="C150" s="36" t="inlineStr">
-        <is>
-          <t>Roll the four hubs into one Network view + members. Public face = hubs / business + partner listings (social members excluded). Internal face = full rolled-up view including social members. Reads the same hub data as the landers.</t>
-        </is>
-      </c>
-      <c r="D150" s="36" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E150" s="36" t="inlineStr">
-        <is>
-          <t>Depends on the portal + identity foundation. Social members are internal-only on The Network. Separate from the member directory (people-only).</t>
+          <t>Instagram comment auto-DM (ManyChat)</t>
         </is>
       </c>
     </row>
     <row r="151" ht="23.85" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>Instagram comment auto-DM (ManyChat)</t>
-        </is>
-      </c>
+      <c r="A151" s="35" t="inlineStr">
+        <is>
+          <t>AI / AGENTS (LATER EFFORT)   ·   2 items</t>
+        </is>
+      </c>
+      <c r="B151" s="31" t="n"/>
+      <c r="C151" s="31" t="n"/>
+      <c r="D151" s="31" t="n"/>
+      <c r="E151" s="31" t="n"/>
     </row>
     <row r="152" ht="23.85" customHeight="1">
-      <c r="A152" s="35" t="inlineStr">
-        <is>
-          <t>AI / AGENTS (LATER EFFORT)   ·   2 items</t>
-        </is>
-      </c>
-      <c r="B152" s="31" t="n"/>
-      <c r="C152" s="31" t="n"/>
-      <c r="D152" s="31" t="n"/>
-      <c r="E152" s="31" t="n"/>
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>AI concierge + agent platform</t>
+        </is>
+      </c>
+      <c r="B152" s="29" t="n"/>
+      <c r="C152" s="29" t="n"/>
+      <c r="D152" s="29" t="n"/>
+      <c r="E152" s="30" t="n"/>
     </row>
     <row r="153" ht="23.85" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>AI concierge + agent platform</t>
-        </is>
-      </c>
-      <c r="B153" s="29" t="n"/>
-      <c r="C153" s="29" t="n"/>
-      <c r="D153" s="29" t="n"/>
-      <c r="E153" s="30" t="n"/>
+          <t>AI foundations (memory, embeddings, coordination)</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>Supporting infra for the agents: shared memory, member embeddings, multi-agent coordination, model routing.</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>pgvector + embeddings, agent_memory, multi-agent coordination, model routing.</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>A later effort; supports the agents (embeddings, memory, routing).</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>AI foundations (memory, embeddings, coordination)</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>Supporting infra for the agents: shared memory, member embeddings, multi-agent coordination, model routing.</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t>pgvector + embeddings, agent_memory, multi-agent coordination, model routing.</t>
-        </is>
-      </c>
-      <c r="D154" s="10" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t>A later effort; supports the agents (embeddings, memory, routing).</t>
-        </is>
-      </c>
+      <c r="A154" s="35" t="inlineStr">
+        <is>
+          <t>EVENT DISCUSSION &amp; NOTIFICATIONS + JUL-5/6 FINDINGS — IN-HOUSE (NOT ON THE DEVELOPER SHEET)   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B154" s="31" t="n"/>
+      <c r="C154" s="31" t="n"/>
+      <c r="D154" s="31" t="n"/>
+      <c r="E154" s="31" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="35" t="inlineStr">
-        <is>
-          <t>EVENT DISCUSSION &amp; NOTIFICATIONS + JUL-5/6 FINDINGS — IN-HOUSE (NOT ON THE DEVELOPER SHEET)   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B155" s="31" t="n"/>
-      <c r="C155" s="31" t="n"/>
-      <c r="D155" s="31" t="n"/>
-      <c r="E155" s="31" t="n"/>
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>Rotate the R2 media token (exposed key)</t>
+        </is>
+      </c>
+      <c r="B155" s="36" t="inlineStr">
+        <is>
+          <t>The R2 Access Key ID + Secret for bucket 704-discussion-media were exposed in a working chat (screenshot/paste). Scope = that one media bucket only — low blast radius, but rotate.</t>
+        </is>
+      </c>
+      <c r="C155" s="36" t="inlineStr">
+        <is>
+          <t>After 6c ships: Cloudflare -&gt; R2 -&gt; API tokens -&gt; re-create 704-discussion-upload (Object Read &amp; Write, bucket-scoped) -&gt; supabase secrets set the two new values -&gt; confirm an upload still works.</t>
+        </is>
+      </c>
+      <c r="D155" s="36" t="inlineStr">
+        <is>
+          <t>Declined</t>
+        </is>
+      </c>
+      <c r="E155" s="36" t="inlineStr">
+        <is>
+          <t>Adam declined rotation Jul 5 - standing watch item. Key scope = one media bucket only (no member data / money / DB). Say 'rotate' anytime: ~2 min.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>Rotate the R2 media token (exposed key)</t>
-        </is>
-      </c>
-      <c r="B156" s="36" t="inlineStr">
-        <is>
-          <t>The R2 Access Key ID + Secret for bucket 704-discussion-media were exposed in a working chat (screenshot/paste). Scope = that one media bucket only — low blast radius, but rotate.</t>
-        </is>
-      </c>
-      <c r="C156" s="36" t="inlineStr">
-        <is>
-          <t>After 6c ships: Cloudflare -&gt; R2 -&gt; API tokens -&gt; re-create 704-discussion-upload (Object Read &amp; Write, bucket-scoped) -&gt; supabase secrets set the two new values -&gt; confirm an upload still works.</t>
-        </is>
-      </c>
-      <c r="D156" s="36" t="inlineStr">
-        <is>
-          <t>Declined</t>
-        </is>
-      </c>
-      <c r="E156" s="36" t="inlineStr">
-        <is>
-          <t>Adam declined rotation Jul 5 - standing watch item. Key scope = one media bucket only (no member data / money / DB). Say 'rotate' anytime: ~2 min.</t>
+          <t>Verify/finish the Alerts page (full history, discussion types)</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>Locked: bell badge clears on open, items dismiss via X, but the ALERTS PAGE keeps every notification forever - markable read (single + all). PARTIAL Jul 5: /dashboard/notifications now honors action_url (deep-links verified end to end). Remaining: full-history + mark-read behavior verification.</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>Read the Alerts page code; verify full-history + mark-read behavior and that all discussion notification types display with correct deep-links; fix gaps. Desktop + mobile test.</t>
+        </is>
+      </c>
+      <c r="D156" s="20" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>Deep-links fixed+verified Jul 5 (commit e9f6250). Remaining: verify full-history retention + mark-read (single + all).</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>Verify/finish the Alerts page (full history, discussion types)</t>
+          <t>Messaging: bells for messages in existing conversations</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Locked: bell badge clears on open, items dismiss via X, but the ALERTS PAGE keeps every notification forever - markable read (single + all). PARTIAL Jul 5: /dashboard/notifications now honors action_url (deep-links verified end to end). Remaining: full-history + mark-read behavior verification.</t>
+          <t>Messaging was resurrected Jul 5 (DMs/groups had NEVER worked since launch: RETURNING/RLS deadlock, participants-insert policy tautology, content-vs-body + title-vs-name schema mismatches, 4 missing messages columns - all fixed and verified end to end). Remaining gap: notifyNewConversation only fires on conversation CREATION, so messages into an existing thread produce no bell.</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Read the Alerts page code; verify full-history + mark-read behavior and that all discussion notification types display with correct deep-links; fix gaps. Desktop + mobile test.</t>
+          <t>Add a new_message bell per message into an existing conversation, throttled (e.g. skip if an unread new_message bell for that conversation already exists).</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Deep-links fixed+verified Jul 5 (commit e9f6250). Remaining: verify full-history retention + mark-read (single + all).</t>
+          <t>Follow-on to the Jul 5 messaging resurrection. Recipients currently only get notified on the first-ever message.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>Messaging: bells for messages in existing conversations</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="inlineStr">
-        <is>
-          <t>Messaging was resurrected Jul 5 (DMs/groups had NEVER worked since launch: RETURNING/RLS deadlock, participants-insert policy tautology, content-vs-body + title-vs-name schema mismatches, 4 missing messages columns - all fixed and verified end to end). Remaining gap: notifyNewConversation only fires on conversation CREATION, so messages into an existing thread produce no bell.</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t>Add a new_message bell per message into an existing conversation, throttled (e.g. skip if an unread new_message bell for that conversation already exists).</t>
-        </is>
-      </c>
-      <c r="D158" s="20" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t>Follow-on to the Jul 5 messaging resurrection. Recipients currently only get notified on the first-ever message.</t>
+          <t>Messaging: attachment uploads (images/files)</t>
+        </is>
+      </c>
+      <c r="B158" s="37" t="inlineStr">
+        <is>
+          <t>MessagingView has image/file upload code paths and messages now has image_urls/file_urls/file_names columns (added Jul 5), but the storage wiring (bucket, upload flow) has never been tested and may not exist.</t>
+        </is>
+      </c>
+      <c r="C158" s="37" t="inlineStr">
+        <is>
+          <t>Audit the attachment path end to end: storage bucket, upload call, render. Fix or wire what's missing. Desktop + mobile test.</t>
+        </is>
+      </c>
+      <c r="D158" s="37" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E158" s="38" t="inlineStr">
+        <is>
+          <t>Text messaging + edits verified Jul 5; attachments explicitly skipped in that test.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>Messaging: attachment uploads (images/files)</t>
-        </is>
-      </c>
-      <c r="B159" s="37" t="inlineStr">
-        <is>
-          <t>MessagingView has image/file upload code paths and messages now has image_urls/file_urls/file_names columns (added Jul 5), but the storage wiring (bucket, upload flow) has never been tested and may not exist.</t>
-        </is>
-      </c>
-      <c r="C159" s="37" t="inlineStr">
-        <is>
-          <t>Audit the attachment path end to end: storage bucket, upload call, render. Fix or wire what's missing. Desktop + mobile test.</t>
-        </is>
-      </c>
-      <c r="D159" s="37" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E159" s="38" t="inlineStr">
-        <is>
-          <t>Text messaging + edits verified Jul 5; attachments explicitly skipped in that test.</t>
+          <t>Verify the first real-money admin refund (Remove &amp; Refund)</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>Admin Remove &amp; Refund shipped Jul 5 (edge fn admin-refund-ticket: admin gate, Stripe refund, void credential, seat freed; + attendee-dialog button, mobile-safe). Every branch proven EXCEPT the successful real-money refund line: void-only path, 403 gate, already-voided idempotency, and the Stripe-failure 502 fail-safe (no seat freed without money returned) all tested live.</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>WAIT mode: on the next genuine member refund request, use Remove &amp; Refund in the event attendee dialog and verify: Stripe refunded, credential voided, seat freed, toast correct.</t>
+        </is>
+      </c>
+      <c r="D159" s="20" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>Zero-cost proof on the next real request. Sacred Walker (Jul 5) handled manually pre-feature; her case is the template.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="21.75" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>Verify the first real-money admin refund (Remove &amp; Refund)</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>Admin Remove &amp; Refund shipped Jul 5 (edge fn admin-refund-ticket: admin gate, Stripe refund, void credential, seat freed; + attendee-dialog button, mobile-safe). Every branch proven EXCEPT the successful real-money refund line: void-only path, 403 gate, already-voided idempotency, and the Stripe-failure 502 fail-safe (no seat freed without money returned) all tested live.</t>
-        </is>
-      </c>
-      <c r="C160" s="8" t="inlineStr">
-        <is>
-          <t>WAIT mode: on the next genuine member refund request, use Remove &amp; Refund in the event attendee dialog and verify: Stripe refunded, credential voided, seat freed, toast correct.</t>
-        </is>
-      </c>
-      <c r="D160" s="20" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t>Zero-cost proof on the next real request. Sacred Walker (Jul 5) handled manually pre-feature; her case is the template.</t>
-        </is>
-      </c>
+      <c r="A160" s="41" t="inlineStr">
+        <is>
+          <t>SESSION LOG — JUL 7–9 2026 (COMPLETED; kept as record, esp. the security fix)</t>
+        </is>
+      </c>
+      <c r="B160" s="32" t="n"/>
+      <c r="C160" s="32" t="n"/>
+      <c r="D160" s="32" t="n"/>
+      <c r="E160" s="32" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="41" t="inlineStr">
-        <is>
-          <t>SESSION LOG — JUL 7–9 2026 (COMPLETED; kept as record, esp. the security fix)</t>
-        </is>
-      </c>
-      <c r="B161" s="32" t="n"/>
-      <c r="C161" s="32" t="n"/>
-      <c r="D161" s="32" t="n"/>
-      <c r="E161" s="32" t="n"/>
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>[DONE] Security: dropped anon-readable active_members view + locked event_participants_view</t>
+        </is>
+      </c>
+      <c r="B161" s="23" t="inlineStr">
+        <is>
+          <t>CRITICAL FIX Jul 9: active_members and event_participants_view were SECURITY DEFINER views with ALL privileges granted to anon — an unauthenticated internet caller could read every member's email/phone/Stripe customer ID + all attendee contact info, AND active_members (auto-updatable single-table view) exposed an anon WRITE path into profiles. active_members had ZERO callers -&gt; DROPPED. event_participants_view -&gt; security_invoker=true + REVOKE anon/authenticated (sole caller send-campaign uses service-role, unaffected). member_counts left as-is (intentional).</t>
+        </is>
+      </c>
+      <c r="C161" s="23" t="inlineStr">
+        <is>
+          <t>DONE via SQL. Verified from OUTSIDE with anon key: active_members=404, event_participants_view=401 permission denied. No rows leaked. send-campaign confirmed still works.</t>
+        </is>
+      </c>
+      <c r="D161" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E161" s="23" t="inlineStr">
+        <is>
+          <t>Biggest find of the session. Was disguised as a 'review Security Definer flags' tracker row.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Security: dropped anon-readable active_members view + locked event_participants_view</t>
+          <t>[DONE] Nine-job cron auth resurrection + 2 guards, all 10 jobs healthy</t>
         </is>
       </c>
       <c r="B162" s="23" t="inlineStr">
         <is>
-          <t>CRITICAL FIX Jul 9: active_members and event_participants_view were SECURITY DEFINER views with ALL privileges granted to anon — an unauthenticated internet caller could read every member's email/phone/Stripe customer ID + all attendee contact info, AND active_members (auto-updatable single-table view) exposed an anon WRITE path into profiles. active_members had ZERO callers -&gt; DROPPED. event_participants_view -&gt; security_invoker=true + REVOKE anon/authenticated (sole caller send-campaign uses service-role, unaffected). member_counts left as-is (intentional).</t>
+          <t>Full audit found NINE broken crons (sheet knew of 2). Fixed: Vault key was legacy JWT but runtime injects sb_secret_ (updated Vault); SQL typo value-&gt;decrypted_secret on jobs 3/4/13; event-reminder had no service-key path + a no-auth-header mass-email hole (both fixed, commit 09d637d). Then built 2 guards: business-profile-reminder 14-day cooldown via contact_activity + internal-account exclusion (503548c); guest-event-match at-capacity exclusion (d722800). Both jobs 2 &amp; 10 re-enabled. All 10 cron jobs now active + healthy.</t>
         </is>
       </c>
       <c r="C162" s="23" t="inlineStr">
         <is>
-          <t>DONE via SQL. Verified from OUTSIDE with anon key: active_members=404, event_participants_view=401 permission denied. No rows leaked. send-campaign confirmed still works.</t>
+          <t>All confirmed 200 on live ticks. Guards dry-run/logic verified. WATCH: first live ticks of job 2 (14:00 UTC every 2 days) + job 10 (13:00 UTC daily) — read-only confirm right people emailed.</t>
         </is>
       </c>
       <c r="D162" s="24" t="inlineStr">
@@ -4394,24 +4394,24 @@
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Biggest find of the session. Was disguised as a 'review Security Definer flags' tracker row.</t>
+          <t>Commits 09d637d, 503548c, d722800 + Vault + SQL. event-reminder security hole closed.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Nine-job cron auth resurrection + 2 guards, all 10 jobs healthy</t>
+          <t>[DONE] Sentry error monitoring — live + verified in prod</t>
         </is>
       </c>
       <c r="B163" s="23" t="inlineStr">
         <is>
-          <t>Full audit found NINE broken crons (sheet knew of 2). Fixed: Vault key was legacy JWT but runtime injects sb_secret_ (updated Vault); SQL typo value-&gt;decrypted_secret on jobs 3/4/13; event-reminder had no service-key path + a no-auth-header mass-email hole (both fixed, commit 09d637d). Then built 2 guards: business-profile-reminder 14-day cooldown via contact_activity + internal-account exclusion (503548c); guest-event-match at-capacity exclusion (d722800). Both jobs 2 &amp; 10 re-enabled. All 10 cron jobs now active + healthy.</t>
+          <t>@sentry/nextjs wired (client+server+API+global-error), CSP allowance, instrumentation moved into src/ (Next ignores root-level with a src/ dir), DSN + source-map auth token in Vercel, /admin/sentry page activated. Prod capture VERIFIED (smoke-test error landed in feed).</t>
         </is>
       </c>
       <c r="C163" s="23" t="inlineStr">
         <is>
-          <t>All confirmed 200 on live ticks. Guards dry-run/logic verified. WATCH: first live ticks of job 2 (14:00 UTC every 2 days) + job 10 (13:00 UTC daily) — read-only confirm right people emailed.</t>
+          <t>Verified. WATCH: confirm Sentry project SLUG is exactly '704-collective' in a Vercel build log (source-map upload) — if wrong, traces stay minified (one-word fix).</t>
         </is>
       </c>
       <c r="D163" s="24" t="inlineStr">
@@ -4421,51 +4421,51 @@
       </c>
       <c r="E163" s="23" t="inlineStr">
         <is>
-          <t>Commits 09d637d, 503548c, d722800 + Vault + SQL. event-reminder security hole closed.</t>
+          <t>Commits 417fb37/d779885/5d12aac/b437166. The safety net — Stage 1 complete.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Sentry error monitoring — live + verified in prod</t>
-        </is>
-      </c>
-      <c r="B164" s="23" t="inlineStr">
-        <is>
-          <t>@sentry/nextjs wired (client+server+API+global-error), CSP allowance, instrumentation moved into src/ (Next ignores root-level with a src/ dir), DSN + source-map auth token in Vercel, /admin/sentry page activated. Prod capture VERIFIED (smoke-test error landed in feed).</t>
-        </is>
-      </c>
-      <c r="C164" s="23" t="inlineStr">
-        <is>
-          <t>Verified. WATCH: confirm Sentry project SLUG is exactly '704-collective' in a Vercel build log (source-map upload) — if wrong, traces stay minified (one-word fix).</t>
-        </is>
-      </c>
-      <c r="D164" s="24" t="inlineStr">
+          <t>[DONE] Josh Ahart full removal (exit workstream)</t>
+        </is>
+      </c>
+      <c r="B164" s="36" t="inlineStr">
+        <is>
+          <t>De-privileged (super_admin-&gt;lead), permanent ban, all 8 sessions + 64 tokens killed, profile deactivated, ambassador row disabled, removed from public /about page (0cc8c66), 2 dormant test dupe accounts hard-deleted. Stripe sub cancelled + Connect account rejected (Adam, dashboard). Platform passwords rotated (Adam).</t>
+        </is>
+      </c>
+      <c r="C164" s="36" t="inlineStr">
+        <is>
+          <t>Verified: role=lead, 0 sessions/tokens, banned. Public site scrubbed. Dashboard-member removal confirmed by Adam.</t>
+        </is>
+      </c>
+      <c r="D164" s="36" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E164" s="23" t="inlineStr">
-        <is>
-          <t>Commits 417fb37/d779885/5d12aac/b437166. The safety net — Stage 1 complete.</t>
+      <c r="E164" s="36" t="inlineStr">
+        <is>
+          <t>NOT on the build sheet — exit workstream. Recorded here for completeness. Aug 25: Josh hub purge DONE - his 4 remaining hub_members rows (one per hub, all joined 2026-05-21 03:11:32, all added by Adam) were deleted; verified afterwards at 0 hub memberships, 0 posts, 0 comments, 0 likes, 0 resources. CORRECTION to an earlier wording of this note: Josh created NO hubs. All four hubs are created_by Adam, so nothing was owned by him and the purge was membership rows only - the cascade risk on hubs.created_by is a separate finding about Adam's profile (see that row). Also noted while verifying: the hub display queries in dashboard/hubs/[id] and admin/hubs join profiles without a deleted_at filter, which is why his soft-deleted profile kept rendering and inflated each hub's member count by one. Closes the hub residue of the exit.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Josh Ahart full removal (exit workstream)</t>
+          <t>[DONE] Member status batch (Jul 9)</t>
         </is>
       </c>
       <c r="B165" s="36" t="inlineStr">
         <is>
-          <t>De-privileged (super_admin-&gt;lead), permanent ban, all 8 sessions + 64 tokens killed, profile deactivated, ambassador row disabled, removed from public /about page (0cc8c66), 2 dormant test dupe accounts hard-deleted. Stripe sub cancelled + Connect account rejected (Adam, dashboard). Platform passwords rotated (Adam).</t>
+          <t>Nicholas Stathopoulos + Robert Villante -&gt; non_member/inactive/override off/lead (Nick admin revoked + sessions killed). Whitney Cleland + Brenna Dunne + Kaelah Torres -&gt; ERASED (auth+profile+people+credentials deleted; all comped, no Stripe to cancel). More status changes flagged as coming.</t>
         </is>
       </c>
       <c r="C165" s="36" t="inlineStr">
         <is>
-          <t>Verified: role=lead, 0 sessions/tokens, banned. Public site scrubbed. Dashboard-member removal confirmed by Adam.</t>
+          <t>All verified via SQL (zeros on erase). Read-first footprint audit confirmed safe (no owned content cascaded).</t>
         </is>
       </c>
       <c r="D165" s="36" t="inlineStr">
@@ -4475,78 +4475,78 @@
       </c>
       <c r="E165" s="36" t="inlineStr">
         <is>
-          <t>NOT on the build sheet — exit workstream. Recorded here for completeness. Aug 25: Josh hub purge DONE - his 4 remaining hub_members rows (one per hub, all joined 2026-05-21 03:11:32, all added by Adam) were deleted; verified afterwards at 0 hub memberships, 0 posts, 0 comments, 0 likes, 0 resources. CORRECTION to an earlier wording of this note: Josh created NO hubs. All four hubs are created_by Adam, so nothing was owned by him and the purge was membership rows only - the cascade risk on hubs.created_by is a separate finding about Adam's profile (see that row). Also noted while verifying: the hub display queries in dashboard/hubs/[id] and admin/hubs join profiles without a deleted_at filter, which is why his soft-deleted profile kept rendering and inflated each hub's member count by one. Closes the hub residue of the exit.</t>
+          <t>Adam noted more member changes coming next session. Aug 25: Audrey Handleton converted to non-member - DONE, and recorded here as the next entry in this running member-status record. Verified end state: profiles reads non_member / inactive / membership_override false; the people row reads roles ['prospect'] with member_tier and member_status both null (never-was, not canceled). She was a comp who had drifted - profile said social while her people row still said business - and she never paid a cent, so there was no Stripe side to cancel.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Member status batch (Jul 9)</t>
-        </is>
-      </c>
-      <c r="B166" s="36" t="inlineStr">
-        <is>
-          <t>Nicholas Stathopoulos + Robert Villante -&gt; non_member/inactive/override off/lead (Nick admin revoked + sessions killed). Whitney Cleland + Brenna Dunne + Kaelah Torres -&gt; ERASED (auth+profile+people+credentials deleted; all comped, no Stripe to cancel). More status changes flagged as coming.</t>
-        </is>
-      </c>
-      <c r="C166" s="36" t="inlineStr">
-        <is>
-          <t>All verified via SQL (zeros on erase). Read-first footprint audit confirmed safe (no owned content cascaded).</t>
-        </is>
-      </c>
-      <c r="D166" s="36" t="inlineStr">
+          <t>[DONE] Business-event RSVP tier leak — closed + Annslee voided</t>
+        </is>
+      </c>
+      <c r="B166" s="23" t="inlineStr">
+        <is>
+          <t>Social members could RSVP business-only events: create-member-rsvp never checked required_tier, and the mobile sticky RSVP bar bypassed the desktop gate. Fixed: server-side tier gate in the edge function (ff20ba9, admins exempt) + mobile CTA respects canRsvp (952fbb2). Annslee Bottoms' live breach credential on Jul-14 Business Member Meeting VOIDED. Past legacy breaches intentionally left (real attendance history).</t>
+        </is>
+      </c>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>Verified: socialtest gets 403 'business members only' + red toast; direct-invoke blocked; Annslee active count on event = 0.</t>
+        </is>
+      </c>
+      <c r="D166" s="24" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E166" s="36" t="inlineStr">
-        <is>
-          <t>Adam noted more member changes coming next session. Aug 25: Audrey Handleton converted to non-member - DONE, and recorded here as the next entry in this running member-status record. Verified end state: profiles reads non_member / inactive / membership_override false; the people row reads roles ['prospect'] with member_tier and member_status both null (never-was, not canceled). She was a comp who had drifted - profile said social while her people row still said business - and she never paid a cent, so there was no Stripe side to cancel.</t>
+      <c r="E166" s="23" t="inlineStr">
+        <is>
+          <t>Commits ff20ba9, 952fbb2. Guest-side email opt-out gap noted -&gt; folds into unsubscribe policy work.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Business-event RSVP tier leak — closed + Annslee voided</t>
-        </is>
-      </c>
-      <c r="B167" s="23" t="inlineStr">
-        <is>
-          <t>Social members could RSVP business-only events: create-member-rsvp never checked required_tier, and the mobile sticky RSVP bar bypassed the desktop gate. Fixed: server-side tier gate in the edge function (ff20ba9, admins exempt) + mobile CTA respects canRsvp (952fbb2). Annslee Bottoms' live breach credential on Jul-14 Business Member Meeting VOIDED. Past legacy breaches intentionally left (real attendance history).</t>
-        </is>
-      </c>
-      <c r="C167" s="23" t="inlineStr">
-        <is>
-          <t>Verified: socialtest gets 403 'business members only' + red toast; direct-invoke blocked; Annslee active count on event = 0.</t>
-        </is>
-      </c>
-      <c r="D167" s="24" t="inlineStr">
+          <t>[DONE] Discussion edit/delete (comments+posts+photos) + admin always-on access</t>
+        </is>
+      </c>
+      <c r="B167" s="36" t="inlineStr">
+        <is>
+          <t>Owners + admins can now edit/delete their own discussion comments (ecec3f8), posts (1e3adc1), and remove their own gallery photos (bcf746f); admins moderate anyone's. '(edited)' marker, soft-delete, silent removal. Also: admins now see the discussion link on any open event regardless of RSVP (583b343 — backend was already admin-exempt; was a missing-link discovery bug). Feed/comment/DM URL linkify (561403e).</t>
+        </is>
+      </c>
+      <c r="C167" s="36" t="inlineStr">
+        <is>
+          <t>All browser-tested desktop+mobile. Backend RLS already permitted; these were frontend gaps.</t>
+        </is>
+      </c>
+      <c r="D167" s="36" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E167" s="23" t="inlineStr">
-        <is>
-          <t>Commits ff20ba9, 952fbb2. Guest-side email opt-out gap noted -&gt; folds into unsubscribe policy work.</t>
+      <c r="E167" s="36" t="inlineStr">
+        <is>
+          <t>5 commits. Discussion feature now fully moderatable.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="16" t="inlineStr">
         <is>
-          <t>[DONE] Discussion edit/delete (comments+posts+photos) + admin always-on access</t>
+          <t>[DONE] Small fixes: hubs 404, week_label, dead components, partners 400, org_settings, last_attended</t>
         </is>
       </c>
       <c r="B168" s="36" t="inlineStr">
         <is>
-          <t>Owners + admins can now edit/delete their own discussion comments (ecec3f8), posts (1e3adc1), and remove their own gallery photos (bcf746f); admins moderate anyone's. '(edited)' marker, soft-delete, silent removal. Also: admins now see the discussion link on any open event regardless of RSVP (583b343 — backend was already admin-exempt; was a missing-link discovery bug). Feed/comment/DM URL linkify (561403e).</t>
+          <t>hubs preview widget queried non-existent 'business_hubs' -&gt; fixed to 'hubs' (a00cc50, restored a silently-broken business-tier feature). ambassador-payout phantom week_label column removed (1f46e88). 3 dead admin components deleted, 1376 lines (306efa4). partners 400 fixed via column aliasing (d95a337, latent partner-disappearing bug). organization_settings tracker row was STALE (schema fine, closed). last_attended already built+firing -&gt; backfilled 17 pre-trigger rows, closed.</t>
         </is>
       </c>
       <c r="C168" s="36" t="inlineStr">
         <is>
-          <t>All browser-tested desktop+mobile. Backend RLS already permitted; these were frontend gaps.</t>
+          <t>All tsc+browser verified. org_settings &amp; last_attended were already-done rows.</t>
         </is>
       </c>
       <c r="D168" s="36" t="inlineStr">
@@ -4556,68 +4556,68 @@
       </c>
       <c r="E168" s="36" t="inlineStr">
         <is>
-          <t>5 commits. Discussion feature now fully moderatable.</t>
+          <t>Commits a00cc50, 1f46e88, 306efa4, d95a337 + 2 SQL closes.</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="16" t="inlineStr">
-        <is>
-          <t>[DONE] Small fixes: hubs 404, week_label, dead components, partners 400, org_settings, last_attended</t>
-        </is>
-      </c>
-      <c r="B169" s="36" t="inlineStr">
-        <is>
-          <t>hubs preview widget queried non-existent 'business_hubs' -&gt; fixed to 'hubs' (a00cc50, restored a silently-broken business-tier feature). ambassador-payout phantom week_label column removed (1f46e88). 3 dead admin components deleted, 1376 lines (306efa4). partners 400 fixed via column aliasing (d95a337, latent partner-disappearing bug). organization_settings tracker row was STALE (schema fine, closed). last_attended already built+firing -&gt; backfilled 17 pre-trigger rows, closed.</t>
-        </is>
-      </c>
-      <c r="C169" s="36" t="inlineStr">
-        <is>
-          <t>All tsc+browser verified. org_settings &amp; last_attended were already-done rows.</t>
-        </is>
-      </c>
-      <c r="D169" s="36" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E169" s="36" t="inlineStr">
-        <is>
-          <t>Commits a00cc50, 1f46e88, 306efa4, d95a337 + 2 SQL closes.</t>
-        </is>
-      </c>
+      <c r="A169" s="42" t="inlineStr">
+        <is>
+          <t>PHASE 2  ·  MAJOR BUILDS (each gets its own detailed scope before build)</t>
+        </is>
+      </c>
+      <c r="B169" s="33" t="n"/>
+      <c r="C169" s="33" t="n"/>
+      <c r="D169" s="33" t="n"/>
+      <c r="E169" s="33" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="42" t="inlineStr">
-        <is>
-          <t>PHASE 2  ·  MAJOR BUILDS (each gets its own detailed scope before build)</t>
-        </is>
-      </c>
-      <c r="B170" s="33" t="n"/>
-      <c r="C170" s="33" t="n"/>
-      <c r="D170" s="33" t="n"/>
-      <c r="E170" s="33" t="n"/>
+      <c r="A170" s="35" t="inlineStr">
+        <is>
+          <t>MAJOR BUILDS — EACH GETS ITS OWN DETAILED SCOPE BEFORE BUILD   ·   5 items</t>
+        </is>
+      </c>
+      <c r="B170" s="31" t="n"/>
+      <c r="C170" s="31" t="n"/>
+      <c r="D170" s="31" t="n"/>
+      <c r="E170" s="31" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="35" t="inlineStr">
-        <is>
-          <t>MAJOR BUILDS — EACH GETS ITS OWN DETAILED SCOPE BEFORE BUILD   ·   5 items</t>
-        </is>
-      </c>
-      <c r="B171" s="31" t="n"/>
-      <c r="C171" s="31" t="n"/>
-      <c r="D171" s="31" t="n"/>
-      <c r="E171" s="31" t="n"/>
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>CRM system</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Full customer-relationship system built ON the merged person record: 360-degree member view, segments/audiences, lifecycle tracking. The internal data model IS the CRM (not a re-introduced external tool).</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>Own detailed scope before build.</t>
+        </is>
+      </c>
+      <c r="D171" s="26" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>Built on the canonical person record from Phase 1. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag (carve-out keeps /admin/crm/campaigns live for the newsletter).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>CRM system</t>
+          <t>Preferred Business Network</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>Full customer-relationship system built ON the merged person record: 360-degree member view, segments/audiences, lifecycle tracking. The internal data model IS the CRM (not a re-introduced external tool).</t>
+          <t>New paid product: vetted local-business listings, $300/mo to be listed. Lives in the portal first, public domains later. Includes the internal 'Seats' system. Social members browse this to find services.</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
@@ -4632,143 +4632,143 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Built on the canonical person record from Phase 1. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag (carve-out keeps /admin/crm/campaigns live for the newsletter).</t>
+          <t>Plugs into The Network surface built in Phase 1.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>Preferred Business Network</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="inlineStr">
-        <is>
-          <t>New paid product: vetted local-business listings, $300/mo to be listed. Lives in the portal first, public domains later. Includes the internal 'Seats' system. Social members browse this to find services.</t>
-        </is>
-      </c>
-      <c r="C173" s="8" t="inlineStr">
+          <t>Partner Portal (audit, then repurpose or remove)</t>
+        </is>
+      </c>
+      <c r="B173" s="36" t="inlineStr">
+        <is>
+          <t>An existing, mostly-built partner portal of unclear purpose. Audit it, then either repurpose it as the Preferred Business Network management surface or remove it. Frozen until then.</t>
+        </is>
+      </c>
+      <c r="C173" s="36" t="inlineStr">
         <is>
           <t>Own detailed scope before build.</t>
         </is>
       </c>
-      <c r="D173" s="26" t="inlineStr">
+      <c r="D173" s="36" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="E173" s="8" t="inlineStr">
-        <is>
-          <t>Plugs into The Network surface built in Phase 1.</t>
+      <c r="E173" s="36" t="inlineStr">
+        <is>
+          <t>Audit first; likely becomes the Preferred Business Network management surface. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>Partner Portal (audit, then repurpose or remove)</t>
-        </is>
-      </c>
-      <c r="B174" s="36" t="inlineStr">
-        <is>
-          <t>An existing, mostly-built partner portal of unclear purpose. Audit it, then either repurpose it as the Preferred Business Network management surface or remove it. Frozen until then.</t>
-        </is>
-      </c>
-      <c r="C174" s="36" t="inlineStr">
+          <t>Shared email inbox view for super-admins</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>A shared inbox view so super-admins can see the team email (hello@) in one place.</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
         <is>
           <t>Own detailed scope before build.</t>
         </is>
       </c>
-      <c r="D174" s="36" t="inlineStr">
+      <c r="D174" s="26" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="E174" s="36" t="inlineStr">
-        <is>
-          <t>Audit first; likely becomes the Preferred Business Network management surface. Currently hidden behind the reversible HIDE_CRM_AND_PARTNERS middleware flag.</t>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>Super-admin visibility into hello@.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>Shared email inbox view for super-admins</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>A shared inbox view so super-admins can see the team email (hello@) in one place.</t>
-        </is>
-      </c>
-      <c r="C175" s="8" t="inlineStr">
+          <t>Corporate / bulk-sales floating-seats portal</t>
+        </is>
+      </c>
+      <c r="B175" s="37" t="inlineStr">
+        <is>
+          <t>A portal for selling memberships in bulk to companies, with reassignable 'floating' seats.</t>
+        </is>
+      </c>
+      <c r="C175" s="37" t="inlineStr">
         <is>
           <t>Own detailed scope before build.</t>
         </is>
       </c>
-      <c r="D175" s="26" t="inlineStr">
+      <c r="D175" s="37" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>Super-admin visibility into hello@.</t>
+      <c r="E175" s="38" t="inlineStr">
+        <is>
+          <t>Reassignable floating seats for companies.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="7" t="inlineStr">
-        <is>
-          <t>Corporate / bulk-sales floating-seats portal</t>
-        </is>
-      </c>
-      <c r="B176" s="37" t="inlineStr">
-        <is>
-          <t>A portal for selling memberships in bulk to companies, with reassignable 'floating' seats.</t>
-        </is>
-      </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>Own detailed scope before build.</t>
-        </is>
-      </c>
-      <c r="D176" s="37" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E176" s="38" t="inlineStr">
-        <is>
-          <t>Reassignable floating seats for companies.</t>
-        </is>
-      </c>
+      <c r="A176" s="35" t="inlineStr">
+        <is>
+          <t>OPEN WATCH ITEMS — ADDED 2026-07-19   ·   6 items</t>
+        </is>
+      </c>
+      <c r="B176" s="31" t="n"/>
+      <c r="C176" s="31" t="n"/>
+      <c r="D176" s="31" t="n"/>
+      <c r="E176" s="31" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="35" t="inlineStr">
-        <is>
-          <t>OPEN WATCH ITEMS — ADDED 2026-07-19   ·   6 items</t>
-        </is>
-      </c>
-      <c r="B177" s="31" t="n"/>
-      <c r="C177" s="31" t="n"/>
-      <c r="D177" s="31" t="n"/>
-      <c r="E177" s="31" t="n"/>
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>Refill the Vercel NEXT_PUBLIC_TURNSTILE_SITE_KEY value (hardcode fallback active)</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>The prod env var was set to an empty string, which made the Turnstile widget render nothing and locked members out during an incident. A hardcoded public site-key fallback in TurnstileWidget.tsx currently masks the missing value. Fallback fails CLOSED (blocks rather than bypasses); the code docstring claims the opposite and is wrong.</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Set the real public site key for NEXT_PUBLIC_TURNSTILE_SITE_KEY in Vercel (production), redeploy, confirm the widget renders from the env var, then optionally remove the hardcoded fallback.</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>Public site key (safe): 0x4AAAAAAD3gqCivsYyImeUH. Fallback keeps login working today; refill so config isn't hidden in code.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>Refill the Vercel NEXT_PUBLIC_TURNSTILE_SITE_KEY value (hardcode fallback active)</t>
+          <t>Resolve the capacity-trigger split-brain (tickets vs attendance_credentials counting)</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>The prod env var was set to an empty string, which made the Turnstile widget render nothing and locked members out during an incident. A hardcoded public site-key fallback in TurnstileWidget.tsx currently masks the missing value. Fallback fails CLOSED (blocks rather than bypasses); the code docstring claims the opposite and is wrong.</t>
+          <t>Event capacity is enforced by triggers on two tables (attendance_credentials and legacy tickets) that count independently, so the seated count can disagree depending on the write path.</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Set the real public site key for NEXT_PUBLIC_TURNSTILE_SITE_KEY in Vercel (production), redeploy, confirm the widget renders from the env var, then optionally remove the hardcoded fallback.</t>
+          <t>Pick one source of truth (attendance_credentials); make both trigger families count consistently, or retire the legacy tickets capacity path once tickets is fully retired. Coordinates with 'Finish retiring the old ticket tables'.</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
@@ -4778,24 +4778,24 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Public site key (safe): 0x4AAAAAAD3gqCivsYyImeUH. Fallback keeps login working today; refill so config isn't hidden in code.</t>
+          <t>Closes with identity Wave 9 (tickets), which now rides before the mobile app. The admin_override bypass spans both trigger families; the counting split remains until tickets is retired.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>Resolve the capacity-trigger split-brain (tickets vs attendance_credentials counting)</t>
+          <t>Delete the stray Stripe Connect account</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>Event capacity is enforced by triggers on two tables (attendance_credentials and legacy tickets) that count independently, so the seated count can disagree depending on the write path.</t>
+          <t>A leftover Stripe Connect (Express) account from the ambassador / exit workstream needs removing so it doesn't linger.</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Pick one source of truth (attendance_credentials); make both trigger families count consistently, or retire the legacy tickets capacity path once tickets is fully retired. Coordinates with 'Finish retiring the old ticket tables'.</t>
+          <t>Confirm the account has no pending balance or payouts, then delete/reject it in the Stripe dashboard. Owner task.</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
@@ -4805,24 +4805,24 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Closes with identity Wave 9 (tickets), which now rides before the mobile app. The admin_override bypass spans both trigger families; the counting split remains until tickets is retired.</t>
+          <t>Cleanup item from the ambassador / Connect work; low blast radius.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>Delete the stray Stripe Connect account</t>
+          <t>ManyChat - disconnect the Instagram-side integration</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>A leftover Stripe Connect (Express) account from the ambassador / exit workstream needs removing so it doesn't linger.</t>
+          <t>The IG-side ManyChat connection needs to be disconnected / cleaned up. This is teardown of the current Instagram link, separate from the auto-DM build.</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Confirm the account has no pending balance or payouts, then delete/reject it in the Stripe dashboard. Owner task.</t>
+          <t>Disconnect the Instagram account from ManyChat (owner task in ManyChat / Meta); confirm no active automations still reference it.</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
@@ -4832,451 +4832,451 @@
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Cleanup item from the ambassador / Connect work; low blast radius.</t>
+          <t>Distinct from the 'Instagram comment auto-DM (ManyChat)' build row above - that row stays as-is.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>ManyChat - disconnect the Instagram-side integration</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>The IG-side ManyChat connection needs to be disconnected / cleaned up. This is teardown of the current Instagram link, separate from the auto-DM build.</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="inlineStr">
-        <is>
-          <t>Disconnect the Instagram account from ManyChat (owner task in ManyChat / Meta); confirm no active automations still reference it.</t>
-        </is>
-      </c>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="E181" s="8" t="inlineStr">
-        <is>
-          <t>Distinct from the 'Instagram comment auto-DM (ManyChat)' build row above - that row stays as-is.</t>
+          <t>DB / Stripe drift watch items</t>
+        </is>
+      </c>
+      <c r="B181" s="37" t="inlineStr">
+        <is>
+          <t>Ongoing watch on the places where the database and Stripe can drift out of sync: subscription statuses, customer email on email-change, retired legacy prices, orphaned Stripe customers.</t>
+        </is>
+      </c>
+      <c r="C181" s="37" t="inlineStr">
+        <is>
+          <t>Track and periodically reconcile; surface on the admin health dashboard. Pairs with the Q6 tripwire and the 'email change keeps Stripe billing in sync' verify.</t>
+        </is>
+      </c>
+      <c r="D181" s="37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E181" s="38" t="inlineStr">
+        <is>
+          <t>Status drift is now DETECTED nightly by stripe-drift-check (Wave 10, live Sep 18: drift_checks receipts, super-admin bell + email on ghost-member / still-billed shapes; first manual run on prod was clean, 0 alerts). Remaining watch items here: customer email on email-change (Wave 7), retired legacy prices, orphaned Stripe customers. Payment-ledger drift is the Financial Truth phase 3 row.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>DB / Stripe drift watch items</t>
-        </is>
-      </c>
-      <c r="B182" s="37" t="inlineStr">
-        <is>
-          <t>Ongoing watch on the places where the database and Stripe can drift out of sync: subscription statuses, customer email on email-change, retired legacy prices, orphaned Stripe customers.</t>
-        </is>
-      </c>
-      <c r="C182" s="37" t="inlineStr">
-        <is>
-          <t>Track and periodically reconcile; surface on the admin health dashboard. Pairs with the Q6 tripwire and the 'email change keeps Stripe billing in sync' verify.</t>
-        </is>
-      </c>
-      <c r="D182" s="37" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="E182" s="38" t="inlineStr">
-        <is>
-          <t>Status drift is now DETECTED nightly by stripe-drift-check (Wave 10, live Sep 18: drift_checks receipts, super-admin bell + email on ghost-member / still-billed shapes; first manual run on prod was clean, 0 alerts). Remaining watch items here: customer email on email-change (Wave 7), retired legacy prices, orphaned Stripe customers. Payment-ledger drift is the Financial Truth phase 3 row.</t>
+          <t>Waitlist claim links - monitor first real-world use</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>Cancel frees a seat -&gt; the first waitlister is emailed a 24h claim link -&gt; they claim it. Rehearsed as a full matrix on develop and shipped to prod; needs a read-only confirm on its first genuine use.</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>On the next real cancellation that frees a seat on a full, waitlisted event, confirm: notified_at/expires_at stamped, the email sent, the claimant claimed (member_rsvp with metadata source=waitlist_claim), and the waitlist row deleted.</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>Shipped 2026-07-19. Zero-cost proof on first real use, like the Remove &amp; Refund WAIT-mode row.</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t>Waitlist claim links - monitor first real-world use</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>Cancel frees a seat -&gt; the first waitlister is emailed a 24h claim link -&gt; they claim it. Rehearsed as a full matrix on develop and shipped to prod; needs a read-only confirm on its first genuine use.</t>
-        </is>
-      </c>
-      <c r="C183" s="8" t="inlineStr">
-        <is>
-          <t>On the next real cancellation that frees a seat on a full, waitlisted event, confirm: notified_at/expires_at stamped, the email sent, the claimant claimed (member_rsvp with metadata source=waitlist_claim), and the waitlist row deleted.</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="E183" s="8" t="inlineStr">
-        <is>
-          <t>Shipped 2026-07-19. Zero-cost proof on first real use, like the Remove &amp; Refund WAIT-mode row.</t>
-        </is>
-      </c>
+      <c r="A183" s="43" t="inlineStr">
+        <is>
+          <t>BILLING-VIEWS ERA — ADDED 2026-08-03   ·   12 items</t>
+        </is>
+      </c>
+      <c r="B183" s="34" t="n"/>
+      <c r="C183" s="34" t="n"/>
+      <c r="D183" s="34" t="n"/>
+      <c r="E183" s="34" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="43" t="inlineStr">
-        <is>
-          <t>BILLING-VIEWS ERA — ADDED 2026-08-03   ·   12 items</t>
-        </is>
-      </c>
-      <c r="B184" s="34" t="n"/>
-      <c r="C184" s="34" t="n"/>
-      <c r="D184" s="34" t="n"/>
-      <c r="E184" s="34" t="n"/>
+      <c r="A184" s="28" t="inlineStr">
+        <is>
+          <t>Billing views: admin billing panel + member price/renewal display</t>
+        </is>
+      </c>
+      <c r="B184" s="28" t="inlineStr">
+        <is>
+          <t>Admin contact billing panel + member-facing price/renewal display. Three new profile columns (comp_reason, external_paid_through, external_payment_note) are live on both DBs; the UI/code build is in flight.</t>
+        </is>
+      </c>
+      <c r="C184" s="28" t="inlineStr">
+        <is>
+          <t>Extend admin contact detail with live Stripe billing; surface price/renewal/discount on member settings; wire the three new profile columns into admin editors.</t>
+        </is>
+      </c>
+      <c r="D184" s="28" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="E184" s="28" t="inlineStr">
+        <is>
+          <t>Columns live both DBs; code build in flight.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="28" t="inlineStr">
         <is>
-          <t>Billing views: admin billing panel + member price/renewal display</t>
+          <t>Report builder: admin/super_admin any-filter member/payment reports</t>
         </is>
       </c>
       <c r="B185" s="28" t="inlineStr">
         <is>
-          <t>Admin contact billing panel + member-facing price/renewal display. Three new profile columns (comp_reason, external_paid_through, external_payment_note) are live on both DBs; the UI/code build is in flight.</t>
+          <t>Admin/super_admin reporting with arbitrary filters over members and payments. Data-cleanup prerequisite is DONE; build after billing views.</t>
         </is>
       </c>
       <c r="C185" s="28" t="inlineStr">
         <is>
-          <t>Extend admin contact detail with live Stripe billing; surface price/renewal/discount on member settings; wire the three new profile columns into admin editors.</t>
+          <t>Build after billing views lands. Admin/super_admin only; any-filter member + payment reports.</t>
         </is>
       </c>
       <c r="D185" s="28" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>QUEUED-BACKLOGGED</t>
         </is>
       </c>
       <c r="E185" s="28" t="inlineStr">
         <is>
-          <t>Columns live both DBs; code build in flight.</t>
+          <t>v1 proposal complete and approved-in-principle (DB-only cut, 3 entities, column picker, CSV export, 4 presets, server-paginated, ~7 files); resume at build sign-off. Cheap adds discussed: ambassador-referred, price tier, cancel reasons.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="28" t="inlineStr">
         <is>
-          <t>Report builder: admin/super_admin any-filter member/payment reports</t>
+          <t>Business comp invite flow: welcome template + admin invite tool</t>
         </is>
       </c>
       <c r="B186" s="28" t="inlineStr">
         <is>
-          <t>Admin/super_admin reporting with arbitrary filters over members and payments. Data-cleanup prerequisite is DONE; build after billing views.</t>
+          <t>Welcome email template plus an admin tool to invite a business member (comp path).</t>
         </is>
       </c>
       <c r="C186" s="28" t="inlineStr">
         <is>
-          <t>Build after billing views lands. Admin/super_admin only; any-filter member + payment reports.</t>
+          <t>Blocked on Adam: invitee list + design answers. Then template + admin invite UI.</t>
         </is>
       </c>
       <c r="D186" s="28" t="inlineStr">
         <is>
-          <t>QUEUED-BACKLOGGED</t>
+          <t>WAITING ON ADAM: list + design answers</t>
         </is>
       </c>
       <c r="E186" s="28" t="inlineStr">
         <is>
-          <t>v1 proposal complete and approved-in-principle (DB-only cut, 3 entities, column picker, CSV export, 4 presets, server-paginated, ~7 files); resume at build sign-off. Cheap adds discussed: ambassador-referred, price tier, cancel reasons.</t>
+          <t>Needs invitee list + design answers from Adam.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="28" t="inlineStr">
         <is>
-          <t>Business comp invite flow: welcome template + admin invite tool</t>
+          <t>Admin 'Invite comp member' button - form (name, company, email, phone, comp note), creates comp'd account + sends welcome email, note auto-attached to billing view (member + admin); v1 invite flow built without UI, button is the addon</t>
         </is>
       </c>
       <c r="B187" s="28" t="inlineStr">
         <is>
-          <t>Welcome email template plus an admin tool to invite a business member (comp path).</t>
+          <t>Admin UI button/form to invite a complimentary business member: name, company, email, phone, and comp note. Creates the comp'd account, sends the welcome email, and attaches the note to the billing view for both member and admin.</t>
         </is>
       </c>
       <c r="C187" s="28" t="inlineStr">
         <is>
-          <t>Blocked on Adam: invitee list + design answers. Then template + admin invite UI.</t>
+          <t>Addon after v1 invite flow (API/ops path without UI). Build the Invite comp member button + form once the headless invite path exists.</t>
         </is>
       </c>
       <c r="D187" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: list + design answers</t>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="E187" s="28" t="inlineStr">
         <is>
-          <t>Needs invitee list + design answers from Adam.</t>
+          <t>v1 invite flow built without UI; this button is the future addon.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="28" t="inlineStr">
         <is>
-          <t>Admin 'Invite comp member' button - form (name, company, email, phone, comp note), creates comp'd account + sends welcome email, note auto-attached to billing view (member + admin); v1 invite flow built without UI, button is the addon</t>
+          <t>Zane Mackey comp_reason entry</t>
         </is>
       </c>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Admin UI button/form to invite a complimentary business member: name, company, email, phone, and comp note. Creates the comp'd account, sends the welcome email, and attaches the note to the billing view for both member and admin.</t>
+          <t>Record a one-phrase comp_reason on Zane Mackey's profile now that the column exists.</t>
         </is>
       </c>
       <c r="C188" s="28" t="inlineStr">
         <is>
-          <t>Addon after v1 invite flow (API/ops path without UI). Build the Invite comp member button + form once the headless invite path exists.</t>
+          <t>WAITING ON ADAM: one phrase for comp_reason.</t>
         </is>
       </c>
       <c r="D188" s="28" t="inlineStr">
         <is>
-          <t>QUEUED</t>
+          <t>WAITING ON ADAM: one phrase</t>
         </is>
       </c>
       <c r="E188" s="28" t="inlineStr">
         <is>
-          <t>v1 invite flow built without UI; this button is the future addon.</t>
+          <t>One phrase for comp_reason.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="28" t="inlineStr">
         <is>
-          <t>Zane Mackey comp_reason entry</t>
+          <t>Zach Trusky renewal ~Nov/Dec 2026 — honored $1,034 annual</t>
         </is>
       </c>
       <c r="B189" s="28" t="inlineStr">
         <is>
-          <t>Record a one-phrase comp_reason on Zane Mackey's profile now that the column exists.</t>
+          <t>Zach's annual amount lives outside Stripe ($1,034 honored). Need reminder + collection path decision around Nov/Dec 2026.</t>
         </is>
       </c>
       <c r="C189" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: one phrase for comp_reason.</t>
+          <t>Schedule reminder; decide collection path (manual invoice vs Stripe annual vs override).</t>
         </is>
       </c>
       <c r="D189" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM: one phrase</t>
+          <t>SCHEDULED NOV 2026</t>
         </is>
       </c>
       <c r="E189" s="28" t="inlineStr">
         <is>
-          <t>One phrase for comp_reason.</t>
+          <t>Honored $1,034 annual; no Stripe customer today.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="28" t="inlineStr">
         <is>
-          <t>Zach Trusky renewal ~Nov/Dec 2026 — honored $1,034 annual</t>
+          <t>Security: unknown third-party script (batatatech.com) on Glue Up admin pages</t>
         </is>
       </c>
       <c r="B190" s="28" t="inlineStr">
         <is>
-          <t>Zach's annual amount lives outside Stripe ($1,034 honored). Need reminder + collection path decision around Nov/Dec 2026.</t>
+          <t>Unknown batatatech.com script firing on Glue Up admin pages — treat as extension/malware until proven otherwise; audit browsers + rotate passwords.</t>
         </is>
       </c>
       <c r="C190" s="28" t="inlineStr">
         <is>
-          <t>Schedule reminder; decide collection path (manual invoice vs Stripe annual vs override).</t>
+          <t>Browser extension audit on machines that use Glue Up admin; password rotation for affected accounts.</t>
         </is>
       </c>
       <c r="D190" s="28" t="inlineStr">
         <is>
-          <t>SCHEDULED NOV 2026</t>
+          <t>OPEN - Adam chrome://extensions only</t>
         </is>
       </c>
       <c r="E190" s="28" t="inlineStr">
         <is>
-          <t>Honored $1,034 annual; no Stripe customer today.</t>
+          <t>repo confirmed clean 8/4 - scope is Adam's chrome://extensions only</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="28" t="inlineStr">
         <is>
-          <t>Security: unknown third-party script (batatatech.com) on Glue Up admin pages</t>
+          <t>Calendar update-leg verification via throwaway event</t>
         </is>
       </c>
       <c r="B191" s="28" t="inlineStr">
         <is>
-          <t>Unknown batatatech.com script firing on Glue Up admin pages — treat as extension/malware until proven otherwise; audit browsers + rotate passwords.</t>
+          <t>Verify that event-edit REQUEST invites actually move real calendars (ICS sequence / update leg) using a throwaway event.</t>
         </is>
       </c>
       <c r="C191" s="28" t="inlineStr">
         <is>
-          <t>Browser extension audit on machines that use Glue Up admin; password rotation for affected accounts.</t>
+          <t>Create throwaway event, subscribe, edit, confirm calendars update; then delete throwaway.</t>
         </is>
       </c>
       <c r="D191" s="28" t="inlineStr">
         <is>
-          <t>OPEN - Adam chrome://extensions only</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E191" s="28" t="inlineStr">
         <is>
-          <t>repo confirmed clean 8/4 - scope is Adam's chrome://extensions only</t>
+          <t>Throwaway event verification of REQUEST/update path.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="28" t="inlineStr">
         <is>
-          <t>Calendar update-leg verification via throwaway event</t>
+          <t>Resend click-tracking subdomain (DNS)</t>
         </is>
       </c>
       <c r="B192" s="28" t="inlineStr">
         <is>
-          <t>Verify that event-edit REQUEST invites actually move real calendars (ICS sequence / update leg) using a throwaway event.</t>
+          <t>Configure Resend click-tracking subdomain — Adam hands / DNS.</t>
         </is>
       </c>
       <c r="C192" s="28" t="inlineStr">
         <is>
-          <t>Create throwaway event, subscribe, edit, confirm calendars update; then delete throwaway.</t>
+          <t>ADAM DNS: add Resend click-tracking subdomain CNAME + add Resend to SPF include (current SPF is Google-only). Confirmed missing 8/4.</t>
         </is>
       </c>
       <c r="D192" s="28" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADAM - DNS</t>
         </is>
       </c>
       <c r="E192" s="28" t="inlineStr">
         <is>
-          <t>Throwaway event verification of REQUEST/update path.</t>
+          <t>confirmed NOT configured 8/4; also add Resend to SPF include during same DNS visit</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="28" t="inlineStr">
         <is>
-          <t>Resend click-tracking subdomain (DNS)</t>
+          <t>/welcome checkout-flow coverage on develop</t>
         </is>
       </c>
       <c r="B193" s="28" t="inlineStr">
         <is>
-          <t>Configure Resend click-tracking subdomain — Adam hands / DNS.</t>
+          <t>/welcome checkout flow is still untested on develop (no Stripe checkout env there).</t>
         </is>
       </c>
       <c r="C193" s="28" t="inlineStr">
         <is>
-          <t>ADAM DNS: add Resend click-tracking subdomain CNAME + add Resend to SPF include (current SPF is Google-only). Confirmed missing 8/4.</t>
+          <t>WATCH until develop has a Stripe checkout path; then cover /welcome end to end.</t>
         </is>
       </c>
       <c r="D193" s="28" t="inlineStr">
         <is>
-          <t>ADAM - DNS</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E193" s="28" t="inlineStr">
         <is>
-          <t>confirmed NOT configured 8/4; also add Resend to SPF include during same DNS visit</t>
+          <t>Untested on develop; no Stripe checkout env.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="28" t="inlineStr">
         <is>
-          <t>/welcome checkout-flow coverage on develop</t>
+          <t>Retire the Google Sheets tracker path</t>
         </is>
       </c>
       <c r="B194" s="28" t="inlineStr">
         <is>
-          <t>/welcome checkout flow is still untested on develop (no Stripe checkout env there).</t>
+          <t>Repo xlsx under docs/ is the source of truth. Remove/deprecate update-backlog-sheet edge function, its secrets (BACKLOG_*, GOOGLE_SHEETS_SERVICE_ACCOUNT_JSON if unused elsewhere), and the delete/agent-auth additions.</t>
         </is>
       </c>
       <c r="C194" s="28" t="inlineStr">
         <is>
-          <t>WATCH until develop has a Stripe checkout path; then cover /welcome end to end.</t>
+          <t>QUEUED cleanup: delete the edge function (or stub 410), remove BACKLOG_AUTH_SECRET / BACKLOG_AGENT_SECRET / BACKLOG_SHEET_ID (and SA JSON if unused), scrub temp scripts.</t>
         </is>
       </c>
       <c r="D194" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>QUEUED - cleanup</t>
         </is>
       </c>
       <c r="E194" s="28" t="inlineStr">
         <is>
-          <t>Untested on develop; no Stripe checkout env.</t>
+          <t>debug_env already stripped 2026-08-03; full retirement queued.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="28" t="inlineStr">
         <is>
-          <t>Retire the Google Sheets tracker path</t>
+          <t>Admin card PATCH date normalization - external dates should save as noon UTC to avoid timezone off-by-one (Zach precedent)</t>
         </is>
       </c>
       <c r="B195" s="28" t="inlineStr">
         <is>
-          <t>Repo xlsx under docs/ is the source of truth. Remove/deprecate update-backlog-sheet edge function, its secrets (BACKLOG_*, GOOGLE_SHEETS_SERVICE_ACCOUNT_JSON if unused elsewhere), and the delete/agent-auth additions.</t>
+          <t>external_paid_through saved as midnight UTC displays as prior calendar day in US Eastern (Zach showed Nov 30 instead of Dec 1). Admin billing PATCH should normalize date-only inputs to noon UTC.</t>
         </is>
       </c>
       <c r="C195" s="28" t="inlineStr">
         <is>
-          <t>QUEUED cleanup: delete the edge function (or stub 410), remove BACKLOG_AUTH_SECRET / BACKLOG_AGENT_SECRET / BACKLOG_SHEET_ID (and SA JSON if unused), scrub temp scripts.</t>
+          <t>In PATCH /api/admin/members/[id]/billing (and any similar writers), coerce external_paid_through date-only values to YYYY-MM-DDT12:00:00.000Z before save. SMALL.</t>
         </is>
       </c>
       <c r="D195" s="28" t="inlineStr">
         <is>
-          <t>QUEUED - cleanup</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E195" s="28" t="inlineStr">
         <is>
-          <t>debug_env already stripped 2026-08-03; full retirement queued.</t>
+          <t>SMALL/OPEN. Precedent: Zach Trusky external_paid_through 2026-12-01T00:00:00Z → Nov 30 in America/New_York.</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="28" t="inlineStr">
-        <is>
-          <t>Admin card PATCH date normalization - external dates should save as noon UTC to avoid timezone off-by-one (Zach precedent)</t>
-        </is>
-      </c>
-      <c r="B196" s="28" t="inlineStr">
-        <is>
-          <t>external_paid_through saved as midnight UTC displays as prior calendar day in US Eastern (Zach showed Nov 30 instead of Dec 1). Admin billing PATCH should normalize date-only inputs to noon UTC.</t>
-        </is>
-      </c>
-      <c r="C196" s="28" t="inlineStr">
-        <is>
-          <t>In PATCH /api/admin/members/[id]/billing (and any similar writers), coerce external_paid_through date-only values to YYYY-MM-DDT12:00:00.000Z before save. SMALL.</t>
-        </is>
-      </c>
-      <c r="D196" s="28" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E196" s="28" t="inlineStr">
-        <is>
-          <t>SMALL/OPEN. Precedent: Zach Trusky external_paid_through 2026-12-01T00:00:00Z → Nov 30 in America/New_York.</t>
-        </is>
-      </c>
+      <c r="A196" s="43" t="inlineStr">
+        <is>
+          <t>IDENTITY WAVES 0-6A + EXCHANGE ERA — ADDED 2026-08-24   ·   9 items</t>
+        </is>
+      </c>
+      <c r="B196" s="34" t="n"/>
+      <c r="C196" s="34" t="n"/>
+      <c r="D196" s="34" t="n"/>
+      <c r="E196" s="34" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="43" t="inlineStr">
-        <is>
-          <t>IDENTITY WAVES 0-6A + EXCHANGE ERA — ADDED 2026-08-24   ·   9 items</t>
-        </is>
-      </c>
-      <c r="B197" s="34" t="n"/>
-      <c r="C197" s="34" t="n"/>
-      <c r="D197" s="34" t="n"/>
-      <c r="E197" s="34" t="n"/>
+      <c r="A197" s="28" t="inlineStr">
+        <is>
+          <t>Event editor silently reverts required_tier from the deprecated access dials on every save</t>
+        </is>
+      </c>
+      <c r="B197" s="28" t="inlineStr">
+        <is>
+          <t>AdminEventsTab loads the access dials from the deprecated columns (access_type_deprecated ?? access_type, line 713) and then re-derives the canonical required_tier from those dials on every save (lines 827-838 create, 890-901 edit). On any event whose deprecated dials disagree with its canonical required_tier, an unrelated save - a typo fix, a time change - silently reverts access. Confirmed root cause of the Exchange event flipping from public back to social between Aug 11 and Aug 13; it was corrected by hand through the admin UI on Aug 13 and will flip again on the next save.</t>
+        </is>
+      </c>
+      <c r="C197" s="28" t="inlineStr">
+        <is>
+          <t>Make required_tier the value the editor loads FROM, not a value re-derived from deprecated columns on write. Either load the dials from required_tier and dual-write the deprecated columns as the derived side, or drop the deprecated read entirely once the 11 remaining reader files are repointed. Until then, audit for events whose dials disagree with required_tier and reconcile them. Rehearse on develop - this touches every event save path.</t>
+        </is>
+      </c>
+      <c r="D197" s="28" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E197" s="28" t="inlineStr">
+        <is>
+          <t>Root-caused 2026-08-13 during the Exchange flip-back hunt. High blast radius: any event whose dials disagree is one save away from a silent access change.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="28" t="inlineStr">
         <is>
-          <t>Event editor silently reverts required_tier from the deprecated access dials on every save</t>
+          <t>manifest.json declared but missing (site-wide 404)</t>
         </is>
       </c>
       <c r="B198" s="28" t="inlineStr">
         <is>
-          <t>AdminEventsTab loads the access dials from the deprecated columns (access_type_deprecated ?? access_type, line 713) and then re-derives the canonical required_tier from those dials on every save (lines 827-838 create, 890-901 edit). On any event whose deprecated dials disagree with its canonical required_tier, an unrelated save - a typo fix, a time change - silently reverts access. Confirmed root cause of the Exchange event flipping from public back to social between Aug 11 and Aug 13; it was corrected by hand through the admin UI on Aug 13 and will flip again on the next save.</t>
+          <t>src/app/layout.tsx:91 declares manifest: "/manifest.json" and middleware.ts:9 allow-lists the path, but no manifest.json exists in public/. Every page load requests it and gets a 404, so every public page carries a console error and the PWA install prompt never appears.</t>
         </is>
       </c>
       <c r="C198" s="28" t="inlineStr">
         <is>
-          <t>Make required_tier the value the editor loads FROM, not a value re-derived from deprecated columns on write. Either load the dials from required_tier and dual-write the deprecated columns as the derived side, or drop the deprecated read entirely once the 11 remaining reader files are repointed. Until then, audit for events whose dials disagree with required_tier and reconcile them. Rehearse on develop - this touches every event save path.</t>
+          <t>Add public/manifest.json with name, short_name, start_url, display, theme/background colours and the icon-192x192.png / icon-512x512.png already in public/. One file, no code change. Confirm the console is clean on / and /events afterwards.</t>
         </is>
       </c>
       <c r="D198" s="28" t="inlineStr">
@@ -5286,24 +5286,24 @@
       </c>
       <c r="E198" s="28" t="inlineStr">
         <is>
-          <t>Root-caused 2026-08-13 during the Exchange flip-back hunt. High blast radius: any event whose dials disagree is one save away from a silent access change.</t>
+          <t>One-file fix. It is the only console error left on the public pages, so it masks real errors in every console assertion the rehearsals run.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="28" t="inlineStr">
         <is>
-          <t>manifest.json declared but missing (site-wide 404)</t>
+          <t>Anonymous event page 401s (attendance count + host name)</t>
         </is>
       </c>
       <c r="B199" s="28" t="inlineStr">
         <is>
-          <t>src/app/layout.tsx:91 declares manifest: "/manifest.json" and middleware.ts:9 allow-lists the path, but no manifest.json exists in public/. Every page load requests it and gets a 404, so every public page carries a console error and the PWA install prompt never appears.</t>
+          <t>Logged-out visitors on an event page get 401s on two reads: the attendance count and the host name lookup. Fallout from the Jul 9 lockdown that revoked anon on event_participants_view and dropped active_members - correct security, but the public page was never given a sanctioned path to the two harmless values it still displays, so both render empty.</t>
         </is>
       </c>
       <c r="C199" s="28" t="inlineStr">
         <is>
-          <t>Add public/manifest.json with name, short_name, start_url, display, theme/background colours and the icon-192x192.png / icon-512x512.png already in public/. One file, no code change. Confirm the console is clean on / and /events afterwards.</t>
+          <t>Expose only those two values anonymously: a SECURITY DEFINER function returning a scalar attendance count for an event, and one returning a host display name (no email, no phone), both with anon EXECUTE. Do NOT re-grant anon on the underlying views. Verify from outside with the anon key that nothing else leaks.</t>
         </is>
       </c>
       <c r="D199" s="28" t="inlineStr">
@@ -5313,24 +5313,24 @@
       </c>
       <c r="E199" s="28" t="inlineStr">
         <is>
-          <t>One-file fix. It is the only console error left on the public pages, so it masks real errors in every console assertion the rehearsals run.</t>
+          <t>Console noise on every public event page today. Direct consequence of the (correct) Jul 9 anon-readable-view lockdown.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="28" t="inlineStr">
         <is>
-          <t>Anonymous event page 401s (attendance count + host name)</t>
+          <t>Localhost dev reads LIVE Stripe + Resend keys from .env.local</t>
         </is>
       </c>
       <c r="B200" s="28" t="inlineStr">
         <is>
-          <t>Logged-out visitors on an event page get 401s on two reads: the attendance count and the host name lookup. Fallout from the Jul 9 lockdown that revoked anon on event_participants_view and dropped active_members - correct security, but the public page was never given a sanctioned path to the two harmless values it still displays, so both render empty.</t>
+          <t>Local development loads .env.local, which carries production Stripe and Resend credentials. A checkout exercised locally hits live Stripe; a send path exercised locally hits live Resend against real member addresses. Nothing has fired by accident yet - the only thing preventing it is care.</t>
         </is>
       </c>
       <c r="C200" s="28" t="inlineStr">
         <is>
-          <t>Expose only those two values anonymously: a SECURITY DEFINER function returning a scalar attendance count for an event, and one returning a host display name (no email, no phone), both with anon EXECUTE. Do NOT re-grant anon on the underlying views. Verify from outside with the anon key that nothing else leaks.</t>
+          <t>Put TEST Stripe keys and a sandbox Resend key in .env.development.local, which Next loads ahead of .env.local for next dev while leaving production builds untouched. Then confirm a local checkout lands in the Stripe test dashboard and a local send reaches no real inbox.</t>
         </is>
       </c>
       <c r="D200" s="28" t="inlineStr">
@@ -5340,24 +5340,24 @@
       </c>
       <c r="E200" s="28" t="inlineStr">
         <is>
-          <t>Console noise on every public event page today. Direct consequence of the (correct) Jul 9 anon-readable-view lockdown.</t>
+          <t>Raised during the Exchange develop rehearsals. Low effort, removes an entire class of accident. Pairs with the develop seed gaps row.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="28" t="inlineStr">
         <is>
-          <t>Localhost dev reads LIVE Stripe + Resend keys from .env.local</t>
+          <t>Develop seed gaps: no handle_new_user trigger, missing membership-card credential, fake sub_SEED003</t>
         </is>
       </c>
       <c r="B201" s="28" t="inlineStr">
         <is>
-          <t>Local development loads .env.local, which carries production Stripe and Resend credentials. A checkout exercised locally hits live Stripe; a send path exercised locally hits live Resend against real member addresses. Nothing has fired by accident yet - the only thing preventing it is care.</t>
+          <t>The develop database is not a faithful rehearsal surface in three ways. (1) The handle_new_user trigger that creates a profile on signup does not exist there, so signup behaves differently than prod. (2) The membership-card attendance credential that the wallet and door flows expect is missing from the seed. (3) A seeded subscription id (sub_SEED003) is not a real Stripe object, so any path that retrieves it from Stripe fails in a way prod never would.</t>
         </is>
       </c>
       <c r="C201" s="28" t="inlineStr">
         <is>
-          <t>Put TEST Stripe keys and a sandbox Resend key in .env.development.local, which Next loads ahead of .env.local for next dev while leaving production builds untouched. Then confirm a local checkout lands in the Stripe test dashboard and a local send reaches no real inbox.</t>
+          <t>Add all three to the develop seed: install handle_new_user on develop to match prod, seed the membership-card credential, and either create a real Stripe test subscription or make the seeded id obviously non-Stripe so code short-circuits instead of erroring. Re-run one signup, one door scan and one billing read on develop to confirm parity.</t>
         </is>
       </c>
       <c r="D201" s="28" t="inlineStr">
@@ -5367,170 +5367,170 @@
       </c>
       <c r="E201" s="28" t="inlineStr">
         <is>
-          <t>Raised during the Exchange develop rehearsals. Low effort, removes an entire class of accident. Pairs with the develop seed gaps row.</t>
+          <t>Each gap has already cost rehearsal time by producing a develop-only failure that does not exist in prod. Closing them is what makes future rehearsals trustworthy.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="28" t="inlineStr">
         <is>
-          <t>Develop seed gaps: no handle_new_user trigger, missing membership-card credential, fake sub_SEED003</t>
+          <t>comp-invite carries a local resolver replica (three copies of resolution logic)</t>
         </is>
       </c>
       <c r="B202" s="28" t="inlineStr">
         <is>
-          <t>The develop database is not a faithful rehearsal surface in three ways. (1) The handle_new_user trigger that creates a profile on signup does not exist there, so signup behaves differently than prod. (2) The membership-card attendance credential that the wallet and door flows expect is missing from the seed. (3) A seeded subscription id (sub_SEED003) is not a real Stripe object, so any path that retrieves it from Stripe fails in a way prod never would.</t>
+          <t>comp-invite implements its own person-resolution logic instead of importing _shared/resolvePerson, so identity resolution now lives in three places: the shared resolver (15 adopters), the three Wave 3D database functions, and this local replica. Each copy drifts independently the next time the resolution rules change.</t>
         </is>
       </c>
       <c r="C202" s="28" t="inlineStr">
         <is>
-          <t>Add all three to the develop seed: install handle_new_user on develop to match prod, seed the membership-card credential, and either create a real Stripe test subscription or make the seeded id obviously non-Stripe so code short-circuits instead of erroring. Re-run one signup, one door scan and one billing read on develop to confirm parity.</t>
+          <t>Repoint comp-invite onto _shared/resolvePerson and delete the replica. Do not modify the shared resolver to accommodate it; if the adoption is impossible without a resolver change, stop and report which prior adopters would need redeploy.</t>
         </is>
       </c>
       <c r="D202" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E202" s="28" t="inlineStr">
         <is>
-          <t>Each gap has already cost rehearsal time by producing a develop-only failure that does not exist in prod. Closing them is what makes future rehearsals trustworthy.</t>
+          <t>Drift watch. Not wrong today, but it is the one edge function guaranteed to disagree with the other 15 after the next rule change.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="28" t="inlineStr">
         <is>
-          <t>comp-invite carries a local resolver replica (three copies of resolution logic)</t>
+          <t>Duplicate people rows labeled, merge adjudication deferred (Josh x3, Lance x3)</t>
         </is>
       </c>
       <c r="B203" s="28" t="inlineStr">
         <is>
-          <t>comp-invite implements its own person-resolution logic instead of importing _shared/resolvePerson, so identity resolution now lives in three places: the shared resolver (15 adopters), the three Wave 3D database functions, and this local replica. Each copy drifts independently the next time the resolution rules change.</t>
+          <t>Two humans hold three people rows each. Josh: two canceled member rows plus a crystal.66 row. Lance: one active row plus two relics that hold zero attendance credentials and zero exchange_intake references. All six were labeled during the status pass; none were merged, because choosing the canonical row is a judgment call and Adam adjudicates fuzzies.</t>
         </is>
       </c>
       <c r="C203" s="28" t="inlineStr">
         <is>
-          <t>Repoint comp-invite onto _shared/resolvePerson and delete the replica. Do not modify the shared resolver to accommodate it; if the adoption is impossible without a resolver change, stop and report which prior adopters would need redeploy.</t>
+          <t>Adam picks the surviving row per human. Then merge additively: repoint references to the survivor and keep the losers as tombstones with metadata rather than deleting them. Re-confirm the two Lance relics still hold zero references immediately before any merge.</t>
         </is>
       </c>
       <c r="D203" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WAITING ON ADAM</t>
         </is>
       </c>
       <c r="E203" s="28" t="inlineStr">
         <is>
-          <t>Drift watch. Not wrong today, but it is the one edge function guaranteed to disagree with the other 15 after the next rule change.</t>
+          <t>Labeled during the Aug 19 status pass and deliberately left unmerged. Six rows, two humans. Folds naturally into the contacts fold (6B-6E). 2026-08-25: Josh's 4 hub_members rows were purged on the primary identity (a5f1b294) only; both duplicate rows held zero hub memberships, so that cleanup did not depend on this adjudication and does not constrain it.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="28" t="inlineStr">
         <is>
-          <t>Duplicate people rows labeled, merge adjudication deferred (Josh x3, Lance x3)</t>
+          <t>Andrea Baquero past_due watch (invited Exchange registrant)</t>
         </is>
       </c>
       <c r="B204" s="28" t="inlineStr">
         <is>
-          <t>Two humans hold three people rows each. Josh: two canceled member rows plus a crystal.66 row. Lance: one active row plus two relics that hold zero attendance credentials and zero exchange_intake references. All six were labeled during the status pass; none were merged, because choosing the canonical row is a judgment call and Adam adjudicates fuzzies.</t>
+          <t>Andrea Baquero is past_due on billing and is also an invited registrant for the Aug 27 Exchange. If the past_due state persists, member gating could turn her away at a door she was personally invited to.</t>
         </is>
       </c>
       <c r="C204" s="28" t="inlineStr">
         <is>
-          <t>Adam picks the surviving row per human. Then merge additively: repoint references to the survivor and keep the losers as tombstones with metadata rather than deleting them. Re-confirm the two Lance relics still hold zero references immediately before any merge.</t>
+          <t>Watch through Aug 27. Either resolve the billing state before the event or confirm her Exchange credential is not tier-gated. Read-only until Adam decides how to handle the billing side.</t>
         </is>
       </c>
       <c r="D204" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E204" s="28" t="inlineStr">
         <is>
-          <t>Labeled during the Aug 19 status pass and deliberately left unmerged. Six rows, two humans. Folds naturally into the contacts fold (6B-6E). 2026-08-25: Josh's 4 hub_members rows were purged on the primary identity (a5f1b294) only; both duplicate rows held zero hub memberships, so that cleanup did not depend on this adjudication and does not constrain it.</t>
+          <t>Time-boxed: this row closes after the Aug 27 Exchange, either resolved or converted into an ordinary billing follow-up. Aug 25: the 3+1 member_tier repairs done tonight included the tier-null row the payment-failure webhook re-created on this account Aug 24 — see the member_tier invariant row. The past_due watch itself still stands through Aug 27. Aug 26: RESOLVED to watch-only — billing email sent Aug 26; card in Stripe auto-retry; attends Aug 27 event; Adam reports ~2 attended events never captured at check-in.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="28" t="inlineStr">
         <is>
-          <t>Andrea Baquero past_due watch (invited Exchange registrant)</t>
+          <t>Exchange v2 blueprint (mixer + intake, post-Aug-27)</t>
         </is>
       </c>
       <c r="B205" s="28" t="inlineStr">
         <is>
-          <t>Andrea Baquero is past_due on billing and is also an invited registrant for the Aug 27 Exchange. If the past_due state persists, member gating could turn her away at a door she was personally invited to.</t>
+          <t>Everything the dress rehearsal surfaced that did not justify building before the event: a reset control with a confirm guard; a standalone discard for a pending round (today only reshuffle exists, which replaces rather than discards); drag-a-person-between-tables; revisiting the 30-second minimum clamp on round duration (saveConfig floors it, so short demo rounds are impossible from the UI); a create-flow for setting up a mixer night from scratch; a partner-pool toggle; and answer-aware matching that seats people by their four intake answers rather than purely by repeat-pair avoidance.</t>
         </is>
       </c>
       <c r="C205" s="28" t="inlineStr">
         <is>
-          <t>Watch through Aug 27. Either resolve the billing state before the event or confirm her Exchange credential is not tier-gated. Read-only until Adam decides how to handle the billing side.</t>
+          <t>Own detailed scope after Aug 27, informed by what actually happens on the night. Nothing here blocks v1. Sequence by what the night proves is missing, not by the order of this list.</t>
         </is>
       </c>
       <c r="D205" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="E205" s="28" t="inlineStr">
         <is>
-          <t>Time-boxed: this row closes after the Aug 27 Exchange, either resolved or converted into an ordinary billing follow-up. Aug 25: the 3+1 member_tier repairs done tonight included the tier-null row the payment-failure webhook re-created on this account Aug 24 — see the member_tier invariant row. The past_due watch itself still stands through Aug 27. Aug 26: RESOLVED to watch-only — billing email sent Aug 26; card in Stripe auto-retry; attends Aug 27 event; Adam reports ~2 attended events never captured at check-in.</t>
+          <t>Compiled from the Aug 24 full-dress rehearsal. v1 shipped Aug 24 (viewer, mixer engine, board, UTM capture); the two findings worth fixing immediately - unseated visibility and the board email fallback - already shipped.</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="28" t="inlineStr">
-        <is>
-          <t>Exchange v2 blueprint (mixer + intake, post-Aug-27)</t>
-        </is>
-      </c>
-      <c r="B206" s="28" t="inlineStr">
-        <is>
-          <t>Everything the dress rehearsal surfaced that did not justify building before the event: a reset control with a confirm guard; a standalone discard for a pending round (today only reshuffle exists, which replaces rather than discards); drag-a-person-between-tables; revisiting the 30-second minimum clamp on round duration (saveConfig floors it, so short demo rounds are impossible from the UI); a create-flow for setting up a mixer night from scratch; a partner-pool toggle; and answer-aware matching that seats people by their four intake answers rather than purely by repeat-pair avoidance.</t>
-        </is>
-      </c>
-      <c r="C206" s="28" t="inlineStr">
-        <is>
-          <t>Own detailed scope after Aug 27, informed by what actually happens on the night. Nothing here blocks v1. Sequence by what the night proves is missing, not by the order of this list.</t>
-        </is>
-      </c>
-      <c r="D206" s="28" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="E206" s="28" t="inlineStr">
-        <is>
-          <t>Compiled from the Aug 24 full-dress rehearsal. v1 shipped Aug 24 (viewer, mixer engine, board, UTM capture); the two findings worth fixing immediately - unseated visibility and the board email fallback - already shipped.</t>
-        </is>
-      </c>
+      <c r="A206" s="43" t="inlineStr">
+        <is>
+          <t>[P0] FINANCIAL TRUTH PROJECT + AUG 25 FINDINGS — ADDED 2026-08-25   ·   8 items</t>
+        </is>
+      </c>
+      <c r="B206" s="34" t="n"/>
+      <c r="C206" s="34" t="n"/>
+      <c r="D206" s="34" t="n"/>
+      <c r="E206" s="34" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="43" t="inlineStr">
-        <is>
-          <t>[P0] FINANCIAL TRUTH PROJECT + AUG 25 FINDINGS — ADDED 2026-08-25   ·   8 items</t>
-        </is>
-      </c>
-      <c r="B207" s="34" t="n"/>
-      <c r="C207" s="34" t="n"/>
-      <c r="D207" s="34" t="n"/>
-      <c r="E207" s="34" t="n"/>
+      <c r="A207" s="28" t="inlineStr">
+        <is>
+          <t>[P0] Financial truth phase 1 — backfill the payment ledger from Stripe (all-time)</t>
+        </is>
+      </c>
+      <c r="B207" s="28" t="inlineStr">
+        <is>
+          <t>The database has never held a complete record of money received. 62 payment rows are confirmed missing, and the gap is not a single window: it spans the pre-app era (money collected before this application existed and therefore never written anywhere), the 5 subscribers who were never migrated into the app, and ordinary in-app payments the webhook dropped. Trinity French is the worked case study — $225 paid to Stripe, $0 of it in the ledger — and she is one of 62, not an exception. Every downstream number (MRR, churn, revenue by tier, the financial dashboard, any report built on payments) is computed from this incomplete table, so all of them are wrong by an unknown amount until the ledger is whole.</t>
+        </is>
+      </c>
+      <c r="C207" s="28" t="inlineStr">
+        <is>
+          <t>Backfill from Stripe as the source of truth, all-time, before touching anything downstream. Pull every charge / invoice / payment_intent from account creation forward, match to the person record through the unified resolver, and write the missing rows idempotently keyed on the Stripe object id so a re-run cannot double-post. Cover the three populations explicitly: pre-app-era payments, the 5 unmigrated subscribers, and the 62 confirmed misses. Reconcile the $809 of open invoices in the same pass — $645 is stranded on canceled subscriptions and should be voided, $170 is pre-app era, and only $114 is genuinely collectible. Rehearse the whole backfill on develop and diff the resulting totals against Stripe before running it against prod.</t>
+        </is>
+      </c>
+      <c r="D207" s="28" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E207" s="28" t="inlineStr">
+        <is>
+          <t>Phase 1 of 4. Blocks phases 2-4 and every financial number in the product. Evidence: 62 confirmed missing payment rows; Trinity French $225 paid / $0 recorded; $809 open invoices ($645 to void on canceled subs, $170 pre-app era, $114 real). Backfill must be idempotent — it will be run more than once.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 1 — backfill the payment ledger from Stripe (all-time)</t>
+          <t>[P0] Financial truth phase 2 — fix the webhook silent-skip defect + add stripe_payment_intent_id</t>
         </is>
       </c>
       <c r="B208" s="28" t="inlineStr">
         <is>
-          <t>The database has never held a complete record of money received. 62 payment rows are confirmed missing, and the gap is not a single window: it spans the pre-app era (money collected before this application existed and therefore never written anywhere), the 5 subscribers who were never migrated into the app, and ordinary in-app payments the webhook dropped. Trinity French is the worked case study — $225 paid to Stripe, $0 of it in the ledger — and she is one of 62, not an exception. Every downstream number (MRR, churn, revenue by tier, the financial dashboard, any report built on payments) is computed from this incomplete table, so all of them are wrong by an unknown amount until the ledger is whole.</t>
+          <t>The Stripe webhook silently skips payments rather than failing loudly, which is why the ledger drifted without anyone noticing: a dropped payment produces no error, no alert and no row, so the only evidence is an absence nobody is looking for. The payments table also has no stripe_payment_intent_id column, so there is no durable key tying a stored row back to the Stripe object it came from — which makes both deduplication and reconciliation guesswork.</t>
         </is>
       </c>
       <c r="C208" s="28" t="inlineStr">
         <is>
-          <t>Backfill from Stripe as the source of truth, all-time, before touching anything downstream. Pull every charge / invoice / payment_intent from account creation forward, match to the person record through the unified resolver, and write the missing rows idempotently keyed on the Stripe object id so a re-run cannot double-post. Cover the three populations explicitly: pre-app-era payments, the 5 unmigrated subscribers, and the 62 confirmed misses. Reconcile the $809 of open invoices in the same pass — $645 is stranded on canceled subscriptions and should be voided, $170 is pre-app era, and only $114 is genuinely collectible. Rehearse the whole backfill on develop and diff the resulting totals against Stripe before running it against prod.</t>
+          <t>Two changes, both prerequisites for the reconciliation in phase 3. (1) Replace every silent skip in the webhook handler with a loud failure: log the Stripe event id, the reason, and alert — never return 200 on an unwritten payment. (2) Add stripe_payment_intent_id to the payments table with a unique index, populate it in the phase 1 backfill, and write it on every new payment. Prove the fix with a Stripe-CLI replay of the exact event shapes that were being skipped, on develop first.</t>
         </is>
       </c>
       <c r="D208" s="28" t="inlineStr">
@@ -5540,24 +5540,24 @@
       </c>
       <c r="E208" s="28" t="inlineStr">
         <is>
-          <t>Phase 1 of 4. Blocks phases 2-4 and every financial number in the product. Evidence: 62 confirmed missing payment rows; Trinity French $225 paid / $0 recorded; $809 open invoices ($645 to void on canceled subs, $170 pre-app era, $114 real). Backfill must be idempotent — it will be run more than once.</t>
+          <t>Phase 2 of 4. This is the defect that created the hole — fixing it stops the ledger re-diverging the moment phase 1 finishes. The new column is what phase 3 joins on. Aug 26: Requirement: journal invoice.voided (Stripe currently sole truth on voids, Rich case Aug 26).</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 2 — fix the webhook silent-skip defect + add stripe_payment_intent_id</t>
+          <t>[P0] Financial truth phase 3 — nightly two-way reconciliation with loud mismatch alerts</t>
         </is>
       </c>
       <c r="B209" s="28" t="inlineStr">
         <is>
-          <t>The Stripe webhook silently skips payments rather than failing loudly, which is why the ledger drifted without anyone noticing: a dropped payment produces no error, no alert and no row, so the only evidence is an absence nobody is looking for. The payments table also has no stripe_payment_intent_id column, so there is no durable key tying a stored row back to the Stripe object it came from — which makes both deduplication and reconciliation guesswork.</t>
+          <t>Once the ledger is whole (phase 1) and the webhook stops dropping rows (phase 2), the remaining risk is silent drift: any future gap between Stripe and the database is invisible until someone audits by hand, which is exactly how 62 rows accumulated. Nothing today compares the two systems on a schedule.</t>
         </is>
       </c>
       <c r="C209" s="28" t="inlineStr">
         <is>
-          <t>Two changes, both prerequisites for the reconciliation in phase 3. (1) Replace every silent skip in the webhook handler with a loud failure: log the Stripe event id, the reason, and alert — never return 200 on an unwritten payment. (2) Add stripe_payment_intent_id to the payments table with a unique index, populate it in the phase 1 backfill, and write it on every new payment. Prove the fix with a Stripe-CLI replay of the exact event shapes that were being skipped, on develop first.</t>
+          <t>Scheduled nightly job that reconciles in BOTH directions — every Stripe payment must exist in the ledger, and every ledger row must exist in Stripe — joined on stripe_payment_intent_id. Any mismatch alerts loudly (not a log line nobody reads) with the offending ids attached, and surfaces on the admin health dashboard alongside the cron / webhook widgets. Pairs with the Q6 canceled-drift tripwire and the DB/Stripe drift watch rows; consider folding them into one money-drift check rather than three.</t>
         </is>
       </c>
       <c r="D209" s="28" t="inlineStr">
@@ -5567,24 +5567,24 @@
       </c>
       <c r="E209" s="28" t="inlineStr">
         <is>
-          <t>Phase 2 of 4. This is the defect that created the hole — fixing it stops the ledger re-diverging the moment phase 1 finishes. The new column is what phase 3 joins on. Aug 26: Requirement: journal invoice.voided (Stripe currently sole truth on voids, Rich case Aug 26).</t>
+          <t>Phase 3 of 4. Turns 'the numbers are right tonight' into 'the numbers stay right'. Depends on the stripe_payment_intent_id column from phase 2.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 3 — nightly two-way reconciliation with loud mismatch alerts</t>
+          <t>[P0] Financial truth phase 4 — rebuild the financial dashboard on the clean ledger</t>
         </is>
       </c>
       <c r="B210" s="28" t="inlineStr">
         <is>
-          <t>Once the ledger is whole (phase 1) and the webhook stops dropping rows (phase 2), the remaining risk is silent drift: any future gap between Stripe and the database is invisible until someone audits by hand, which is exactly how 62 rows accumulated. Nothing today compares the two systems on a schedule.</t>
+          <t>The financial dashboard was built in Lovable on the incomplete payments table and has never been trusted (churn once displayed 2055%). Rebuilding it before the ledger is whole would only re-derive wrong numbers from a wrong source, so it is deliberately sequenced last.</t>
         </is>
       </c>
       <c r="C210" s="28" t="inlineStr">
         <is>
-          <t>Scheduled nightly job that reconciles in BOTH directions — every Stripe payment must exist in the ledger, and every ledger row must exist in Stripe — joined on stripe_payment_intent_id. Any mismatch alerts loudly (not a log line nobody reads) with the offending ids attached, and surfaces on the admin health dashboard alongside the cron / webhook widgets. Pairs with the Q6 canceled-drift tripwire and the DB/Stripe drift watch rows; consider folding them into one money-drift check rather than three.</t>
+          <t>After phases 1-3 land, rebuild MRR, churn and revenue-by-tier directly on the reconciled ledger, then verify each figure against Stripe by hand once before trusting it. Absorbs the existing 'verify the financial dashboard' and 'verify the admin financial data function' rows, and is where the three-bucket collected / projected / churned view should land.</t>
         </is>
       </c>
       <c r="D210" s="28" t="inlineStr">
@@ -5594,24 +5594,24 @@
       </c>
       <c r="E210" s="28" t="inlineStr">
         <is>
-          <t>Phase 3 of 4. Turns 'the numbers are right tonight' into 'the numbers stay right'. Depends on the stripe_payment_intent_id column from phase 2.</t>
+          <t>Phase 4 of 4. Do NOT start before phase 1 completes — a dashboard on a partial ledger is the current problem, rebuilt. Supersedes the older FINANCIALS verify rows.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="28" t="inlineStr">
         <is>
-          <t>[P0] Financial truth phase 4 — rebuild the financial dashboard on the clean ledger</t>
+          <t>member_tier invariant hole: an active member can hold a null tier, and the webhook re-creates them</t>
         </is>
       </c>
       <c r="B211" s="28" t="inlineStr">
         <is>
-          <t>The financial dashboard was built in Lovable on the incomplete payments table and has never been trusted (churn once displayed 2055%). Rebuilding it before the ledger is whole would only re-derive wrong numbers from a wrong source, so it is deliberately sequenced last.</t>
+          <t>Nothing in the schema forbids the broken state. There is no CHECK constraint and no default preventing an active member from having a null member_tier, the partner member type has no tier mapping at all (so partners are structurally tier-null), and the payment-failure webhook re-creates tier-null rows even after they have been repaired by hand — Andrea's Aug 24 case is the proof that manual repair alone does not hold. Anything that gates on tier (event access, portal views, pricing) behaves unpredictably against a null.</t>
         </is>
       </c>
       <c r="C211" s="28" t="inlineStr">
         <is>
-          <t>After phases 1-3 land, rebuild MRR, churn and revenue-by-tier directly on the reconciled ledger, then verify each figure against Stripe by hand once before trusting it. Absorbs the existing 'verify the financial dashboard' and 'verify the admin financial data function' rows, and is where the three-bucket collected / projected / churned view should land.</t>
+          <t>Close the hole at the database level rather than by repeated repair. Decide the correct tier for the partner type first (it needs a real mapping, not a null), then add a CHECK constraint or default that makes 'active with null tier' unrepresentable, and fix the payment-failure webhook path so it preserves the existing tier instead of writing a row without one. Repair the outstanding rows in the same pass and re-check after the next real payment failure. Follow the incremental CHECK-constraint approach already agreed on the enums row — one table, carefully, not a schema-wide sweep.</t>
         </is>
       </c>
       <c r="D211" s="28" t="inlineStr">
@@ -5621,24 +5621,24 @@
       </c>
       <c r="E211" s="28" t="inlineStr">
         <is>
-          <t>Phase 4 of 4. Do NOT start before phase 1 completes — a dashboard on a partial ledger is the current problem, rebuilt. Supersedes the older FINANCIALS verify rows.</t>
+          <t>Aug 25: the 3+1 tier repairs were done tonight, but they are repairs, not a fix — the webhook will re-create tier-null rows until the write path and the constraint both change. Partner-type mapping is the open decision inside this row. Verified end state 2026-08-25: Jacob Cohen, JD Davis and Vaishali Willis all read member_tier 'social'; Andrea Baquero's row reads social too (updated 20:19:51 UTC) but she is still past_due, so the Stripe retry did not clear the money. 13 people rows holding a member role still carry a null tier, and exactly ONE of those is active - partnertest@704collective.com - which is the partner-type mapping hole above rather than a missed repair. ~20 people rows carry member role with null status; partnertest maps to no tier; normalize during invariant fix.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="28" t="inlineStr">
         <is>
-          <t>member_tier invariant hole: an active member can hold a null tier, and the webhook re-creates them</t>
+          <t>hubs.created_by is NOT NULL ON DELETE CASCADE — deleting a creator profile destroys their hubs</t>
         </is>
       </c>
       <c r="B212" s="28" t="inlineStr">
         <is>
-          <t>Nothing in the schema forbids the broken state. There is no CHECK constraint and no default preventing an active member from having a null member_tier, the partner member type has no tier mapping at all (so partners are structurally tier-null), and the payment-failure webhook re-creates tier-null rows even after they have been repaired by hand — Andrea's Aug 24 case is the proof that manual repair alone does not hold. Anything that gates on tier (event access, portal views, pricing) behaves unpredictably against a null.</t>
+          <t>The hubs.created_by foreign key is NOT NULL with ON DELETE CASCADE, so hard-deleting a profile deletes every hub that person created and everything those hubs contain. This is a live footgun on any exit or cleanup workstream: an ordinary-looking profile delete silently takes member-facing content with it, and there is nothing in the admin UI that warns about it.</t>
         </is>
       </c>
       <c r="C212" s="28" t="inlineStr">
         <is>
-          <t>Close the hole at the database level rather than by repeated repair. Decide the correct tier for the partner type first (it needs a real mapping, not a null), then add a CHECK constraint or default that makes 'active with null tier' unrepresentable, and fix the payment-failure webhook path so it preserves the existing tier instead of writing a row without one. Repair the outstanding rows in the same pass and re-check after the next real payment failure. Follow the incremental CHECK-constraint approach already agreed on the enums row — one table, carefully, not a schema-wide sweep.</t>
+          <t>Change the cascade to something survivable: make created_by nullable with ON DELETE SET NULL, or repoint deleted creators to an organisation-owned system account, so hubs outlive the person who made them. Until that lands, treat any profile hard-delete as a two-step operation — audit owned content first (the read-first footprint audit already used on member removals), reassign or purge deliberately, then delete.</t>
         </is>
       </c>
       <c r="D212" s="28" t="inlineStr">
@@ -5648,209 +5648,455 @@
       </c>
       <c r="E212" s="28" t="inlineStr">
         <is>
-          <t>Aug 25: the 3+1 tier repairs were done tonight, but they are repairs, not a fix — the webhook will re-create tier-null rows until the write path and the constraint both change. Partner-type mapping is the open decision inside this row. Verified end state 2026-08-25: Jacob Cohen, JD Davis and Vaishali Willis all read member_tier 'social'; Andrea Baquero's row reads social too (updated 20:19:51 UTC) but she is still past_due, so the Stripe retry did not clear the money. 13 people rows holding a member role still carry a null tier, and exactly ONE of those is active - partnertest@704collective.com - which is the partner-type mapping hole above rather than a missed repair. ~20 people rows carry member role with null status; partnertest maps to no tier; normalize during invariant fix.</t>
+          <t>Aug 25: surfaced during the Josh hub-membership cleanup forensics, not because Josh owned anything - he created zero hubs. All four hubs (The Arrival, Business Founders, Eats &amp; Experiences, The Wellness) are created_by Adam, so the whole Network content structure hangs off one profile row and that is where the exposure sits. Soft deletes are safe; the hard-delete path (admin-delete-user, manual profile delete) is the footgun. Same class as the bulk-delete atomicity row.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>hubs.created_by is NOT NULL ON DELETE CASCADE — deleting a creator profile destroys their hubs</t>
+          <t>Retention watch: 7 members exiting by Sep 13 — $287/mo MRR at risk</t>
         </is>
       </c>
       <c r="B213" s="28" t="inlineStr">
         <is>
-          <t>The hubs.created_by foreign key is NOT NULL with ON DELETE CASCADE, so hard-deleting a profile deletes every hub that person created and everything those hubs contain. This is a live footgun on any exit or cleanup workstream: an ordinary-looking profile delete silently takes member-facing content with it, and there is nothing in the admin UI that warns about it.</t>
+          <t>Seven members are on track to exit by Sep 13, representing $287 per month of recurring revenue. Recorded as a dated watch so the number is tracked deliberately rather than discovered in a month-end total.</t>
         </is>
       </c>
       <c r="C213" s="28" t="inlineStr">
         <is>
-          <t>Change the cascade to something survivable: make created_by nullable with ON DELETE SET NULL, or repoint deleted creators to an organisation-owned system account, so hubs outlive the person who made them. Until that lands, treat any profile hard-delete as a two-step operation — audit owned content first (the read-first footprint audit already used on member removals), reassign or purge deliberately, then delete.</t>
+          <t>Track through Sep 13. Decide per member whether anything is worth doing (conversation, offer, pause instead of cancel) before the exits land, and confirm the actual outcome against this figure afterwards. Feeds the member-cancellation retention flow row — that build should be scoped by what these seven actually say.</t>
         </is>
       </c>
       <c r="D213" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="E213" s="28" t="inlineStr">
         <is>
-          <t>Aug 25: surfaced during the Josh hub-membership cleanup forensics, not because Josh owned anything - he created zero hubs. All four hubs (The Arrival, Business Founders, Eats &amp; Experiences, The Wellness) are created_by Adam, so the whole Network content structure hangs off one profile row and that is where the exposure sits. Soft deletes are safe; the hard-delete path (admin-delete-user, manual profile delete) is the footgun. Same class as the bulk-delete atomicity row.</t>
+          <t>Time-boxed: this row closes after Sep 13, either as a recorded loss or as retained members. $287/mo across 7 members. Note the financial figures here come from Stripe, not from the ledger the financial-truth project is fixing.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="28" t="inlineStr">
         <is>
-          <t>Retention watch: 7 members exiting by Sep 13 — $287/mo MRR at risk</t>
+          <t>Members-by-type admin view — spec discussion in progress, build pending Adam's five answers</t>
         </is>
       </c>
       <c r="B214" s="28" t="inlineStr">
         <is>
-          <t>Seven members are on track to exit by Sep 13, representing $287 per month of recurring revenue. Recorded as a dated watch so the number is tracked deliberately rather than discovered in a month-end total.</t>
+          <t>An admin view of members broken out by type. The spec conversation with Adam is underway but not finished: five questions remain open, and the build is deliberately not started until they are answered, so that the view is built once against a settled definition rather than reworked.</t>
         </is>
       </c>
       <c r="C214" s="28" t="inlineStr">
         <is>
-          <t>Track through Sep 13. Decide per member whether anything is worth doing (conversation, offer, pause instead of cancel) before the exits land, and confirm the actual outcome against this figure afterwards. Feeds the member-cancellation retention flow row — that build should be scoped by what these seven actually say.</t>
+          <t>Finish the spec discussion with Adam and capture the five answers here, then build. Reuse the canonical person record and the existing member-type vocabulary rather than inventing a parallel definition — the same classification that the member_counts view and the directory work already use.</t>
         </is>
       </c>
       <c r="D214" s="28" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WAITING ON ADAM: five answers</t>
         </is>
       </c>
       <c r="E214" s="28" t="inlineStr">
         <is>
-          <t>Time-boxed: this row closes after Sep 13, either as a recorded loss or as retained members. $287/mo across 7 members. Note the financial figures here come from Stripe, not from the ledger the financial-truth project is fixing.</t>
+          <t>Spec in progress as of Aug 25. Build is intentionally blocked, not forgotten. Related to the unified admin users view and the member directory rows.</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="28" t="inlineStr">
-        <is>
-          <t>Members-by-type admin view — spec discussion in progress, build pending Adam's five answers</t>
-        </is>
-      </c>
-      <c r="B215" s="28" t="inlineStr">
-        <is>
-          <t>An admin view of members broken out by type. The spec conversation with Adam is underway but not finished: five questions remain open, and the build is deliberately not started until they are answered, so that the view is built once against a settled definition rather than reworked.</t>
-        </is>
-      </c>
-      <c r="C215" s="28" t="inlineStr">
-        <is>
-          <t>Finish the spec discussion with Adam and capture the five answers here, then build. Reuse the canonical person record and the existing member-type vocabulary rather than inventing a parallel definition — the same classification that the member_counts view and the directory work already use.</t>
-        </is>
-      </c>
-      <c r="D215" s="28" t="inlineStr">
-        <is>
-          <t>WAITING ON ADAM: five answers</t>
-        </is>
-      </c>
-      <c r="E215" s="28" t="inlineStr">
-        <is>
-          <t>Spec in progress as of Aug 25. Build is intentionally blocked, not forgotten. Related to the unified admin users view and the member directory rows.</t>
-        </is>
-      </c>
+      <c r="A215" s="43" t="inlineStr">
+        <is>
+          <t>AUG 26 FINDINGS — ADDED 2026-08-26   ·   4 items</t>
+        </is>
+      </c>
+      <c r="B215" s="34" t="n"/>
+      <c r="C215" s="34" t="n"/>
+      <c r="D215" s="34" t="n"/>
+      <c r="E215" s="34" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="43" t="inlineStr">
-        <is>
-          <t>AUG 26 FINDINGS — ADDED 2026-08-26   ·   4 items</t>
-        </is>
-      </c>
-      <c r="B216" s="34" t="n"/>
-      <c r="C216" s="34" t="n"/>
-      <c r="D216" s="34" t="n"/>
-      <c r="E216" s="34" t="n"/>
+      <c r="A216" s="28" t="inlineStr">
+        <is>
+          <t>Attendance undercount is systemic — door discipline, not a data bug</t>
+        </is>
+      </c>
+      <c r="B216" s="28" t="inlineStr">
+        <is>
+          <t>Attendance is only ever as true as the door. Adam reports roughly two events Andrea Baquero attended that were never captured at check-in, and the same gap exists for anyone scanned inconsistently. This is not a reporting defect: the records are never written at all, so every downstream number that rests on attendance is quietly low and nothing signals it. It is event-critical for the Exchange specifically, because the mixer roster is built from check-ins — an uncaptured arrival is a person the engine will never seat.</t>
+        </is>
+      </c>
+      <c r="C216" s="28" t="inlineStr">
+        <is>
+          <t>Treat as an operations fix first, not a code fix. Add an explicit check-in line to the run-of-show for the Aug 27 Exchange so every arrival is scanned or recorded by hand, then measure that night's capture against the known headcount. Only if capture is still short does this become an instrumentation problem in the door path. Backfilling historical attendance is a separate decision, and not worth making until live capture is trustworthy.</t>
+        </is>
+      </c>
+      <c r="D216" s="28" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E216" s="28" t="inlineStr">
+        <is>
+          <t>Raised Aug 26 from the Andrea Baquero case (~2 attended events never captured). Immediate lever is the Aug 27 run-of-show line.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="28" t="inlineStr">
         <is>
-          <t>Attendance undercount is systemic — door discipline, not a data bug</t>
+          <t>Hub add-member search still surfaces banned business members</t>
         </is>
       </c>
       <c r="B217" s="28" t="inlineStr">
         <is>
-          <t>Attendance is only ever as true as the door. Adam reports roughly two events Andrea Baquero attended that were never captured at check-in, and the same gap exists for anyone scanned inconsistently. This is not a reporting defect: the records are never written at all, so every downstream number that rests on attendance is quietly low and nothing signals it. It is event-critical for the Exchange specifically, because the mixer roster is built from check-ins — an uncaptured arrival is a person the engine will never seat.</t>
+          <t>The add-member search on /admin/hubs was narrowed Aug 26 to active business members with is_internal false, but banned was deliberately left out of the filter set. A banned business member with an active subscription therefore still appears in the search and can still be added to a hub. The member-facing hub tab hides them correctly, so the effect is an invisible member occupying a row rather than a data leak.</t>
         </is>
       </c>
       <c r="C217" s="28" t="inlineStr">
         <is>
-          <t>Treat as an operations fix first, not a code fix. Add an explicit check-in line to the run-of-show for the Aug 27 Exchange so every arrival is scanned or recorded by hand, then measure that night's capture against the known headcount. Only if capture is still short does this become an instrumentation problem in the door path. Backfilling historical attendance is a separate decision, and not worth making until live capture is trustworthy.</t>
+          <t>One line in the add-member search query: .eq('banned', false), alongside the existing deleted_at, member_type and is_internal filters. Same rehearsal shape as the Aug 26 hub work — seed a banned business member, confirm it is absent from the search, and confirm the member-facing tab is unchanged.</t>
         </is>
       </c>
       <c r="D217" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WAITING ON ADAM</t>
         </is>
       </c>
       <c r="E217" s="28" t="inlineStr">
         <is>
-          <t>Raised Aug 26 from the Andrea Baquero case (~2 attended events never captured). Immediate lever is the Aug 27 run-of-show line.</t>
+          <t>Left open on purpose Aug 26: the shipped scope named member_type and is_internal only, so the gap was reported rather than silently widened. One-line change whenever Adam approves.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="28" t="inlineStr">
         <is>
-          <t>Hub add-member search still surfaces banned business members</t>
+          <t>Email logo still partially inverts in Gmail dark mode</t>
         </is>
       </c>
       <c r="B218" s="28" t="inlineStr">
         <is>
-          <t>The add-member search on /admin/hubs was narrowed Aug 26 to active business members with is_internal false, but banned was deliberately left out of the filter set. A banned business member with an active subscription therefore still appears in the search and can still be added to a hub. The member-facing hub tab hides them correctly, so the effect is an invisible member occupying a row rather than a data leak.</t>
+          <t>The member blast logo was changed Aug 26 from the white-on-dark mark to the circular badge on an opaque white circle. That fixed the logo disappearing entirely and was render-verified for contrast in both light and dark-emulated views. In real Gmail, dark-mode inversion still partially affects the surrounding shell, so the badge is legible but the treatment is an improvement rather than a complete answer.</t>
         </is>
       </c>
       <c r="C218" s="28" t="inlineStr">
         <is>
-          <t>One line in the add-member search query: .eq('banned', false), alongside the existing deleted_at, member_type and is_internal filters. Same rehearsal shape as the Aug 26 hub work — seed a banned business member, confirm it is absent from the search, and confirm the member-facing tab is unchanged.</t>
+          <t>Next lever is a dark-mode-aware CSS asset: prefers-color-scheme rules plus explicit background locks on the shell, and where Gmail ignores those, a pre-composited image asset that cannot be inverted. Verify against a real Gmail dark-mode client, not only an emulated render — the emulated view is what passed while the real client still differed.</t>
         </is>
       </c>
       <c r="D218" s="28" t="inlineStr">
         <is>
-          <t>WAITING ON ADAM</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E218" s="28" t="inlineStr">
         <is>
-          <t>Left open on purpose Aug 26: the shipped scope named member_type and is_internal only, so the gap was reported rather than silently widened. One-line change whenever Adam approves.</t>
+          <t>Badge shipped Aug 26 and is legible; this row covers the remaining shell inversion. Cosmetic and low urgency, but it touches every member-facing send.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="28" t="inlineStr">
         <is>
-          <t>Email logo still partially inverts in Gmail dark mode</t>
+          <t>Sentry: "load" error thrown on /dashboard (~Aug 24), undiagnosed</t>
         </is>
       </c>
       <c r="B219" s="28" t="inlineStr">
         <is>
-          <t>The member blast logo was changed Aug 26 from the white-on-dark mark to the circular badge on an opaque white circle. That fixed the logo disappearing entirely and was render-verified for contrast in both light and dark-emulated views. In real Gmail, dark-mode inversion still partially affects the surrounding shell, so the badge is legible but the treatment is an improvement rather than a complete answer.</t>
+          <t>Sentry reports an error on the member dashboard in which a Supabase error object appears to be thrown rather than handled, surfacing with the message "load". It first appears around Aug 24. Nothing else is known — frequency, affected users, and whether the page actually degrades are all unread, because the issue detail has not been opened.</t>
         </is>
       </c>
       <c r="C219" s="28" t="inlineStr">
         <is>
-          <t>Next lever is a dark-mode-aware CSS asset: prefers-color-scheme rules plus explicit background locks on the shell, and where Gmail ignores those, a pre-composited image asset that cannot be inverted. Verify against a real Gmail dark-mode client, not only an emulated render — the emulated view is what passed while the real client still differed.</t>
+          <t>Blocked on evidence, not on effort. Adam sends the Sentry issue-detail screenshot (stack, breadcrumbs, event count, affected users) and diagnosis follows from there. Likely shape is an unchecked Supabase call whose error object is thrown as-is, which is why the message reads as the object rather than a cause — but that is a guess until the throw site is visible.</t>
         </is>
       </c>
       <c r="D219" s="28" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>WAITING ON ADAM: issue-detail screenshot</t>
         </is>
       </c>
       <c r="E219" s="28" t="inlineStr">
         <is>
-          <t>Badge shipped Aug 26 and is legible; this row covers the remaining shell inversion. Cosmetic and low urgency, but it touches every member-facing send.</t>
+          <t>Raised Aug 26. Cannot be triaged from the title alone; the throw site is what identifies it. First seen ~Aug 24.</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="28" t="inlineStr">
-        <is>
-          <t>Sentry: "load" error thrown on /dashboard (~Aug 24), undiagnosed</t>
-        </is>
-      </c>
-      <c r="B220" s="28" t="inlineStr">
-        <is>
-          <t>Sentry reports an error on the member dashboard in which a Supabase error object appears to be thrown rather than handled, surfacing with the message "load". It first appears around Aug 24. Nothing else is known — frequency, affected users, and whether the page actually degrades are all unread, because the issue detail has not been opened.</t>
-        </is>
-      </c>
-      <c r="C220" s="28" t="inlineStr">
-        <is>
-          <t>Blocked on evidence, not on effort. Adam sends the Sentry issue-detail screenshot (stack, breadcrumbs, event count, affected users) and diagnosis follows from there. Likely shape is an unchecked Supabase call whose error object is thrown as-is, which is why the message reads as the object rather than a cause — but that is a guess until the throw site is visible.</t>
-        </is>
-      </c>
-      <c r="D220" s="28" t="inlineStr">
-        <is>
-          <t>WAITING ON ADAM: issue-detail screenshot</t>
-        </is>
-      </c>
-      <c r="E220" s="28" t="inlineStr">
-        <is>
-          <t>Raised Aug 26. Cannot be triaged from the title alone; the throw site is what identifies it. First seen ~Aug 24.</t>
-        </is>
-      </c>
+      <c r="A220" s="43" t="inlineStr">
+        <is>
+          <t>OCT 21 — HUB LAUNCH / LEADS — PARKED, NOT LOCKED   ·   7 items</t>
+        </is>
+      </c>
+      <c r="B220" s="34" t="n"/>
+      <c r="C220" s="34" t="n"/>
+      <c r="D220" s="34" t="n"/>
+      <c r="E220" s="34" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="28" t="inlineStr">
+        <is>
+          <t>Lead emails: proposal = business + copy to hello@. Need lead emails from Larry, CAF, Jon, Antonio. Confirm which emails fire per lead today.</t>
+        </is>
+      </c>
+      <c r="B221" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C221" s="28" t="n"/>
+      <c r="D221" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E221" s="28" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="28" t="inlineStr">
+        <is>
+          <t>CAF: waiting on their shared lead inbox; check if one listing can have 3 logins.</t>
+        </is>
+      </c>
+      <c r="B222" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C222" s="28" t="n"/>
+      <c r="D222" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E222" s="28" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="28" t="inlineStr">
+        <is>
+          <t>2-day reply nudge: proposal = on at launch; Adam tells businesses the reply expectation first.</t>
+        </is>
+      </c>
+      <c r="B223" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C223" s="28" t="n"/>
+      <c r="D223" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E223" s="28" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="28" t="inlineStr">
+        <is>
+          <t>Moving-to-Charlotte funnel: separate cltbucketlist.com build after hub launch; dual CLTBucketlist + 704 partners only (CAF, Larry); listing fee TBD; decide if Zach/Tyler become dual partners; Ascent content never routes to CAF.</t>
+        </is>
+      </c>
+      <c r="B224" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C224" s="28" t="n"/>
+      <c r="D224" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E224" s="28" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="28" t="inlineStr">
+        <is>
+          <t>Tyler (Gold Medal Wealth / NM): compliance answer pending.</t>
+        </is>
+      </c>
+      <c r="B225" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C225" s="28" t="n"/>
+      <c r="D225" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E225" s="28" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="28" t="inlineStr">
+        <is>
+          <t>Roster replies pending: CAF, Zach, Tyler, Larry, Jon, Antonio. Headshots on hand: Zach, Antonio, Tyler.</t>
+        </is>
+      </c>
+      <c r="B226" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C226" s="28" t="n"/>
+      <c r="D226" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E226" s="28" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="28" t="inlineStr">
+        <is>
+          <t>After hub launch: re-submit sitemap in Google Search Console + Bing.</t>
+        </is>
+      </c>
+      <c r="B227" s="28" t="inlineStr">
+        <is>
+          <t>Parked with hub launch. Not locked.</t>
+        </is>
+      </c>
+      <c r="C227" s="28" t="n"/>
+      <c r="D227" s="28" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="E227" s="28" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="43" t="inlineStr">
+        <is>
+          <t>OCT 21 — OTHER OPEN   ·   6 items</t>
+        </is>
+      </c>
+      <c r="B228" s="34" t="n"/>
+      <c r="C228" s="34" t="n"/>
+      <c r="D228" s="34" t="n"/>
+      <c r="E228" s="34" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="28" t="inlineStr">
+        <is>
+          <t>Door check-in: build the server-side lock BEFORE any host/volunteer gets an admin login.</t>
+        </is>
+      </c>
+      <c r="B229" s="28" t="inlineStr">
+        <is>
+          <t>Must land before any host or volunteer admin login.</t>
+        </is>
+      </c>
+      <c r="C229" s="28" t="n"/>
+      <c r="D229" s="28" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E229" s="28" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="28" t="inlineStr">
+        <is>
+          <t>Ambassadors: 4 have unfinished Stripe setup (1 rejected by Stripe) — decide on a nudge email.</t>
+        </is>
+      </c>
+      <c r="B230" s="28" t="inlineStr">
+        <is>
+          <t>Decision only. No email until Adam says so.</t>
+        </is>
+      </c>
+      <c r="C230" s="28" t="n"/>
+      <c r="D230" s="28" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E230" s="28" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="28" t="inlineStr">
+        <is>
+          <t>Wallet pass scan: real test at the door (Putt Putt Oct 22).</t>
+        </is>
+      </c>
+      <c r="B231" s="28" t="inlineStr">
+        <is>
+          <t>Real-device scan at the door.</t>
+        </is>
+      </c>
+      <c r="C231" s="28" t="n"/>
+      <c r="D231" s="28" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="E231" s="28" t="inlineStr">
+        <is>
+          <t>Putt Putt Oct 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="28" t="inlineStr">
+        <is>
+          <t>Optional: real "Sign in with Google" test with a non-member Google account.</t>
+        </is>
+      </c>
+      <c r="B232" s="28" t="inlineStr">
+        <is>
+          <t>Optional live test.</t>
+        </is>
+      </c>
+      <c r="C232" s="28" t="n"/>
+      <c r="D232" s="28" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E232" s="28" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="28" t="inlineStr">
+        <is>
+          <t>Optional: React #418 on mobile home — watch only (not reproducible).</t>
+        </is>
+      </c>
+      <c r="B233" s="28" t="inlineStr">
+        <is>
+          <t>Watch only. Not reproducible.</t>
+        </is>
+      </c>
+      <c r="C233" s="28" t="n"/>
+      <c r="D233" s="28" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E233" s="28" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="28" t="inlineStr">
+        <is>
+          <t>Cosmetic, later: stripe-webhook should clear canceled_at on reactivation (bundle with next webhook change).</t>
+        </is>
+      </c>
+      <c r="B234" s="28" t="inlineStr">
+        <is>
+          <t>Do not touch stripe-webhook until the next webhook change.</t>
+        </is>
+      </c>
+      <c r="C234" s="28" t="n"/>
+      <c r="D234" s="28" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E234" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
